--- a/TC/나이트크로우_일반제작_TC.xlsx
+++ b/TC/나이트크로우_일반제작_TC.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leegm\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\leegm0430\01_포토폴리오\TC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4884F15-C63A-4438-83CD-D37105732209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{485CA0C0-1BE4-447F-9C65-6EF55A5483A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="1133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1966" uniqueCount="1129">
   <si>
     <t>Project name (프로젝트 명칭)</t>
   </si>
@@ -2263,9 +2263,6 @@
     <t>"강화된 권갑" 아이템이 아이콘 및 명칭과 함께 목록에 정상 노출됨</t>
   </si>
   <si>
-    <t>리서치 캡처 판독 신뢰도가 낮아 정확한 아이템명 실기기 재확인 필요</t>
-  </si>
-  <si>
     <t>[무기 아이템 목록] "강화된 권갑" 아이템 선택</t>
   </si>
   <si>
@@ -2902,9 +2899,6 @@
     <t>재화+기본 재료+상위/대체 재료 등 4종 내외의 재료가 누락 없이 모두 표시됨</t>
   </si>
   <si>
-    <t>재료 구성 샘플링 - 복합 재료(재화+기본재료+상위/대체재료)</t>
-  </si>
-  <si>
     <t>귀속/비귀속 재료 혼용 아이템 사전 식별</t>
   </si>
   <si>
@@ -2914,9 +2908,6 @@
     <t>재료 목록에 귀속 재료와 비귀속 재료가 함께 표시되며 각 항목에 귀속 여부가 구분되어 표기됨</t>
   </si>
   <si>
-    <t>재료 구성 샘플링 - 귀속/비귀속 혼용. 리서치 캡처에서 명확한 혼용 사례를 확인하지 못해 기획 데이터로 대상 아이템 사전 확정 필요</t>
-  </si>
-  <si>
     <t>임의 아이템 선택 상태</t>
   </si>
   <si>
@@ -3113,9 +3104,6 @@
   </si>
   <si>
     <t>노출되는 성공률/대성공률 수치가 기획 데이터와 100% 일치함</t>
-  </si>
-  <si>
-    <t>확률 표기 오류(과장 표기) 전례가 있어 반드시 실측 검증 필요</t>
   </si>
   <si>
     <t>제한 및 잠금</t>
@@ -3833,18 +3821,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -3857,16 +3833,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3874,6 +3847,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4704,76 +4692,76 @@
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1"/>
     <row r="2" spans="2:10" ht="15" customHeight="1">
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="34" t="s">
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="15" customHeight="1">
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="34" t="s">
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="31" t="s">
-        <v>1131</v>
+      <c r="J3" s="27" t="s">
+        <v>1127</v>
       </c>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="34" t="s">
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="31" t="s">
-        <v>1132</v>
+      <c r="J4" s="27" t="s">
+        <v>1128</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="31.2" customHeight="1">
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="E5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="35" t="s">
+      <c r="G5" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="35" t="s">
+      <c r="H5" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="29" t="s">
+      <c r="J5" s="25" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4784,13 +4772,13 @@
       <c r="C6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="F6" s="38" t="s">
         <v>16</v>
       </c>
       <c r="G6" s="23" t="s">
@@ -4809,9 +4797,9 @@
       <c r="C7" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
       <c r="G7" s="23" t="s">
         <v>20</v>
       </c>
@@ -4828,9 +4816,9 @@
       <c r="C8" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
       <c r="G8" s="22" t="s">
         <v>22</v>
       </c>
@@ -4847,9 +4835,9 @@
       <c r="C9" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
       <c r="G9" s="22" t="s">
         <v>25</v>
       </c>
@@ -4868,9 +4856,9 @@
       <c r="C10" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="25" t="s">
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="39" t="s">
         <v>27</v>
       </c>
       <c r="G10" s="22" t="s">
@@ -4891,9 +4879,9 @@
       <c r="C11" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="25"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="39"/>
       <c r="G11" s="22" t="s">
         <v>28</v>
       </c>
@@ -4912,9 +4900,9 @@
       <c r="C12" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="25"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="39"/>
       <c r="G12" s="22" t="s">
         <v>28</v>
       </c>
@@ -4933,9 +4921,9 @@
       <c r="C13" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="25"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="39"/>
       <c r="G13" s="22" t="s">
         <v>28</v>
       </c>
@@ -4954,9 +4942,9 @@
       <c r="C14" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="25"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="39"/>
       <c r="G14" s="22" t="s">
         <v>28</v>
       </c>
@@ -4975,9 +4963,9 @@
       <c r="C15" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="25" t="s">
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="39" t="s">
         <v>40</v>
       </c>
       <c r="G15" s="22" t="s">
@@ -4998,9 +4986,9 @@
       <c r="C16" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="25"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="39"/>
       <c r="G16" s="22" t="s">
         <v>44</v>
       </c>
@@ -5019,9 +5007,9 @@
       <c r="C17" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="25"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="39"/>
       <c r="G17" s="22" t="s">
         <v>47</v>
       </c>
@@ -5040,9 +5028,9 @@
       <c r="C18" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="25"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="39"/>
       <c r="G18" s="22" t="s">
         <v>44</v>
       </c>
@@ -5061,9 +5049,9 @@
       <c r="C19" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="25" t="s">
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="39" t="s">
         <v>27</v>
       </c>
       <c r="G19" s="22" t="s">
@@ -5084,9 +5072,9 @@
       <c r="C20" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="25"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="39"/>
       <c r="G20" s="22" t="s">
         <v>28</v>
       </c>
@@ -5105,9 +5093,9 @@
       <c r="C21" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="25"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="39"/>
       <c r="G21" s="22" t="s">
         <v>28</v>
       </c>
@@ -5126,9 +5114,9 @@
       <c r="C22" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="25"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="39"/>
       <c r="G22" s="22" t="s">
         <v>28</v>
       </c>
@@ -5147,9 +5135,9 @@
       <c r="C23" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="25"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="39"/>
       <c r="G23" s="22" t="s">
         <v>60</v>
       </c>
@@ -5168,9 +5156,9 @@
       <c r="C24" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="25"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="39"/>
       <c r="G24" s="22" t="s">
         <v>28</v>
       </c>
@@ -5189,9 +5177,9 @@
       <c r="C25" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="25"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="39"/>
       <c r="G25" s="22" t="s">
         <v>28</v>
       </c>
@@ -5210,9 +5198,9 @@
       <c r="C26" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="25"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="39"/>
       <c r="G26" s="22" t="s">
         <v>28</v>
       </c>
@@ -5229,9 +5217,9 @@
       <c r="C27" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="25"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="39"/>
       <c r="G27" s="22" t="s">
         <v>28</v>
       </c>
@@ -5245,12 +5233,12 @@
     </row>
     <row r="28" spans="2:10" ht="49.95" customHeight="1">
       <c r="B28" s="22"/>
-      <c r="C28" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="25"/>
+      <c r="C28" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="39"/>
       <c r="G28" s="22" t="s">
         <v>28</v>
       </c>
@@ -5267,9 +5255,9 @@
       <c r="C29" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="26" t="s">
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="35" t="s">
         <v>74</v>
       </c>
       <c r="G29" s="22" t="s">
@@ -5288,9 +5276,9 @@
       <c r="C30" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="27"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="36"/>
       <c r="G30" s="22" t="s">
         <v>28</v>
       </c>
@@ -5307,9 +5295,9 @@
       <c r="C31" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="27"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="36"/>
       <c r="G31" s="22" t="s">
         <v>79</v>
       </c>
@@ -5326,9 +5314,9 @@
       <c r="C32" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="27"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="36"/>
       <c r="G32" s="22" t="s">
         <v>82</v>
       </c>
@@ -5345,9 +5333,9 @@
       <c r="C33" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="28"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="37"/>
       <c r="G33" s="22" t="s">
         <v>84</v>
       </c>
@@ -5366,11 +5354,11 @@
       <c r="C34" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="32"/>
-      <c r="E34" s="25" t="s">
+      <c r="D34" s="38"/>
+      <c r="E34" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="F34" s="26" t="s">
+      <c r="F34" s="35" t="s">
         <v>86</v>
       </c>
       <c r="G34" s="22" t="s">
@@ -5391,9 +5379,9 @@
       <c r="C35" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D35" s="32"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="27"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="36"/>
       <c r="G35" s="22" t="s">
         <v>87</v>
       </c>
@@ -5412,9 +5400,9 @@
       <c r="C36" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="32"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="27"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="36"/>
       <c r="G36" s="22" t="s">
         <v>87</v>
       </c>
@@ -5433,9 +5421,9 @@
       <c r="C37" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D37" s="32"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="28"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="37"/>
       <c r="G37" s="22" t="s">
         <v>87</v>
       </c>
@@ -5454,9 +5442,9 @@
       <c r="C38" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D38" s="32"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="26" t="s">
+      <c r="D38" s="38"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="35" t="s">
         <v>27</v>
       </c>
       <c r="G38" s="22" t="s">
@@ -5477,9 +5465,9 @@
       <c r="C39" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="32"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="27"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="36"/>
       <c r="G39" s="22" t="s">
         <v>28</v>
       </c>
@@ -5498,9 +5486,9 @@
       <c r="C40" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D40" s="32"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="28"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="37"/>
       <c r="G40" s="22" t="s">
         <v>100</v>
       </c>
@@ -5521,9 +5509,9 @@
       <c r="C41" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D41" s="32"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="26" t="s">
+      <c r="D41" s="38"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="35" t="s">
         <v>104</v>
       </c>
       <c r="G41" s="22" t="s">
@@ -5544,9 +5532,9 @@
       <c r="C42" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D42" s="32"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="27"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="36"/>
       <c r="G42" s="22" t="s">
         <v>28</v>
       </c>
@@ -5565,9 +5553,9 @@
       <c r="C43" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D43" s="32"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="27"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="39"/>
+      <c r="F43" s="36"/>
       <c r="G43" s="22" t="s">
         <v>28</v>
       </c>
@@ -5586,9 +5574,9 @@
       <c r="C44" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D44" s="32"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="27"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="36"/>
       <c r="G44" s="22" t="s">
         <v>28</v>
       </c>
@@ -5596,7 +5584,7 @@
         <v>111</v>
       </c>
       <c r="I44" s="22" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="J44" s="22"/>
     </row>
@@ -5607,9 +5595,9 @@
       <c r="C45" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D45" s="32"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="27"/>
+      <c r="D45" s="38"/>
+      <c r="E45" s="39"/>
+      <c r="F45" s="36"/>
       <c r="G45" s="22" t="s">
         <v>28</v>
       </c>
@@ -5617,7 +5605,7 @@
         <v>112</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="J45" s="22"/>
     </row>
@@ -5628,9 +5616,9 @@
       <c r="C46" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D46" s="32"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="27"/>
+      <c r="D46" s="38"/>
+      <c r="E46" s="39"/>
+      <c r="F46" s="36"/>
       <c r="G46" s="22" t="s">
         <v>28</v>
       </c>
@@ -5638,7 +5626,7 @@
         <v>113</v>
       </c>
       <c r="I46" s="22" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="J46" s="22"/>
     </row>
@@ -5649,14 +5637,14 @@
       <c r="C47" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D47" s="32"/>
-      <c r="E47" s="25"/>
-      <c r="F47" s="27"/>
+      <c r="D47" s="38"/>
+      <c r="E47" s="39"/>
+      <c r="F47" s="36"/>
       <c r="G47" s="22" t="s">
         <v>114</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="I47" s="22" t="s">
         <v>115</v>
@@ -5670,9 +5658,9 @@
       <c r="C48" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D48" s="32"/>
-      <c r="E48" s="25"/>
-      <c r="F48" s="27"/>
+      <c r="D48" s="38"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="36"/>
       <c r="G48" s="22" t="s">
         <v>116</v>
       </c>
@@ -5691,9 +5679,9 @@
       <c r="C49" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D49" s="32"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="28"/>
+      <c r="D49" s="38"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="37"/>
       <c r="G49" s="22" t="s">
         <v>119</v>
       </c>
@@ -5712,9 +5700,9 @@
       <c r="C50" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D50" s="32"/>
-      <c r="E50" s="25"/>
-      <c r="F50" s="26" t="s">
+      <c r="D50" s="38"/>
+      <c r="E50" s="39"/>
+      <c r="F50" s="35" t="s">
         <v>122</v>
       </c>
       <c r="G50" s="22" t="s">
@@ -5735,9 +5723,9 @@
       <c r="C51" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D51" s="32"/>
-      <c r="E51" s="25"/>
-      <c r="F51" s="28"/>
+      <c r="D51" s="38"/>
+      <c r="E51" s="39"/>
+      <c r="F51" s="37"/>
       <c r="G51" s="22" t="s">
         <v>126</v>
       </c>
@@ -5756,9 +5744,9 @@
       <c r="C52" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D52" s="32"/>
-      <c r="E52" s="25"/>
-      <c r="F52" s="26" t="s">
+      <c r="D52" s="38"/>
+      <c r="E52" s="39"/>
+      <c r="F52" s="35" t="s">
         <v>129</v>
       </c>
       <c r="G52" s="22" t="s">
@@ -5779,9 +5767,9 @@
       <c r="C53" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D53" s="32"/>
-      <c r="E53" s="25"/>
-      <c r="F53" s="27"/>
+      <c r="D53" s="38"/>
+      <c r="E53" s="39"/>
+      <c r="F53" s="36"/>
       <c r="G53" s="22" t="s">
         <v>130</v>
       </c>
@@ -5800,9 +5788,9 @@
       <c r="C54" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D54" s="32"/>
-      <c r="E54" s="25"/>
-      <c r="F54" s="27"/>
+      <c r="D54" s="38"/>
+      <c r="E54" s="39"/>
+      <c r="F54" s="36"/>
       <c r="G54" s="22" t="s">
         <v>130</v>
       </c>
@@ -5821,9 +5809,9 @@
       <c r="C55" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D55" s="32"/>
-      <c r="E55" s="25"/>
-      <c r="F55" s="27"/>
+      <c r="D55" s="38"/>
+      <c r="E55" s="39"/>
+      <c r="F55" s="36"/>
       <c r="G55" s="22" t="s">
         <v>130</v>
       </c>
@@ -5842,9 +5830,9 @@
       <c r="C56" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D56" s="32"/>
-      <c r="E56" s="25"/>
-      <c r="F56" s="27"/>
+      <c r="D56" s="38"/>
+      <c r="E56" s="39"/>
+      <c r="F56" s="36"/>
       <c r="G56" s="22" t="s">
         <v>130</v>
       </c>
@@ -5863,9 +5851,9 @@
       <c r="C57" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D57" s="32"/>
-      <c r="E57" s="25"/>
-      <c r="F57" s="27"/>
+      <c r="D57" s="38"/>
+      <c r="E57" s="39"/>
+      <c r="F57" s="36"/>
       <c r="G57" s="22" t="s">
         <v>130</v>
       </c>
@@ -5884,9 +5872,9 @@
       <c r="C58" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D58" s="32"/>
-      <c r="E58" s="25"/>
-      <c r="F58" s="27"/>
+      <c r="D58" s="38"/>
+      <c r="E58" s="39"/>
+      <c r="F58" s="36"/>
       <c r="G58" s="22" t="s">
         <v>130</v>
       </c>
@@ -5905,9 +5893,9 @@
       <c r="C59" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D59" s="32"/>
-      <c r="E59" s="25"/>
-      <c r="F59" s="27"/>
+      <c r="D59" s="38"/>
+      <c r="E59" s="39"/>
+      <c r="F59" s="36"/>
       <c r="G59" s="22" t="s">
         <v>130</v>
       </c>
@@ -5926,9 +5914,9 @@
       <c r="C60" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D60" s="32"/>
-      <c r="E60" s="25"/>
-      <c r="F60" s="27"/>
+      <c r="D60" s="38"/>
+      <c r="E60" s="39"/>
+      <c r="F60" s="36"/>
       <c r="G60" s="22" t="s">
         <v>130</v>
       </c>
@@ -5947,9 +5935,9 @@
       <c r="C61" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D61" s="32"/>
-      <c r="E61" s="25"/>
-      <c r="F61" s="27"/>
+      <c r="D61" s="38"/>
+      <c r="E61" s="39"/>
+      <c r="F61" s="36"/>
       <c r="G61" s="22" t="s">
         <v>130</v>
       </c>
@@ -5968,9 +5956,9 @@
       <c r="C62" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D62" s="32"/>
-      <c r="E62" s="25"/>
-      <c r="F62" s="27"/>
+      <c r="D62" s="38"/>
+      <c r="E62" s="39"/>
+      <c r="F62" s="36"/>
       <c r="G62" s="22" t="s">
         <v>130</v>
       </c>
@@ -5989,9 +5977,9 @@
       <c r="C63" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D63" s="32"/>
-      <c r="E63" s="25"/>
-      <c r="F63" s="27"/>
+      <c r="D63" s="38"/>
+      <c r="E63" s="39"/>
+      <c r="F63" s="36"/>
       <c r="G63" s="22" t="s">
         <v>130</v>
       </c>
@@ -6010,9 +5998,9 @@
       <c r="C64" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D64" s="32"/>
-      <c r="E64" s="25"/>
-      <c r="F64" s="27"/>
+      <c r="D64" s="38"/>
+      <c r="E64" s="39"/>
+      <c r="F64" s="36"/>
       <c r="G64" s="22" t="s">
         <v>130</v>
       </c>
@@ -6031,9 +6019,9 @@
       <c r="C65" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D65" s="32"/>
-      <c r="E65" s="25"/>
-      <c r="F65" s="27"/>
+      <c r="D65" s="38"/>
+      <c r="E65" s="39"/>
+      <c r="F65" s="36"/>
       <c r="G65" s="22" t="s">
         <v>130</v>
       </c>
@@ -6052,9 +6040,9 @@
       <c r="C66" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D66" s="32"/>
-      <c r="E66" s="25"/>
-      <c r="F66" s="27"/>
+      <c r="D66" s="38"/>
+      <c r="E66" s="39"/>
+      <c r="F66" s="36"/>
       <c r="G66" s="22" t="s">
         <v>130</v>
       </c>
@@ -6073,9 +6061,9 @@
       <c r="C67" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D67" s="32"/>
-      <c r="E67" s="25"/>
-      <c r="F67" s="27"/>
+      <c r="D67" s="38"/>
+      <c r="E67" s="39"/>
+      <c r="F67" s="36"/>
       <c r="G67" s="22" t="s">
         <v>130</v>
       </c>
@@ -6094,9 +6082,9 @@
       <c r="C68" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D68" s="32"/>
-      <c r="E68" s="25"/>
-      <c r="F68" s="27"/>
+      <c r="D68" s="38"/>
+      <c r="E68" s="39"/>
+      <c r="F68" s="36"/>
       <c r="G68" s="22" t="s">
         <v>130</v>
       </c>
@@ -6115,9 +6103,9 @@
       <c r="C69" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D69" s="32"/>
-      <c r="E69" s="25"/>
-      <c r="F69" s="27"/>
+      <c r="D69" s="38"/>
+      <c r="E69" s="39"/>
+      <c r="F69" s="36"/>
       <c r="G69" s="22" t="s">
         <v>130</v>
       </c>
@@ -6136,9 +6124,9 @@
       <c r="C70" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D70" s="32"/>
-      <c r="E70" s="25"/>
-      <c r="F70" s="27"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="36"/>
       <c r="G70" s="22" t="s">
         <v>130</v>
       </c>
@@ -6157,9 +6145,9 @@
       <c r="C71" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D71" s="32"/>
-      <c r="E71" s="25"/>
-      <c r="F71" s="27"/>
+      <c r="D71" s="38"/>
+      <c r="E71" s="39"/>
+      <c r="F71" s="36"/>
       <c r="G71" s="22" t="s">
         <v>130</v>
       </c>
@@ -6178,9 +6166,9 @@
       <c r="C72" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D72" s="32"/>
-      <c r="E72" s="25"/>
-      <c r="F72" s="27"/>
+      <c r="D72" s="38"/>
+      <c r="E72" s="39"/>
+      <c r="F72" s="36"/>
       <c r="G72" s="22" t="s">
         <v>130</v>
       </c>
@@ -6199,9 +6187,9 @@
       <c r="C73" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D73" s="32"/>
-      <c r="E73" s="25"/>
-      <c r="F73" s="27"/>
+      <c r="D73" s="38"/>
+      <c r="E73" s="39"/>
+      <c r="F73" s="36"/>
       <c r="G73" s="22" t="s">
         <v>130</v>
       </c>
@@ -6220,9 +6208,9 @@
       <c r="C74" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D74" s="32"/>
-      <c r="E74" s="25"/>
-      <c r="F74" s="27"/>
+      <c r="D74" s="38"/>
+      <c r="E74" s="39"/>
+      <c r="F74" s="36"/>
       <c r="G74" s="22" t="s">
         <v>130</v>
       </c>
@@ -6241,9 +6229,9 @@
       <c r="C75" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D75" s="32"/>
-      <c r="E75" s="25"/>
-      <c r="F75" s="28"/>
+      <c r="D75" s="38"/>
+      <c r="E75" s="39"/>
+      <c r="F75" s="37"/>
       <c r="G75" s="22" t="s">
         <v>130</v>
       </c>
@@ -6262,9 +6250,9 @@
       <c r="C76" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D76" s="32"/>
-      <c r="E76" s="25"/>
-      <c r="F76" s="26" t="s">
+      <c r="D76" s="38"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="35" t="s">
         <v>122</v>
       </c>
       <c r="G76" s="22" t="s">
@@ -6285,9 +6273,9 @@
       <c r="C77" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D77" s="32"/>
-      <c r="E77" s="25"/>
-      <c r="F77" s="28"/>
+      <c r="D77" s="38"/>
+      <c r="E77" s="39"/>
+      <c r="F77" s="37"/>
       <c r="G77" s="22" t="s">
         <v>182</v>
       </c>
@@ -6306,9 +6294,9 @@
       <c r="C78" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D78" s="32"/>
-      <c r="E78" s="25"/>
-      <c r="F78" s="26" t="s">
+      <c r="D78" s="38"/>
+      <c r="E78" s="39"/>
+      <c r="F78" s="35" t="s">
         <v>129</v>
       </c>
       <c r="G78" s="22" t="s">
@@ -6329,9 +6317,9 @@
       <c r="C79" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D79" s="32"/>
-      <c r="E79" s="25"/>
-      <c r="F79" s="27"/>
+      <c r="D79" s="38"/>
+      <c r="E79" s="39"/>
+      <c r="F79" s="36"/>
       <c r="G79" s="22" t="s">
         <v>185</v>
       </c>
@@ -6350,9 +6338,9 @@
       <c r="C80" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D80" s="32"/>
-      <c r="E80" s="25"/>
-      <c r="F80" s="27"/>
+      <c r="D80" s="38"/>
+      <c r="E80" s="39"/>
+      <c r="F80" s="36"/>
       <c r="G80" s="22" t="s">
         <v>185</v>
       </c>
@@ -6371,9 +6359,9 @@
       <c r="C81" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D81" s="32"/>
-      <c r="E81" s="25"/>
-      <c r="F81" s="27"/>
+      <c r="D81" s="38"/>
+      <c r="E81" s="39"/>
+      <c r="F81" s="36"/>
       <c r="G81" s="22" t="s">
         <v>185</v>
       </c>
@@ -6392,9 +6380,9 @@
       <c r="C82" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D82" s="32"/>
-      <c r="E82" s="25"/>
-      <c r="F82" s="27"/>
+      <c r="D82" s="38"/>
+      <c r="E82" s="39"/>
+      <c r="F82" s="36"/>
       <c r="G82" s="22" t="s">
         <v>185</v>
       </c>
@@ -6413,9 +6401,9 @@
       <c r="C83" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D83" s="32"/>
-      <c r="E83" s="25"/>
-      <c r="F83" s="27"/>
+      <c r="D83" s="38"/>
+      <c r="E83" s="39"/>
+      <c r="F83" s="36"/>
       <c r="G83" s="22" t="s">
         <v>185</v>
       </c>
@@ -6434,9 +6422,9 @@
       <c r="C84" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D84" s="32"/>
-      <c r="E84" s="25"/>
-      <c r="F84" s="27"/>
+      <c r="D84" s="38"/>
+      <c r="E84" s="39"/>
+      <c r="F84" s="36"/>
       <c r="G84" s="22" t="s">
         <v>185</v>
       </c>
@@ -6455,9 +6443,9 @@
       <c r="C85" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D85" s="32"/>
-      <c r="E85" s="25"/>
-      <c r="F85" s="27"/>
+      <c r="D85" s="38"/>
+      <c r="E85" s="39"/>
+      <c r="F85" s="36"/>
       <c r="G85" s="22" t="s">
         <v>185</v>
       </c>
@@ -6476,9 +6464,9 @@
       <c r="C86" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D86" s="32"/>
-      <c r="E86" s="25"/>
-      <c r="F86" s="27"/>
+      <c r="D86" s="38"/>
+      <c r="E86" s="39"/>
+      <c r="F86" s="36"/>
       <c r="G86" s="22" t="s">
         <v>185</v>
       </c>
@@ -6497,9 +6485,9 @@
       <c r="C87" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D87" s="32"/>
-      <c r="E87" s="25"/>
-      <c r="F87" s="27"/>
+      <c r="D87" s="38"/>
+      <c r="E87" s="39"/>
+      <c r="F87" s="36"/>
       <c r="G87" s="22" t="s">
         <v>185</v>
       </c>
@@ -6518,9 +6506,9 @@
       <c r="C88" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D88" s="32"/>
-      <c r="E88" s="25"/>
-      <c r="F88" s="27"/>
+      <c r="D88" s="38"/>
+      <c r="E88" s="39"/>
+      <c r="F88" s="36"/>
       <c r="G88" s="22" t="s">
         <v>185</v>
       </c>
@@ -6539,9 +6527,9 @@
       <c r="C89" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D89" s="32"/>
-      <c r="E89" s="25"/>
-      <c r="F89" s="27"/>
+      <c r="D89" s="38"/>
+      <c r="E89" s="39"/>
+      <c r="F89" s="36"/>
       <c r="G89" s="22" t="s">
         <v>185</v>
       </c>
@@ -6560,9 +6548,9 @@
       <c r="C90" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D90" s="32"/>
-      <c r="E90" s="25"/>
-      <c r="F90" s="27"/>
+      <c r="D90" s="38"/>
+      <c r="E90" s="39"/>
+      <c r="F90" s="36"/>
       <c r="G90" s="22" t="s">
         <v>185</v>
       </c>
@@ -6581,9 +6569,9 @@
       <c r="C91" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D91" s="32"/>
-      <c r="E91" s="25"/>
-      <c r="F91" s="27"/>
+      <c r="D91" s="38"/>
+      <c r="E91" s="39"/>
+      <c r="F91" s="36"/>
       <c r="G91" s="22" t="s">
         <v>185</v>
       </c>
@@ -6602,9 +6590,9 @@
       <c r="C92" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D92" s="32"/>
-      <c r="E92" s="25"/>
-      <c r="F92" s="27"/>
+      <c r="D92" s="38"/>
+      <c r="E92" s="39"/>
+      <c r="F92" s="36"/>
       <c r="G92" s="22" t="s">
         <v>185</v>
       </c>
@@ -6623,9 +6611,9 @@
       <c r="C93" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D93" s="32"/>
-      <c r="E93" s="25"/>
-      <c r="F93" s="27"/>
+      <c r="D93" s="38"/>
+      <c r="E93" s="39"/>
+      <c r="F93" s="36"/>
       <c r="G93" s="22" t="s">
         <v>185</v>
       </c>
@@ -6644,9 +6632,9 @@
       <c r="C94" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D94" s="32"/>
-      <c r="E94" s="25"/>
-      <c r="F94" s="27"/>
+      <c r="D94" s="38"/>
+      <c r="E94" s="39"/>
+      <c r="F94" s="36"/>
       <c r="G94" s="22" t="s">
         <v>185</v>
       </c>
@@ -6665,9 +6653,9 @@
       <c r="C95" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D95" s="32"/>
-      <c r="E95" s="25"/>
-      <c r="F95" s="27"/>
+      <c r="D95" s="38"/>
+      <c r="E95" s="39"/>
+      <c r="F95" s="36"/>
       <c r="G95" s="22" t="s">
         <v>185</v>
       </c>
@@ -6686,9 +6674,9 @@
       <c r="C96" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D96" s="32"/>
-      <c r="E96" s="25"/>
-      <c r="F96" s="27"/>
+      <c r="D96" s="38"/>
+      <c r="E96" s="39"/>
+      <c r="F96" s="36"/>
       <c r="G96" s="22" t="s">
         <v>185</v>
       </c>
@@ -6707,9 +6695,9 @@
       <c r="C97" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D97" s="32"/>
-      <c r="E97" s="25"/>
-      <c r="F97" s="28"/>
+      <c r="D97" s="38"/>
+      <c r="E97" s="39"/>
+      <c r="F97" s="37"/>
       <c r="G97" s="22" t="s">
         <v>185</v>
       </c>
@@ -6728,9 +6716,9 @@
       <c r="C98" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D98" s="32"/>
-      <c r="E98" s="25"/>
-      <c r="F98" s="26" t="s">
+      <c r="D98" s="38"/>
+      <c r="E98" s="39"/>
+      <c r="F98" s="35" t="s">
         <v>122</v>
       </c>
       <c r="G98" s="22" t="s">
@@ -6751,9 +6739,9 @@
       <c r="C99" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D99" s="32"/>
-      <c r="E99" s="25"/>
-      <c r="F99" s="28"/>
+      <c r="D99" s="38"/>
+      <c r="E99" s="39"/>
+      <c r="F99" s="37"/>
       <c r="G99" s="22" t="s">
         <v>229</v>
       </c>
@@ -6772,9 +6760,9 @@
       <c r="C100" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D100" s="32"/>
-      <c r="E100" s="25"/>
-      <c r="F100" s="26" t="s">
+      <c r="D100" s="38"/>
+      <c r="E100" s="39"/>
+      <c r="F100" s="35" t="s">
         <v>129</v>
       </c>
       <c r="G100" s="22" t="s">
@@ -6795,9 +6783,9 @@
       <c r="C101" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D101" s="32"/>
-      <c r="E101" s="25"/>
-      <c r="F101" s="27"/>
+      <c r="D101" s="38"/>
+      <c r="E101" s="39"/>
+      <c r="F101" s="36"/>
       <c r="G101" s="22" t="s">
         <v>232</v>
       </c>
@@ -6816,9 +6804,9 @@
       <c r="C102" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D102" s="32"/>
-      <c r="E102" s="25"/>
-      <c r="F102" s="27"/>
+      <c r="D102" s="38"/>
+      <c r="E102" s="39"/>
+      <c r="F102" s="36"/>
       <c r="G102" s="22" t="s">
         <v>232</v>
       </c>
@@ -6837,9 +6825,9 @@
       <c r="C103" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D103" s="32"/>
-      <c r="E103" s="25"/>
-      <c r="F103" s="27"/>
+      <c r="D103" s="38"/>
+      <c r="E103" s="39"/>
+      <c r="F103" s="36"/>
       <c r="G103" s="22" t="s">
         <v>232</v>
       </c>
@@ -6858,9 +6846,9 @@
       <c r="C104" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D104" s="32"/>
-      <c r="E104" s="25"/>
-      <c r="F104" s="27"/>
+      <c r="D104" s="38"/>
+      <c r="E104" s="39"/>
+      <c r="F104" s="36"/>
       <c r="G104" s="22" t="s">
         <v>232</v>
       </c>
@@ -6879,9 +6867,9 @@
       <c r="C105" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D105" s="32"/>
-      <c r="E105" s="25"/>
-      <c r="F105" s="27"/>
+      <c r="D105" s="38"/>
+      <c r="E105" s="39"/>
+      <c r="F105" s="36"/>
       <c r="G105" s="22" t="s">
         <v>232</v>
       </c>
@@ -6900,9 +6888,9 @@
       <c r="C106" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D106" s="32"/>
-      <c r="E106" s="25"/>
-      <c r="F106" s="27"/>
+      <c r="D106" s="38"/>
+      <c r="E106" s="39"/>
+      <c r="F106" s="36"/>
       <c r="G106" s="22" t="s">
         <v>232</v>
       </c>
@@ -6921,9 +6909,9 @@
       <c r="C107" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D107" s="32"/>
-      <c r="E107" s="25"/>
-      <c r="F107" s="27"/>
+      <c r="D107" s="38"/>
+      <c r="E107" s="39"/>
+      <c r="F107" s="36"/>
       <c r="G107" s="22" t="s">
         <v>232</v>
       </c>
@@ -6942,9 +6930,9 @@
       <c r="C108" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D108" s="32"/>
-      <c r="E108" s="25"/>
-      <c r="F108" s="27"/>
+      <c r="D108" s="38"/>
+      <c r="E108" s="39"/>
+      <c r="F108" s="36"/>
       <c r="G108" s="22" t="s">
         <v>232</v>
       </c>
@@ -6963,9 +6951,9 @@
       <c r="C109" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D109" s="32"/>
-      <c r="E109" s="25"/>
-      <c r="F109" s="27"/>
+      <c r="D109" s="38"/>
+      <c r="E109" s="39"/>
+      <c r="F109" s="36"/>
       <c r="G109" s="22" t="s">
         <v>232</v>
       </c>
@@ -6984,9 +6972,9 @@
       <c r="C110" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D110" s="32"/>
-      <c r="E110" s="25"/>
-      <c r="F110" s="27"/>
+      <c r="D110" s="38"/>
+      <c r="E110" s="39"/>
+      <c r="F110" s="36"/>
       <c r="G110" s="22" t="s">
         <v>232</v>
       </c>
@@ -7005,9 +6993,9 @@
       <c r="C111" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D111" s="32"/>
-      <c r="E111" s="25"/>
-      <c r="F111" s="27"/>
+      <c r="D111" s="38"/>
+      <c r="E111" s="39"/>
+      <c r="F111" s="36"/>
       <c r="G111" s="22" t="s">
         <v>232</v>
       </c>
@@ -7026,9 +7014,9 @@
       <c r="C112" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D112" s="32"/>
-      <c r="E112" s="25"/>
-      <c r="F112" s="27"/>
+      <c r="D112" s="38"/>
+      <c r="E112" s="39"/>
+      <c r="F112" s="36"/>
       <c r="G112" s="22" t="s">
         <v>232</v>
       </c>
@@ -7047,9 +7035,9 @@
       <c r="C113" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D113" s="32"/>
-      <c r="E113" s="25"/>
-      <c r="F113" s="27"/>
+      <c r="D113" s="38"/>
+      <c r="E113" s="39"/>
+      <c r="F113" s="36"/>
       <c r="G113" s="22" t="s">
         <v>232</v>
       </c>
@@ -7068,9 +7056,9 @@
       <c r="C114" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D114" s="32"/>
-      <c r="E114" s="25"/>
-      <c r="F114" s="27"/>
+      <c r="D114" s="38"/>
+      <c r="E114" s="39"/>
+      <c r="F114" s="36"/>
       <c r="G114" s="22" t="s">
         <v>232</v>
       </c>
@@ -7089,9 +7077,9 @@
       <c r="C115" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D115" s="32"/>
-      <c r="E115" s="25"/>
-      <c r="F115" s="28"/>
+      <c r="D115" s="38"/>
+      <c r="E115" s="39"/>
+      <c r="F115" s="37"/>
       <c r="G115" s="22" t="s">
         <v>232</v>
       </c>
@@ -7110,9 +7098,9 @@
       <c r="C116" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D116" s="32"/>
-      <c r="E116" s="25"/>
-      <c r="F116" s="26" t="s">
+      <c r="D116" s="38"/>
+      <c r="E116" s="39"/>
+      <c r="F116" s="35" t="s">
         <v>122</v>
       </c>
       <c r="G116" s="22" t="s">
@@ -7133,9 +7121,9 @@
       <c r="C117" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D117" s="32"/>
-      <c r="E117" s="25"/>
-      <c r="F117" s="28"/>
+      <c r="D117" s="38"/>
+      <c r="E117" s="39"/>
+      <c r="F117" s="37"/>
       <c r="G117" s="22" t="s">
         <v>268</v>
       </c>
@@ -7154,9 +7142,9 @@
       <c r="C118" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D118" s="32"/>
-      <c r="E118" s="25"/>
-      <c r="F118" s="26" t="s">
+      <c r="D118" s="38"/>
+      <c r="E118" s="39"/>
+      <c r="F118" s="35" t="s">
         <v>129</v>
       </c>
       <c r="G118" s="22" t="s">
@@ -7177,9 +7165,9 @@
       <c r="C119" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D119" s="32"/>
-      <c r="E119" s="25"/>
-      <c r="F119" s="27"/>
+      <c r="D119" s="38"/>
+      <c r="E119" s="39"/>
+      <c r="F119" s="36"/>
       <c r="G119" s="22" t="s">
         <v>271</v>
       </c>
@@ -7198,9 +7186,9 @@
       <c r="C120" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D120" s="32"/>
-      <c r="E120" s="25"/>
-      <c r="F120" s="27"/>
+      <c r="D120" s="38"/>
+      <c r="E120" s="39"/>
+      <c r="F120" s="36"/>
       <c r="G120" s="22" t="s">
         <v>271</v>
       </c>
@@ -7219,9 +7207,9 @@
       <c r="C121" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D121" s="32"/>
-      <c r="E121" s="25"/>
-      <c r="F121" s="27"/>
+      <c r="D121" s="38"/>
+      <c r="E121" s="39"/>
+      <c r="F121" s="36"/>
       <c r="G121" s="22" t="s">
         <v>271</v>
       </c>
@@ -7240,9 +7228,9 @@
       <c r="C122" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D122" s="32"/>
-      <c r="E122" s="25"/>
-      <c r="F122" s="27"/>
+      <c r="D122" s="38"/>
+      <c r="E122" s="39"/>
+      <c r="F122" s="36"/>
       <c r="G122" s="22" t="s">
         <v>271</v>
       </c>
@@ -7261,9 +7249,9 @@
       <c r="C123" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D123" s="32"/>
-      <c r="E123" s="25"/>
-      <c r="F123" s="27"/>
+      <c r="D123" s="38"/>
+      <c r="E123" s="39"/>
+      <c r="F123" s="36"/>
       <c r="G123" s="22" t="s">
         <v>271</v>
       </c>
@@ -7282,9 +7270,9 @@
       <c r="C124" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D124" s="32"/>
-      <c r="E124" s="25"/>
-      <c r="F124" s="27"/>
+      <c r="D124" s="38"/>
+      <c r="E124" s="39"/>
+      <c r="F124" s="36"/>
       <c r="G124" s="22" t="s">
         <v>271</v>
       </c>
@@ -7303,9 +7291,9 @@
       <c r="C125" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D125" s="32"/>
-      <c r="E125" s="25"/>
-      <c r="F125" s="27"/>
+      <c r="D125" s="38"/>
+      <c r="E125" s="39"/>
+      <c r="F125" s="36"/>
       <c r="G125" s="22" t="s">
         <v>271</v>
       </c>
@@ -7324,9 +7312,9 @@
       <c r="C126" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D126" s="32"/>
-      <c r="E126" s="25"/>
-      <c r="F126" s="27"/>
+      <c r="D126" s="38"/>
+      <c r="E126" s="39"/>
+      <c r="F126" s="36"/>
       <c r="G126" s="22" t="s">
         <v>271</v>
       </c>
@@ -7345,9 +7333,9 @@
       <c r="C127" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D127" s="32"/>
-      <c r="E127" s="25"/>
-      <c r="F127" s="27"/>
+      <c r="D127" s="38"/>
+      <c r="E127" s="39"/>
+      <c r="F127" s="36"/>
       <c r="G127" s="22" t="s">
         <v>271</v>
       </c>
@@ -7366,9 +7354,9 @@
       <c r="C128" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D128" s="32"/>
-      <c r="E128" s="25"/>
-      <c r="F128" s="27"/>
+      <c r="D128" s="38"/>
+      <c r="E128" s="39"/>
+      <c r="F128" s="36"/>
       <c r="G128" s="22" t="s">
         <v>271</v>
       </c>
@@ -7387,9 +7375,9 @@
       <c r="C129" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D129" s="32"/>
-      <c r="E129" s="25"/>
-      <c r="F129" s="28"/>
+      <c r="D129" s="38"/>
+      <c r="E129" s="39"/>
+      <c r="F129" s="37"/>
       <c r="G129" s="22" t="s">
         <v>271</v>
       </c>
@@ -7408,9 +7396,9 @@
       <c r="C130" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D130" s="32"/>
-      <c r="E130" s="25"/>
-      <c r="F130" s="26" t="s">
+      <c r="D130" s="38"/>
+      <c r="E130" s="39"/>
+      <c r="F130" s="35" t="s">
         <v>122</v>
       </c>
       <c r="G130" s="22" t="s">
@@ -7431,9 +7419,9 @@
       <c r="C131" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D131" s="32"/>
-      <c r="E131" s="25"/>
-      <c r="F131" s="28"/>
+      <c r="D131" s="38"/>
+      <c r="E131" s="39"/>
+      <c r="F131" s="37"/>
       <c r="G131" s="22" t="s">
         <v>299</v>
       </c>
@@ -7452,9 +7440,9 @@
       <c r="C132" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D132" s="32"/>
-      <c r="E132" s="25"/>
-      <c r="F132" s="26" t="s">
+      <c r="D132" s="38"/>
+      <c r="E132" s="39"/>
+      <c r="F132" s="35" t="s">
         <v>129</v>
       </c>
       <c r="G132" s="22" t="s">
@@ -7475,9 +7463,9 @@
       <c r="C133" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D133" s="32"/>
-      <c r="E133" s="25"/>
-      <c r="F133" s="27"/>
+      <c r="D133" s="38"/>
+      <c r="E133" s="39"/>
+      <c r="F133" s="36"/>
       <c r="G133" s="22" t="s">
         <v>302</v>
       </c>
@@ -7496,9 +7484,9 @@
       <c r="C134" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D134" s="32"/>
-      <c r="E134" s="25"/>
-      <c r="F134" s="27"/>
+      <c r="D134" s="38"/>
+      <c r="E134" s="39"/>
+      <c r="F134" s="36"/>
       <c r="G134" s="22" t="s">
         <v>302</v>
       </c>
@@ -7517,9 +7505,9 @@
       <c r="C135" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D135" s="32"/>
-      <c r="E135" s="25"/>
-      <c r="F135" s="27"/>
+      <c r="D135" s="38"/>
+      <c r="E135" s="39"/>
+      <c r="F135" s="36"/>
       <c r="G135" s="22" t="s">
         <v>302</v>
       </c>
@@ -7538,9 +7526,9 @@
       <c r="C136" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D136" s="32"/>
-      <c r="E136" s="25"/>
-      <c r="F136" s="27"/>
+      <c r="D136" s="38"/>
+      <c r="E136" s="39"/>
+      <c r="F136" s="36"/>
       <c r="G136" s="22" t="s">
         <v>302</v>
       </c>
@@ -7559,9 +7547,9 @@
       <c r="C137" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D137" s="32"/>
-      <c r="E137" s="25"/>
-      <c r="F137" s="27"/>
+      <c r="D137" s="38"/>
+      <c r="E137" s="39"/>
+      <c r="F137" s="36"/>
       <c r="G137" s="22" t="s">
         <v>302</v>
       </c>
@@ -7580,9 +7568,9 @@
       <c r="C138" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D138" s="32"/>
-      <c r="E138" s="25"/>
-      <c r="F138" s="27"/>
+      <c r="D138" s="38"/>
+      <c r="E138" s="39"/>
+      <c r="F138" s="36"/>
       <c r="G138" s="22" t="s">
         <v>302</v>
       </c>
@@ -7601,9 +7589,9 @@
       <c r="C139" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D139" s="32"/>
-      <c r="E139" s="25"/>
-      <c r="F139" s="27"/>
+      <c r="D139" s="38"/>
+      <c r="E139" s="39"/>
+      <c r="F139" s="36"/>
       <c r="G139" s="22" t="s">
         <v>302</v>
       </c>
@@ -7622,9 +7610,9 @@
       <c r="C140" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D140" s="32"/>
-      <c r="E140" s="25"/>
-      <c r="F140" s="27"/>
+      <c r="D140" s="38"/>
+      <c r="E140" s="39"/>
+      <c r="F140" s="36"/>
       <c r="G140" s="22" t="s">
         <v>302</v>
       </c>
@@ -7643,9 +7631,9 @@
       <c r="C141" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D141" s="32"/>
-      <c r="E141" s="25"/>
-      <c r="F141" s="28"/>
+      <c r="D141" s="38"/>
+      <c r="E141" s="39"/>
+      <c r="F141" s="37"/>
       <c r="G141" s="22" t="s">
         <v>302</v>
       </c>
@@ -7664,9 +7652,9 @@
       <c r="C142" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D142" s="32"/>
-      <c r="E142" s="25"/>
-      <c r="F142" s="26" t="s">
+      <c r="D142" s="38"/>
+      <c r="E142" s="39"/>
+      <c r="F142" s="35" t="s">
         <v>122</v>
       </c>
       <c r="G142" s="22" t="s">
@@ -7687,9 +7675,9 @@
       <c r="C143" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D143" s="32"/>
-      <c r="E143" s="25"/>
-      <c r="F143" s="28"/>
+      <c r="D143" s="38"/>
+      <c r="E143" s="39"/>
+      <c r="F143" s="37"/>
       <c r="G143" s="22" t="s">
         <v>326</v>
       </c>
@@ -7708,9 +7696,9 @@
       <c r="C144" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D144" s="32"/>
-      <c r="E144" s="25"/>
-      <c r="F144" s="26" t="s">
+      <c r="D144" s="38"/>
+      <c r="E144" s="39"/>
+      <c r="F144" s="35" t="s">
         <v>129</v>
       </c>
       <c r="G144" s="22" t="s">
@@ -7731,9 +7719,9 @@
       <c r="C145" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D145" s="32"/>
-      <c r="E145" s="25"/>
-      <c r="F145" s="27"/>
+      <c r="D145" s="38"/>
+      <c r="E145" s="39"/>
+      <c r="F145" s="36"/>
       <c r="G145" s="22" t="s">
         <v>329</v>
       </c>
@@ -7752,9 +7740,9 @@
       <c r="C146" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D146" s="32"/>
-      <c r="E146" s="25"/>
-      <c r="F146" s="27"/>
+      <c r="D146" s="38"/>
+      <c r="E146" s="39"/>
+      <c r="F146" s="36"/>
       <c r="G146" s="22" t="s">
         <v>329</v>
       </c>
@@ -7773,9 +7761,9 @@
       <c r="C147" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D147" s="32"/>
-      <c r="E147" s="25"/>
-      <c r="F147" s="28"/>
+      <c r="D147" s="38"/>
+      <c r="E147" s="39"/>
+      <c r="F147" s="37"/>
       <c r="G147" s="22" t="s">
         <v>329</v>
       </c>
@@ -7794,9 +7782,9 @@
       <c r="C148" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D148" s="32"/>
-      <c r="E148" s="25"/>
-      <c r="F148" s="26" t="s">
+      <c r="D148" s="38"/>
+      <c r="E148" s="39"/>
+      <c r="F148" s="35" t="s">
         <v>122</v>
       </c>
       <c r="G148" s="22" t="s">
@@ -7817,9 +7805,9 @@
       <c r="C149" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D149" s="32"/>
-      <c r="E149" s="25"/>
-      <c r="F149" s="28"/>
+      <c r="D149" s="38"/>
+      <c r="E149" s="39"/>
+      <c r="F149" s="37"/>
       <c r="G149" s="22" t="s">
         <v>341</v>
       </c>
@@ -7838,9 +7826,9 @@
       <c r="C150" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D150" s="32"/>
-      <c r="E150" s="25"/>
-      <c r="F150" s="26" t="s">
+      <c r="D150" s="38"/>
+      <c r="E150" s="39"/>
+      <c r="F150" s="35" t="s">
         <v>129</v>
       </c>
       <c r="G150" s="22" t="s">
@@ -7861,9 +7849,9 @@
       <c r="C151" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D151" s="32"/>
-      <c r="E151" s="25"/>
-      <c r="F151" s="27"/>
+      <c r="D151" s="38"/>
+      <c r="E151" s="39"/>
+      <c r="F151" s="36"/>
       <c r="G151" s="22" t="s">
         <v>344</v>
       </c>
@@ -7882,9 +7870,9 @@
       <c r="C152" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D152" s="32"/>
-      <c r="E152" s="25"/>
-      <c r="F152" s="27"/>
+      <c r="D152" s="38"/>
+      <c r="E152" s="39"/>
+      <c r="F152" s="36"/>
       <c r="G152" s="22" t="s">
         <v>344</v>
       </c>
@@ -7903,9 +7891,9 @@
       <c r="C153" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D153" s="32"/>
-      <c r="E153" s="25"/>
-      <c r="F153" s="27"/>
+      <c r="D153" s="38"/>
+      <c r="E153" s="39"/>
+      <c r="F153" s="36"/>
       <c r="G153" s="22" t="s">
         <v>344</v>
       </c>
@@ -7924,9 +7912,9 @@
       <c r="C154" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D154" s="32"/>
-      <c r="E154" s="25"/>
-      <c r="F154" s="27"/>
+      <c r="D154" s="38"/>
+      <c r="E154" s="39"/>
+      <c r="F154" s="36"/>
       <c r="G154" s="22" t="s">
         <v>344</v>
       </c>
@@ -7945,9 +7933,9 @@
       <c r="C155" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D155" s="32"/>
-      <c r="E155" s="25"/>
-      <c r="F155" s="28"/>
+      <c r="D155" s="38"/>
+      <c r="E155" s="39"/>
+      <c r="F155" s="37"/>
       <c r="G155" s="22" t="s">
         <v>344</v>
       </c>
@@ -7966,9 +7954,9 @@
       <c r="C156" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D156" s="32"/>
-      <c r="E156" s="25"/>
-      <c r="F156" s="26" t="s">
+      <c r="D156" s="38"/>
+      <c r="E156" s="39"/>
+      <c r="F156" s="35" t="s">
         <v>122</v>
       </c>
       <c r="G156" s="22" t="s">
@@ -7989,9 +7977,9 @@
       <c r="C157" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D157" s="32"/>
-      <c r="E157" s="25"/>
-      <c r="F157" s="27"/>
+      <c r="D157" s="38"/>
+      <c r="E157" s="39"/>
+      <c r="F157" s="36"/>
       <c r="G157" s="22" t="s">
         <v>360</v>
       </c>
@@ -8010,9 +7998,9 @@
       <c r="C158" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D158" s="32"/>
-      <c r="E158" s="25"/>
-      <c r="F158" s="27"/>
+      <c r="D158" s="38"/>
+      <c r="E158" s="39"/>
+      <c r="F158" s="36"/>
       <c r="G158" s="22" t="s">
         <v>363</v>
       </c>
@@ -8031,9 +8019,9 @@
       <c r="C159" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D159" s="32"/>
-      <c r="E159" s="25"/>
-      <c r="F159" s="27"/>
+      <c r="D159" s="38"/>
+      <c r="E159" s="39"/>
+      <c r="F159" s="36"/>
       <c r="G159" s="22" t="s">
         <v>366</v>
       </c>
@@ -8052,9 +8040,9 @@
       <c r="C160" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D160" s="32"/>
-      <c r="E160" s="25"/>
-      <c r="F160" s="27"/>
+      <c r="D160" s="38"/>
+      <c r="E160" s="39"/>
+      <c r="F160" s="36"/>
       <c r="G160" s="22" t="s">
         <v>369</v>
       </c>
@@ -8073,9 +8061,9 @@
       <c r="C161" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D161" s="32"/>
-      <c r="E161" s="25"/>
-      <c r="F161" s="28"/>
+      <c r="D161" s="38"/>
+      <c r="E161" s="39"/>
+      <c r="F161" s="37"/>
       <c r="G161" s="22" t="s">
         <v>372</v>
       </c>
@@ -8094,9 +8082,9 @@
       <c r="C162" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D162" s="32"/>
-      <c r="E162" s="25"/>
-      <c r="F162" s="26" t="s">
+      <c r="D162" s="38"/>
+      <c r="E162" s="39"/>
+      <c r="F162" s="35" t="s">
         <v>129</v>
       </c>
       <c r="G162" s="22" t="s">
@@ -8117,9 +8105,9 @@
       <c r="C163" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D163" s="32"/>
-      <c r="E163" s="25"/>
-      <c r="F163" s="27"/>
+      <c r="D163" s="38"/>
+      <c r="E163" s="39"/>
+      <c r="F163" s="36"/>
       <c r="G163" s="22" t="s">
         <v>375</v>
       </c>
@@ -8138,9 +8126,9 @@
       <c r="C164" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D164" s="32"/>
-      <c r="E164" s="25"/>
-      <c r="F164" s="27"/>
+      <c r="D164" s="38"/>
+      <c r="E164" s="39"/>
+      <c r="F164" s="36"/>
       <c r="G164" s="22" t="s">
         <v>375</v>
       </c>
@@ -8159,9 +8147,9 @@
       <c r="C165" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D165" s="32"/>
-      <c r="E165" s="25"/>
-      <c r="F165" s="27"/>
+      <c r="D165" s="38"/>
+      <c r="E165" s="39"/>
+      <c r="F165" s="36"/>
       <c r="G165" s="22" t="s">
         <v>375</v>
       </c>
@@ -8180,9 +8168,9 @@
       <c r="C166" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D166" s="32"/>
-      <c r="E166" s="25"/>
-      <c r="F166" s="27"/>
+      <c r="D166" s="38"/>
+      <c r="E166" s="39"/>
+      <c r="F166" s="36"/>
       <c r="G166" s="22" t="s">
         <v>375</v>
       </c>
@@ -8201,9 +8189,9 @@
       <c r="C167" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D167" s="32"/>
-      <c r="E167" s="25"/>
-      <c r="F167" s="27"/>
+      <c r="D167" s="38"/>
+      <c r="E167" s="39"/>
+      <c r="F167" s="36"/>
       <c r="G167" s="22" t="s">
         <v>375</v>
       </c>
@@ -8222,9 +8210,9 @@
       <c r="C168" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D168" s="32"/>
-      <c r="E168" s="25"/>
-      <c r="F168" s="27"/>
+      <c r="D168" s="38"/>
+      <c r="E168" s="39"/>
+      <c r="F168" s="36"/>
       <c r="G168" s="22" t="s">
         <v>375</v>
       </c>
@@ -8243,9 +8231,9 @@
       <c r="C169" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D169" s="32"/>
-      <c r="E169" s="25"/>
-      <c r="F169" s="27"/>
+      <c r="D169" s="38"/>
+      <c r="E169" s="39"/>
+      <c r="F169" s="36"/>
       <c r="G169" s="22" t="s">
         <v>375</v>
       </c>
@@ -8264,9 +8252,9 @@
       <c r="C170" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D170" s="32"/>
-      <c r="E170" s="25"/>
-      <c r="F170" s="27"/>
+      <c r="D170" s="38"/>
+      <c r="E170" s="39"/>
+      <c r="F170" s="36"/>
       <c r="G170" s="22" t="s">
         <v>375</v>
       </c>
@@ -8285,9 +8273,9 @@
       <c r="C171" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D171" s="32"/>
-      <c r="E171" s="25"/>
-      <c r="F171" s="28"/>
+      <c r="D171" s="38"/>
+      <c r="E171" s="39"/>
+      <c r="F171" s="37"/>
       <c r="G171" s="22" t="s">
         <v>375</v>
       </c>
@@ -8306,9 +8294,9 @@
       <c r="C172" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D172" s="32"/>
-      <c r="E172" s="25"/>
-      <c r="F172" s="26" t="s">
+      <c r="D172" s="38"/>
+      <c r="E172" s="39"/>
+      <c r="F172" s="35" t="s">
         <v>122</v>
       </c>
       <c r="G172" s="22" t="s">
@@ -8329,9 +8317,9 @@
       <c r="C173" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D173" s="32"/>
-      <c r="E173" s="25"/>
-      <c r="F173" s="27"/>
+      <c r="D173" s="38"/>
+      <c r="E173" s="39"/>
+      <c r="F173" s="36"/>
       <c r="G173" s="22" t="s">
         <v>399</v>
       </c>
@@ -8350,9 +8338,9 @@
       <c r="C174" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D174" s="32"/>
-      <c r="E174" s="25"/>
-      <c r="F174" s="27"/>
+      <c r="D174" s="38"/>
+      <c r="E174" s="39"/>
+      <c r="F174" s="36"/>
       <c r="G174" s="22" t="s">
         <v>402</v>
       </c>
@@ -8371,9 +8359,9 @@
       <c r="C175" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D175" s="32"/>
-      <c r="E175" s="25"/>
-      <c r="F175" s="28"/>
+      <c r="D175" s="38"/>
+      <c r="E175" s="39"/>
+      <c r="F175" s="37"/>
       <c r="G175" s="22" t="s">
         <v>405</v>
       </c>
@@ -8392,9 +8380,9 @@
       <c r="C176" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D176" s="32"/>
-      <c r="E176" s="25"/>
-      <c r="F176" s="37" t="s">
+      <c r="D176" s="38"/>
+      <c r="E176" s="39"/>
+      <c r="F176" s="32" t="s">
         <v>129</v>
       </c>
       <c r="G176" s="23" t="s">
@@ -8415,9 +8403,9 @@
       <c r="C177" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D177" s="32"/>
-      <c r="E177" s="25"/>
-      <c r="F177" s="38"/>
+      <c r="D177" s="38"/>
+      <c r="E177" s="39"/>
+      <c r="F177" s="33"/>
       <c r="G177" s="23" t="s">
         <v>408</v>
       </c>
@@ -8436,9 +8424,9 @@
       <c r="C178" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D178" s="32"/>
-      <c r="E178" s="25"/>
-      <c r="F178" s="38"/>
+      <c r="D178" s="38"/>
+      <c r="E178" s="39"/>
+      <c r="F178" s="33"/>
       <c r="G178" s="23" t="s">
         <v>408</v>
       </c>
@@ -8457,9 +8445,9 @@
       <c r="C179" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D179" s="32"/>
-      <c r="E179" s="25"/>
-      <c r="F179" s="39"/>
+      <c r="D179" s="38"/>
+      <c r="E179" s="39"/>
+      <c r="F179" s="34"/>
       <c r="G179" s="23" t="s">
         <v>408</v>
       </c>
@@ -8478,9 +8466,9 @@
       <c r="C180" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D180" s="32"/>
-      <c r="E180" s="25"/>
-      <c r="F180" s="37" t="s">
+      <c r="D180" s="38"/>
+      <c r="E180" s="39"/>
+      <c r="F180" s="32" t="s">
         <v>122</v>
       </c>
       <c r="G180" s="23" t="s">
@@ -8501,9 +8489,9 @@
       <c r="C181" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D181" s="32"/>
-      <c r="E181" s="25"/>
-      <c r="F181" s="39"/>
+      <c r="D181" s="38"/>
+      <c r="E181" s="39"/>
+      <c r="F181" s="34"/>
       <c r="G181" s="23" t="s">
         <v>420</v>
       </c>
@@ -8522,9 +8510,9 @@
       <c r="C182" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D182" s="32"/>
-      <c r="E182" s="25"/>
-      <c r="F182" s="37" t="s">
+      <c r="D182" s="38"/>
+      <c r="E182" s="39"/>
+      <c r="F182" s="32" t="s">
         <v>129</v>
       </c>
       <c r="G182" s="23" t="s">
@@ -8545,9 +8533,9 @@
       <c r="C183" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D183" s="32"/>
-      <c r="E183" s="25"/>
-      <c r="F183" s="38"/>
+      <c r="D183" s="38"/>
+      <c r="E183" s="39"/>
+      <c r="F183" s="33"/>
       <c r="G183" s="23" t="s">
         <v>423</v>
       </c>
@@ -8566,9 +8554,9 @@
       <c r="C184" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D184" s="32"/>
-      <c r="E184" s="25"/>
-      <c r="F184" s="38"/>
+      <c r="D184" s="38"/>
+      <c r="E184" s="39"/>
+      <c r="F184" s="33"/>
       <c r="G184" s="23" t="s">
         <v>423</v>
       </c>
@@ -8587,9 +8575,9 @@
       <c r="C185" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D185" s="32"/>
-      <c r="E185" s="25"/>
-      <c r="F185" s="38"/>
+      <c r="D185" s="38"/>
+      <c r="E185" s="39"/>
+      <c r="F185" s="33"/>
       <c r="G185" s="23" t="s">
         <v>423</v>
       </c>
@@ -8608,9 +8596,9 @@
       <c r="C186" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D186" s="32"/>
-      <c r="E186" s="25"/>
-      <c r="F186" s="38"/>
+      <c r="D186" s="38"/>
+      <c r="E186" s="39"/>
+      <c r="F186" s="33"/>
       <c r="G186" s="23" t="s">
         <v>423</v>
       </c>
@@ -8629,9 +8617,9 @@
       <c r="C187" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D187" s="32"/>
-      <c r="E187" s="25"/>
-      <c r="F187" s="39"/>
+      <c r="D187" s="38"/>
+      <c r="E187" s="39"/>
+      <c r="F187" s="34"/>
       <c r="G187" s="23" t="s">
         <v>423</v>
       </c>
@@ -8650,9 +8638,9 @@
       <c r="C188" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D188" s="32"/>
-      <c r="E188" s="25"/>
-      <c r="F188" s="37" t="s">
+      <c r="D188" s="38"/>
+      <c r="E188" s="39"/>
+      <c r="F188" s="32" t="s">
         <v>122</v>
       </c>
       <c r="G188" s="23" t="s">
@@ -8673,9 +8661,9 @@
       <c r="C189" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D189" s="32"/>
-      <c r="E189" s="25"/>
-      <c r="F189" s="39"/>
+      <c r="D189" s="38"/>
+      <c r="E189" s="39"/>
+      <c r="F189" s="34"/>
       <c r="G189" s="23" t="s">
         <v>439</v>
       </c>
@@ -8694,9 +8682,9 @@
       <c r="C190" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D190" s="32"/>
-      <c r="E190" s="25"/>
-      <c r="F190" s="37" t="s">
+      <c r="D190" s="38"/>
+      <c r="E190" s="39"/>
+      <c r="F190" s="32" t="s">
         <v>129</v>
       </c>
       <c r="G190" s="23" t="s">
@@ -8717,9 +8705,9 @@
       <c r="C191" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D191" s="32"/>
-      <c r="E191" s="25"/>
-      <c r="F191" s="38"/>
+      <c r="D191" s="38"/>
+      <c r="E191" s="39"/>
+      <c r="F191" s="33"/>
       <c r="G191" s="23" t="s">
         <v>442</v>
       </c>
@@ -8738,9 +8726,9 @@
       <c r="C192" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D192" s="32"/>
-      <c r="E192" s="25"/>
-      <c r="F192" s="38"/>
+      <c r="D192" s="38"/>
+      <c r="E192" s="39"/>
+      <c r="F192" s="33"/>
       <c r="G192" s="23" t="s">
         <v>442</v>
       </c>
@@ -8759,9 +8747,9 @@
       <c r="C193" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D193" s="32"/>
-      <c r="E193" s="25"/>
-      <c r="F193" s="38"/>
+      <c r="D193" s="38"/>
+      <c r="E193" s="39"/>
+      <c r="F193" s="33"/>
       <c r="G193" s="23" t="s">
         <v>442</v>
       </c>
@@ -8780,9 +8768,9 @@
       <c r="C194" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D194" s="32"/>
-      <c r="E194" s="25"/>
-      <c r="F194" s="38"/>
+      <c r="D194" s="38"/>
+      <c r="E194" s="39"/>
+      <c r="F194" s="33"/>
       <c r="G194" s="23" t="s">
         <v>442</v>
       </c>
@@ -8801,9 +8789,9 @@
       <c r="C195" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D195" s="32"/>
-      <c r="E195" s="25"/>
-      <c r="F195" s="38"/>
+      <c r="D195" s="38"/>
+      <c r="E195" s="39"/>
+      <c r="F195" s="33"/>
       <c r="G195" s="23" t="s">
         <v>442</v>
       </c>
@@ -8822,9 +8810,9 @@
       <c r="C196" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D196" s="32"/>
-      <c r="E196" s="25"/>
-      <c r="F196" s="38"/>
+      <c r="D196" s="38"/>
+      <c r="E196" s="39"/>
+      <c r="F196" s="33"/>
       <c r="G196" s="23" t="s">
         <v>442</v>
       </c>
@@ -8843,9 +8831,9 @@
       <c r="C197" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D197" s="32"/>
-      <c r="E197" s="25"/>
-      <c r="F197" s="38"/>
+      <c r="D197" s="38"/>
+      <c r="E197" s="39"/>
+      <c r="F197" s="33"/>
       <c r="G197" s="23" t="s">
         <v>442</v>
       </c>
@@ -8864,9 +8852,9 @@
       <c r="C198" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D198" s="32"/>
-      <c r="E198" s="25"/>
-      <c r="F198" s="38"/>
+      <c r="D198" s="38"/>
+      <c r="E198" s="39"/>
+      <c r="F198" s="33"/>
       <c r="G198" s="23" t="s">
         <v>442</v>
       </c>
@@ -8885,9 +8873,9 @@
       <c r="C199" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D199" s="32"/>
-      <c r="E199" s="25"/>
-      <c r="F199" s="38"/>
+      <c r="D199" s="38"/>
+      <c r="E199" s="39"/>
+      <c r="F199" s="33"/>
       <c r="G199" s="23" t="s">
         <v>442</v>
       </c>
@@ -8906,9 +8894,9 @@
       <c r="C200" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D200" s="32"/>
-      <c r="E200" s="25"/>
-      <c r="F200" s="38"/>
+      <c r="D200" s="38"/>
+      <c r="E200" s="39"/>
+      <c r="F200" s="33"/>
       <c r="G200" s="23" t="s">
         <v>442</v>
       </c>
@@ -8927,9 +8915,9 @@
       <c r="C201" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D201" s="32"/>
-      <c r="E201" s="25"/>
-      <c r="F201" s="38"/>
+      <c r="D201" s="38"/>
+      <c r="E201" s="39"/>
+      <c r="F201" s="33"/>
       <c r="G201" s="23" t="s">
         <v>442</v>
       </c>
@@ -8948,9 +8936,9 @@
       <c r="C202" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D202" s="32"/>
-      <c r="E202" s="25"/>
-      <c r="F202" s="38"/>
+      <c r="D202" s="38"/>
+      <c r="E202" s="39"/>
+      <c r="F202" s="33"/>
       <c r="G202" s="23" t="s">
         <v>442</v>
       </c>
@@ -8969,9 +8957,9 @@
       <c r="C203" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D203" s="32"/>
-      <c r="E203" s="25"/>
-      <c r="F203" s="38"/>
+      <c r="D203" s="38"/>
+      <c r="E203" s="39"/>
+      <c r="F203" s="33"/>
       <c r="G203" s="23" t="s">
         <v>442</v>
       </c>
@@ -8990,9 +8978,9 @@
       <c r="C204" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D204" s="32"/>
-      <c r="E204" s="25"/>
-      <c r="F204" s="38"/>
+      <c r="D204" s="38"/>
+      <c r="E204" s="39"/>
+      <c r="F204" s="33"/>
       <c r="G204" s="23" t="s">
         <v>442</v>
       </c>
@@ -9011,9 +8999,9 @@
       <c r="C205" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D205" s="32"/>
-      <c r="E205" s="25"/>
-      <c r="F205" s="38"/>
+      <c r="D205" s="38"/>
+      <c r="E205" s="39"/>
+      <c r="F205" s="33"/>
       <c r="G205" s="23" t="s">
         <v>442</v>
       </c>
@@ -9032,9 +9020,9 @@
       <c r="C206" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D206" s="32"/>
-      <c r="E206" s="25"/>
-      <c r="F206" s="38"/>
+      <c r="D206" s="38"/>
+      <c r="E206" s="39"/>
+      <c r="F206" s="33"/>
       <c r="G206" s="23" t="s">
         <v>442</v>
       </c>
@@ -9053,9 +9041,9 @@
       <c r="C207" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D207" s="32"/>
-      <c r="E207" s="25"/>
-      <c r="F207" s="39"/>
+      <c r="D207" s="38"/>
+      <c r="E207" s="39"/>
+      <c r="F207" s="34"/>
       <c r="G207" s="23" t="s">
         <v>442</v>
       </c>
@@ -9074,9 +9062,9 @@
       <c r="C208" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D208" s="32"/>
-      <c r="E208" s="25"/>
-      <c r="F208" s="37" t="s">
+      <c r="D208" s="38"/>
+      <c r="E208" s="39"/>
+      <c r="F208" s="32" t="s">
         <v>122</v>
       </c>
       <c r="G208" s="23" t="s">
@@ -9097,9 +9085,9 @@
       <c r="C209" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D209" s="32"/>
-      <c r="E209" s="25"/>
-      <c r="F209" s="39"/>
+      <c r="D209" s="38"/>
+      <c r="E209" s="39"/>
+      <c r="F209" s="34"/>
       <c r="G209" s="23" t="s">
         <v>482</v>
       </c>
@@ -9118,9 +9106,9 @@
       <c r="C210" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D210" s="32"/>
-      <c r="E210" s="25"/>
-      <c r="F210" s="37" t="s">
+      <c r="D210" s="38"/>
+      <c r="E210" s="39"/>
+      <c r="F210" s="32" t="s">
         <v>129</v>
       </c>
       <c r="G210" s="23" t="s">
@@ -9141,9 +9129,9 @@
       <c r="C211" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D211" s="32"/>
-      <c r="E211" s="25"/>
-      <c r="F211" s="38"/>
+      <c r="D211" s="38"/>
+      <c r="E211" s="39"/>
+      <c r="F211" s="33"/>
       <c r="G211" s="23" t="s">
         <v>485</v>
       </c>
@@ -9162,9 +9150,9 @@
       <c r="C212" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D212" s="32"/>
-      <c r="E212" s="25"/>
-      <c r="F212" s="38"/>
+      <c r="D212" s="38"/>
+      <c r="E212" s="39"/>
+      <c r="F212" s="33"/>
       <c r="G212" s="23" t="s">
         <v>485</v>
       </c>
@@ -9183,9 +9171,9 @@
       <c r="C213" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D213" s="32"/>
-      <c r="E213" s="25"/>
-      <c r="F213" s="38"/>
+      <c r="D213" s="38"/>
+      <c r="E213" s="39"/>
+      <c r="F213" s="33"/>
       <c r="G213" s="23" t="s">
         <v>485</v>
       </c>
@@ -9204,9 +9192,9 @@
       <c r="C214" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D214" s="32"/>
-      <c r="E214" s="25"/>
-      <c r="F214" s="38"/>
+      <c r="D214" s="38"/>
+      <c r="E214" s="39"/>
+      <c r="F214" s="33"/>
       <c r="G214" s="23" t="s">
         <v>485</v>
       </c>
@@ -9225,9 +9213,9 @@
       <c r="C215" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D215" s="32"/>
-      <c r="E215" s="25"/>
-      <c r="F215" s="39"/>
+      <c r="D215" s="38"/>
+      <c r="E215" s="39"/>
+      <c r="F215" s="34"/>
       <c r="G215" s="23" t="s">
         <v>485</v>
       </c>
@@ -9246,9 +9234,9 @@
       <c r="C216" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D216" s="32"/>
-      <c r="E216" s="25"/>
-      <c r="F216" s="37" t="s">
+      <c r="D216" s="38"/>
+      <c r="E216" s="39"/>
+      <c r="F216" s="32" t="s">
         <v>122</v>
       </c>
       <c r="G216" s="23" t="s">
@@ -9269,9 +9257,9 @@
       <c r="C217" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D217" s="32"/>
-      <c r="E217" s="25"/>
-      <c r="F217" s="39"/>
+      <c r="D217" s="38"/>
+      <c r="E217" s="39"/>
+      <c r="F217" s="34"/>
       <c r="G217" s="23" t="s">
         <v>499</v>
       </c>
@@ -9290,9 +9278,9 @@
       <c r="C218" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D218" s="32"/>
-      <c r="E218" s="25"/>
-      <c r="F218" s="37" t="s">
+      <c r="D218" s="38"/>
+      <c r="E218" s="39"/>
+      <c r="F218" s="32" t="s">
         <v>129</v>
       </c>
       <c r="G218" s="23" t="s">
@@ -9313,9 +9301,9 @@
       <c r="C219" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D219" s="32"/>
-      <c r="E219" s="25"/>
-      <c r="F219" s="38"/>
+      <c r="D219" s="38"/>
+      <c r="E219" s="39"/>
+      <c r="F219" s="33"/>
       <c r="G219" s="23" t="s">
         <v>502</v>
       </c>
@@ -9334,9 +9322,9 @@
       <c r="C220" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D220" s="32"/>
-      <c r="E220" s="25"/>
-      <c r="F220" s="38"/>
+      <c r="D220" s="38"/>
+      <c r="E220" s="39"/>
+      <c r="F220" s="33"/>
       <c r="G220" s="23" t="s">
         <v>502</v>
       </c>
@@ -9355,9 +9343,9 @@
       <c r="C221" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D221" s="32"/>
-      <c r="E221" s="25"/>
-      <c r="F221" s="38"/>
+      <c r="D221" s="38"/>
+      <c r="E221" s="39"/>
+      <c r="F221" s="33"/>
       <c r="G221" s="23" t="s">
         <v>502</v>
       </c>
@@ -9376,9 +9364,9 @@
       <c r="C222" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D222" s="32"/>
-      <c r="E222" s="25"/>
-      <c r="F222" s="38"/>
+      <c r="D222" s="38"/>
+      <c r="E222" s="39"/>
+      <c r="F222" s="33"/>
       <c r="G222" s="23" t="s">
         <v>502</v>
       </c>
@@ -9397,9 +9385,9 @@
       <c r="C223" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D223" s="32"/>
-      <c r="E223" s="25"/>
-      <c r="F223" s="39"/>
+      <c r="D223" s="38"/>
+      <c r="E223" s="39"/>
+      <c r="F223" s="34"/>
       <c r="G223" s="23" t="s">
         <v>502</v>
       </c>
@@ -9418,9 +9406,9 @@
       <c r="C224" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D224" s="32"/>
-      <c r="E224" s="25"/>
-      <c r="F224" s="37" t="s">
+      <c r="D224" s="38"/>
+      <c r="E224" s="39"/>
+      <c r="F224" s="32" t="s">
         <v>122</v>
       </c>
       <c r="G224" s="23" t="s">
@@ -9441,9 +9429,9 @@
       <c r="C225" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D225" s="32"/>
-      <c r="E225" s="25"/>
-      <c r="F225" s="38"/>
+      <c r="D225" s="38"/>
+      <c r="E225" s="39"/>
+      <c r="F225" s="33"/>
       <c r="G225" s="23" t="s">
         <v>518</v>
       </c>
@@ -9462,9 +9450,9 @@
       <c r="C226" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D226" s="32"/>
-      <c r="E226" s="25"/>
-      <c r="F226" s="38"/>
+      <c r="D226" s="38"/>
+      <c r="E226" s="39"/>
+      <c r="F226" s="33"/>
       <c r="G226" s="23" t="s">
         <v>521</v>
       </c>
@@ -9483,9 +9471,9 @@
       <c r="C227" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D227" s="32"/>
-      <c r="E227" s="25"/>
-      <c r="F227" s="38"/>
+      <c r="D227" s="38"/>
+      <c r="E227" s="39"/>
+      <c r="F227" s="33"/>
       <c r="G227" s="23" t="s">
         <v>524</v>
       </c>
@@ -9504,9 +9492,9 @@
       <c r="C228" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D228" s="32"/>
-      <c r="E228" s="25"/>
-      <c r="F228" s="38"/>
+      <c r="D228" s="38"/>
+      <c r="E228" s="39"/>
+      <c r="F228" s="33"/>
       <c r="G228" s="23" t="s">
         <v>527</v>
       </c>
@@ -9525,9 +9513,9 @@
       <c r="C229" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D229" s="32"/>
-      <c r="E229" s="25"/>
-      <c r="F229" s="38"/>
+      <c r="D229" s="38"/>
+      <c r="E229" s="39"/>
+      <c r="F229" s="33"/>
       <c r="G229" s="23" t="s">
         <v>530</v>
       </c>
@@ -9546,9 +9534,9 @@
       <c r="C230" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D230" s="32"/>
-      <c r="E230" s="25"/>
-      <c r="F230" s="38"/>
+      <c r="D230" s="38"/>
+      <c r="E230" s="39"/>
+      <c r="F230" s="33"/>
       <c r="G230" s="23" t="s">
         <v>533</v>
       </c>
@@ -9567,9 +9555,9 @@
       <c r="C231" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D231" s="32"/>
-      <c r="E231" s="25"/>
-      <c r="F231" s="38"/>
+      <c r="D231" s="38"/>
+      <c r="E231" s="39"/>
+      <c r="F231" s="33"/>
       <c r="G231" s="23" t="s">
         <v>536</v>
       </c>
@@ -9588,9 +9576,9 @@
       <c r="C232" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D232" s="32"/>
-      <c r="E232" s="25"/>
-      <c r="F232" s="38"/>
+      <c r="D232" s="38"/>
+      <c r="E232" s="39"/>
+      <c r="F232" s="33"/>
       <c r="G232" s="23" t="s">
         <v>539</v>
       </c>
@@ -9609,9 +9597,9 @@
       <c r="C233" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D233" s="32"/>
-      <c r="E233" s="25"/>
-      <c r="F233" s="39"/>
+      <c r="D233" s="38"/>
+      <c r="E233" s="39"/>
+      <c r="F233" s="34"/>
       <c r="G233" s="23" t="s">
         <v>542</v>
       </c>
@@ -9630,9 +9618,9 @@
       <c r="C234" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D234" s="32"/>
-      <c r="E234" s="25"/>
-      <c r="F234" s="37" t="s">
+      <c r="D234" s="38"/>
+      <c r="E234" s="39"/>
+      <c r="F234" s="32" t="s">
         <v>129</v>
       </c>
       <c r="G234" s="23" t="s">
@@ -9653,9 +9641,9 @@
       <c r="C235" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D235" s="32"/>
-      <c r="E235" s="25"/>
-      <c r="F235" s="38"/>
+      <c r="D235" s="38"/>
+      <c r="E235" s="39"/>
+      <c r="F235" s="33"/>
       <c r="G235" s="23" t="s">
         <v>545</v>
       </c>
@@ -9674,9 +9662,9 @@
       <c r="C236" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D236" s="32"/>
-      <c r="E236" s="25"/>
-      <c r="F236" s="38"/>
+      <c r="D236" s="38"/>
+      <c r="E236" s="39"/>
+      <c r="F236" s="33"/>
       <c r="G236" s="23" t="s">
         <v>545</v>
       </c>
@@ -9695,9 +9683,9 @@
       <c r="C237" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D237" s="32"/>
-      <c r="E237" s="25"/>
-      <c r="F237" s="38"/>
+      <c r="D237" s="38"/>
+      <c r="E237" s="39"/>
+      <c r="F237" s="33"/>
       <c r="G237" s="23" t="s">
         <v>545</v>
       </c>
@@ -9716,9 +9704,9 @@
       <c r="C238" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D238" s="32"/>
-      <c r="E238" s="25"/>
-      <c r="F238" s="38"/>
+      <c r="D238" s="38"/>
+      <c r="E238" s="39"/>
+      <c r="F238" s="33"/>
       <c r="G238" s="23" t="s">
         <v>545</v>
       </c>
@@ -9737,9 +9725,9 @@
       <c r="C239" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D239" s="32"/>
-      <c r="E239" s="25"/>
-      <c r="F239" s="38"/>
+      <c r="D239" s="38"/>
+      <c r="E239" s="39"/>
+      <c r="F239" s="33"/>
       <c r="G239" s="23" t="s">
         <v>545</v>
       </c>
@@ -9758,9 +9746,9 @@
       <c r="C240" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D240" s="32"/>
-      <c r="E240" s="25"/>
-      <c r="F240" s="38"/>
+      <c r="D240" s="38"/>
+      <c r="E240" s="39"/>
+      <c r="F240" s="33"/>
       <c r="G240" s="23" t="s">
         <v>545</v>
       </c>
@@ -9779,9 +9767,9 @@
       <c r="C241" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D241" s="32"/>
-      <c r="E241" s="25"/>
-      <c r="F241" s="39"/>
+      <c r="D241" s="38"/>
+      <c r="E241" s="39"/>
+      <c r="F241" s="34"/>
       <c r="G241" s="23" t="s">
         <v>545</v>
       </c>
@@ -9800,9 +9788,9 @@
       <c r="C242" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D242" s="32"/>
-      <c r="E242" s="25"/>
-      <c r="F242" s="37" t="s">
+      <c r="D242" s="38"/>
+      <c r="E242" s="39"/>
+      <c r="F242" s="32" t="s">
         <v>122</v>
       </c>
       <c r="G242" s="23" t="s">
@@ -9823,9 +9811,9 @@
       <c r="C243" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D243" s="32"/>
-      <c r="E243" s="25"/>
-      <c r="F243" s="39"/>
+      <c r="D243" s="38"/>
+      <c r="E243" s="39"/>
+      <c r="F243" s="34"/>
       <c r="G243" s="23" t="s">
         <v>565</v>
       </c>
@@ -9844,9 +9832,9 @@
       <c r="C244" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D244" s="32"/>
-      <c r="E244" s="25"/>
-      <c r="F244" s="37" t="s">
+      <c r="D244" s="38"/>
+      <c r="E244" s="39"/>
+      <c r="F244" s="32" t="s">
         <v>129</v>
       </c>
       <c r="G244" s="23" t="s">
@@ -9867,9 +9855,9 @@
       <c r="C245" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D245" s="32"/>
-      <c r="E245" s="25"/>
-      <c r="F245" s="38"/>
+      <c r="D245" s="38"/>
+      <c r="E245" s="39"/>
+      <c r="F245" s="33"/>
       <c r="G245" s="23" t="s">
         <v>568</v>
       </c>
@@ -9888,9 +9876,9 @@
       <c r="C246" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D246" s="32"/>
-      <c r="E246" s="25"/>
-      <c r="F246" s="38"/>
+      <c r="D246" s="38"/>
+      <c r="E246" s="39"/>
+      <c r="F246" s="33"/>
       <c r="G246" s="23" t="s">
         <v>568</v>
       </c>
@@ -9909,9 +9897,9 @@
       <c r="C247" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D247" s="32"/>
-      <c r="E247" s="25"/>
-      <c r="F247" s="39"/>
+      <c r="D247" s="38"/>
+      <c r="E247" s="39"/>
+      <c r="F247" s="34"/>
       <c r="G247" s="23" t="s">
         <v>568</v>
       </c>
@@ -9930,9 +9918,9 @@
       <c r="C248" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D248" s="32"/>
-      <c r="E248" s="25"/>
-      <c r="F248" s="37" t="s">
+      <c r="D248" s="38"/>
+      <c r="E248" s="39"/>
+      <c r="F248" s="32" t="s">
         <v>122</v>
       </c>
       <c r="G248" s="23" t="s">
@@ -9953,9 +9941,9 @@
       <c r="C249" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D249" s="32"/>
-      <c r="E249" s="25"/>
-      <c r="F249" s="38"/>
+      <c r="D249" s="38"/>
+      <c r="E249" s="39"/>
+      <c r="F249" s="33"/>
       <c r="G249" s="23" t="s">
         <v>580</v>
       </c>
@@ -9974,9 +9962,9 @@
       <c r="C250" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D250" s="32"/>
-      <c r="E250" s="25"/>
-      <c r="F250" s="38"/>
+      <c r="D250" s="38"/>
+      <c r="E250" s="39"/>
+      <c r="F250" s="33"/>
       <c r="G250" s="23" t="s">
         <v>583</v>
       </c>
@@ -9995,9 +9983,9 @@
       <c r="C251" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D251" s="32"/>
-      <c r="E251" s="25"/>
-      <c r="F251" s="39"/>
+      <c r="D251" s="38"/>
+      <c r="E251" s="39"/>
+      <c r="F251" s="34"/>
       <c r="G251" s="23" t="s">
         <v>586</v>
       </c>
@@ -10016,9 +10004,9 @@
       <c r="C252" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D252" s="32"/>
-      <c r="E252" s="25"/>
-      <c r="F252" s="37" t="s">
+      <c r="D252" s="38"/>
+      <c r="E252" s="39"/>
+      <c r="F252" s="32" t="s">
         <v>129</v>
       </c>
       <c r="G252" s="23" t="s">
@@ -10039,9 +10027,9 @@
       <c r="C253" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D253" s="32"/>
-      <c r="E253" s="25"/>
-      <c r="F253" s="38"/>
+      <c r="D253" s="38"/>
+      <c r="E253" s="39"/>
+      <c r="F253" s="33"/>
       <c r="G253" s="23" t="s">
         <v>589</v>
       </c>
@@ -10060,9 +10048,9 @@
       <c r="C254" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D254" s="32"/>
-      <c r="E254" s="25"/>
-      <c r="F254" s="38"/>
+      <c r="D254" s="38"/>
+      <c r="E254" s="39"/>
+      <c r="F254" s="33"/>
       <c r="G254" s="23" t="s">
         <v>589</v>
       </c>
@@ -10081,9 +10069,9 @@
       <c r="C255" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D255" s="32"/>
-      <c r="E255" s="25"/>
-      <c r="F255" s="38"/>
+      <c r="D255" s="38"/>
+      <c r="E255" s="39"/>
+      <c r="F255" s="33"/>
       <c r="G255" s="23" t="s">
         <v>589</v>
       </c>
@@ -10102,9 +10090,9 @@
       <c r="C256" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D256" s="32"/>
-      <c r="E256" s="25"/>
-      <c r="F256" s="38"/>
+      <c r="D256" s="38"/>
+      <c r="E256" s="39"/>
+      <c r="F256" s="33"/>
       <c r="G256" s="23" t="s">
         <v>589</v>
       </c>
@@ -10123,9 +10111,9 @@
       <c r="C257" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D257" s="32"/>
-      <c r="E257" s="25"/>
-      <c r="F257" s="39"/>
+      <c r="D257" s="38"/>
+      <c r="E257" s="39"/>
+      <c r="F257" s="34"/>
       <c r="G257" s="23" t="s">
         <v>589</v>
       </c>
@@ -10144,9 +10132,9 @@
       <c r="C258" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D258" s="32"/>
-      <c r="E258" s="25"/>
-      <c r="F258" s="37" t="s">
+      <c r="D258" s="38"/>
+      <c r="E258" s="39"/>
+      <c r="F258" s="32" t="s">
         <v>122</v>
       </c>
       <c r="G258" s="23" t="s">
@@ -10167,9 +10155,9 @@
       <c r="C259" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D259" s="32"/>
-      <c r="E259" s="25"/>
-      <c r="F259" s="38"/>
+      <c r="D259" s="38"/>
+      <c r="E259" s="39"/>
+      <c r="F259" s="33"/>
       <c r="G259" s="23" t="s">
         <v>605</v>
       </c>
@@ -10188,9 +10176,9 @@
       <c r="C260" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D260" s="32"/>
-      <c r="E260" s="25"/>
-      <c r="F260" s="38"/>
+      <c r="D260" s="38"/>
+      <c r="E260" s="39"/>
+      <c r="F260" s="33"/>
       <c r="G260" s="23" t="s">
         <v>608</v>
       </c>
@@ -10209,9 +10197,9 @@
       <c r="C261" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D261" s="32"/>
-      <c r="E261" s="25"/>
-      <c r="F261" s="38"/>
+      <c r="D261" s="38"/>
+      <c r="E261" s="39"/>
+      <c r="F261" s="33"/>
       <c r="G261" s="23" t="s">
         <v>611</v>
       </c>
@@ -10230,9 +10218,9 @@
       <c r="C262" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D262" s="32"/>
-      <c r="E262" s="25"/>
-      <c r="F262" s="39"/>
+      <c r="D262" s="38"/>
+      <c r="E262" s="39"/>
+      <c r="F262" s="34"/>
       <c r="G262" s="23" t="s">
         <v>28</v>
       </c>
@@ -10251,9 +10239,9 @@
       <c r="C263" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D263" s="32"/>
-      <c r="E263" s="25"/>
-      <c r="F263" s="37" t="s">
+      <c r="D263" s="38"/>
+      <c r="E263" s="39"/>
+      <c r="F263" s="32" t="s">
         <v>616</v>
       </c>
       <c r="G263" s="23" t="s">
@@ -10274,9 +10262,9 @@
       <c r="C264" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D264" s="32"/>
-      <c r="E264" s="25"/>
-      <c r="F264" s="38"/>
+      <c r="D264" s="38"/>
+      <c r="E264" s="39"/>
+      <c r="F264" s="33"/>
       <c r="G264" s="23" t="s">
         <v>617</v>
       </c>
@@ -10295,9 +10283,9 @@
       <c r="C265" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D265" s="32"/>
-      <c r="E265" s="25"/>
-      <c r="F265" s="38"/>
+      <c r="D265" s="38"/>
+      <c r="E265" s="39"/>
+      <c r="F265" s="33"/>
       <c r="G265" s="23" t="s">
         <v>617</v>
       </c>
@@ -10316,9 +10304,9 @@
       <c r="C266" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D266" s="32"/>
-      <c r="E266" s="25"/>
-      <c r="F266" s="38"/>
+      <c r="D266" s="38"/>
+      <c r="E266" s="39"/>
+      <c r="F266" s="33"/>
       <c r="G266" s="23" t="s">
         <v>617</v>
       </c>
@@ -10337,9 +10325,9 @@
       <c r="C267" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D267" s="32"/>
-      <c r="E267" s="25"/>
-      <c r="F267" s="38"/>
+      <c r="D267" s="38"/>
+      <c r="E267" s="39"/>
+      <c r="F267" s="33"/>
       <c r="G267" s="23" t="s">
         <v>617</v>
       </c>
@@ -10358,9 +10346,9 @@
       <c r="C268" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D268" s="32"/>
-      <c r="E268" s="25"/>
-      <c r="F268" s="38"/>
+      <c r="D268" s="38"/>
+      <c r="E268" s="39"/>
+      <c r="F268" s="33"/>
       <c r="G268" s="23" t="s">
         <v>617</v>
       </c>
@@ -10379,9 +10367,9 @@
       <c r="C269" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D269" s="32"/>
-      <c r="E269" s="25"/>
-      <c r="F269" s="38"/>
+      <c r="D269" s="38"/>
+      <c r="E269" s="39"/>
+      <c r="F269" s="33"/>
       <c r="G269" s="23" t="s">
         <v>617</v>
       </c>
@@ -10400,9 +10388,9 @@
       <c r="C270" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D270" s="32"/>
-      <c r="E270" s="25"/>
-      <c r="F270" s="38"/>
+      <c r="D270" s="38"/>
+      <c r="E270" s="39"/>
+      <c r="F270" s="33"/>
       <c r="G270" s="23" t="s">
         <v>617</v>
       </c>
@@ -10421,9 +10409,9 @@
       <c r="C271" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D271" s="32"/>
-      <c r="E271" s="25"/>
-      <c r="F271" s="38"/>
+      <c r="D271" s="38"/>
+      <c r="E271" s="39"/>
+      <c r="F271" s="33"/>
       <c r="G271" s="23" t="s">
         <v>617</v>
       </c>
@@ -10442,9 +10430,9 @@
       <c r="C272" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D272" s="32"/>
-      <c r="E272" s="25"/>
-      <c r="F272" s="38"/>
+      <c r="D272" s="38"/>
+      <c r="E272" s="39"/>
+      <c r="F272" s="33"/>
       <c r="G272" s="23" t="s">
         <v>617</v>
       </c>
@@ -10463,9 +10451,9 @@
       <c r="C273" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D273" s="32"/>
-      <c r="E273" s="25"/>
-      <c r="F273" s="38"/>
+      <c r="D273" s="38"/>
+      <c r="E273" s="39"/>
+      <c r="F273" s="33"/>
       <c r="G273" s="23" t="s">
         <v>617</v>
       </c>
@@ -10484,9 +10472,9 @@
       <c r="C274" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D274" s="32"/>
-      <c r="E274" s="25"/>
-      <c r="F274" s="38"/>
+      <c r="D274" s="38"/>
+      <c r="E274" s="39"/>
+      <c r="F274" s="33"/>
       <c r="G274" s="23" t="s">
         <v>617</v>
       </c>
@@ -10505,9 +10493,9 @@
       <c r="C275" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D275" s="32"/>
-      <c r="E275" s="25"/>
-      <c r="F275" s="38"/>
+      <c r="D275" s="38"/>
+      <c r="E275" s="39"/>
+      <c r="F275" s="33"/>
       <c r="G275" s="23" t="s">
         <v>642</v>
       </c>
@@ -10526,9 +10514,9 @@
       <c r="C276" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D276" s="32"/>
-      <c r="E276" s="25"/>
-      <c r="F276" s="38"/>
+      <c r="D276" s="38"/>
+      <c r="E276" s="39"/>
+      <c r="F276" s="33"/>
       <c r="G276" s="23" t="s">
         <v>642</v>
       </c>
@@ -10547,9 +10535,9 @@
       <c r="C277" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D277" s="32"/>
-      <c r="E277" s="25"/>
-      <c r="F277" s="38"/>
+      <c r="D277" s="38"/>
+      <c r="E277" s="39"/>
+      <c r="F277" s="33"/>
       <c r="G277" s="23" t="s">
         <v>642</v>
       </c>
@@ -10568,9 +10556,9 @@
       <c r="C278" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D278" s="32"/>
-      <c r="E278" s="25"/>
-      <c r="F278" s="38"/>
+      <c r="D278" s="38"/>
+      <c r="E278" s="39"/>
+      <c r="F278" s="33"/>
       <c r="G278" s="23" t="s">
         <v>642</v>
       </c>
@@ -10589,9 +10577,9 @@
       <c r="C279" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D279" s="32"/>
-      <c r="E279" s="25"/>
-      <c r="F279" s="38"/>
+      <c r="D279" s="38"/>
+      <c r="E279" s="39"/>
+      <c r="F279" s="33"/>
       <c r="G279" s="23" t="s">
         <v>642</v>
       </c>
@@ -10610,9 +10598,9 @@
       <c r="C280" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D280" s="32"/>
-      <c r="E280" s="25"/>
-      <c r="F280" s="38"/>
+      <c r="D280" s="38"/>
+      <c r="E280" s="39"/>
+      <c r="F280" s="33"/>
       <c r="G280" s="23" t="s">
         <v>642</v>
       </c>
@@ -10631,9 +10619,9 @@
       <c r="C281" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D281" s="32"/>
-      <c r="E281" s="25"/>
-      <c r="F281" s="38"/>
+      <c r="D281" s="38"/>
+      <c r="E281" s="39"/>
+      <c r="F281" s="33"/>
       <c r="G281" s="23" t="s">
         <v>642</v>
       </c>
@@ -10652,9 +10640,9 @@
       <c r="C282" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D282" s="32"/>
-      <c r="E282" s="25"/>
-      <c r="F282" s="38"/>
+      <c r="D282" s="38"/>
+      <c r="E282" s="39"/>
+      <c r="F282" s="33"/>
       <c r="G282" s="23" t="s">
         <v>642</v>
       </c>
@@ -10673,9 +10661,9 @@
       <c r="C283" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D283" s="32"/>
-      <c r="E283" s="25"/>
-      <c r="F283" s="38"/>
+      <c r="D283" s="38"/>
+      <c r="E283" s="39"/>
+      <c r="F283" s="33"/>
       <c r="G283" s="23" t="s">
         <v>642</v>
       </c>
@@ -10694,9 +10682,9 @@
       <c r="C284" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D284" s="32"/>
-      <c r="E284" s="25"/>
-      <c r="F284" s="38"/>
+      <c r="D284" s="38"/>
+      <c r="E284" s="39"/>
+      <c r="F284" s="33"/>
       <c r="G284" s="23" t="s">
         <v>642</v>
       </c>
@@ -10715,9 +10703,9 @@
       <c r="C285" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D285" s="32"/>
-      <c r="E285" s="25"/>
-      <c r="F285" s="38"/>
+      <c r="D285" s="38"/>
+      <c r="E285" s="39"/>
+      <c r="F285" s="33"/>
       <c r="G285" s="23" t="s">
         <v>642</v>
       </c>
@@ -10736,9 +10724,9 @@
       <c r="C286" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D286" s="32"/>
-      <c r="E286" s="25"/>
-      <c r="F286" s="38"/>
+      <c r="D286" s="38"/>
+      <c r="E286" s="39"/>
+      <c r="F286" s="33"/>
       <c r="G286" s="23" t="s">
         <v>642</v>
       </c>
@@ -10757,9 +10745,9 @@
       <c r="C287" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D287" s="32"/>
-      <c r="E287" s="25"/>
-      <c r="F287" s="38"/>
+      <c r="D287" s="38"/>
+      <c r="E287" s="39"/>
+      <c r="F287" s="33"/>
       <c r="G287" s="23" t="s">
         <v>667</v>
       </c>
@@ -10778,9 +10766,9 @@
       <c r="C288" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D288" s="32"/>
-      <c r="E288" s="25"/>
-      <c r="F288" s="38"/>
+      <c r="D288" s="38"/>
+      <c r="E288" s="39"/>
+      <c r="F288" s="33"/>
       <c r="G288" s="23" t="s">
         <v>667</v>
       </c>
@@ -10799,9 +10787,9 @@
       <c r="C289" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D289" s="32"/>
-      <c r="E289" s="25"/>
-      <c r="F289" s="38"/>
+      <c r="D289" s="38"/>
+      <c r="E289" s="39"/>
+      <c r="F289" s="33"/>
       <c r="G289" s="23" t="s">
         <v>667</v>
       </c>
@@ -10820,9 +10808,9 @@
       <c r="C290" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D290" s="32"/>
-      <c r="E290" s="25"/>
-      <c r="F290" s="38"/>
+      <c r="D290" s="38"/>
+      <c r="E290" s="39"/>
+      <c r="F290" s="33"/>
       <c r="G290" s="23" t="s">
         <v>667</v>
       </c>
@@ -10841,9 +10829,9 @@
       <c r="C291" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D291" s="32"/>
-      <c r="E291" s="25"/>
-      <c r="F291" s="38"/>
+      <c r="D291" s="38"/>
+      <c r="E291" s="39"/>
+      <c r="F291" s="33"/>
       <c r="G291" s="23" t="s">
         <v>667</v>
       </c>
@@ -10862,9 +10850,9 @@
       <c r="C292" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D292" s="32"/>
-      <c r="E292" s="25"/>
-      <c r="F292" s="38"/>
+      <c r="D292" s="38"/>
+      <c r="E292" s="39"/>
+      <c r="F292" s="33"/>
       <c r="G292" s="23" t="s">
         <v>667</v>
       </c>
@@ -10883,9 +10871,9 @@
       <c r="C293" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D293" s="32"/>
-      <c r="E293" s="25"/>
-      <c r="F293" s="38"/>
+      <c r="D293" s="38"/>
+      <c r="E293" s="39"/>
+      <c r="F293" s="33"/>
       <c r="G293" s="23" t="s">
         <v>667</v>
       </c>
@@ -10904,9 +10892,9 @@
       <c r="C294" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D294" s="32"/>
-      <c r="E294" s="25"/>
-      <c r="F294" s="38"/>
+      <c r="D294" s="38"/>
+      <c r="E294" s="39"/>
+      <c r="F294" s="33"/>
       <c r="G294" s="23" t="s">
         <v>667</v>
       </c>
@@ -10925,9 +10913,9 @@
       <c r="C295" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D295" s="32"/>
-      <c r="E295" s="25"/>
-      <c r="F295" s="38"/>
+      <c r="D295" s="38"/>
+      <c r="E295" s="39"/>
+      <c r="F295" s="33"/>
       <c r="G295" s="23" t="s">
         <v>667</v>
       </c>
@@ -10946,9 +10934,9 @@
       <c r="C296" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D296" s="32"/>
-      <c r="E296" s="25"/>
-      <c r="F296" s="38"/>
+      <c r="D296" s="38"/>
+      <c r="E296" s="39"/>
+      <c r="F296" s="33"/>
       <c r="G296" s="23" t="s">
         <v>667</v>
       </c>
@@ -10967,9 +10955,9 @@
       <c r="C297" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D297" s="32"/>
-      <c r="E297" s="25"/>
-      <c r="F297" s="38"/>
+      <c r="D297" s="38"/>
+      <c r="E297" s="39"/>
+      <c r="F297" s="33"/>
       <c r="G297" s="23" t="s">
         <v>667</v>
       </c>
@@ -10988,9 +10976,9 @@
       <c r="C298" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D298" s="32"/>
-      <c r="E298" s="25"/>
-      <c r="F298" s="38"/>
+      <c r="D298" s="38"/>
+      <c r="E298" s="39"/>
+      <c r="F298" s="33"/>
       <c r="G298" s="23" t="s">
         <v>667</v>
       </c>
@@ -11009,9 +10997,9 @@
       <c r="C299" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D299" s="32"/>
-      <c r="E299" s="25"/>
-      <c r="F299" s="38"/>
+      <c r="D299" s="38"/>
+      <c r="E299" s="39"/>
+      <c r="F299" s="33"/>
       <c r="G299" s="23" t="s">
         <v>692</v>
       </c>
@@ -11030,9 +11018,9 @@
       <c r="C300" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D300" s="32"/>
-      <c r="E300" s="25"/>
-      <c r="F300" s="38"/>
+      <c r="D300" s="38"/>
+      <c r="E300" s="39"/>
+      <c r="F300" s="33"/>
       <c r="G300" s="23" t="s">
         <v>692</v>
       </c>
@@ -11051,9 +11039,9 @@
       <c r="C301" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D301" s="32"/>
-      <c r="E301" s="25"/>
-      <c r="F301" s="38"/>
+      <c r="D301" s="38"/>
+      <c r="E301" s="39"/>
+      <c r="F301" s="33"/>
       <c r="G301" s="23" t="s">
         <v>692</v>
       </c>
@@ -11072,9 +11060,9 @@
       <c r="C302" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D302" s="32"/>
-      <c r="E302" s="25"/>
-      <c r="F302" s="38"/>
+      <c r="D302" s="38"/>
+      <c r="E302" s="39"/>
+      <c r="F302" s="33"/>
       <c r="G302" s="23" t="s">
         <v>692</v>
       </c>
@@ -11093,9 +11081,9 @@
       <c r="C303" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D303" s="32"/>
-      <c r="E303" s="25"/>
-      <c r="F303" s="38"/>
+      <c r="D303" s="38"/>
+      <c r="E303" s="39"/>
+      <c r="F303" s="33"/>
       <c r="G303" s="23" t="s">
         <v>692</v>
       </c>
@@ -11114,9 +11102,9 @@
       <c r="C304" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D304" s="32"/>
-      <c r="E304" s="25"/>
-      <c r="F304" s="38"/>
+      <c r="D304" s="38"/>
+      <c r="E304" s="39"/>
+      <c r="F304" s="33"/>
       <c r="G304" s="23" t="s">
         <v>692</v>
       </c>
@@ -11135,9 +11123,9 @@
       <c r="C305" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D305" s="32"/>
-      <c r="E305" s="25"/>
-      <c r="F305" s="38"/>
+      <c r="D305" s="38"/>
+      <c r="E305" s="39"/>
+      <c r="F305" s="33"/>
       <c r="G305" s="23" t="s">
         <v>692</v>
       </c>
@@ -11156,9 +11144,9 @@
       <c r="C306" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D306" s="32"/>
-      <c r="E306" s="25"/>
-      <c r="F306" s="38"/>
+      <c r="D306" s="38"/>
+      <c r="E306" s="39"/>
+      <c r="F306" s="33"/>
       <c r="G306" s="23" t="s">
         <v>692</v>
       </c>
@@ -11177,9 +11165,9 @@
       <c r="C307" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D307" s="32"/>
-      <c r="E307" s="25"/>
-      <c r="F307" s="38"/>
+      <c r="D307" s="38"/>
+      <c r="E307" s="39"/>
+      <c r="F307" s="33"/>
       <c r="G307" s="23" t="s">
         <v>692</v>
       </c>
@@ -11198,9 +11186,9 @@
       <c r="C308" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D308" s="32"/>
-      <c r="E308" s="25"/>
-      <c r="F308" s="38"/>
+      <c r="D308" s="38"/>
+      <c r="E308" s="39"/>
+      <c r="F308" s="33"/>
       <c r="G308" s="23" t="s">
         <v>692</v>
       </c>
@@ -11219,9 +11207,9 @@
       <c r="C309" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D309" s="32"/>
-      <c r="E309" s="25"/>
-      <c r="F309" s="38"/>
+      <c r="D309" s="38"/>
+      <c r="E309" s="39"/>
+      <c r="F309" s="33"/>
       <c r="G309" s="23" t="s">
         <v>692</v>
       </c>
@@ -11240,9 +11228,9 @@
       <c r="C310" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D310" s="32"/>
-      <c r="E310" s="25"/>
-      <c r="F310" s="38"/>
+      <c r="D310" s="38"/>
+      <c r="E310" s="39"/>
+      <c r="F310" s="33"/>
       <c r="G310" s="23" t="s">
         <v>692</v>
       </c>
@@ -11261,9 +11249,9 @@
       <c r="C311" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D311" s="32"/>
-      <c r="E311" s="25"/>
-      <c r="F311" s="38"/>
+      <c r="D311" s="38"/>
+      <c r="E311" s="39"/>
+      <c r="F311" s="33"/>
       <c r="G311" s="23" t="s">
         <v>717</v>
       </c>
@@ -11282,9 +11270,9 @@
       <c r="C312" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D312" s="32"/>
-      <c r="E312" s="25"/>
-      <c r="F312" s="38"/>
+      <c r="D312" s="38"/>
+      <c r="E312" s="39"/>
+      <c r="F312" s="33"/>
       <c r="G312" s="23" t="s">
         <v>717</v>
       </c>
@@ -11303,9 +11291,9 @@
       <c r="C313" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D313" s="32"/>
-      <c r="E313" s="25"/>
-      <c r="F313" s="38"/>
+      <c r="D313" s="38"/>
+      <c r="E313" s="39"/>
+      <c r="F313" s="33"/>
       <c r="G313" s="23" t="s">
         <v>717</v>
       </c>
@@ -11324,9 +11312,9 @@
       <c r="C314" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D314" s="32"/>
-      <c r="E314" s="25"/>
-      <c r="F314" s="38"/>
+      <c r="D314" s="38"/>
+      <c r="E314" s="39"/>
+      <c r="F314" s="33"/>
       <c r="G314" s="23" t="s">
         <v>717</v>
       </c>
@@ -11345,9 +11333,9 @@
       <c r="C315" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D315" s="32"/>
-      <c r="E315" s="25"/>
-      <c r="F315" s="38"/>
+      <c r="D315" s="38"/>
+      <c r="E315" s="39"/>
+      <c r="F315" s="33"/>
       <c r="G315" s="23" t="s">
         <v>717</v>
       </c>
@@ -11366,9 +11354,9 @@
       <c r="C316" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D316" s="32"/>
-      <c r="E316" s="25"/>
-      <c r="F316" s="38"/>
+      <c r="D316" s="38"/>
+      <c r="E316" s="39"/>
+      <c r="F316" s="33"/>
       <c r="G316" s="23" t="s">
         <v>717</v>
       </c>
@@ -11387,9 +11375,9 @@
       <c r="C317" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D317" s="32"/>
-      <c r="E317" s="25"/>
-      <c r="F317" s="38"/>
+      <c r="D317" s="38"/>
+      <c r="E317" s="39"/>
+      <c r="F317" s="33"/>
       <c r="G317" s="23" t="s">
         <v>717</v>
       </c>
@@ -11408,17 +11396,17 @@
       <c r="C318" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D318" s="32"/>
-      <c r="E318" s="25"/>
-      <c r="F318" s="38"/>
+      <c r="D318" s="38"/>
+      <c r="E318" s="39"/>
+      <c r="F318" s="33"/>
       <c r="G318" s="23" t="s">
         <v>717</v>
       </c>
       <c r="H318" s="23" t="s">
+        <v>732</v>
+      </c>
+      <c r="I318" s="23" t="s">
         <v>733</v>
-      </c>
-      <c r="I318" s="23" t="s">
-        <v>734</v>
       </c>
       <c r="J318" s="23"/>
     </row>
@@ -11429,17 +11417,17 @@
       <c r="C319" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D319" s="32"/>
-      <c r="E319" s="25"/>
-      <c r="F319" s="38"/>
+      <c r="D319" s="38"/>
+      <c r="E319" s="39"/>
+      <c r="F319" s="33"/>
       <c r="G319" s="23" t="s">
         <v>717</v>
       </c>
       <c r="H319" s="23" t="s">
+        <v>734</v>
+      </c>
+      <c r="I319" s="23" t="s">
         <v>735</v>
-      </c>
-      <c r="I319" s="23" t="s">
-        <v>736</v>
       </c>
       <c r="J319" s="23"/>
     </row>
@@ -11450,17 +11438,17 @@
       <c r="C320" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D320" s="32"/>
-      <c r="E320" s="25"/>
-      <c r="F320" s="38"/>
+      <c r="D320" s="38"/>
+      <c r="E320" s="39"/>
+      <c r="F320" s="33"/>
       <c r="G320" s="23" t="s">
         <v>717</v>
       </c>
       <c r="H320" s="23" t="s">
+        <v>736</v>
+      </c>
+      <c r="I320" s="23" t="s">
         <v>737</v>
-      </c>
-      <c r="I320" s="23" t="s">
-        <v>738</v>
       </c>
       <c r="J320" s="23"/>
     </row>
@@ -11471,17 +11459,17 @@
       <c r="C321" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D321" s="32"/>
-      <c r="E321" s="25"/>
-      <c r="F321" s="38"/>
+      <c r="D321" s="38"/>
+      <c r="E321" s="39"/>
+      <c r="F321" s="33"/>
       <c r="G321" s="23" t="s">
         <v>717</v>
       </c>
       <c r="H321" s="23" t="s">
+        <v>738</v>
+      </c>
+      <c r="I321" s="23" t="s">
         <v>739</v>
-      </c>
-      <c r="I321" s="23" t="s">
-        <v>740</v>
       </c>
       <c r="J321" s="23"/>
     </row>
@@ -11492,17 +11480,17 @@
       <c r="C322" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D322" s="32"/>
-      <c r="E322" s="25"/>
-      <c r="F322" s="38"/>
+      <c r="D322" s="38"/>
+      <c r="E322" s="39"/>
+      <c r="F322" s="33"/>
       <c r="G322" s="23" t="s">
         <v>717</v>
       </c>
       <c r="H322" s="23" t="s">
+        <v>740</v>
+      </c>
+      <c r="I322" s="23" t="s">
         <v>741</v>
-      </c>
-      <c r="I322" s="23" t="s">
-        <v>742</v>
       </c>
       <c r="J322" s="23"/>
     </row>
@@ -11513,17 +11501,17 @@
       <c r="C323" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D323" s="32"/>
-      <c r="E323" s="25"/>
-      <c r="F323" s="38"/>
+      <c r="D323" s="38"/>
+      <c r="E323" s="39"/>
+      <c r="F323" s="33"/>
       <c r="G323" s="23" t="s">
+        <v>742</v>
+      </c>
+      <c r="H323" s="23" t="s">
         <v>743</v>
       </c>
-      <c r="H323" s="23" t="s">
+      <c r="I323" s="23" t="s">
         <v>744</v>
-      </c>
-      <c r="I323" s="23" t="s">
-        <v>745</v>
       </c>
       <c r="J323" s="23"/>
     </row>
@@ -11534,17 +11522,17 @@
       <c r="C324" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D324" s="32"/>
-      <c r="E324" s="25"/>
-      <c r="F324" s="38"/>
+      <c r="D324" s="38"/>
+      <c r="E324" s="39"/>
+      <c r="F324" s="33"/>
       <c r="G324" s="23" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H324" s="23" t="s">
+        <v>745</v>
+      </c>
+      <c r="I324" s="23" t="s">
         <v>746</v>
-      </c>
-      <c r="I324" s="23" t="s">
-        <v>747</v>
       </c>
       <c r="J324" s="23"/>
     </row>
@@ -11555,17 +11543,17 @@
       <c r="C325" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D325" s="32"/>
-      <c r="E325" s="25"/>
-      <c r="F325" s="38"/>
+      <c r="D325" s="38"/>
+      <c r="E325" s="39"/>
+      <c r="F325" s="33"/>
       <c r="G325" s="23" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H325" s="23" t="s">
+        <v>747</v>
+      </c>
+      <c r="I325" s="23" t="s">
         <v>748</v>
-      </c>
-      <c r="I325" s="23" t="s">
-        <v>749</v>
       </c>
       <c r="J325" s="23"/>
     </row>
@@ -11576,17 +11564,17 @@
       <c r="C326" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D326" s="32"/>
-      <c r="E326" s="25"/>
-      <c r="F326" s="38"/>
+      <c r="D326" s="38"/>
+      <c r="E326" s="39"/>
+      <c r="F326" s="33"/>
       <c r="G326" s="23" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H326" s="23" t="s">
+        <v>749</v>
+      </c>
+      <c r="I326" s="23" t="s">
         <v>750</v>
-      </c>
-      <c r="I326" s="23" t="s">
-        <v>751</v>
       </c>
       <c r="J326" s="23"/>
     </row>
@@ -11597,17 +11585,17 @@
       <c r="C327" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D327" s="32"/>
-      <c r="E327" s="25"/>
-      <c r="F327" s="38"/>
+      <c r="D327" s="38"/>
+      <c r="E327" s="39"/>
+      <c r="F327" s="33"/>
       <c r="G327" s="23" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H327" s="23" t="s">
+        <v>751</v>
+      </c>
+      <c r="I327" s="23" t="s">
         <v>752</v>
-      </c>
-      <c r="I327" s="23" t="s">
-        <v>753</v>
       </c>
       <c r="J327" s="23"/>
     </row>
@@ -11618,17 +11606,17 @@
       <c r="C328" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D328" s="32"/>
-      <c r="E328" s="25"/>
-      <c r="F328" s="38"/>
+      <c r="D328" s="38"/>
+      <c r="E328" s="39"/>
+      <c r="F328" s="33"/>
       <c r="G328" s="23" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H328" s="23" t="s">
+        <v>753</v>
+      </c>
+      <c r="I328" s="23" t="s">
         <v>754</v>
-      </c>
-      <c r="I328" s="23" t="s">
-        <v>755</v>
       </c>
       <c r="J328" s="23"/>
     </row>
@@ -11639,17 +11627,17 @@
       <c r="C329" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D329" s="32"/>
-      <c r="E329" s="25"/>
-      <c r="F329" s="38"/>
+      <c r="D329" s="38"/>
+      <c r="E329" s="39"/>
+      <c r="F329" s="33"/>
       <c r="G329" s="23" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H329" s="23" t="s">
+        <v>755</v>
+      </c>
+      <c r="I329" s="23" t="s">
         <v>756</v>
-      </c>
-      <c r="I329" s="23" t="s">
-        <v>757</v>
       </c>
       <c r="J329" s="23"/>
     </row>
@@ -11660,17 +11648,17 @@
       <c r="C330" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D330" s="32"/>
-      <c r="E330" s="25"/>
-      <c r="F330" s="38"/>
+      <c r="D330" s="38"/>
+      <c r="E330" s="39"/>
+      <c r="F330" s="33"/>
       <c r="G330" s="23" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H330" s="23" t="s">
+        <v>757</v>
+      </c>
+      <c r="I330" s="23" t="s">
         <v>758</v>
-      </c>
-      <c r="I330" s="23" t="s">
-        <v>759</v>
       </c>
       <c r="J330" s="23"/>
     </row>
@@ -11681,17 +11669,17 @@
       <c r="C331" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D331" s="32"/>
-      <c r="E331" s="25"/>
-      <c r="F331" s="38"/>
+      <c r="D331" s="38"/>
+      <c r="E331" s="39"/>
+      <c r="F331" s="33"/>
       <c r="G331" s="23" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H331" s="23" t="s">
+        <v>759</v>
+      </c>
+      <c r="I331" s="23" t="s">
         <v>760</v>
-      </c>
-      <c r="I331" s="23" t="s">
-        <v>761</v>
       </c>
       <c r="J331" s="23"/>
     </row>
@@ -11702,17 +11690,17 @@
       <c r="C332" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D332" s="32"/>
-      <c r="E332" s="25"/>
-      <c r="F332" s="38"/>
+      <c r="D332" s="38"/>
+      <c r="E332" s="39"/>
+      <c r="F332" s="33"/>
       <c r="G332" s="23" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H332" s="23" t="s">
+        <v>761</v>
+      </c>
+      <c r="I332" s="23" t="s">
         <v>762</v>
-      </c>
-      <c r="I332" s="23" t="s">
-        <v>763</v>
       </c>
       <c r="J332" s="23"/>
     </row>
@@ -11723,17 +11711,17 @@
       <c r="C333" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D333" s="32"/>
-      <c r="E333" s="25"/>
-      <c r="F333" s="38"/>
+      <c r="D333" s="38"/>
+      <c r="E333" s="39"/>
+      <c r="F333" s="33"/>
       <c r="G333" s="23" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H333" s="23" t="s">
+        <v>763</v>
+      </c>
+      <c r="I333" s="23" t="s">
         <v>764</v>
-      </c>
-      <c r="I333" s="23" t="s">
-        <v>765</v>
       </c>
       <c r="J333" s="23"/>
     </row>
@@ -11744,17 +11732,17 @@
       <c r="C334" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D334" s="32"/>
-      <c r="E334" s="25"/>
-      <c r="F334" s="38"/>
+      <c r="D334" s="38"/>
+      <c r="E334" s="39"/>
+      <c r="F334" s="33"/>
       <c r="G334" s="23" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H334" s="23" t="s">
+        <v>765</v>
+      </c>
+      <c r="I334" s="23" t="s">
         <v>766</v>
-      </c>
-      <c r="I334" s="23" t="s">
-        <v>767</v>
       </c>
       <c r="J334" s="23"/>
     </row>
@@ -11765,17 +11753,17 @@
       <c r="C335" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D335" s="32"/>
-      <c r="E335" s="25"/>
-      <c r="F335" s="38"/>
+      <c r="D335" s="38"/>
+      <c r="E335" s="39"/>
+      <c r="F335" s="33"/>
       <c r="G335" s="23" t="s">
+        <v>767</v>
+      </c>
+      <c r="H335" s="23" t="s">
         <v>768</v>
       </c>
-      <c r="H335" s="23" t="s">
+      <c r="I335" s="23" t="s">
         <v>769</v>
-      </c>
-      <c r="I335" s="23" t="s">
-        <v>770</v>
       </c>
       <c r="J335" s="23"/>
     </row>
@@ -11786,17 +11774,17 @@
       <c r="C336" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D336" s="32"/>
-      <c r="E336" s="25"/>
-      <c r="F336" s="38"/>
+      <c r="D336" s="38"/>
+      <c r="E336" s="39"/>
+      <c r="F336" s="33"/>
       <c r="G336" s="23" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H336" s="23" t="s">
+        <v>770</v>
+      </c>
+      <c r="I336" s="23" t="s">
         <v>771</v>
-      </c>
-      <c r="I336" s="23" t="s">
-        <v>772</v>
       </c>
       <c r="J336" s="23"/>
     </row>
@@ -11807,17 +11795,17 @@
       <c r="C337" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D337" s="32"/>
-      <c r="E337" s="25"/>
-      <c r="F337" s="38"/>
+      <c r="D337" s="38"/>
+      <c r="E337" s="39"/>
+      <c r="F337" s="33"/>
       <c r="G337" s="23" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H337" s="23" t="s">
+        <v>772</v>
+      </c>
+      <c r="I337" s="23" t="s">
         <v>773</v>
-      </c>
-      <c r="I337" s="23" t="s">
-        <v>774</v>
       </c>
       <c r="J337" s="23"/>
     </row>
@@ -11828,17 +11816,17 @@
       <c r="C338" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D338" s="32"/>
-      <c r="E338" s="25"/>
-      <c r="F338" s="38"/>
+      <c r="D338" s="38"/>
+      <c r="E338" s="39"/>
+      <c r="F338" s="33"/>
       <c r="G338" s="23" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H338" s="23" t="s">
+        <v>774</v>
+      </c>
+      <c r="I338" s="23" t="s">
         <v>775</v>
-      </c>
-      <c r="I338" s="23" t="s">
-        <v>776</v>
       </c>
       <c r="J338" s="23"/>
     </row>
@@ -11849,17 +11837,17 @@
       <c r="C339" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D339" s="32"/>
-      <c r="E339" s="25"/>
-      <c r="F339" s="38"/>
+      <c r="D339" s="38"/>
+      <c r="E339" s="39"/>
+      <c r="F339" s="33"/>
       <c r="G339" s="23" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H339" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="I339" s="23" t="s">
         <v>777</v>
-      </c>
-      <c r="I339" s="23" t="s">
-        <v>778</v>
       </c>
       <c r="J339" s="23"/>
     </row>
@@ -11870,17 +11858,17 @@
       <c r="C340" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D340" s="32"/>
-      <c r="E340" s="25"/>
-      <c r="F340" s="38"/>
+      <c r="D340" s="38"/>
+      <c r="E340" s="39"/>
+      <c r="F340" s="33"/>
       <c r="G340" s="23" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H340" s="23" t="s">
+        <v>778</v>
+      </c>
+      <c r="I340" s="23" t="s">
         <v>779</v>
-      </c>
-      <c r="I340" s="23" t="s">
-        <v>780</v>
       </c>
       <c r="J340" s="23"/>
     </row>
@@ -11891,17 +11879,17 @@
       <c r="C341" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D341" s="32"/>
-      <c r="E341" s="25"/>
-      <c r="F341" s="38"/>
+      <c r="D341" s="38"/>
+      <c r="E341" s="39"/>
+      <c r="F341" s="33"/>
       <c r="G341" s="23" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H341" s="23" t="s">
+        <v>780</v>
+      </c>
+      <c r="I341" s="23" t="s">
         <v>781</v>
-      </c>
-      <c r="I341" s="23" t="s">
-        <v>782</v>
       </c>
       <c r="J341" s="23"/>
     </row>
@@ -11912,17 +11900,17 @@
       <c r="C342" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D342" s="32"/>
-      <c r="E342" s="25"/>
-      <c r="F342" s="38"/>
+      <c r="D342" s="38"/>
+      <c r="E342" s="39"/>
+      <c r="F342" s="33"/>
       <c r="G342" s="23" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H342" s="23" t="s">
+        <v>782</v>
+      </c>
+      <c r="I342" s="23" t="s">
         <v>783</v>
-      </c>
-      <c r="I342" s="23" t="s">
-        <v>784</v>
       </c>
       <c r="J342" s="23"/>
     </row>
@@ -11933,17 +11921,17 @@
       <c r="C343" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D343" s="32"/>
-      <c r="E343" s="25"/>
-      <c r="F343" s="38"/>
+      <c r="D343" s="38"/>
+      <c r="E343" s="39"/>
+      <c r="F343" s="33"/>
       <c r="G343" s="23" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H343" s="23" t="s">
+        <v>784</v>
+      </c>
+      <c r="I343" s="23" t="s">
         <v>785</v>
-      </c>
-      <c r="I343" s="23" t="s">
-        <v>786</v>
       </c>
       <c r="J343" s="23"/>
     </row>
@@ -11954,17 +11942,17 @@
       <c r="C344" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D344" s="32"/>
-      <c r="E344" s="25"/>
-      <c r="F344" s="38"/>
+      <c r="D344" s="38"/>
+      <c r="E344" s="39"/>
+      <c r="F344" s="33"/>
       <c r="G344" s="23" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H344" s="23" t="s">
+        <v>786</v>
+      </c>
+      <c r="I344" s="23" t="s">
         <v>787</v>
-      </c>
-      <c r="I344" s="23" t="s">
-        <v>788</v>
       </c>
       <c r="J344" s="23"/>
     </row>
@@ -11975,17 +11963,17 @@
       <c r="C345" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D345" s="32"/>
-      <c r="E345" s="25"/>
-      <c r="F345" s="38"/>
+      <c r="D345" s="38"/>
+      <c r="E345" s="39"/>
+      <c r="F345" s="33"/>
       <c r="G345" s="23" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H345" s="23" t="s">
+        <v>788</v>
+      </c>
+      <c r="I345" s="23" t="s">
         <v>789</v>
-      </c>
-      <c r="I345" s="23" t="s">
-        <v>790</v>
       </c>
       <c r="J345" s="23"/>
     </row>
@@ -11996,17 +11984,17 @@
       <c r="C346" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D346" s="32"/>
-      <c r="E346" s="25"/>
-      <c r="F346" s="38"/>
+      <c r="D346" s="38"/>
+      <c r="E346" s="39"/>
+      <c r="F346" s="33"/>
       <c r="G346" s="23" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H346" s="23" t="s">
+        <v>790</v>
+      </c>
+      <c r="I346" s="23" t="s">
         <v>791</v>
-      </c>
-      <c r="I346" s="23" t="s">
-        <v>792</v>
       </c>
       <c r="J346" s="23"/>
     </row>
@@ -12017,17 +12005,17 @@
       <c r="C347" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D347" s="32"/>
-      <c r="E347" s="25"/>
-      <c r="F347" s="38"/>
+      <c r="D347" s="38"/>
+      <c r="E347" s="39"/>
+      <c r="F347" s="33"/>
       <c r="G347" s="23" t="s">
+        <v>792</v>
+      </c>
+      <c r="H347" s="23" t="s">
         <v>793</v>
       </c>
-      <c r="H347" s="23" t="s">
+      <c r="I347" s="23" t="s">
         <v>794</v>
-      </c>
-      <c r="I347" s="23" t="s">
-        <v>795</v>
       </c>
       <c r="J347" s="23"/>
     </row>
@@ -12038,17 +12026,17 @@
       <c r="C348" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D348" s="32"/>
-      <c r="E348" s="25"/>
-      <c r="F348" s="38"/>
+      <c r="D348" s="38"/>
+      <c r="E348" s="39"/>
+      <c r="F348" s="33"/>
       <c r="G348" s="23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H348" s="23" t="s">
+        <v>795</v>
+      </c>
+      <c r="I348" s="23" t="s">
         <v>796</v>
-      </c>
-      <c r="I348" s="23" t="s">
-        <v>797</v>
       </c>
       <c r="J348" s="23"/>
     </row>
@@ -12059,17 +12047,17 @@
       <c r="C349" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D349" s="32"/>
-      <c r="E349" s="25"/>
-      <c r="F349" s="38"/>
+      <c r="D349" s="38"/>
+      <c r="E349" s="39"/>
+      <c r="F349" s="33"/>
       <c r="G349" s="23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H349" s="23" t="s">
+        <v>797</v>
+      </c>
+      <c r="I349" s="23" t="s">
         <v>798</v>
-      </c>
-      <c r="I349" s="23" t="s">
-        <v>799</v>
       </c>
       <c r="J349" s="23"/>
     </row>
@@ -12080,17 +12068,17 @@
       <c r="C350" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D350" s="32"/>
-      <c r="E350" s="25"/>
-      <c r="F350" s="38"/>
+      <c r="D350" s="38"/>
+      <c r="E350" s="39"/>
+      <c r="F350" s="33"/>
       <c r="G350" s="23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H350" s="23" t="s">
+        <v>799</v>
+      </c>
+      <c r="I350" s="23" t="s">
         <v>800</v>
-      </c>
-      <c r="I350" s="23" t="s">
-        <v>801</v>
       </c>
       <c r="J350" s="23"/>
     </row>
@@ -12101,17 +12089,17 @@
       <c r="C351" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D351" s="32"/>
-      <c r="E351" s="25"/>
-      <c r="F351" s="38"/>
+      <c r="D351" s="38"/>
+      <c r="E351" s="39"/>
+      <c r="F351" s="33"/>
       <c r="G351" s="23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H351" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="I351" s="23" t="s">
         <v>802</v>
-      </c>
-      <c r="I351" s="23" t="s">
-        <v>803</v>
       </c>
       <c r="J351" s="23"/>
     </row>
@@ -12122,17 +12110,17 @@
       <c r="C352" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D352" s="32"/>
-      <c r="E352" s="25"/>
-      <c r="F352" s="38"/>
+      <c r="D352" s="38"/>
+      <c r="E352" s="39"/>
+      <c r="F352" s="33"/>
       <c r="G352" s="23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H352" s="23" t="s">
+        <v>803</v>
+      </c>
+      <c r="I352" s="23" t="s">
         <v>804</v>
-      </c>
-      <c r="I352" s="23" t="s">
-        <v>805</v>
       </c>
       <c r="J352" s="23"/>
     </row>
@@ -12143,17 +12131,17 @@
       <c r="C353" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D353" s="32"/>
-      <c r="E353" s="25"/>
-      <c r="F353" s="38"/>
+      <c r="D353" s="38"/>
+      <c r="E353" s="39"/>
+      <c r="F353" s="33"/>
       <c r="G353" s="23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H353" s="23" t="s">
+        <v>805</v>
+      </c>
+      <c r="I353" s="23" t="s">
         <v>806</v>
-      </c>
-      <c r="I353" s="23" t="s">
-        <v>807</v>
       </c>
       <c r="J353" s="23"/>
     </row>
@@ -12164,17 +12152,17 @@
       <c r="C354" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D354" s="32"/>
-      <c r="E354" s="25"/>
-      <c r="F354" s="38"/>
+      <c r="D354" s="38"/>
+      <c r="E354" s="39"/>
+      <c r="F354" s="33"/>
       <c r="G354" s="23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H354" s="23" t="s">
+        <v>807</v>
+      </c>
+      <c r="I354" s="23" t="s">
         <v>808</v>
-      </c>
-      <c r="I354" s="23" t="s">
-        <v>809</v>
       </c>
       <c r="J354" s="23"/>
     </row>
@@ -12185,17 +12173,17 @@
       <c r="C355" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D355" s="32"/>
-      <c r="E355" s="25"/>
-      <c r="F355" s="38"/>
+      <c r="D355" s="38"/>
+      <c r="E355" s="39"/>
+      <c r="F355" s="33"/>
       <c r="G355" s="23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H355" s="23" t="s">
+        <v>809</v>
+      </c>
+      <c r="I355" s="23" t="s">
         <v>810</v>
-      </c>
-      <c r="I355" s="23" t="s">
-        <v>811</v>
       </c>
       <c r="J355" s="23"/>
     </row>
@@ -12206,17 +12194,17 @@
       <c r="C356" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D356" s="32"/>
-      <c r="E356" s="25"/>
-      <c r="F356" s="38"/>
+      <c r="D356" s="38"/>
+      <c r="E356" s="39"/>
+      <c r="F356" s="33"/>
       <c r="G356" s="23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H356" s="23" t="s">
+        <v>811</v>
+      </c>
+      <c r="I356" s="23" t="s">
         <v>812</v>
-      </c>
-      <c r="I356" s="23" t="s">
-        <v>813</v>
       </c>
       <c r="J356" s="23"/>
     </row>
@@ -12227,17 +12215,17 @@
       <c r="C357" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D357" s="32"/>
-      <c r="E357" s="25"/>
-      <c r="F357" s="38"/>
+      <c r="D357" s="38"/>
+      <c r="E357" s="39"/>
+      <c r="F357" s="33"/>
       <c r="G357" s="23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H357" s="23" t="s">
+        <v>813</v>
+      </c>
+      <c r="I357" s="23" t="s">
         <v>814</v>
-      </c>
-      <c r="I357" s="23" t="s">
-        <v>815</v>
       </c>
       <c r="J357" s="23"/>
     </row>
@@ -12248,17 +12236,17 @@
       <c r="C358" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D358" s="32"/>
-      <c r="E358" s="25"/>
-      <c r="F358" s="38"/>
+      <c r="D358" s="38"/>
+      <c r="E358" s="39"/>
+      <c r="F358" s="33"/>
       <c r="G358" s="23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H358" s="23" t="s">
+        <v>815</v>
+      </c>
+      <c r="I358" s="23" t="s">
         <v>816</v>
-      </c>
-      <c r="I358" s="23" t="s">
-        <v>817</v>
       </c>
       <c r="J358" s="23"/>
     </row>
@@ -12269,17 +12257,17 @@
       <c r="C359" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D359" s="32"/>
-      <c r="E359" s="25"/>
-      <c r="F359" s="38"/>
+      <c r="D359" s="38"/>
+      <c r="E359" s="39"/>
+      <c r="F359" s="33"/>
       <c r="G359" s="23" t="s">
+        <v>817</v>
+      </c>
+      <c r="H359" s="23" t="s">
         <v>818</v>
       </c>
-      <c r="H359" s="23" t="s">
+      <c r="I359" s="23" t="s">
         <v>819</v>
-      </c>
-      <c r="I359" s="23" t="s">
-        <v>820</v>
       </c>
       <c r="J359" s="23"/>
     </row>
@@ -12290,17 +12278,17 @@
       <c r="C360" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D360" s="32"/>
-      <c r="E360" s="25"/>
-      <c r="F360" s="38"/>
+      <c r="D360" s="38"/>
+      <c r="E360" s="39"/>
+      <c r="F360" s="33"/>
       <c r="G360" s="23" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H360" s="23" t="s">
+        <v>820</v>
+      </c>
+      <c r="I360" s="23" t="s">
         <v>821</v>
-      </c>
-      <c r="I360" s="23" t="s">
-        <v>822</v>
       </c>
       <c r="J360" s="23"/>
     </row>
@@ -12311,17 +12299,17 @@
       <c r="C361" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D361" s="32"/>
-      <c r="E361" s="25"/>
-      <c r="F361" s="38"/>
+      <c r="D361" s="38"/>
+      <c r="E361" s="39"/>
+      <c r="F361" s="33"/>
       <c r="G361" s="23" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H361" s="23" t="s">
+        <v>822</v>
+      </c>
+      <c r="I361" s="23" t="s">
         <v>823</v>
-      </c>
-      <c r="I361" s="23" t="s">
-        <v>824</v>
       </c>
       <c r="J361" s="23"/>
     </row>
@@ -12332,17 +12320,17 @@
       <c r="C362" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D362" s="32"/>
-      <c r="E362" s="25"/>
-      <c r="F362" s="38"/>
+      <c r="D362" s="38"/>
+      <c r="E362" s="39"/>
+      <c r="F362" s="33"/>
       <c r="G362" s="23" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H362" s="23" t="s">
+        <v>824</v>
+      </c>
+      <c r="I362" s="23" t="s">
         <v>825</v>
-      </c>
-      <c r="I362" s="23" t="s">
-        <v>826</v>
       </c>
       <c r="J362" s="23"/>
     </row>
@@ -12353,17 +12341,17 @@
       <c r="C363" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D363" s="32"/>
-      <c r="E363" s="25"/>
-      <c r="F363" s="38"/>
+      <c r="D363" s="38"/>
+      <c r="E363" s="39"/>
+      <c r="F363" s="33"/>
       <c r="G363" s="23" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H363" s="23" t="s">
+        <v>826</v>
+      </c>
+      <c r="I363" s="23" t="s">
         <v>827</v>
-      </c>
-      <c r="I363" s="23" t="s">
-        <v>828</v>
       </c>
       <c r="J363" s="23"/>
     </row>
@@ -12374,17 +12362,17 @@
       <c r="C364" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D364" s="32"/>
-      <c r="E364" s="25"/>
-      <c r="F364" s="38"/>
+      <c r="D364" s="38"/>
+      <c r="E364" s="39"/>
+      <c r="F364" s="33"/>
       <c r="G364" s="23" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H364" s="23" t="s">
+        <v>828</v>
+      </c>
+      <c r="I364" s="23" t="s">
         <v>829</v>
-      </c>
-      <c r="I364" s="23" t="s">
-        <v>830</v>
       </c>
       <c r="J364" s="23"/>
     </row>
@@ -12395,17 +12383,17 @@
       <c r="C365" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D365" s="32"/>
-      <c r="E365" s="25"/>
-      <c r="F365" s="38"/>
+      <c r="D365" s="38"/>
+      <c r="E365" s="39"/>
+      <c r="F365" s="33"/>
       <c r="G365" s="23" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H365" s="23" t="s">
+        <v>830</v>
+      </c>
+      <c r="I365" s="23" t="s">
         <v>831</v>
-      </c>
-      <c r="I365" s="23" t="s">
-        <v>832</v>
       </c>
       <c r="J365" s="23"/>
     </row>
@@ -12416,17 +12404,17 @@
       <c r="C366" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D366" s="32"/>
-      <c r="E366" s="25"/>
-      <c r="F366" s="38"/>
+      <c r="D366" s="38"/>
+      <c r="E366" s="39"/>
+      <c r="F366" s="33"/>
       <c r="G366" s="23" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H366" s="23" t="s">
+        <v>832</v>
+      </c>
+      <c r="I366" s="23" t="s">
         <v>833</v>
-      </c>
-      <c r="I366" s="23" t="s">
-        <v>834</v>
       </c>
       <c r="J366" s="23"/>
     </row>
@@ -12437,17 +12425,17 @@
       <c r="C367" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D367" s="32"/>
-      <c r="E367" s="25"/>
-      <c r="F367" s="38"/>
+      <c r="D367" s="38"/>
+      <c r="E367" s="39"/>
+      <c r="F367" s="33"/>
       <c r="G367" s="23" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H367" s="23" t="s">
+        <v>834</v>
+      </c>
+      <c r="I367" s="23" t="s">
         <v>835</v>
-      </c>
-      <c r="I367" s="23" t="s">
-        <v>836</v>
       </c>
       <c r="J367" s="23"/>
     </row>
@@ -12458,17 +12446,17 @@
       <c r="C368" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D368" s="32"/>
-      <c r="E368" s="25"/>
-      <c r="F368" s="38"/>
+      <c r="D368" s="38"/>
+      <c r="E368" s="39"/>
+      <c r="F368" s="33"/>
       <c r="G368" s="23" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H368" s="23" t="s">
+        <v>836</v>
+      </c>
+      <c r="I368" s="23" t="s">
         <v>837</v>
-      </c>
-      <c r="I368" s="23" t="s">
-        <v>838</v>
       </c>
       <c r="J368" s="23"/>
     </row>
@@ -12479,17 +12467,17 @@
       <c r="C369" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D369" s="32"/>
-      <c r="E369" s="25"/>
-      <c r="F369" s="38"/>
+      <c r="D369" s="38"/>
+      <c r="E369" s="39"/>
+      <c r="F369" s="33"/>
       <c r="G369" s="23" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H369" s="23" t="s">
+        <v>838</v>
+      </c>
+      <c r="I369" s="23" t="s">
         <v>839</v>
-      </c>
-      <c r="I369" s="23" t="s">
-        <v>840</v>
       </c>
       <c r="J369" s="23"/>
     </row>
@@ -12500,17 +12488,17 @@
       <c r="C370" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D370" s="32"/>
-      <c r="E370" s="25"/>
-      <c r="F370" s="38"/>
+      <c r="D370" s="38"/>
+      <c r="E370" s="39"/>
+      <c r="F370" s="33"/>
       <c r="G370" s="23" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H370" s="23" t="s">
+        <v>840</v>
+      </c>
+      <c r="I370" s="23" t="s">
         <v>841</v>
-      </c>
-      <c r="I370" s="23" t="s">
-        <v>842</v>
       </c>
       <c r="J370" s="23"/>
     </row>
@@ -12521,17 +12509,17 @@
       <c r="C371" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D371" s="32"/>
-      <c r="E371" s="25"/>
-      <c r="F371" s="38"/>
+      <c r="D371" s="38"/>
+      <c r="E371" s="39"/>
+      <c r="F371" s="33"/>
       <c r="G371" s="23" t="s">
+        <v>842</v>
+      </c>
+      <c r="H371" s="23" t="s">
         <v>843</v>
       </c>
-      <c r="H371" s="23" t="s">
+      <c r="I371" s="23" t="s">
         <v>844</v>
-      </c>
-      <c r="I371" s="23" t="s">
-        <v>845</v>
       </c>
       <c r="J371" s="23"/>
     </row>
@@ -12542,17 +12530,17 @@
       <c r="C372" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D372" s="32"/>
-      <c r="E372" s="25"/>
-      <c r="F372" s="38"/>
+      <c r="D372" s="38"/>
+      <c r="E372" s="39"/>
+      <c r="F372" s="33"/>
       <c r="G372" s="23" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H372" s="23" t="s">
+        <v>845</v>
+      </c>
+      <c r="I372" s="23" t="s">
         <v>846</v>
-      </c>
-      <c r="I372" s="23" t="s">
-        <v>847</v>
       </c>
       <c r="J372" s="23"/>
     </row>
@@ -12563,17 +12551,17 @@
       <c r="C373" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D373" s="32"/>
-      <c r="E373" s="25"/>
-      <c r="F373" s="38"/>
+      <c r="D373" s="38"/>
+      <c r="E373" s="39"/>
+      <c r="F373" s="33"/>
       <c r="G373" s="23" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H373" s="23" t="s">
+        <v>847</v>
+      </c>
+      <c r="I373" s="23" t="s">
         <v>848</v>
-      </c>
-      <c r="I373" s="23" t="s">
-        <v>849</v>
       </c>
       <c r="J373" s="23"/>
     </row>
@@ -12584,17 +12572,17 @@
       <c r="C374" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D374" s="32"/>
-      <c r="E374" s="25"/>
-      <c r="F374" s="38"/>
+      <c r="D374" s="38"/>
+      <c r="E374" s="39"/>
+      <c r="F374" s="33"/>
       <c r="G374" s="23" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H374" s="23" t="s">
+        <v>849</v>
+      </c>
+      <c r="I374" s="23" t="s">
         <v>850</v>
-      </c>
-      <c r="I374" s="23" t="s">
-        <v>851</v>
       </c>
       <c r="J374" s="23"/>
     </row>
@@ -12605,17 +12593,17 @@
       <c r="C375" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D375" s="32"/>
-      <c r="E375" s="25"/>
-      <c r="F375" s="38"/>
+      <c r="D375" s="38"/>
+      <c r="E375" s="39"/>
+      <c r="F375" s="33"/>
       <c r="G375" s="23" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H375" s="23" t="s">
+        <v>851</v>
+      </c>
+      <c r="I375" s="23" t="s">
         <v>852</v>
-      </c>
-      <c r="I375" s="23" t="s">
-        <v>853</v>
       </c>
       <c r="J375" s="23"/>
     </row>
@@ -12626,17 +12614,17 @@
       <c r="C376" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D376" s="32"/>
-      <c r="E376" s="25"/>
-      <c r="F376" s="38"/>
+      <c r="D376" s="38"/>
+      <c r="E376" s="39"/>
+      <c r="F376" s="33"/>
       <c r="G376" s="23" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H376" s="23" t="s">
+        <v>853</v>
+      </c>
+      <c r="I376" s="23" t="s">
         <v>854</v>
-      </c>
-      <c r="I376" s="23" t="s">
-        <v>855</v>
       </c>
       <c r="J376" s="23"/>
     </row>
@@ -12647,17 +12635,17 @@
       <c r="C377" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D377" s="32"/>
-      <c r="E377" s="25"/>
-      <c r="F377" s="38"/>
+      <c r="D377" s="38"/>
+      <c r="E377" s="39"/>
+      <c r="F377" s="33"/>
       <c r="G377" s="23" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H377" s="23" t="s">
+        <v>855</v>
+      </c>
+      <c r="I377" s="23" t="s">
         <v>856</v>
-      </c>
-      <c r="I377" s="23" t="s">
-        <v>857</v>
       </c>
       <c r="J377" s="23"/>
     </row>
@@ -12668,17 +12656,17 @@
       <c r="C378" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D378" s="32"/>
-      <c r="E378" s="25"/>
-      <c r="F378" s="38"/>
+      <c r="D378" s="38"/>
+      <c r="E378" s="39"/>
+      <c r="F378" s="33"/>
       <c r="G378" s="23" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H378" s="23" t="s">
+        <v>857</v>
+      </c>
+      <c r="I378" s="23" t="s">
         <v>858</v>
-      </c>
-      <c r="I378" s="23" t="s">
-        <v>859</v>
       </c>
       <c r="J378" s="23"/>
     </row>
@@ -12689,17 +12677,17 @@
       <c r="C379" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D379" s="32"/>
-      <c r="E379" s="25"/>
-      <c r="F379" s="38"/>
+      <c r="D379" s="38"/>
+      <c r="E379" s="39"/>
+      <c r="F379" s="33"/>
       <c r="G379" s="23" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H379" s="23" t="s">
+        <v>859</v>
+      </c>
+      <c r="I379" s="23" t="s">
         <v>860</v>
-      </c>
-      <c r="I379" s="23" t="s">
-        <v>861</v>
       </c>
       <c r="J379" s="23"/>
     </row>
@@ -12710,17 +12698,17 @@
       <c r="C380" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D380" s="32"/>
-      <c r="E380" s="25"/>
-      <c r="F380" s="38"/>
+      <c r="D380" s="38"/>
+      <c r="E380" s="39"/>
+      <c r="F380" s="33"/>
       <c r="G380" s="23" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H380" s="23" t="s">
+        <v>861</v>
+      </c>
+      <c r="I380" s="23" t="s">
         <v>862</v>
-      </c>
-      <c r="I380" s="23" t="s">
-        <v>863</v>
       </c>
       <c r="J380" s="23"/>
     </row>
@@ -12731,17 +12719,17 @@
       <c r="C381" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D381" s="32"/>
-      <c r="E381" s="25"/>
-      <c r="F381" s="38"/>
+      <c r="D381" s="38"/>
+      <c r="E381" s="39"/>
+      <c r="F381" s="33"/>
       <c r="G381" s="23" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H381" s="23" t="s">
+        <v>863</v>
+      </c>
+      <c r="I381" s="23" t="s">
         <v>864</v>
-      </c>
-      <c r="I381" s="23" t="s">
-        <v>865</v>
       </c>
       <c r="J381" s="23"/>
     </row>
@@ -12752,17 +12740,17 @@
       <c r="C382" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D382" s="32"/>
-      <c r="E382" s="25"/>
-      <c r="F382" s="38"/>
+      <c r="D382" s="38"/>
+      <c r="E382" s="39"/>
+      <c r="F382" s="33"/>
       <c r="G382" s="23" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H382" s="23" t="s">
+        <v>865</v>
+      </c>
+      <c r="I382" s="23" t="s">
         <v>866</v>
-      </c>
-      <c r="I382" s="23" t="s">
-        <v>867</v>
       </c>
       <c r="J382" s="23"/>
     </row>
@@ -12773,17 +12761,17 @@
       <c r="C383" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D383" s="32"/>
-      <c r="E383" s="25"/>
-      <c r="F383" s="38"/>
+      <c r="D383" s="38"/>
+      <c r="E383" s="39"/>
+      <c r="F383" s="33"/>
       <c r="G383" s="23" t="s">
+        <v>867</v>
+      </c>
+      <c r="H383" s="23" t="s">
         <v>868</v>
       </c>
-      <c r="H383" s="23" t="s">
+      <c r="I383" s="23" t="s">
         <v>869</v>
-      </c>
-      <c r="I383" s="23" t="s">
-        <v>870</v>
       </c>
       <c r="J383" s="23"/>
     </row>
@@ -12794,17 +12782,17 @@
       <c r="C384" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D384" s="32"/>
-      <c r="E384" s="25"/>
-      <c r="F384" s="38"/>
+      <c r="D384" s="38"/>
+      <c r="E384" s="39"/>
+      <c r="F384" s="33"/>
       <c r="G384" s="23" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H384" s="23" t="s">
+        <v>870</v>
+      </c>
+      <c r="I384" s="23" t="s">
         <v>871</v>
-      </c>
-      <c r="I384" s="23" t="s">
-        <v>872</v>
       </c>
       <c r="J384" s="23"/>
     </row>
@@ -12815,17 +12803,17 @@
       <c r="C385" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D385" s="32"/>
-      <c r="E385" s="25"/>
-      <c r="F385" s="38"/>
+      <c r="D385" s="38"/>
+      <c r="E385" s="39"/>
+      <c r="F385" s="33"/>
       <c r="G385" s="23" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H385" s="23" t="s">
+        <v>872</v>
+      </c>
+      <c r="I385" s="23" t="s">
         <v>873</v>
-      </c>
-      <c r="I385" s="23" t="s">
-        <v>874</v>
       </c>
       <c r="J385" s="23"/>
     </row>
@@ -12836,17 +12824,17 @@
       <c r="C386" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D386" s="32"/>
-      <c r="E386" s="25"/>
-      <c r="F386" s="38"/>
+      <c r="D386" s="38"/>
+      <c r="E386" s="39"/>
+      <c r="F386" s="33"/>
       <c r="G386" s="23" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H386" s="23" t="s">
+        <v>874</v>
+      </c>
+      <c r="I386" s="23" t="s">
         <v>875</v>
-      </c>
-      <c r="I386" s="23" t="s">
-        <v>876</v>
       </c>
       <c r="J386" s="23"/>
     </row>
@@ -12857,17 +12845,17 @@
       <c r="C387" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D387" s="32"/>
-      <c r="E387" s="25"/>
-      <c r="F387" s="38"/>
+      <c r="D387" s="38"/>
+      <c r="E387" s="39"/>
+      <c r="F387" s="33"/>
       <c r="G387" s="23" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H387" s="23" t="s">
+        <v>876</v>
+      </c>
+      <c r="I387" s="23" t="s">
         <v>877</v>
-      </c>
-      <c r="I387" s="23" t="s">
-        <v>878</v>
       </c>
       <c r="J387" s="23"/>
     </row>
@@ -12878,17 +12866,17 @@
       <c r="C388" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D388" s="32"/>
-      <c r="E388" s="25"/>
-      <c r="F388" s="38"/>
+      <c r="D388" s="38"/>
+      <c r="E388" s="39"/>
+      <c r="F388" s="33"/>
       <c r="G388" s="23" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H388" s="23" t="s">
+        <v>878</v>
+      </c>
+      <c r="I388" s="23" t="s">
         <v>879</v>
-      </c>
-      <c r="I388" s="23" t="s">
-        <v>880</v>
       </c>
       <c r="J388" s="23"/>
     </row>
@@ -12899,17 +12887,17 @@
       <c r="C389" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D389" s="32"/>
-      <c r="E389" s="25"/>
-      <c r="F389" s="38"/>
+      <c r="D389" s="38"/>
+      <c r="E389" s="39"/>
+      <c r="F389" s="33"/>
       <c r="G389" s="23" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H389" s="23" t="s">
+        <v>880</v>
+      </c>
+      <c r="I389" s="23" t="s">
         <v>881</v>
-      </c>
-      <c r="I389" s="23" t="s">
-        <v>882</v>
       </c>
       <c r="J389" s="23"/>
     </row>
@@ -12920,17 +12908,17 @@
       <c r="C390" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D390" s="32"/>
-      <c r="E390" s="25"/>
-      <c r="F390" s="38"/>
+      <c r="D390" s="38"/>
+      <c r="E390" s="39"/>
+      <c r="F390" s="33"/>
       <c r="G390" s="23" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H390" s="23" t="s">
+        <v>882</v>
+      </c>
+      <c r="I390" s="23" t="s">
         <v>883</v>
-      </c>
-      <c r="I390" s="23" t="s">
-        <v>884</v>
       </c>
       <c r="J390" s="23"/>
     </row>
@@ -12941,17 +12929,17 @@
       <c r="C391" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D391" s="32"/>
-      <c r="E391" s="25"/>
-      <c r="F391" s="38"/>
+      <c r="D391" s="38"/>
+      <c r="E391" s="39"/>
+      <c r="F391" s="33"/>
       <c r="G391" s="23" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H391" s="23" t="s">
+        <v>884</v>
+      </c>
+      <c r="I391" s="23" t="s">
         <v>885</v>
-      </c>
-      <c r="I391" s="23" t="s">
-        <v>886</v>
       </c>
       <c r="J391" s="23"/>
     </row>
@@ -12962,17 +12950,17 @@
       <c r="C392" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D392" s="32"/>
-      <c r="E392" s="25"/>
-      <c r="F392" s="38"/>
+      <c r="D392" s="38"/>
+      <c r="E392" s="39"/>
+      <c r="F392" s="33"/>
       <c r="G392" s="23" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H392" s="23" t="s">
+        <v>886</v>
+      </c>
+      <c r="I392" s="23" t="s">
         <v>887</v>
-      </c>
-      <c r="I392" s="23" t="s">
-        <v>888</v>
       </c>
       <c r="J392" s="23"/>
     </row>
@@ -12983,17 +12971,17 @@
       <c r="C393" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D393" s="32"/>
-      <c r="E393" s="25"/>
-      <c r="F393" s="38"/>
+      <c r="D393" s="38"/>
+      <c r="E393" s="39"/>
+      <c r="F393" s="33"/>
       <c r="G393" s="23" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H393" s="23" t="s">
+        <v>888</v>
+      </c>
+      <c r="I393" s="23" t="s">
         <v>889</v>
-      </c>
-      <c r="I393" s="23" t="s">
-        <v>890</v>
       </c>
       <c r="J393" s="23"/>
     </row>
@@ -13004,17 +12992,17 @@
       <c r="C394" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D394" s="32"/>
-      <c r="E394" s="25"/>
-      <c r="F394" s="38"/>
+      <c r="D394" s="38"/>
+      <c r="E394" s="39"/>
+      <c r="F394" s="33"/>
       <c r="G394" s="23" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H394" s="23" t="s">
+        <v>890</v>
+      </c>
+      <c r="I394" s="23" t="s">
         <v>891</v>
-      </c>
-      <c r="I394" s="23" t="s">
-        <v>892</v>
       </c>
       <c r="J394" s="23"/>
     </row>
@@ -13025,17 +13013,17 @@
       <c r="C395" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D395" s="32"/>
-      <c r="E395" s="25"/>
-      <c r="F395" s="38"/>
+      <c r="D395" s="38"/>
+      <c r="E395" s="39"/>
+      <c r="F395" s="33"/>
       <c r="G395" s="23" t="s">
+        <v>892</v>
+      </c>
+      <c r="H395" s="23" t="s">
         <v>893</v>
       </c>
-      <c r="H395" s="23" t="s">
+      <c r="I395" s="23" t="s">
         <v>894</v>
-      </c>
-      <c r="I395" s="23" t="s">
-        <v>895</v>
       </c>
       <c r="J395" s="23"/>
     </row>
@@ -13046,17 +13034,17 @@
       <c r="C396" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D396" s="32"/>
-      <c r="E396" s="25"/>
-      <c r="F396" s="38"/>
+      <c r="D396" s="38"/>
+      <c r="E396" s="39"/>
+      <c r="F396" s="33"/>
       <c r="G396" s="23" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H396" s="23" t="s">
+        <v>895</v>
+      </c>
+      <c r="I396" s="23" t="s">
         <v>896</v>
-      </c>
-      <c r="I396" s="23" t="s">
-        <v>897</v>
       </c>
       <c r="J396" s="23"/>
     </row>
@@ -13067,17 +13055,17 @@
       <c r="C397" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D397" s="32"/>
-      <c r="E397" s="25"/>
-      <c r="F397" s="38"/>
+      <c r="D397" s="38"/>
+      <c r="E397" s="39"/>
+      <c r="F397" s="33"/>
       <c r="G397" s="23" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H397" s="23" t="s">
+        <v>897</v>
+      </c>
+      <c r="I397" s="23" t="s">
         <v>898</v>
-      </c>
-      <c r="I397" s="23" t="s">
-        <v>899</v>
       </c>
       <c r="J397" s="23"/>
     </row>
@@ -13088,17 +13076,17 @@
       <c r="C398" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D398" s="32"/>
-      <c r="E398" s="25"/>
-      <c r="F398" s="38"/>
+      <c r="D398" s="38"/>
+      <c r="E398" s="39"/>
+      <c r="F398" s="33"/>
       <c r="G398" s="23" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H398" s="23" t="s">
+        <v>899</v>
+      </c>
+      <c r="I398" s="23" t="s">
         <v>900</v>
-      </c>
-      <c r="I398" s="23" t="s">
-        <v>901</v>
       </c>
       <c r="J398" s="23"/>
     </row>
@@ -13109,17 +13097,17 @@
       <c r="C399" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D399" s="32"/>
-      <c r="E399" s="25"/>
-      <c r="F399" s="38"/>
+      <c r="D399" s="38"/>
+      <c r="E399" s="39"/>
+      <c r="F399" s="33"/>
       <c r="G399" s="23" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H399" s="23" t="s">
+        <v>901</v>
+      </c>
+      <c r="I399" s="23" t="s">
         <v>902</v>
-      </c>
-      <c r="I399" s="23" t="s">
-        <v>903</v>
       </c>
       <c r="J399" s="23"/>
     </row>
@@ -13130,17 +13118,17 @@
       <c r="C400" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D400" s="32"/>
-      <c r="E400" s="25"/>
-      <c r="F400" s="38"/>
+      <c r="D400" s="38"/>
+      <c r="E400" s="39"/>
+      <c r="F400" s="33"/>
       <c r="G400" s="23" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H400" s="23" t="s">
+        <v>903</v>
+      </c>
+      <c r="I400" s="23" t="s">
         <v>904</v>
-      </c>
-      <c r="I400" s="23" t="s">
-        <v>905</v>
       </c>
       <c r="J400" s="23"/>
     </row>
@@ -13151,17 +13139,17 @@
       <c r="C401" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D401" s="32"/>
-      <c r="E401" s="25"/>
-      <c r="F401" s="38"/>
+      <c r="D401" s="38"/>
+      <c r="E401" s="39"/>
+      <c r="F401" s="33"/>
       <c r="G401" s="23" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H401" s="23" t="s">
+        <v>905</v>
+      </c>
+      <c r="I401" s="23" t="s">
         <v>906</v>
-      </c>
-      <c r="I401" s="23" t="s">
-        <v>907</v>
       </c>
       <c r="J401" s="23"/>
     </row>
@@ -13172,17 +13160,17 @@
       <c r="C402" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D402" s="32"/>
-      <c r="E402" s="25"/>
-      <c r="F402" s="38"/>
+      <c r="D402" s="38"/>
+      <c r="E402" s="39"/>
+      <c r="F402" s="33"/>
       <c r="G402" s="23" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H402" s="23" t="s">
+        <v>907</v>
+      </c>
+      <c r="I402" s="23" t="s">
         <v>908</v>
-      </c>
-      <c r="I402" s="23" t="s">
-        <v>909</v>
       </c>
       <c r="J402" s="23"/>
     </row>
@@ -13193,21 +13181,19 @@
       <c r="C403" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D403" s="32"/>
-      <c r="E403" s="25"/>
-      <c r="F403" s="38"/>
+      <c r="D403" s="38"/>
+      <c r="E403" s="39"/>
+      <c r="F403" s="33"/>
       <c r="G403" s="23" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H403" s="23" t="s">
+        <v>909</v>
+      </c>
+      <c r="I403" s="23" t="s">
         <v>910</v>
       </c>
-      <c r="I403" s="23" t="s">
-        <v>911</v>
-      </c>
-      <c r="J403" s="23" t="s">
-        <v>732</v>
-      </c>
+      <c r="J403" s="23"/>
     </row>
     <row r="404" spans="2:10" ht="49.95" customHeight="1">
       <c r="B404" s="23">
@@ -13216,21 +13202,19 @@
       <c r="C404" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D404" s="32"/>
-      <c r="E404" s="25"/>
-      <c r="F404" s="38"/>
+      <c r="D404" s="38"/>
+      <c r="E404" s="39"/>
+      <c r="F404" s="33"/>
       <c r="G404" s="23" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H404" s="23" t="s">
+        <v>911</v>
+      </c>
+      <c r="I404" s="23" t="s">
         <v>912</v>
       </c>
-      <c r="I404" s="23" t="s">
-        <v>913</v>
-      </c>
-      <c r="J404" s="23" t="s">
-        <v>732</v>
-      </c>
+      <c r="J404" s="23"/>
     </row>
     <row r="405" spans="2:10" ht="49.95" customHeight="1">
       <c r="B405" s="23">
@@ -13239,17 +13223,17 @@
       <c r="C405" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D405" s="32"/>
-      <c r="E405" s="25"/>
-      <c r="F405" s="38"/>
+      <c r="D405" s="38"/>
+      <c r="E405" s="39"/>
+      <c r="F405" s="33"/>
       <c r="G405" s="23" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H405" s="23" t="s">
+        <v>913</v>
+      </c>
+      <c r="I405" s="23" t="s">
         <v>914</v>
-      </c>
-      <c r="I405" s="23" t="s">
-        <v>915</v>
       </c>
       <c r="J405" s="23"/>
     </row>
@@ -13260,17 +13244,17 @@
       <c r="C406" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D406" s="32"/>
-      <c r="E406" s="25"/>
-      <c r="F406" s="39"/>
+      <c r="D406" s="38"/>
+      <c r="E406" s="39"/>
+      <c r="F406" s="34"/>
       <c r="G406" s="23" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H406" s="23" t="s">
+        <v>915</v>
+      </c>
+      <c r="I406" s="23" t="s">
         <v>916</v>
-      </c>
-      <c r="I406" s="23" t="s">
-        <v>917</v>
       </c>
       <c r="J406" s="23"/>
     </row>
@@ -13281,19 +13265,19 @@
       <c r="C407" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D407" s="32"/>
-      <c r="E407" s="25"/>
-      <c r="F407" s="37" t="s">
+      <c r="D407" s="38"/>
+      <c r="E407" s="39"/>
+      <c r="F407" s="32" t="s">
+        <v>917</v>
+      </c>
+      <c r="G407" s="23" t="s">
         <v>918</v>
       </c>
-      <c r="G407" s="23" t="s">
+      <c r="H407" s="23" t="s">
         <v>919</v>
       </c>
-      <c r="H407" s="23" t="s">
+      <c r="I407" s="23" t="s">
         <v>920</v>
-      </c>
-      <c r="I407" s="23" t="s">
-        <v>921</v>
       </c>
       <c r="J407" s="23"/>
     </row>
@@ -13304,20 +13288,20 @@
       <c r="C408" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D408" s="32"/>
-      <c r="E408" s="25"/>
-      <c r="F408" s="38"/>
+      <c r="D408" s="38"/>
+      <c r="E408" s="39"/>
+      <c r="F408" s="33"/>
       <c r="G408" s="23" t="s">
+        <v>921</v>
+      </c>
+      <c r="H408" s="23" t="s">
         <v>922</v>
       </c>
-      <c r="H408" s="23" t="s">
+      <c r="I408" s="23" t="s">
         <v>923</v>
       </c>
-      <c r="I408" s="23" t="s">
+      <c r="J408" s="23" t="s">
         <v>924</v>
-      </c>
-      <c r="J408" s="23" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="409" spans="2:10" ht="49.95" customHeight="1">
@@ -13327,20 +13311,20 @@
       <c r="C409" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D409" s="32"/>
-      <c r="E409" s="25"/>
-      <c r="F409" s="38"/>
+      <c r="D409" s="38"/>
+      <c r="E409" s="39"/>
+      <c r="F409" s="33"/>
       <c r="G409" s="23" t="s">
+        <v>925</v>
+      </c>
+      <c r="H409" s="23" t="s">
         <v>926</v>
       </c>
-      <c r="H409" s="23" t="s">
+      <c r="I409" s="23" t="s">
         <v>927</v>
       </c>
-      <c r="I409" s="23" t="s">
+      <c r="J409" s="23" t="s">
         <v>928</v>
-      </c>
-      <c r="J409" s="23" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="410" spans="2:10" ht="49.95" customHeight="1">
@@ -13350,20 +13334,20 @@
       <c r="C410" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D410" s="32"/>
-      <c r="E410" s="25"/>
-      <c r="F410" s="38"/>
+      <c r="D410" s="38"/>
+      <c r="E410" s="39"/>
+      <c r="F410" s="33"/>
       <c r="G410" s="23" t="s">
+        <v>929</v>
+      </c>
+      <c r="H410" s="23" t="s">
         <v>930</v>
       </c>
-      <c r="H410" s="23" t="s">
+      <c r="I410" s="23" t="s">
         <v>931</v>
       </c>
-      <c r="I410" s="23" t="s">
+      <c r="J410" s="23" t="s">
         <v>932</v>
-      </c>
-      <c r="J410" s="23" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="411" spans="2:10" ht="49.95" customHeight="1">
@@ -13373,20 +13357,20 @@
       <c r="C411" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D411" s="32"/>
-      <c r="E411" s="25"/>
-      <c r="F411" s="38"/>
+      <c r="D411" s="38"/>
+      <c r="E411" s="39"/>
+      <c r="F411" s="33"/>
       <c r="G411" s="23" t="s">
+        <v>933</v>
+      </c>
+      <c r="H411" s="23" t="s">
         <v>934</v>
       </c>
-      <c r="H411" s="23" t="s">
+      <c r="I411" s="23" t="s">
         <v>935</v>
       </c>
-      <c r="I411" s="23" t="s">
+      <c r="J411" s="23" t="s">
         <v>936</v>
-      </c>
-      <c r="J411" s="23" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="412" spans="2:10" ht="49.95" customHeight="1">
@@ -13396,20 +13380,20 @@
       <c r="C412" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D412" s="32"/>
-      <c r="E412" s="25"/>
-      <c r="F412" s="38"/>
+      <c r="D412" s="38"/>
+      <c r="E412" s="39"/>
+      <c r="F412" s="33"/>
       <c r="G412" s="23" t="s">
+        <v>937</v>
+      </c>
+      <c r="H412" s="23" t="s">
         <v>938</v>
       </c>
-      <c r="H412" s="23" t="s">
+      <c r="I412" s="23" t="s">
         <v>939</v>
       </c>
-      <c r="I412" s="23" t="s">
+      <c r="J412" s="23" t="s">
         <v>940</v>
-      </c>
-      <c r="J412" s="23" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="413" spans="2:10" ht="49.95" customHeight="1">
@@ -13419,21 +13403,19 @@
       <c r="C413" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D413" s="32"/>
-      <c r="E413" s="25"/>
-      <c r="F413" s="38"/>
+      <c r="D413" s="38"/>
+      <c r="E413" s="39"/>
+      <c r="F413" s="33"/>
       <c r="G413" s="23" t="s">
+        <v>941</v>
+      </c>
+      <c r="H413" s="23" t="s">
         <v>942</v>
       </c>
-      <c r="H413" s="23" t="s">
+      <c r="I413" s="23" t="s">
         <v>943</v>
       </c>
-      <c r="I413" s="23" t="s">
-        <v>944</v>
-      </c>
-      <c r="J413" s="23" t="s">
-        <v>945</v>
-      </c>
+      <c r="J413" s="23"/>
     </row>
     <row r="414" spans="2:10" ht="49.95" customHeight="1">
       <c r="B414" s="23">
@@ -13442,21 +13424,19 @@
       <c r="C414" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D414" s="32"/>
-      <c r="E414" s="25"/>
-      <c r="F414" s="38"/>
+      <c r="D414" s="38"/>
+      <c r="E414" s="39"/>
+      <c r="F414" s="33"/>
       <c r="G414" s="23" t="s">
+        <v>944</v>
+      </c>
+      <c r="H414" s="23" t="s">
+        <v>945</v>
+      </c>
+      <c r="I414" s="23" t="s">
         <v>946</v>
       </c>
-      <c r="H414" s="23" t="s">
-        <v>947</v>
-      </c>
-      <c r="I414" s="23" t="s">
-        <v>948</v>
-      </c>
-      <c r="J414" s="23" t="s">
-        <v>949</v>
-      </c>
+      <c r="J414" s="23"/>
     </row>
     <row r="415" spans="2:10" ht="49.95" customHeight="1">
       <c r="B415" s="23">
@@ -13465,17 +13445,17 @@
       <c r="C415" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D415" s="32"/>
-      <c r="E415" s="25"/>
-      <c r="F415" s="38"/>
+      <c r="D415" s="38"/>
+      <c r="E415" s="39"/>
+      <c r="F415" s="33"/>
       <c r="G415" s="23" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="H415" s="23" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="I415" s="23" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="J415" s="23"/>
     </row>
@@ -13486,17 +13466,17 @@
       <c r="C416" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D416" s="32"/>
-      <c r="E416" s="25"/>
-      <c r="F416" s="38"/>
+      <c r="D416" s="38"/>
+      <c r="E416" s="39"/>
+      <c r="F416" s="33"/>
       <c r="G416" s="23" t="s">
+        <v>947</v>
+      </c>
+      <c r="H416" s="23" t="s">
         <v>950</v>
       </c>
-      <c r="H416" s="23" t="s">
-        <v>953</v>
-      </c>
       <c r="I416" s="23" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="J416" s="23"/>
     </row>
@@ -13507,17 +13487,17 @@
       <c r="C417" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D417" s="32"/>
-      <c r="E417" s="25"/>
-      <c r="F417" s="38"/>
+      <c r="D417" s="38"/>
+      <c r="E417" s="39"/>
+      <c r="F417" s="33"/>
       <c r="G417" s="23" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="H417" s="23" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="I417" s="23" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="J417" s="23"/>
     </row>
@@ -13528,17 +13508,17 @@
       <c r="C418" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D418" s="32"/>
-      <c r="E418" s="25"/>
-      <c r="F418" s="39"/>
+      <c r="D418" s="38"/>
+      <c r="E418" s="39"/>
+      <c r="F418" s="34"/>
       <c r="G418" s="23" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="H418" s="23" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="I418" s="23" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="J418" s="23"/>
     </row>
@@ -13549,19 +13529,19 @@
       <c r="C419" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D419" s="32"/>
-      <c r="E419" s="25"/>
-      <c r="F419" s="37" t="s">
+      <c r="D419" s="38"/>
+      <c r="E419" s="39"/>
+      <c r="F419" s="32" t="s">
+        <v>958</v>
+      </c>
+      <c r="G419" s="23" t="s">
+        <v>959</v>
+      </c>
+      <c r="H419" s="23" t="s">
+        <v>960</v>
+      </c>
+      <c r="I419" s="23" t="s">
         <v>961</v>
-      </c>
-      <c r="G419" s="23" t="s">
-        <v>962</v>
-      </c>
-      <c r="H419" s="23" t="s">
-        <v>963</v>
-      </c>
-      <c r="I419" s="23" t="s">
-        <v>964</v>
       </c>
       <c r="J419" s="23"/>
     </row>
@@ -13572,17 +13552,17 @@
       <c r="C420" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D420" s="32"/>
-      <c r="E420" s="25"/>
-      <c r="F420" s="38"/>
+      <c r="D420" s="38"/>
+      <c r="E420" s="39"/>
+      <c r="F420" s="33"/>
       <c r="G420" s="23" t="s">
+        <v>959</v>
+      </c>
+      <c r="H420" s="23" t="s">
         <v>962</v>
       </c>
-      <c r="H420" s="23" t="s">
-        <v>965</v>
-      </c>
       <c r="I420" s="23" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="J420" s="23"/>
     </row>
@@ -13593,17 +13573,17 @@
       <c r="C421" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D421" s="32"/>
-      <c r="E421" s="25"/>
-      <c r="F421" s="38"/>
+      <c r="D421" s="38"/>
+      <c r="E421" s="39"/>
+      <c r="F421" s="33"/>
       <c r="G421" s="23" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="H421" s="23" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="I421" s="23" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="J421" s="23"/>
     </row>
@@ -13614,17 +13594,17 @@
       <c r="C422" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D422" s="32"/>
-      <c r="E422" s="25"/>
-      <c r="F422" s="38"/>
+      <c r="D422" s="38"/>
+      <c r="E422" s="39"/>
+      <c r="F422" s="33"/>
       <c r="G422" s="23" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="H422" s="23" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="I422" s="23" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="J422" s="23"/>
     </row>
@@ -13635,17 +13615,17 @@
       <c r="C423" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D423" s="32"/>
-      <c r="E423" s="25"/>
-      <c r="F423" s="38"/>
+      <c r="D423" s="38"/>
+      <c r="E423" s="39"/>
+      <c r="F423" s="33"/>
       <c r="G423" s="23" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="H423" s="23" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="I423" s="23" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="J423" s="23"/>
     </row>
@@ -13656,17 +13636,17 @@
       <c r="C424" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D424" s="32"/>
-      <c r="E424" s="25"/>
-      <c r="F424" s="38"/>
+      <c r="D424" s="38"/>
+      <c r="E424" s="39"/>
+      <c r="F424" s="33"/>
       <c r="G424" s="23" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="H424" s="23" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="I424" s="23" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="J424" s="23"/>
     </row>
@@ -13677,17 +13657,17 @@
       <c r="C425" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D425" s="32"/>
-      <c r="E425" s="25"/>
-      <c r="F425" s="38"/>
+      <c r="D425" s="38"/>
+      <c r="E425" s="39"/>
+      <c r="F425" s="33"/>
       <c r="G425" s="23" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="H425" s="23" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="I425" s="23" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="J425" s="23"/>
     </row>
@@ -13698,17 +13678,17 @@
       <c r="C426" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D426" s="32"/>
-      <c r="E426" s="25"/>
-      <c r="F426" s="38"/>
+      <c r="D426" s="38"/>
+      <c r="E426" s="39"/>
+      <c r="F426" s="33"/>
       <c r="G426" s="23" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="H426" s="23" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="I426" s="23" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="J426" s="23"/>
     </row>
@@ -13719,17 +13699,17 @@
       <c r="C427" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D427" s="32"/>
-      <c r="E427" s="25"/>
-      <c r="F427" s="38"/>
+      <c r="D427" s="38"/>
+      <c r="E427" s="39"/>
+      <c r="F427" s="33"/>
       <c r="G427" s="23" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="H427" s="23" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="I427" s="23" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="J427" s="23"/>
     </row>
@@ -13740,17 +13720,17 @@
       <c r="C428" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D428" s="32"/>
-      <c r="E428" s="25"/>
-      <c r="F428" s="38"/>
+      <c r="D428" s="38"/>
+      <c r="E428" s="39"/>
+      <c r="F428" s="33"/>
       <c r="G428" s="23" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="H428" s="23" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="I428" s="23" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="J428" s="23"/>
     </row>
@@ -13761,17 +13741,17 @@
       <c r="C429" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D429" s="32"/>
-      <c r="E429" s="25"/>
-      <c r="F429" s="38"/>
+      <c r="D429" s="38"/>
+      <c r="E429" s="39"/>
+      <c r="F429" s="33"/>
       <c r="G429" s="23" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="H429" s="23" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="I429" s="23" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="J429" s="23"/>
     </row>
@@ -13782,17 +13762,17 @@
       <c r="C430" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D430" s="32"/>
-      <c r="E430" s="25"/>
-      <c r="F430" s="38"/>
+      <c r="D430" s="38"/>
+      <c r="E430" s="39"/>
+      <c r="F430" s="33"/>
       <c r="G430" s="23" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="H430" s="23" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="I430" s="23" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="J430" s="23"/>
     </row>
@@ -13803,17 +13783,17 @@
       <c r="C431" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D431" s="32"/>
-      <c r="E431" s="25"/>
-      <c r="F431" s="39"/>
+      <c r="D431" s="38"/>
+      <c r="E431" s="39"/>
+      <c r="F431" s="34"/>
       <c r="G431" s="23" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="H431" s="23" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="I431" s="23" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="J431" s="23"/>
     </row>
@@ -13824,19 +13804,19 @@
       <c r="C432" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D432" s="32"/>
-      <c r="E432" s="25"/>
-      <c r="F432" s="37" t="s">
+      <c r="D432" s="38"/>
+      <c r="E432" s="39"/>
+      <c r="F432" s="32" t="s">
+        <v>995</v>
+      </c>
+      <c r="G432" s="23" t="s">
+        <v>996</v>
+      </c>
+      <c r="H432" s="23" t="s">
+        <v>997</v>
+      </c>
+      <c r="I432" s="23" t="s">
         <v>998</v>
-      </c>
-      <c r="G432" s="23" t="s">
-        <v>999</v>
-      </c>
-      <c r="H432" s="23" t="s">
-        <v>1000</v>
-      </c>
-      <c r="I432" s="23" t="s">
-        <v>1001</v>
       </c>
       <c r="J432" s="23"/>
     </row>
@@ -13847,17 +13827,17 @@
       <c r="C433" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D433" s="32"/>
-      <c r="E433" s="25"/>
-      <c r="F433" s="38"/>
+      <c r="D433" s="38"/>
+      <c r="E433" s="39"/>
+      <c r="F433" s="33"/>
       <c r="G433" s="23" t="s">
+        <v>996</v>
+      </c>
+      <c r="H433" s="23" t="s">
         <v>999</v>
       </c>
-      <c r="H433" s="23" t="s">
-        <v>1002</v>
-      </c>
       <c r="I433" s="23" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="J433" s="23"/>
     </row>
@@ -13868,17 +13848,17 @@
       <c r="C434" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D434" s="32"/>
-      <c r="E434" s="25"/>
-      <c r="F434" s="38"/>
+      <c r="D434" s="38"/>
+      <c r="E434" s="39"/>
+      <c r="F434" s="33"/>
       <c r="G434" s="23" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="H434" s="23" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="I434" s="23" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="J434" s="23"/>
     </row>
@@ -13889,17 +13869,17 @@
       <c r="C435" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D435" s="32"/>
-      <c r="E435" s="25"/>
-      <c r="F435" s="38"/>
+      <c r="D435" s="38"/>
+      <c r="E435" s="39"/>
+      <c r="F435" s="33"/>
       <c r="G435" s="23" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="H435" s="23" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="I435" s="23" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="J435" s="23"/>
     </row>
@@ -13910,17 +13890,17 @@
       <c r="C436" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D436" s="32"/>
-      <c r="E436" s="25"/>
-      <c r="F436" s="38"/>
+      <c r="D436" s="38"/>
+      <c r="E436" s="39"/>
+      <c r="F436" s="33"/>
       <c r="G436" s="23" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="H436" s="23" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="I436" s="23" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="J436" s="23"/>
     </row>
@@ -13931,17 +13911,17 @@
       <c r="C437" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D437" s="32"/>
-      <c r="E437" s="25"/>
-      <c r="F437" s="38"/>
+      <c r="D437" s="38"/>
+      <c r="E437" s="39"/>
+      <c r="F437" s="33"/>
       <c r="G437" s="23" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="H437" s="23" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="I437" s="23" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="J437" s="23"/>
     </row>
@@ -13952,21 +13932,19 @@
       <c r="C438" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D438" s="32"/>
-      <c r="E438" s="25"/>
-      <c r="F438" s="39"/>
+      <c r="D438" s="38"/>
+      <c r="E438" s="39"/>
+      <c r="F438" s="34"/>
       <c r="G438" s="23" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="H438" s="23" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="I438" s="23" t="s">
-        <v>1015</v>
-      </c>
-      <c r="J438" s="23" t="s">
-        <v>1016</v>
-      </c>
+        <v>1012</v>
+      </c>
+      <c r="J438" s="23"/>
     </row>
     <row r="439" spans="2:10" ht="49.95" customHeight="1">
       <c r="B439" s="23">
@@ -13975,19 +13953,19 @@
       <c r="C439" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D439" s="32"/>
-      <c r="E439" s="25"/>
-      <c r="F439" s="37" t="s">
-        <v>1017</v>
+      <c r="D439" s="38"/>
+      <c r="E439" s="39"/>
+      <c r="F439" s="32" t="s">
+        <v>1013</v>
       </c>
       <c r="G439" s="23" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="H439" s="23" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="I439" s="23" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="J439" s="23"/>
     </row>
@@ -13998,17 +13976,17 @@
       <c r="C440" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D440" s="32"/>
-      <c r="E440" s="25"/>
-      <c r="F440" s="38"/>
+      <c r="D440" s="38"/>
+      <c r="E440" s="39"/>
+      <c r="F440" s="33"/>
       <c r="G440" s="23" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="H440" s="23" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="I440" s="23" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="J440" s="23"/>
     </row>
@@ -14019,17 +13997,17 @@
       <c r="C441" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D441" s="32"/>
-      <c r="E441" s="25"/>
-      <c r="F441" s="38"/>
+      <c r="D441" s="38"/>
+      <c r="E441" s="39"/>
+      <c r="F441" s="33"/>
       <c r="G441" s="23" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="H441" s="23" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="I441" s="23" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="J441" s="23"/>
     </row>
@@ -14040,17 +14018,17 @@
       <c r="C442" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D442" s="32"/>
-      <c r="E442" s="25"/>
-      <c r="F442" s="38"/>
+      <c r="D442" s="38"/>
+      <c r="E442" s="39"/>
+      <c r="F442" s="33"/>
       <c r="G442" s="23" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="H442" s="23" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="I442" s="23" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="J442" s="23"/>
     </row>
@@ -14061,17 +14039,17 @@
       <c r="C443" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D443" s="32"/>
-      <c r="E443" s="25"/>
-      <c r="F443" s="38"/>
+      <c r="D443" s="38"/>
+      <c r="E443" s="39"/>
+      <c r="F443" s="33"/>
       <c r="G443" s="23" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="H443" s="23" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="I443" s="23" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="J443" s="23"/>
     </row>
@@ -14082,17 +14060,17 @@
       <c r="C444" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D444" s="32"/>
-      <c r="E444" s="25"/>
-      <c r="F444" s="38"/>
+      <c r="D444" s="38"/>
+      <c r="E444" s="39"/>
+      <c r="F444" s="33"/>
       <c r="G444" s="23" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="H444" s="23" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="I444" s="23" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="J444" s="23"/>
     </row>
@@ -14103,17 +14081,17 @@
       <c r="C445" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D445" s="32"/>
-      <c r="E445" s="25"/>
-      <c r="F445" s="38"/>
+      <c r="D445" s="38"/>
+      <c r="E445" s="39"/>
+      <c r="F445" s="33"/>
       <c r="G445" s="23" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="H445" s="23" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="I445" s="23" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="J445" s="23"/>
     </row>
@@ -14124,17 +14102,17 @@
       <c r="C446" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D446" s="32"/>
-      <c r="E446" s="25"/>
-      <c r="F446" s="39"/>
+      <c r="D446" s="38"/>
+      <c r="E446" s="39"/>
+      <c r="F446" s="34"/>
       <c r="G446" s="23" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="H446" s="23" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="I446" s="23" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="J446" s="23"/>
     </row>
@@ -14145,19 +14123,19 @@
       <c r="C447" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D447" s="32"/>
-      <c r="E447" s="25"/>
-      <c r="F447" s="37" t="s">
-        <v>1042</v>
+      <c r="D447" s="38"/>
+      <c r="E447" s="39"/>
+      <c r="F447" s="32" t="s">
+        <v>1038</v>
       </c>
       <c r="G447" s="23" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="H447" s="23" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="I447" s="23" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="J447" s="23"/>
     </row>
@@ -14168,17 +14146,17 @@
       <c r="C448" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D448" s="32"/>
-      <c r="E448" s="25"/>
-      <c r="F448" s="38"/>
+      <c r="D448" s="38"/>
+      <c r="E448" s="39"/>
+      <c r="F448" s="33"/>
       <c r="G448" s="23" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="H448" s="23" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="I448" s="23" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="J448" s="23"/>
     </row>
@@ -14189,17 +14167,17 @@
       <c r="C449" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D449" s="32"/>
-      <c r="E449" s="25"/>
-      <c r="F449" s="39"/>
+      <c r="D449" s="38"/>
+      <c r="E449" s="39"/>
+      <c r="F449" s="34"/>
       <c r="G449" s="23" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="H449" s="23" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="I449" s="23" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="J449" s="23"/>
     </row>
@@ -14210,19 +14188,19 @@
       <c r="C450" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D450" s="32"/>
-      <c r="E450" s="25"/>
-      <c r="F450" s="37" t="s">
-        <v>1052</v>
+      <c r="D450" s="38"/>
+      <c r="E450" s="39"/>
+      <c r="F450" s="32" t="s">
+        <v>1048</v>
       </c>
       <c r="G450" s="23" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="H450" s="23" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="I450" s="23" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="J450" s="23"/>
     </row>
@@ -14233,17 +14211,17 @@
       <c r="C451" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D451" s="32"/>
-      <c r="E451" s="25"/>
-      <c r="F451" s="38"/>
+      <c r="D451" s="38"/>
+      <c r="E451" s="39"/>
+      <c r="F451" s="33"/>
       <c r="G451" s="23" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="H451" s="23" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="I451" s="23" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="J451" s="23"/>
     </row>
@@ -14254,17 +14232,17 @@
       <c r="C452" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D452" s="32"/>
-      <c r="E452" s="25"/>
-      <c r="F452" s="38"/>
+      <c r="D452" s="38"/>
+      <c r="E452" s="39"/>
+      <c r="F452" s="33"/>
       <c r="G452" s="23" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="H452" s="23" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="I452" s="23" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="J452" s="23"/>
     </row>
@@ -14275,17 +14253,17 @@
       <c r="C453" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D453" s="32"/>
-      <c r="E453" s="25"/>
-      <c r="F453" s="38"/>
+      <c r="D453" s="38"/>
+      <c r="E453" s="39"/>
+      <c r="F453" s="33"/>
       <c r="G453" s="23" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="H453" s="23" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="I453" s="23" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="J453" s="23"/>
     </row>
@@ -14296,17 +14274,17 @@
       <c r="C454" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D454" s="32"/>
-      <c r="E454" s="25"/>
-      <c r="F454" s="38"/>
+      <c r="D454" s="38"/>
+      <c r="E454" s="39"/>
+      <c r="F454" s="33"/>
       <c r="G454" s="23" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H454" s="23" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I454" s="23" t="s">
         <v>1062</v>
-      </c>
-      <c r="H454" s="23" t="s">
-        <v>1065</v>
-      </c>
-      <c r="I454" s="23" t="s">
-        <v>1066</v>
       </c>
       <c r="J454" s="23"/>
     </row>
@@ -14317,17 +14295,17 @@
       <c r="C455" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D455" s="32"/>
-      <c r="E455" s="25"/>
-      <c r="F455" s="38"/>
+      <c r="D455" s="38"/>
+      <c r="E455" s="39"/>
+      <c r="F455" s="33"/>
       <c r="G455" s="23" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="H455" s="23" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="I455" s="23" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="J455" s="23"/>
     </row>
@@ -14338,17 +14316,17 @@
       <c r="C456" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D456" s="32"/>
-      <c r="E456" s="25"/>
-      <c r="F456" s="38"/>
+      <c r="D456" s="38"/>
+      <c r="E456" s="39"/>
+      <c r="F456" s="33"/>
       <c r="G456" s="23" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="H456" s="23" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="I456" s="23" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="J456" s="23"/>
     </row>
@@ -14359,17 +14337,17 @@
       <c r="C457" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D457" s="32"/>
-      <c r="E457" s="25"/>
-      <c r="F457" s="38"/>
+      <c r="D457" s="38"/>
+      <c r="E457" s="39"/>
+      <c r="F457" s="33"/>
       <c r="G457" s="23" t="s">
+        <v>1065</v>
+      </c>
+      <c r="H457" s="23" t="s">
+        <v>1068</v>
+      </c>
+      <c r="I457" s="23" t="s">
         <v>1069</v>
-      </c>
-      <c r="H457" s="23" t="s">
-        <v>1072</v>
-      </c>
-      <c r="I457" s="23" t="s">
-        <v>1073</v>
       </c>
       <c r="J457" s="23"/>
     </row>
@@ -14380,17 +14358,17 @@
       <c r="C458" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D458" s="32"/>
-      <c r="E458" s="25"/>
-      <c r="F458" s="38"/>
+      <c r="D458" s="38"/>
+      <c r="E458" s="39"/>
+      <c r="F458" s="33"/>
       <c r="G458" s="23" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="H458" s="23" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="I458" s="23" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="J458" s="23"/>
     </row>
@@ -14401,17 +14379,17 @@
       <c r="C459" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D459" s="32"/>
-      <c r="E459" s="25"/>
-      <c r="F459" s="38"/>
+      <c r="D459" s="38"/>
+      <c r="E459" s="39"/>
+      <c r="F459" s="33"/>
       <c r="G459" s="23" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="H459" s="23" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="I459" s="23" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="J459" s="23"/>
     </row>
@@ -14422,17 +14400,17 @@
       <c r="C460" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D460" s="32"/>
-      <c r="E460" s="25"/>
-      <c r="F460" s="38"/>
+      <c r="D460" s="38"/>
+      <c r="E460" s="39"/>
+      <c r="F460" s="33"/>
       <c r="G460" s="23" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="H460" s="23" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="I460" s="23" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="J460" s="23"/>
     </row>
@@ -14443,17 +14421,17 @@
       <c r="C461" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D461" s="32"/>
-      <c r="E461" s="25"/>
-      <c r="F461" s="38"/>
+      <c r="D461" s="38"/>
+      <c r="E461" s="39"/>
+      <c r="F461" s="33"/>
       <c r="G461" s="23" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="H461" s="23" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="I461" s="23" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="J461" s="23"/>
     </row>
@@ -14464,17 +14442,17 @@
       <c r="C462" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D462" s="32"/>
-      <c r="E462" s="25"/>
-      <c r="F462" s="39"/>
+      <c r="D462" s="38"/>
+      <c r="E462" s="39"/>
+      <c r="F462" s="34"/>
       <c r="G462" s="23" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="H462" s="23" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="I462" s="23" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="J462" s="23"/>
     </row>
@@ -14485,19 +14463,19 @@
       <c r="C463" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D463" s="32"/>
-      <c r="E463" s="25"/>
-      <c r="F463" s="37" t="s">
-        <v>1087</v>
+      <c r="D463" s="38"/>
+      <c r="E463" s="39"/>
+      <c r="F463" s="32" t="s">
+        <v>1083</v>
       </c>
       <c r="G463" s="23" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="H463" s="23" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="I463" s="23" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="J463" s="23"/>
     </row>
@@ -14508,17 +14486,17 @@
       <c r="C464" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D464" s="32"/>
-      <c r="E464" s="25"/>
-      <c r="F464" s="38"/>
+      <c r="D464" s="38"/>
+      <c r="E464" s="39"/>
+      <c r="F464" s="33"/>
       <c r="G464" s="23" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="H464" s="23" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="I464" s="23" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="J464" s="23"/>
     </row>
@@ -14529,17 +14507,17 @@
       <c r="C465" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D465" s="32"/>
-      <c r="E465" s="25"/>
-      <c r="F465" s="38"/>
+      <c r="D465" s="38"/>
+      <c r="E465" s="39"/>
+      <c r="F465" s="33"/>
       <c r="G465" s="23" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="H465" s="23" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="I465" s="23" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="J465" s="23"/>
     </row>
@@ -14550,17 +14528,17 @@
       <c r="C466" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D466" s="32"/>
-      <c r="E466" s="25"/>
-      <c r="F466" s="38"/>
+      <c r="D466" s="38"/>
+      <c r="E466" s="39"/>
+      <c r="F466" s="33"/>
       <c r="G466" s="23" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="H466" s="23" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="I466" s="23" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="J466" s="23"/>
     </row>
@@ -14571,17 +14549,17 @@
       <c r="C467" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D467" s="32"/>
-      <c r="E467" s="25"/>
-      <c r="F467" s="38"/>
+      <c r="D467" s="38"/>
+      <c r="E467" s="39"/>
+      <c r="F467" s="33"/>
       <c r="G467" s="23" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="H467" s="23" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="I467" s="23" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="J467" s="23"/>
     </row>
@@ -14592,17 +14570,17 @@
       <c r="C468" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D468" s="32"/>
-      <c r="E468" s="25"/>
-      <c r="F468" s="38"/>
+      <c r="D468" s="38"/>
+      <c r="E468" s="39"/>
+      <c r="F468" s="33"/>
       <c r="G468" s="23" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="H468" s="23" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="I468" s="23" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="J468" s="23"/>
     </row>
@@ -14613,17 +14591,17 @@
       <c r="C469" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D469" s="32"/>
-      <c r="E469" s="25"/>
-      <c r="F469" s="38"/>
+      <c r="D469" s="38"/>
+      <c r="E469" s="39"/>
+      <c r="F469" s="33"/>
       <c r="G469" s="23" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="H469" s="23" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="I469" s="23" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="J469" s="23"/>
     </row>
@@ -14634,17 +14612,17 @@
       <c r="C470" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D470" s="32"/>
-      <c r="E470" s="25"/>
-      <c r="F470" s="38"/>
+      <c r="D470" s="38"/>
+      <c r="E470" s="39"/>
+      <c r="F470" s="33"/>
       <c r="G470" s="23" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="H470" s="23" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="I470" s="23" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="J470" s="23"/>
     </row>
@@ -14655,17 +14633,17 @@
       <c r="C471" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D471" s="32"/>
-      <c r="E471" s="25"/>
-      <c r="F471" s="38"/>
+      <c r="D471" s="38"/>
+      <c r="E471" s="39"/>
+      <c r="F471" s="33"/>
       <c r="G471" s="23" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="H471" s="23" t="s">
-        <v>1113</v>
+        <v>1109</v>
       </c>
       <c r="I471" s="23" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="J471" s="23"/>
     </row>
@@ -14676,17 +14654,17 @@
       <c r="C472" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D472" s="32"/>
-      <c r="E472" s="25"/>
-      <c r="F472" s="39"/>
+      <c r="D472" s="38"/>
+      <c r="E472" s="39"/>
+      <c r="F472" s="34"/>
       <c r="G472" s="23" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="H472" s="23" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="I472" s="23" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="J472" s="23"/>
     </row>
@@ -14697,19 +14675,19 @@
       <c r="C473" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D473" s="32"/>
-      <c r="E473" s="25"/>
-      <c r="F473" s="37" t="s">
-        <v>1117</v>
+      <c r="D473" s="38"/>
+      <c r="E473" s="39"/>
+      <c r="F473" s="32" t="s">
+        <v>1113</v>
       </c>
       <c r="G473" s="23" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="H473" s="23" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="I473" s="23" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="J473" s="23"/>
     </row>
@@ -14720,17 +14698,17 @@
       <c r="C474" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D474" s="32"/>
-      <c r="E474" s="25"/>
-      <c r="F474" s="38"/>
+      <c r="D474" s="38"/>
+      <c r="E474" s="39"/>
+      <c r="F474" s="33"/>
       <c r="G474" s="23" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="H474" s="23" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="I474" s="23" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="J474" s="23"/>
     </row>
@@ -14741,65 +14719,22 @@
       <c r="C475" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D475" s="32"/>
-      <c r="E475" s="25"/>
-      <c r="F475" s="39"/>
+      <c r="D475" s="38"/>
+      <c r="E475" s="39"/>
+      <c r="F475" s="34"/>
       <c r="G475" s="23" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="H475" s="23" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="I475" s="23" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="J475" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="F473:F475"/>
-    <mergeCell ref="F419:F431"/>
-    <mergeCell ref="F432:F438"/>
-    <mergeCell ref="F439:F446"/>
-    <mergeCell ref="F447:F449"/>
-    <mergeCell ref="F450:F462"/>
-    <mergeCell ref="F463:F472"/>
-    <mergeCell ref="F244:F247"/>
-    <mergeCell ref="F248:F251"/>
-    <mergeCell ref="F252:F257"/>
-    <mergeCell ref="F258:F262"/>
-    <mergeCell ref="F263:F406"/>
-    <mergeCell ref="F407:F418"/>
-    <mergeCell ref="F210:F215"/>
-    <mergeCell ref="F216:F217"/>
-    <mergeCell ref="F218:F223"/>
-    <mergeCell ref="F224:F233"/>
-    <mergeCell ref="F234:F241"/>
-    <mergeCell ref="F242:F243"/>
-    <mergeCell ref="F176:F179"/>
-    <mergeCell ref="F180:F181"/>
-    <mergeCell ref="F182:F187"/>
-    <mergeCell ref="F188:F189"/>
-    <mergeCell ref="F190:F207"/>
-    <mergeCell ref="F208:F209"/>
-    <mergeCell ref="F144:F147"/>
-    <mergeCell ref="F148:F149"/>
-    <mergeCell ref="F150:F155"/>
-    <mergeCell ref="F156:F161"/>
-    <mergeCell ref="F162:F171"/>
-    <mergeCell ref="F172:F175"/>
-    <mergeCell ref="F100:F115"/>
-    <mergeCell ref="F116:F117"/>
-    <mergeCell ref="F118:F129"/>
-    <mergeCell ref="F130:F131"/>
-    <mergeCell ref="F132:F141"/>
-    <mergeCell ref="F142:F143"/>
-    <mergeCell ref="F41:F49"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="F52:F75"/>
-    <mergeCell ref="F76:F77"/>
-    <mergeCell ref="F78:F97"/>
-    <mergeCell ref="F98:F99"/>
     <mergeCell ref="D6:D475"/>
     <mergeCell ref="E6:E33"/>
     <mergeCell ref="E34:E475"/>
@@ -14810,6 +14745,49 @@
     <mergeCell ref="F29:F33"/>
     <mergeCell ref="F34:F37"/>
     <mergeCell ref="F38:F40"/>
+    <mergeCell ref="F142:F143"/>
+    <mergeCell ref="F41:F49"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="F52:F75"/>
+    <mergeCell ref="F76:F77"/>
+    <mergeCell ref="F78:F97"/>
+    <mergeCell ref="F98:F99"/>
+    <mergeCell ref="F100:F115"/>
+    <mergeCell ref="F116:F117"/>
+    <mergeCell ref="F118:F129"/>
+    <mergeCell ref="F130:F131"/>
+    <mergeCell ref="F132:F141"/>
+    <mergeCell ref="F208:F209"/>
+    <mergeCell ref="F144:F147"/>
+    <mergeCell ref="F148:F149"/>
+    <mergeCell ref="F150:F155"/>
+    <mergeCell ref="F156:F161"/>
+    <mergeCell ref="F162:F171"/>
+    <mergeCell ref="F172:F175"/>
+    <mergeCell ref="F176:F179"/>
+    <mergeCell ref="F180:F181"/>
+    <mergeCell ref="F182:F187"/>
+    <mergeCell ref="F188:F189"/>
+    <mergeCell ref="F190:F207"/>
+    <mergeCell ref="F407:F418"/>
+    <mergeCell ref="F210:F215"/>
+    <mergeCell ref="F216:F217"/>
+    <mergeCell ref="F218:F223"/>
+    <mergeCell ref="F224:F233"/>
+    <mergeCell ref="F234:F241"/>
+    <mergeCell ref="F242:F243"/>
+    <mergeCell ref="F244:F247"/>
+    <mergeCell ref="F248:F251"/>
+    <mergeCell ref="F252:F257"/>
+    <mergeCell ref="F258:F262"/>
+    <mergeCell ref="F263:F406"/>
+    <mergeCell ref="F473:F475"/>
+    <mergeCell ref="F419:F431"/>
+    <mergeCell ref="F432:F438"/>
+    <mergeCell ref="F439:F446"/>
+    <mergeCell ref="F447:F449"/>
+    <mergeCell ref="F450:F462"/>
+    <mergeCell ref="F463:F472"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">

--- a/TC/나이트크로우_일반제작_TC.xlsx
+++ b/TC/나이트크로우_일반제작_TC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\leegm0430\01_포토폴리오\TC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{485CA0C0-1BE4-447F-9C65-6EF55A5483A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263C915A-8427-4302-A492-9E2D3C2D2A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3840,13 +3840,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3858,10 +3855,13 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4772,13 +4772,13 @@
       <c r="C6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="38" t="s">
+      <c r="E6" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="F6" s="32" t="s">
         <v>16</v>
       </c>
       <c r="G6" s="23" t="s">
@@ -4793,13 +4793,15 @@
       <c r="J6" s="23"/>
     </row>
     <row r="7" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B7" s="22"/>
+      <c r="B7" s="22">
+        <v>2</v>
+      </c>
       <c r="C7" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
       <c r="G7" s="23" t="s">
         <v>20</v>
       </c>
@@ -4812,13 +4814,15 @@
       <c r="J7" s="23"/>
     </row>
     <row r="8" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B8" s="22"/>
+      <c r="B8" s="22">
+        <v>3</v>
+      </c>
       <c r="C8" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
       <c r="G8" s="22" t="s">
         <v>22</v>
       </c>
@@ -4831,13 +4835,15 @@
       <c r="J8" s="23"/>
     </row>
     <row r="9" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B9" s="22"/>
+      <c r="B9" s="22">
+        <v>4</v>
+      </c>
       <c r="C9" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
       <c r="G9" s="22" t="s">
         <v>25</v>
       </c>
@@ -4851,14 +4857,14 @@
     </row>
     <row r="10" spans="2:10" ht="49.95" customHeight="1">
       <c r="B10" s="22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C10" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="39" t="s">
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="33" t="s">
         <v>27</v>
       </c>
       <c r="G10" s="22" t="s">
@@ -4874,14 +4880,14 @@
     </row>
     <row r="11" spans="2:10" ht="49.95" customHeight="1">
       <c r="B11" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C11" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="39"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="33"/>
       <c r="G11" s="22" t="s">
         <v>28</v>
       </c>
@@ -4895,14 +4901,14 @@
     </row>
     <row r="12" spans="2:10" ht="49.95" customHeight="1">
       <c r="B12" s="22">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C12" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="39"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="33"/>
       <c r="G12" s="22" t="s">
         <v>28</v>
       </c>
@@ -4916,14 +4922,14 @@
     </row>
     <row r="13" spans="2:10" ht="49.95" customHeight="1">
       <c r="B13" s="22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C13" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="39"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="33"/>
       <c r="G13" s="22" t="s">
         <v>28</v>
       </c>
@@ -4937,14 +4943,14 @@
     </row>
     <row r="14" spans="2:10" ht="49.95" customHeight="1">
       <c r="B14" s="22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C14" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="39"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="33"/>
       <c r="G14" s="22" t="s">
         <v>28</v>
       </c>
@@ -4958,14 +4964,14 @@
     </row>
     <row r="15" spans="2:10" ht="49.95" customHeight="1">
       <c r="B15" s="22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C15" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="39" t="s">
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="33" t="s">
         <v>40</v>
       </c>
       <c r="G15" s="22" t="s">
@@ -4981,14 +4987,14 @@
     </row>
     <row r="16" spans="2:10" ht="49.95" customHeight="1">
       <c r="B16" s="22">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="39"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="33"/>
       <c r="G16" s="22" t="s">
         <v>44</v>
       </c>
@@ -5002,14 +5008,14 @@
     </row>
     <row r="17" spans="2:10" ht="49.95" customHeight="1">
       <c r="B17" s="22">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C17" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="39"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="33"/>
       <c r="G17" s="22" t="s">
         <v>47</v>
       </c>
@@ -5023,14 +5029,14 @@
     </row>
     <row r="18" spans="2:10" ht="49.95" customHeight="1">
       <c r="B18" s="22">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C18" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="39"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="33"/>
       <c r="G18" s="22" t="s">
         <v>44</v>
       </c>
@@ -5044,14 +5050,14 @@
     </row>
     <row r="19" spans="2:10" ht="49.95" customHeight="1">
       <c r="B19" s="22">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C19" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="39" t="s">
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="33" t="s">
         <v>27</v>
       </c>
       <c r="G19" s="22" t="s">
@@ -5067,14 +5073,14 @@
     </row>
     <row r="20" spans="2:10" ht="49.95" customHeight="1">
       <c r="B20" s="22">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C20" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="39"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="33"/>
       <c r="G20" s="22" t="s">
         <v>28</v>
       </c>
@@ -5088,14 +5094,14 @@
     </row>
     <row r="21" spans="2:10" ht="49.95" customHeight="1">
       <c r="B21" s="22">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C21" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="39"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="33"/>
       <c r="G21" s="22" t="s">
         <v>28</v>
       </c>
@@ -5109,14 +5115,14 @@
     </row>
     <row r="22" spans="2:10" ht="49.95" customHeight="1">
       <c r="B22" s="22">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C22" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="39"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="33"/>
       <c r="G22" s="22" t="s">
         <v>28</v>
       </c>
@@ -5130,14 +5136,14 @@
     </row>
     <row r="23" spans="2:10" ht="49.95" customHeight="1">
       <c r="B23" s="22">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C23" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="39"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="33"/>
       <c r="G23" s="22" t="s">
         <v>60</v>
       </c>
@@ -5151,14 +5157,14 @@
     </row>
     <row r="24" spans="2:10" ht="49.95" customHeight="1">
       <c r="B24" s="22">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C24" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="39"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="33"/>
       <c r="G24" s="22" t="s">
         <v>28</v>
       </c>
@@ -5172,14 +5178,14 @@
     </row>
     <row r="25" spans="2:10" ht="49.95" customHeight="1">
       <c r="B25" s="22">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C25" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="39"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="33"/>
       <c r="G25" s="22" t="s">
         <v>28</v>
       </c>
@@ -5193,14 +5199,14 @@
     </row>
     <row r="26" spans="2:10" ht="49.95" customHeight="1">
       <c r="B26" s="22">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C26" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="39"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="33"/>
       <c r="G26" s="22" t="s">
         <v>28</v>
       </c>
@@ -5213,13 +5219,15 @@
       <c r="J26" s="22"/>
     </row>
     <row r="27" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B27" s="22"/>
+      <c r="B27" s="22">
+        <v>22</v>
+      </c>
       <c r="C27" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="39"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="33"/>
       <c r="G27" s="22" t="s">
         <v>28</v>
       </c>
@@ -5232,13 +5240,15 @@
       <c r="J27" s="24"/>
     </row>
     <row r="28" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B28" s="22"/>
+      <c r="B28" s="22">
+        <v>23</v>
+      </c>
       <c r="C28" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="39"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="33"/>
       <c r="G28" s="22" t="s">
         <v>28</v>
       </c>
@@ -5251,13 +5261,15 @@
       <c r="J28" s="24"/>
     </row>
     <row r="29" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B29" s="22"/>
+      <c r="B29" s="22">
+        <v>24</v>
+      </c>
       <c r="C29" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="35" t="s">
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="34" t="s">
         <v>74</v>
       </c>
       <c r="G29" s="22" t="s">
@@ -5272,13 +5284,15 @@
       <c r="J29" s="22"/>
     </row>
     <row r="30" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B30" s="22"/>
+      <c r="B30" s="22">
+        <v>25</v>
+      </c>
       <c r="C30" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="36"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="35"/>
       <c r="G30" s="22" t="s">
         <v>28</v>
       </c>
@@ -5291,13 +5305,15 @@
       <c r="J30" s="22"/>
     </row>
     <row r="31" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B31" s="22"/>
+      <c r="B31" s="22">
+        <v>26</v>
+      </c>
       <c r="C31" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="38"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="36"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="35"/>
       <c r="G31" s="22" t="s">
         <v>79</v>
       </c>
@@ -5310,13 +5326,15 @@
       <c r="J31" s="22"/>
     </row>
     <row r="32" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B32" s="22"/>
+      <c r="B32" s="22">
+        <v>27</v>
+      </c>
       <c r="C32" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="36"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="35"/>
       <c r="G32" s="22" t="s">
         <v>82</v>
       </c>
@@ -5329,13 +5347,15 @@
       <c r="J32" s="22"/>
     </row>
     <row r="33" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B33" s="22"/>
+      <c r="B33" s="22">
+        <v>28</v>
+      </c>
       <c r="C33" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="38"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="37"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="36"/>
       <c r="G33" s="22" t="s">
         <v>84</v>
       </c>
@@ -5349,16 +5369,16 @@
     </row>
     <row r="34" spans="2:10" ht="49.95" customHeight="1">
       <c r="B34" s="22">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C34" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="38"/>
-      <c r="E34" s="39" t="s">
+      <c r="D34" s="32"/>
+      <c r="E34" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="F34" s="35" t="s">
+      <c r="F34" s="34" t="s">
         <v>86</v>
       </c>
       <c r="G34" s="22" t="s">
@@ -5374,14 +5394,14 @@
     </row>
     <row r="35" spans="2:10" ht="49.95" customHeight="1">
       <c r="B35" s="22">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C35" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D35" s="38"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="36"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="35"/>
       <c r="G35" s="22" t="s">
         <v>87</v>
       </c>
@@ -5395,14 +5415,14 @@
     </row>
     <row r="36" spans="2:10" ht="49.95" customHeight="1">
       <c r="B36" s="22">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C36" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="38"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="36"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="35"/>
       <c r="G36" s="22" t="s">
         <v>87</v>
       </c>
@@ -5416,14 +5436,14 @@
     </row>
     <row r="37" spans="2:10" ht="49.95" customHeight="1">
       <c r="B37" s="22">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C37" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D37" s="38"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="37"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="36"/>
       <c r="G37" s="22" t="s">
         <v>87</v>
       </c>
@@ -5437,14 +5457,14 @@
     </row>
     <row r="38" spans="2:10" ht="49.95" customHeight="1">
       <c r="B38" s="22">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C38" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D38" s="38"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="35" t="s">
+      <c r="D38" s="32"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="34" t="s">
         <v>27</v>
       </c>
       <c r="G38" s="22" t="s">
@@ -5460,14 +5480,14 @@
     </row>
     <row r="39" spans="2:10" ht="49.95" customHeight="1">
       <c r="B39" s="22">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C39" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="38"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="36"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="35"/>
       <c r="G39" s="22" t="s">
         <v>28</v>
       </c>
@@ -5481,14 +5501,14 @@
     </row>
     <row r="40" spans="2:10" ht="49.95" customHeight="1">
       <c r="B40" s="22">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C40" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D40" s="38"/>
-      <c r="E40" s="39"/>
-      <c r="F40" s="37"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="36"/>
       <c r="G40" s="22" t="s">
         <v>100</v>
       </c>
@@ -5504,14 +5524,14 @@
     </row>
     <row r="41" spans="2:10" ht="49.95" customHeight="1">
       <c r="B41" s="22">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C41" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D41" s="38"/>
-      <c r="E41" s="39"/>
-      <c r="F41" s="35" t="s">
+      <c r="D41" s="32"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="34" t="s">
         <v>104</v>
       </c>
       <c r="G41" s="22" t="s">
@@ -5527,14 +5547,14 @@
     </row>
     <row r="42" spans="2:10" ht="49.95" customHeight="1">
       <c r="B42" s="22">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C42" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D42" s="38"/>
-      <c r="E42" s="39"/>
-      <c r="F42" s="36"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="35"/>
       <c r="G42" s="22" t="s">
         <v>28</v>
       </c>
@@ -5548,14 +5568,14 @@
     </row>
     <row r="43" spans="2:10" ht="49.95" customHeight="1">
       <c r="B43" s="22">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C43" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D43" s="38"/>
-      <c r="E43" s="39"/>
-      <c r="F43" s="36"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="33"/>
+      <c r="F43" s="35"/>
       <c r="G43" s="22" t="s">
         <v>28</v>
       </c>
@@ -5569,14 +5589,14 @@
     </row>
     <row r="44" spans="2:10" ht="49.95" customHeight="1">
       <c r="B44" s="22">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C44" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D44" s="38"/>
-      <c r="E44" s="39"/>
-      <c r="F44" s="36"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="33"/>
+      <c r="F44" s="35"/>
       <c r="G44" s="22" t="s">
         <v>28</v>
       </c>
@@ -5590,14 +5610,14 @@
     </row>
     <row r="45" spans="2:10" ht="49.95" customHeight="1">
       <c r="B45" s="22">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C45" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D45" s="38"/>
-      <c r="E45" s="39"/>
-      <c r="F45" s="36"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="33"/>
+      <c r="F45" s="35"/>
       <c r="G45" s="22" t="s">
         <v>28</v>
       </c>
@@ -5611,14 +5631,14 @@
     </row>
     <row r="46" spans="2:10" ht="49.95" customHeight="1">
       <c r="B46" s="22">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C46" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D46" s="38"/>
-      <c r="E46" s="39"/>
-      <c r="F46" s="36"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="35"/>
       <c r="G46" s="22" t="s">
         <v>28</v>
       </c>
@@ -5632,14 +5652,14 @@
     </row>
     <row r="47" spans="2:10" ht="49.95" customHeight="1">
       <c r="B47" s="22">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C47" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D47" s="38"/>
-      <c r="E47" s="39"/>
-      <c r="F47" s="36"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="33"/>
+      <c r="F47" s="35"/>
       <c r="G47" s="22" t="s">
         <v>114</v>
       </c>
@@ -5653,14 +5673,14 @@
     </row>
     <row r="48" spans="2:10" ht="49.95" customHeight="1">
       <c r="B48" s="22">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C48" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D48" s="38"/>
-      <c r="E48" s="39"/>
-      <c r="F48" s="36"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="33"/>
+      <c r="F48" s="35"/>
       <c r="G48" s="22" t="s">
         <v>116</v>
       </c>
@@ -5674,14 +5694,14 @@
     </row>
     <row r="49" spans="2:10" ht="49.95" customHeight="1">
       <c r="B49" s="22">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C49" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D49" s="38"/>
-      <c r="E49" s="39"/>
-      <c r="F49" s="37"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="33"/>
+      <c r="F49" s="36"/>
       <c r="G49" s="22" t="s">
         <v>119</v>
       </c>
@@ -5695,14 +5715,14 @@
     </row>
     <row r="50" spans="2:10" ht="49.95" customHeight="1">
       <c r="B50" s="22">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C50" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D50" s="38"/>
-      <c r="E50" s="39"/>
-      <c r="F50" s="35" t="s">
+      <c r="D50" s="32"/>
+      <c r="E50" s="33"/>
+      <c r="F50" s="34" t="s">
         <v>122</v>
       </c>
       <c r="G50" s="22" t="s">
@@ -5718,14 +5738,14 @@
     </row>
     <row r="51" spans="2:10" ht="49.95" customHeight="1">
       <c r="B51" s="22">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C51" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D51" s="38"/>
-      <c r="E51" s="39"/>
-      <c r="F51" s="37"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="33"/>
+      <c r="F51" s="36"/>
       <c r="G51" s="22" t="s">
         <v>126</v>
       </c>
@@ -5739,14 +5759,14 @@
     </row>
     <row r="52" spans="2:10" ht="49.95" customHeight="1">
       <c r="B52" s="22">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C52" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D52" s="38"/>
-      <c r="E52" s="39"/>
-      <c r="F52" s="35" t="s">
+      <c r="D52" s="32"/>
+      <c r="E52" s="33"/>
+      <c r="F52" s="34" t="s">
         <v>129</v>
       </c>
       <c r="G52" s="22" t="s">
@@ -5762,14 +5782,14 @@
     </row>
     <row r="53" spans="2:10" ht="49.95" customHeight="1">
       <c r="B53" s="22">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C53" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D53" s="38"/>
-      <c r="E53" s="39"/>
-      <c r="F53" s="36"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="33"/>
+      <c r="F53" s="35"/>
       <c r="G53" s="22" t="s">
         <v>130</v>
       </c>
@@ -5783,14 +5803,14 @@
     </row>
     <row r="54" spans="2:10" ht="49.95" customHeight="1">
       <c r="B54" s="22">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C54" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D54" s="38"/>
-      <c r="E54" s="39"/>
-      <c r="F54" s="36"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="33"/>
+      <c r="F54" s="35"/>
       <c r="G54" s="22" t="s">
         <v>130</v>
       </c>
@@ -5804,14 +5824,14 @@
     </row>
     <row r="55" spans="2:10" ht="49.95" customHeight="1">
       <c r="B55" s="22">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C55" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D55" s="38"/>
-      <c r="E55" s="39"/>
-      <c r="F55" s="36"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="33"/>
+      <c r="F55" s="35"/>
       <c r="G55" s="22" t="s">
         <v>130</v>
       </c>
@@ -5825,14 +5845,14 @@
     </row>
     <row r="56" spans="2:10" ht="49.95" customHeight="1">
       <c r="B56" s="22">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C56" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D56" s="38"/>
-      <c r="E56" s="39"/>
-      <c r="F56" s="36"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="33"/>
+      <c r="F56" s="35"/>
       <c r="G56" s="22" t="s">
         <v>130</v>
       </c>
@@ -5846,14 +5866,14 @@
     </row>
     <row r="57" spans="2:10" ht="49.95" customHeight="1">
       <c r="B57" s="22">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C57" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D57" s="38"/>
-      <c r="E57" s="39"/>
-      <c r="F57" s="36"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="33"/>
+      <c r="F57" s="35"/>
       <c r="G57" s="22" t="s">
         <v>130</v>
       </c>
@@ -5867,14 +5887,14 @@
     </row>
     <row r="58" spans="2:10" ht="49.95" customHeight="1">
       <c r="B58" s="22">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C58" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D58" s="38"/>
-      <c r="E58" s="39"/>
-      <c r="F58" s="36"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="33"/>
+      <c r="F58" s="35"/>
       <c r="G58" s="22" t="s">
         <v>130</v>
       </c>
@@ -5888,14 +5908,14 @@
     </row>
     <row r="59" spans="2:10" ht="49.95" customHeight="1">
       <c r="B59" s="22">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C59" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D59" s="38"/>
-      <c r="E59" s="39"/>
-      <c r="F59" s="36"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="33"/>
+      <c r="F59" s="35"/>
       <c r="G59" s="22" t="s">
         <v>130</v>
       </c>
@@ -5909,14 +5929,14 @@
     </row>
     <row r="60" spans="2:10" ht="49.95" customHeight="1">
       <c r="B60" s="22">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C60" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D60" s="38"/>
-      <c r="E60" s="39"/>
-      <c r="F60" s="36"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="33"/>
+      <c r="F60" s="35"/>
       <c r="G60" s="22" t="s">
         <v>130</v>
       </c>
@@ -5930,14 +5950,14 @@
     </row>
     <row r="61" spans="2:10" ht="49.95" customHeight="1">
       <c r="B61" s="22">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C61" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D61" s="38"/>
-      <c r="E61" s="39"/>
-      <c r="F61" s="36"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="33"/>
+      <c r="F61" s="35"/>
       <c r="G61" s="22" t="s">
         <v>130</v>
       </c>
@@ -5951,14 +5971,14 @@
     </row>
     <row r="62" spans="2:10" ht="49.95" customHeight="1">
       <c r="B62" s="22">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C62" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D62" s="38"/>
-      <c r="E62" s="39"/>
-      <c r="F62" s="36"/>
+      <c r="D62" s="32"/>
+      <c r="E62" s="33"/>
+      <c r="F62" s="35"/>
       <c r="G62" s="22" t="s">
         <v>130</v>
       </c>
@@ -5972,14 +5992,14 @@
     </row>
     <row r="63" spans="2:10" ht="49.95" customHeight="1">
       <c r="B63" s="22">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C63" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D63" s="38"/>
-      <c r="E63" s="39"/>
-      <c r="F63" s="36"/>
+      <c r="D63" s="32"/>
+      <c r="E63" s="33"/>
+      <c r="F63" s="35"/>
       <c r="G63" s="22" t="s">
         <v>130</v>
       </c>
@@ -5993,14 +6013,14 @@
     </row>
     <row r="64" spans="2:10" ht="49.95" customHeight="1">
       <c r="B64" s="22">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C64" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D64" s="38"/>
-      <c r="E64" s="39"/>
-      <c r="F64" s="36"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="33"/>
+      <c r="F64" s="35"/>
       <c r="G64" s="22" t="s">
         <v>130</v>
       </c>
@@ -6014,14 +6034,14 @@
     </row>
     <row r="65" spans="2:10" ht="49.95" customHeight="1">
       <c r="B65" s="22">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C65" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D65" s="38"/>
-      <c r="E65" s="39"/>
-      <c r="F65" s="36"/>
+      <c r="D65" s="32"/>
+      <c r="E65" s="33"/>
+      <c r="F65" s="35"/>
       <c r="G65" s="22" t="s">
         <v>130</v>
       </c>
@@ -6035,14 +6055,14 @@
     </row>
     <row r="66" spans="2:10" ht="49.95" customHeight="1">
       <c r="B66" s="22">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C66" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D66" s="38"/>
-      <c r="E66" s="39"/>
-      <c r="F66" s="36"/>
+      <c r="D66" s="32"/>
+      <c r="E66" s="33"/>
+      <c r="F66" s="35"/>
       <c r="G66" s="22" t="s">
         <v>130</v>
       </c>
@@ -6056,14 +6076,14 @@
     </row>
     <row r="67" spans="2:10" ht="49.95" customHeight="1">
       <c r="B67" s="22">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C67" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D67" s="38"/>
-      <c r="E67" s="39"/>
-      <c r="F67" s="36"/>
+      <c r="D67" s="32"/>
+      <c r="E67" s="33"/>
+      <c r="F67" s="35"/>
       <c r="G67" s="22" t="s">
         <v>130</v>
       </c>
@@ -6077,14 +6097,14 @@
     </row>
     <row r="68" spans="2:10" ht="49.95" customHeight="1">
       <c r="B68" s="22">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C68" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D68" s="38"/>
-      <c r="E68" s="39"/>
-      <c r="F68" s="36"/>
+      <c r="D68" s="32"/>
+      <c r="E68" s="33"/>
+      <c r="F68" s="35"/>
       <c r="G68" s="22" t="s">
         <v>130</v>
       </c>
@@ -6098,14 +6118,14 @@
     </row>
     <row r="69" spans="2:10" ht="49.95" customHeight="1">
       <c r="B69" s="22">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C69" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D69" s="38"/>
-      <c r="E69" s="39"/>
-      <c r="F69" s="36"/>
+      <c r="D69" s="32"/>
+      <c r="E69" s="33"/>
+      <c r="F69" s="35"/>
       <c r="G69" s="22" t="s">
         <v>130</v>
       </c>
@@ -6119,14 +6139,14 @@
     </row>
     <row r="70" spans="2:10" ht="49.95" customHeight="1">
       <c r="B70" s="22">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C70" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D70" s="38"/>
-      <c r="E70" s="39"/>
-      <c r="F70" s="36"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="33"/>
+      <c r="F70" s="35"/>
       <c r="G70" s="22" t="s">
         <v>130</v>
       </c>
@@ -6140,14 +6160,14 @@
     </row>
     <row r="71" spans="2:10" ht="49.95" customHeight="1">
       <c r="B71" s="22">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C71" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D71" s="38"/>
-      <c r="E71" s="39"/>
-      <c r="F71" s="36"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="33"/>
+      <c r="F71" s="35"/>
       <c r="G71" s="22" t="s">
         <v>130</v>
       </c>
@@ -6161,14 +6181,14 @@
     </row>
     <row r="72" spans="2:10" ht="49.95" customHeight="1">
       <c r="B72" s="22">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C72" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D72" s="38"/>
-      <c r="E72" s="39"/>
-      <c r="F72" s="36"/>
+      <c r="D72" s="32"/>
+      <c r="E72" s="33"/>
+      <c r="F72" s="35"/>
       <c r="G72" s="22" t="s">
         <v>130</v>
       </c>
@@ -6182,14 +6202,14 @@
     </row>
     <row r="73" spans="2:10" ht="49.95" customHeight="1">
       <c r="B73" s="22">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C73" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D73" s="38"/>
-      <c r="E73" s="39"/>
-      <c r="F73" s="36"/>
+      <c r="D73" s="32"/>
+      <c r="E73" s="33"/>
+      <c r="F73" s="35"/>
       <c r="G73" s="22" t="s">
         <v>130</v>
       </c>
@@ -6203,14 +6223,14 @@
     </row>
     <row r="74" spans="2:10" ht="49.95" customHeight="1">
       <c r="B74" s="22">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C74" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D74" s="38"/>
-      <c r="E74" s="39"/>
-      <c r="F74" s="36"/>
+      <c r="D74" s="32"/>
+      <c r="E74" s="33"/>
+      <c r="F74" s="35"/>
       <c r="G74" s="22" t="s">
         <v>130</v>
       </c>
@@ -6224,14 +6244,14 @@
     </row>
     <row r="75" spans="2:10" ht="49.95" customHeight="1">
       <c r="B75" s="22">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C75" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D75" s="38"/>
-      <c r="E75" s="39"/>
-      <c r="F75" s="37"/>
+      <c r="D75" s="32"/>
+      <c r="E75" s="33"/>
+      <c r="F75" s="36"/>
       <c r="G75" s="22" t="s">
         <v>130</v>
       </c>
@@ -6245,14 +6265,14 @@
     </row>
     <row r="76" spans="2:10" ht="49.95" customHeight="1">
       <c r="B76" s="22">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C76" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D76" s="38"/>
-      <c r="E76" s="39"/>
-      <c r="F76" s="35" t="s">
+      <c r="D76" s="32"/>
+      <c r="E76" s="33"/>
+      <c r="F76" s="34" t="s">
         <v>122</v>
       </c>
       <c r="G76" s="22" t="s">
@@ -6268,14 +6288,14 @@
     </row>
     <row r="77" spans="2:10" ht="49.95" customHeight="1">
       <c r="B77" s="22">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C77" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D77" s="38"/>
-      <c r="E77" s="39"/>
-      <c r="F77" s="37"/>
+      <c r="D77" s="32"/>
+      <c r="E77" s="33"/>
+      <c r="F77" s="36"/>
       <c r="G77" s="22" t="s">
         <v>182</v>
       </c>
@@ -6289,14 +6309,14 @@
     </row>
     <row r="78" spans="2:10" ht="49.95" customHeight="1">
       <c r="B78" s="22">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C78" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D78" s="38"/>
-      <c r="E78" s="39"/>
-      <c r="F78" s="35" t="s">
+      <c r="D78" s="32"/>
+      <c r="E78" s="33"/>
+      <c r="F78" s="34" t="s">
         <v>129</v>
       </c>
       <c r="G78" s="22" t="s">
@@ -6312,14 +6332,14 @@
     </row>
     <row r="79" spans="2:10" ht="49.95" customHeight="1">
       <c r="B79" s="22">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C79" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D79" s="38"/>
-      <c r="E79" s="39"/>
-      <c r="F79" s="36"/>
+      <c r="D79" s="32"/>
+      <c r="E79" s="33"/>
+      <c r="F79" s="35"/>
       <c r="G79" s="22" t="s">
         <v>185</v>
       </c>
@@ -6333,14 +6353,14 @@
     </row>
     <row r="80" spans="2:10" ht="49.95" customHeight="1">
       <c r="B80" s="22">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C80" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D80" s="38"/>
-      <c r="E80" s="39"/>
-      <c r="F80" s="36"/>
+      <c r="D80" s="32"/>
+      <c r="E80" s="33"/>
+      <c r="F80" s="35"/>
       <c r="G80" s="22" t="s">
         <v>185</v>
       </c>
@@ -6354,14 +6374,14 @@
     </row>
     <row r="81" spans="2:10" ht="49.95" customHeight="1">
       <c r="B81" s="22">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C81" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D81" s="38"/>
-      <c r="E81" s="39"/>
-      <c r="F81" s="36"/>
+      <c r="D81" s="32"/>
+      <c r="E81" s="33"/>
+      <c r="F81" s="35"/>
       <c r="G81" s="22" t="s">
         <v>185</v>
       </c>
@@ -6375,14 +6395,14 @@
     </row>
     <row r="82" spans="2:10" ht="49.95" customHeight="1">
       <c r="B82" s="22">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C82" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D82" s="38"/>
-      <c r="E82" s="39"/>
-      <c r="F82" s="36"/>
+      <c r="D82" s="32"/>
+      <c r="E82" s="33"/>
+      <c r="F82" s="35"/>
       <c r="G82" s="22" t="s">
         <v>185</v>
       </c>
@@ -6396,14 +6416,14 @@
     </row>
     <row r="83" spans="2:10" ht="49.95" customHeight="1">
       <c r="B83" s="22">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C83" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D83" s="38"/>
-      <c r="E83" s="39"/>
-      <c r="F83" s="36"/>
+      <c r="D83" s="32"/>
+      <c r="E83" s="33"/>
+      <c r="F83" s="35"/>
       <c r="G83" s="22" t="s">
         <v>185</v>
       </c>
@@ -6417,14 +6437,14 @@
     </row>
     <row r="84" spans="2:10" ht="49.95" customHeight="1">
       <c r="B84" s="22">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C84" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D84" s="38"/>
-      <c r="E84" s="39"/>
-      <c r="F84" s="36"/>
+      <c r="D84" s="32"/>
+      <c r="E84" s="33"/>
+      <c r="F84" s="35"/>
       <c r="G84" s="22" t="s">
         <v>185</v>
       </c>
@@ -6438,14 +6458,14 @@
     </row>
     <row r="85" spans="2:10" ht="49.95" customHeight="1">
       <c r="B85" s="22">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C85" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D85" s="38"/>
-      <c r="E85" s="39"/>
-      <c r="F85" s="36"/>
+      <c r="D85" s="32"/>
+      <c r="E85" s="33"/>
+      <c r="F85" s="35"/>
       <c r="G85" s="22" t="s">
         <v>185</v>
       </c>
@@ -6459,14 +6479,14 @@
     </row>
     <row r="86" spans="2:10" ht="49.95" customHeight="1">
       <c r="B86" s="22">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C86" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D86" s="38"/>
-      <c r="E86" s="39"/>
-      <c r="F86" s="36"/>
+      <c r="D86" s="32"/>
+      <c r="E86" s="33"/>
+      <c r="F86" s="35"/>
       <c r="G86" s="22" t="s">
         <v>185</v>
       </c>
@@ -6480,14 +6500,14 @@
     </row>
     <row r="87" spans="2:10" ht="49.95" customHeight="1">
       <c r="B87" s="22">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C87" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D87" s="38"/>
-      <c r="E87" s="39"/>
-      <c r="F87" s="36"/>
+      <c r="D87" s="32"/>
+      <c r="E87" s="33"/>
+      <c r="F87" s="35"/>
       <c r="G87" s="22" t="s">
         <v>185</v>
       </c>
@@ -6501,14 +6521,14 @@
     </row>
     <row r="88" spans="2:10" ht="49.95" customHeight="1">
       <c r="B88" s="22">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C88" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D88" s="38"/>
-      <c r="E88" s="39"/>
-      <c r="F88" s="36"/>
+      <c r="D88" s="32"/>
+      <c r="E88" s="33"/>
+      <c r="F88" s="35"/>
       <c r="G88" s="22" t="s">
         <v>185</v>
       </c>
@@ -6522,14 +6542,14 @@
     </row>
     <row r="89" spans="2:10" ht="49.95" customHeight="1">
       <c r="B89" s="22">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C89" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D89" s="38"/>
-      <c r="E89" s="39"/>
-      <c r="F89" s="36"/>
+      <c r="D89" s="32"/>
+      <c r="E89" s="33"/>
+      <c r="F89" s="35"/>
       <c r="G89" s="22" t="s">
         <v>185</v>
       </c>
@@ -6543,14 +6563,14 @@
     </row>
     <row r="90" spans="2:10" ht="49.95" customHeight="1">
       <c r="B90" s="22">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C90" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D90" s="38"/>
-      <c r="E90" s="39"/>
-      <c r="F90" s="36"/>
+      <c r="D90" s="32"/>
+      <c r="E90" s="33"/>
+      <c r="F90" s="35"/>
       <c r="G90" s="22" t="s">
         <v>185</v>
       </c>
@@ -6564,14 +6584,14 @@
     </row>
     <row r="91" spans="2:10" ht="49.95" customHeight="1">
       <c r="B91" s="22">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C91" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D91" s="38"/>
-      <c r="E91" s="39"/>
-      <c r="F91" s="36"/>
+      <c r="D91" s="32"/>
+      <c r="E91" s="33"/>
+      <c r="F91" s="35"/>
       <c r="G91" s="22" t="s">
         <v>185</v>
       </c>
@@ -6585,14 +6605,14 @@
     </row>
     <row r="92" spans="2:10" ht="49.95" customHeight="1">
       <c r="B92" s="22">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C92" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D92" s="38"/>
-      <c r="E92" s="39"/>
-      <c r="F92" s="36"/>
+      <c r="D92" s="32"/>
+      <c r="E92" s="33"/>
+      <c r="F92" s="35"/>
       <c r="G92" s="22" t="s">
         <v>185</v>
       </c>
@@ -6606,14 +6626,14 @@
     </row>
     <row r="93" spans="2:10" ht="49.95" customHeight="1">
       <c r="B93" s="22">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C93" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D93" s="38"/>
-      <c r="E93" s="39"/>
-      <c r="F93" s="36"/>
+      <c r="D93" s="32"/>
+      <c r="E93" s="33"/>
+      <c r="F93" s="35"/>
       <c r="G93" s="22" t="s">
         <v>185</v>
       </c>
@@ -6627,14 +6647,14 @@
     </row>
     <row r="94" spans="2:10" ht="49.95" customHeight="1">
       <c r="B94" s="22">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C94" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D94" s="38"/>
-      <c r="E94" s="39"/>
-      <c r="F94" s="36"/>
+      <c r="D94" s="32"/>
+      <c r="E94" s="33"/>
+      <c r="F94" s="35"/>
       <c r="G94" s="22" t="s">
         <v>185</v>
       </c>
@@ -6648,14 +6668,14 @@
     </row>
     <row r="95" spans="2:10" ht="49.95" customHeight="1">
       <c r="B95" s="22">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C95" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D95" s="38"/>
-      <c r="E95" s="39"/>
-      <c r="F95" s="36"/>
+      <c r="D95" s="32"/>
+      <c r="E95" s="33"/>
+      <c r="F95" s="35"/>
       <c r="G95" s="22" t="s">
         <v>185</v>
       </c>
@@ -6669,14 +6689,14 @@
     </row>
     <row r="96" spans="2:10" ht="49.95" customHeight="1">
       <c r="B96" s="22">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C96" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D96" s="38"/>
-      <c r="E96" s="39"/>
-      <c r="F96" s="36"/>
+      <c r="D96" s="32"/>
+      <c r="E96" s="33"/>
+      <c r="F96" s="35"/>
       <c r="G96" s="22" t="s">
         <v>185</v>
       </c>
@@ -6690,14 +6710,14 @@
     </row>
     <row r="97" spans="2:10" ht="49.95" customHeight="1">
       <c r="B97" s="22">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C97" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D97" s="38"/>
-      <c r="E97" s="39"/>
-      <c r="F97" s="37"/>
+      <c r="D97" s="32"/>
+      <c r="E97" s="33"/>
+      <c r="F97" s="36"/>
       <c r="G97" s="22" t="s">
         <v>185</v>
       </c>
@@ -6711,14 +6731,14 @@
     </row>
     <row r="98" spans="2:10" ht="49.95" customHeight="1">
       <c r="B98" s="22">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C98" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D98" s="38"/>
-      <c r="E98" s="39"/>
-      <c r="F98" s="35" t="s">
+      <c r="D98" s="32"/>
+      <c r="E98" s="33"/>
+      <c r="F98" s="34" t="s">
         <v>122</v>
       </c>
       <c r="G98" s="22" t="s">
@@ -6734,14 +6754,14 @@
     </row>
     <row r="99" spans="2:10" ht="49.95" customHeight="1">
       <c r="B99" s="22">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C99" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D99" s="38"/>
-      <c r="E99" s="39"/>
-      <c r="F99" s="37"/>
+      <c r="D99" s="32"/>
+      <c r="E99" s="33"/>
+      <c r="F99" s="36"/>
       <c r="G99" s="22" t="s">
         <v>229</v>
       </c>
@@ -6755,14 +6775,14 @@
     </row>
     <row r="100" spans="2:10" ht="49.95" customHeight="1">
       <c r="B100" s="22">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C100" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D100" s="38"/>
-      <c r="E100" s="39"/>
-      <c r="F100" s="35" t="s">
+      <c r="D100" s="32"/>
+      <c r="E100" s="33"/>
+      <c r="F100" s="34" t="s">
         <v>129</v>
       </c>
       <c r="G100" s="22" t="s">
@@ -6778,14 +6798,14 @@
     </row>
     <row r="101" spans="2:10" ht="49.95" customHeight="1">
       <c r="B101" s="22">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C101" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D101" s="38"/>
-      <c r="E101" s="39"/>
-      <c r="F101" s="36"/>
+      <c r="D101" s="32"/>
+      <c r="E101" s="33"/>
+      <c r="F101" s="35"/>
       <c r="G101" s="22" t="s">
         <v>232</v>
       </c>
@@ -6799,14 +6819,14 @@
     </row>
     <row r="102" spans="2:10" ht="49.95" customHeight="1">
       <c r="B102" s="22">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C102" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D102" s="38"/>
-      <c r="E102" s="39"/>
-      <c r="F102" s="36"/>
+      <c r="D102" s="32"/>
+      <c r="E102" s="33"/>
+      <c r="F102" s="35"/>
       <c r="G102" s="22" t="s">
         <v>232</v>
       </c>
@@ -6820,14 +6840,14 @@
     </row>
     <row r="103" spans="2:10" ht="49.95" customHeight="1">
       <c r="B103" s="22">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C103" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D103" s="38"/>
-      <c r="E103" s="39"/>
-      <c r="F103" s="36"/>
+      <c r="D103" s="32"/>
+      <c r="E103" s="33"/>
+      <c r="F103" s="35"/>
       <c r="G103" s="22" t="s">
         <v>232</v>
       </c>
@@ -6841,14 +6861,14 @@
     </row>
     <row r="104" spans="2:10" ht="49.95" customHeight="1">
       <c r="B104" s="22">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C104" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D104" s="38"/>
-      <c r="E104" s="39"/>
-      <c r="F104" s="36"/>
+      <c r="D104" s="32"/>
+      <c r="E104" s="33"/>
+      <c r="F104" s="35"/>
       <c r="G104" s="22" t="s">
         <v>232</v>
       </c>
@@ -6862,14 +6882,14 @@
     </row>
     <row r="105" spans="2:10" ht="49.95" customHeight="1">
       <c r="B105" s="22">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C105" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D105" s="38"/>
-      <c r="E105" s="39"/>
-      <c r="F105" s="36"/>
+      <c r="D105" s="32"/>
+      <c r="E105" s="33"/>
+      <c r="F105" s="35"/>
       <c r="G105" s="22" t="s">
         <v>232</v>
       </c>
@@ -6883,14 +6903,14 @@
     </row>
     <row r="106" spans="2:10" ht="49.95" customHeight="1">
       <c r="B106" s="22">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C106" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D106" s="38"/>
-      <c r="E106" s="39"/>
-      <c r="F106" s="36"/>
+      <c r="D106" s="32"/>
+      <c r="E106" s="33"/>
+      <c r="F106" s="35"/>
       <c r="G106" s="22" t="s">
         <v>232</v>
       </c>
@@ -6904,14 +6924,14 @@
     </row>
     <row r="107" spans="2:10" ht="49.95" customHeight="1">
       <c r="B107" s="22">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C107" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D107" s="38"/>
-      <c r="E107" s="39"/>
-      <c r="F107" s="36"/>
+      <c r="D107" s="32"/>
+      <c r="E107" s="33"/>
+      <c r="F107" s="35"/>
       <c r="G107" s="22" t="s">
         <v>232</v>
       </c>
@@ -6925,14 +6945,14 @@
     </row>
     <row r="108" spans="2:10" ht="49.95" customHeight="1">
       <c r="B108" s="22">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C108" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D108" s="38"/>
-      <c r="E108" s="39"/>
-      <c r="F108" s="36"/>
+      <c r="D108" s="32"/>
+      <c r="E108" s="33"/>
+      <c r="F108" s="35"/>
       <c r="G108" s="22" t="s">
         <v>232</v>
       </c>
@@ -6946,14 +6966,14 @@
     </row>
     <row r="109" spans="2:10" ht="49.95" customHeight="1">
       <c r="B109" s="22">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C109" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D109" s="38"/>
-      <c r="E109" s="39"/>
-      <c r="F109" s="36"/>
+      <c r="D109" s="32"/>
+      <c r="E109" s="33"/>
+      <c r="F109" s="35"/>
       <c r="G109" s="22" t="s">
         <v>232</v>
       </c>
@@ -6967,14 +6987,14 @@
     </row>
     <row r="110" spans="2:10" ht="49.95" customHeight="1">
       <c r="B110" s="22">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C110" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D110" s="38"/>
-      <c r="E110" s="39"/>
-      <c r="F110" s="36"/>
+      <c r="D110" s="32"/>
+      <c r="E110" s="33"/>
+      <c r="F110" s="35"/>
       <c r="G110" s="22" t="s">
         <v>232</v>
       </c>
@@ -6988,14 +7008,14 @@
     </row>
     <row r="111" spans="2:10" ht="49.95" customHeight="1">
       <c r="B111" s="22">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C111" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D111" s="38"/>
-      <c r="E111" s="39"/>
-      <c r="F111" s="36"/>
+      <c r="D111" s="32"/>
+      <c r="E111" s="33"/>
+      <c r="F111" s="35"/>
       <c r="G111" s="22" t="s">
         <v>232</v>
       </c>
@@ -7009,14 +7029,14 @@
     </row>
     <row r="112" spans="2:10" ht="49.95" customHeight="1">
       <c r="B112" s="22">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="C112" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D112" s="38"/>
-      <c r="E112" s="39"/>
-      <c r="F112" s="36"/>
+      <c r="D112" s="32"/>
+      <c r="E112" s="33"/>
+      <c r="F112" s="35"/>
       <c r="G112" s="22" t="s">
         <v>232</v>
       </c>
@@ -7030,14 +7050,14 @@
     </row>
     <row r="113" spans="2:10" ht="49.95" customHeight="1">
       <c r="B113" s="22">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C113" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D113" s="38"/>
-      <c r="E113" s="39"/>
-      <c r="F113" s="36"/>
+      <c r="D113" s="32"/>
+      <c r="E113" s="33"/>
+      <c r="F113" s="35"/>
       <c r="G113" s="22" t="s">
         <v>232</v>
       </c>
@@ -7051,14 +7071,14 @@
     </row>
     <row r="114" spans="2:10" ht="49.95" customHeight="1">
       <c r="B114" s="22">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C114" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D114" s="38"/>
-      <c r="E114" s="39"/>
-      <c r="F114" s="36"/>
+      <c r="D114" s="32"/>
+      <c r="E114" s="33"/>
+      <c r="F114" s="35"/>
       <c r="G114" s="22" t="s">
         <v>232</v>
       </c>
@@ -7072,14 +7092,14 @@
     </row>
     <row r="115" spans="2:10" ht="49.95" customHeight="1">
       <c r="B115" s="22">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C115" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D115" s="38"/>
-      <c r="E115" s="39"/>
-      <c r="F115" s="37"/>
+      <c r="D115" s="32"/>
+      <c r="E115" s="33"/>
+      <c r="F115" s="36"/>
       <c r="G115" s="22" t="s">
         <v>232</v>
       </c>
@@ -7093,14 +7113,14 @@
     </row>
     <row r="116" spans="2:10" ht="49.95" customHeight="1">
       <c r="B116" s="22">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C116" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D116" s="38"/>
-      <c r="E116" s="39"/>
-      <c r="F116" s="35" t="s">
+      <c r="D116" s="32"/>
+      <c r="E116" s="33"/>
+      <c r="F116" s="34" t="s">
         <v>122</v>
       </c>
       <c r="G116" s="22" t="s">
@@ -7116,14 +7136,14 @@
     </row>
     <row r="117" spans="2:10" ht="49.95" customHeight="1">
       <c r="B117" s="22">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C117" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D117" s="38"/>
-      <c r="E117" s="39"/>
-      <c r="F117" s="37"/>
+      <c r="D117" s="32"/>
+      <c r="E117" s="33"/>
+      <c r="F117" s="36"/>
       <c r="G117" s="22" t="s">
         <v>268</v>
       </c>
@@ -7137,14 +7157,14 @@
     </row>
     <row r="118" spans="2:10" ht="49.95" customHeight="1">
       <c r="B118" s="22">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C118" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D118" s="38"/>
-      <c r="E118" s="39"/>
-      <c r="F118" s="35" t="s">
+      <c r="D118" s="32"/>
+      <c r="E118" s="33"/>
+      <c r="F118" s="34" t="s">
         <v>129</v>
       </c>
       <c r="G118" s="22" t="s">
@@ -7160,14 +7180,14 @@
     </row>
     <row r="119" spans="2:10" ht="49.95" customHeight="1">
       <c r="B119" s="22">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C119" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D119" s="38"/>
-      <c r="E119" s="39"/>
-      <c r="F119" s="36"/>
+      <c r="D119" s="32"/>
+      <c r="E119" s="33"/>
+      <c r="F119" s="35"/>
       <c r="G119" s="22" t="s">
         <v>271</v>
       </c>
@@ -7181,14 +7201,14 @@
     </row>
     <row r="120" spans="2:10" ht="49.95" customHeight="1">
       <c r="B120" s="22">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="C120" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D120" s="38"/>
-      <c r="E120" s="39"/>
-      <c r="F120" s="36"/>
+      <c r="D120" s="32"/>
+      <c r="E120" s="33"/>
+      <c r="F120" s="35"/>
       <c r="G120" s="22" t="s">
         <v>271</v>
       </c>
@@ -7202,14 +7222,14 @@
     </row>
     <row r="121" spans="2:10" ht="49.95" customHeight="1">
       <c r="B121" s="22">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C121" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D121" s="38"/>
-      <c r="E121" s="39"/>
-      <c r="F121" s="36"/>
+      <c r="D121" s="32"/>
+      <c r="E121" s="33"/>
+      <c r="F121" s="35"/>
       <c r="G121" s="22" t="s">
         <v>271</v>
       </c>
@@ -7223,14 +7243,14 @@
     </row>
     <row r="122" spans="2:10" ht="49.95" customHeight="1">
       <c r="B122" s="22">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C122" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D122" s="38"/>
-      <c r="E122" s="39"/>
-      <c r="F122" s="36"/>
+      <c r="D122" s="32"/>
+      <c r="E122" s="33"/>
+      <c r="F122" s="35"/>
       <c r="G122" s="22" t="s">
         <v>271</v>
       </c>
@@ -7244,14 +7264,14 @@
     </row>
     <row r="123" spans="2:10" ht="49.95" customHeight="1">
       <c r="B123" s="22">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C123" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D123" s="38"/>
-      <c r="E123" s="39"/>
-      <c r="F123" s="36"/>
+      <c r="D123" s="32"/>
+      <c r="E123" s="33"/>
+      <c r="F123" s="35"/>
       <c r="G123" s="22" t="s">
         <v>271</v>
       </c>
@@ -7265,14 +7285,14 @@
     </row>
     <row r="124" spans="2:10" ht="49.95" customHeight="1">
       <c r="B124" s="22">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C124" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D124" s="38"/>
-      <c r="E124" s="39"/>
-      <c r="F124" s="36"/>
+      <c r="D124" s="32"/>
+      <c r="E124" s="33"/>
+      <c r="F124" s="35"/>
       <c r="G124" s="22" t="s">
         <v>271</v>
       </c>
@@ -7286,14 +7306,14 @@
     </row>
     <row r="125" spans="2:10" ht="49.95" customHeight="1">
       <c r="B125" s="22">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C125" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D125" s="38"/>
-      <c r="E125" s="39"/>
-      <c r="F125" s="36"/>
+      <c r="D125" s="32"/>
+      <c r="E125" s="33"/>
+      <c r="F125" s="35"/>
       <c r="G125" s="22" t="s">
         <v>271</v>
       </c>
@@ -7307,14 +7327,14 @@
     </row>
     <row r="126" spans="2:10" ht="49.95" customHeight="1">
       <c r="B126" s="22">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C126" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D126" s="38"/>
-      <c r="E126" s="39"/>
-      <c r="F126" s="36"/>
+      <c r="D126" s="32"/>
+      <c r="E126" s="33"/>
+      <c r="F126" s="35"/>
       <c r="G126" s="22" t="s">
         <v>271</v>
       </c>
@@ -7328,14 +7348,14 @@
     </row>
     <row r="127" spans="2:10" ht="49.95" customHeight="1">
       <c r="B127" s="22">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C127" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D127" s="38"/>
-      <c r="E127" s="39"/>
-      <c r="F127" s="36"/>
+      <c r="D127" s="32"/>
+      <c r="E127" s="33"/>
+      <c r="F127" s="35"/>
       <c r="G127" s="22" t="s">
         <v>271</v>
       </c>
@@ -7349,14 +7369,14 @@
     </row>
     <row r="128" spans="2:10" ht="49.95" customHeight="1">
       <c r="B128" s="22">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C128" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D128" s="38"/>
-      <c r="E128" s="39"/>
-      <c r="F128" s="36"/>
+      <c r="D128" s="32"/>
+      <c r="E128" s="33"/>
+      <c r="F128" s="35"/>
       <c r="G128" s="22" t="s">
         <v>271</v>
       </c>
@@ -7370,14 +7390,14 @@
     </row>
     <row r="129" spans="2:10" ht="49.95" customHeight="1">
       <c r="B129" s="22">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C129" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D129" s="38"/>
-      <c r="E129" s="39"/>
-      <c r="F129" s="37"/>
+      <c r="D129" s="32"/>
+      <c r="E129" s="33"/>
+      <c r="F129" s="36"/>
       <c r="G129" s="22" t="s">
         <v>271</v>
       </c>
@@ -7391,14 +7411,14 @@
     </row>
     <row r="130" spans="2:10" ht="49.95" customHeight="1">
       <c r="B130" s="22">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C130" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D130" s="38"/>
-      <c r="E130" s="39"/>
-      <c r="F130" s="35" t="s">
+      <c r="D130" s="32"/>
+      <c r="E130" s="33"/>
+      <c r="F130" s="34" t="s">
         <v>122</v>
       </c>
       <c r="G130" s="22" t="s">
@@ -7414,14 +7434,14 @@
     </row>
     <row r="131" spans="2:10" ht="49.95" customHeight="1">
       <c r="B131" s="22">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C131" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D131" s="38"/>
-      <c r="E131" s="39"/>
-      <c r="F131" s="37"/>
+      <c r="D131" s="32"/>
+      <c r="E131" s="33"/>
+      <c r="F131" s="36"/>
       <c r="G131" s="22" t="s">
         <v>299</v>
       </c>
@@ -7435,14 +7455,14 @@
     </row>
     <row r="132" spans="2:10" ht="49.95" customHeight="1">
       <c r="B132" s="22">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C132" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D132" s="38"/>
-      <c r="E132" s="39"/>
-      <c r="F132" s="35" t="s">
+      <c r="D132" s="32"/>
+      <c r="E132" s="33"/>
+      <c r="F132" s="34" t="s">
         <v>129</v>
       </c>
       <c r="G132" s="22" t="s">
@@ -7458,14 +7478,14 @@
     </row>
     <row r="133" spans="2:10" ht="49.95" customHeight="1">
       <c r="B133" s="22">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C133" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D133" s="38"/>
-      <c r="E133" s="39"/>
-      <c r="F133" s="36"/>
+      <c r="D133" s="32"/>
+      <c r="E133" s="33"/>
+      <c r="F133" s="35"/>
       <c r="G133" s="22" t="s">
         <v>302</v>
       </c>
@@ -7479,14 +7499,14 @@
     </row>
     <row r="134" spans="2:10" ht="49.95" customHeight="1">
       <c r="B134" s="22">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C134" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D134" s="38"/>
-      <c r="E134" s="39"/>
-      <c r="F134" s="36"/>
+      <c r="D134" s="32"/>
+      <c r="E134" s="33"/>
+      <c r="F134" s="35"/>
       <c r="G134" s="22" t="s">
         <v>302</v>
       </c>
@@ -7500,14 +7520,14 @@
     </row>
     <row r="135" spans="2:10" ht="49.95" customHeight="1">
       <c r="B135" s="22">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C135" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D135" s="38"/>
-      <c r="E135" s="39"/>
-      <c r="F135" s="36"/>
+      <c r="D135" s="32"/>
+      <c r="E135" s="33"/>
+      <c r="F135" s="35"/>
       <c r="G135" s="22" t="s">
         <v>302</v>
       </c>
@@ -7521,14 +7541,14 @@
     </row>
     <row r="136" spans="2:10" ht="49.95" customHeight="1">
       <c r="B136" s="22">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="C136" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D136" s="38"/>
-      <c r="E136" s="39"/>
-      <c r="F136" s="36"/>
+      <c r="D136" s="32"/>
+      <c r="E136" s="33"/>
+      <c r="F136" s="35"/>
       <c r="G136" s="22" t="s">
         <v>302</v>
       </c>
@@ -7542,14 +7562,14 @@
     </row>
     <row r="137" spans="2:10" ht="49.95" customHeight="1">
       <c r="B137" s="22">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="C137" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D137" s="38"/>
-      <c r="E137" s="39"/>
-      <c r="F137" s="36"/>
+      <c r="D137" s="32"/>
+      <c r="E137" s="33"/>
+      <c r="F137" s="35"/>
       <c r="G137" s="22" t="s">
         <v>302</v>
       </c>
@@ -7563,14 +7583,14 @@
     </row>
     <row r="138" spans="2:10" ht="49.95" customHeight="1">
       <c r="B138" s="22">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C138" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D138" s="38"/>
-      <c r="E138" s="39"/>
-      <c r="F138" s="36"/>
+      <c r="D138" s="32"/>
+      <c r="E138" s="33"/>
+      <c r="F138" s="35"/>
       <c r="G138" s="22" t="s">
         <v>302</v>
       </c>
@@ -7584,14 +7604,14 @@
     </row>
     <row r="139" spans="2:10" ht="49.95" customHeight="1">
       <c r="B139" s="22">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="C139" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D139" s="38"/>
-      <c r="E139" s="39"/>
-      <c r="F139" s="36"/>
+      <c r="D139" s="32"/>
+      <c r="E139" s="33"/>
+      <c r="F139" s="35"/>
       <c r="G139" s="22" t="s">
         <v>302</v>
       </c>
@@ -7605,14 +7625,14 @@
     </row>
     <row r="140" spans="2:10" ht="49.95" customHeight="1">
       <c r="B140" s="22">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C140" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D140" s="38"/>
-      <c r="E140" s="39"/>
-      <c r="F140" s="36"/>
+      <c r="D140" s="32"/>
+      <c r="E140" s="33"/>
+      <c r="F140" s="35"/>
       <c r="G140" s="22" t="s">
         <v>302</v>
       </c>
@@ -7626,14 +7646,14 @@
     </row>
     <row r="141" spans="2:10" ht="49.95" customHeight="1">
       <c r="B141" s="22">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="C141" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D141" s="38"/>
-      <c r="E141" s="39"/>
-      <c r="F141" s="37"/>
+      <c r="D141" s="32"/>
+      <c r="E141" s="33"/>
+      <c r="F141" s="36"/>
       <c r="G141" s="22" t="s">
         <v>302</v>
       </c>
@@ -7647,14 +7667,14 @@
     </row>
     <row r="142" spans="2:10" ht="49.95" customHeight="1">
       <c r="B142" s="22">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C142" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D142" s="38"/>
-      <c r="E142" s="39"/>
-      <c r="F142" s="35" t="s">
+      <c r="D142" s="32"/>
+      <c r="E142" s="33"/>
+      <c r="F142" s="34" t="s">
         <v>122</v>
       </c>
       <c r="G142" s="22" t="s">
@@ -7670,14 +7690,14 @@
     </row>
     <row r="143" spans="2:10" ht="49.95" customHeight="1">
       <c r="B143" s="22">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C143" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D143" s="38"/>
-      <c r="E143" s="39"/>
-      <c r="F143" s="37"/>
+      <c r="D143" s="32"/>
+      <c r="E143" s="33"/>
+      <c r="F143" s="36"/>
       <c r="G143" s="22" t="s">
         <v>326</v>
       </c>
@@ -7691,14 +7711,14 @@
     </row>
     <row r="144" spans="2:10" ht="49.95" customHeight="1">
       <c r="B144" s="22">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C144" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D144" s="38"/>
-      <c r="E144" s="39"/>
-      <c r="F144" s="35" t="s">
+      <c r="D144" s="32"/>
+      <c r="E144" s="33"/>
+      <c r="F144" s="34" t="s">
         <v>129</v>
       </c>
       <c r="G144" s="22" t="s">
@@ -7714,14 +7734,14 @@
     </row>
     <row r="145" spans="2:10" ht="49.95" customHeight="1">
       <c r="B145" s="22">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C145" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D145" s="38"/>
-      <c r="E145" s="39"/>
-      <c r="F145" s="36"/>
+      <c r="D145" s="32"/>
+      <c r="E145" s="33"/>
+      <c r="F145" s="35"/>
       <c r="G145" s="22" t="s">
         <v>329</v>
       </c>
@@ -7735,14 +7755,14 @@
     </row>
     <row r="146" spans="2:10" ht="49.95" customHeight="1">
       <c r="B146" s="22">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C146" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D146" s="38"/>
-      <c r="E146" s="39"/>
-      <c r="F146" s="36"/>
+      <c r="D146" s="32"/>
+      <c r="E146" s="33"/>
+      <c r="F146" s="35"/>
       <c r="G146" s="22" t="s">
         <v>329</v>
       </c>
@@ -7756,14 +7776,14 @@
     </row>
     <row r="147" spans="2:10" ht="49.95" customHeight="1">
       <c r="B147" s="22">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C147" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D147" s="38"/>
-      <c r="E147" s="39"/>
-      <c r="F147" s="37"/>
+      <c r="D147" s="32"/>
+      <c r="E147" s="33"/>
+      <c r="F147" s="36"/>
       <c r="G147" s="22" t="s">
         <v>329</v>
       </c>
@@ -7777,14 +7797,14 @@
     </row>
     <row r="148" spans="2:10" ht="49.95" customHeight="1">
       <c r="B148" s="22">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C148" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D148" s="38"/>
-      <c r="E148" s="39"/>
-      <c r="F148" s="35" t="s">
+      <c r="D148" s="32"/>
+      <c r="E148" s="33"/>
+      <c r="F148" s="34" t="s">
         <v>122</v>
       </c>
       <c r="G148" s="22" t="s">
@@ -7800,14 +7820,14 @@
     </row>
     <row r="149" spans="2:10" ht="49.95" customHeight="1">
       <c r="B149" s="22">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="C149" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D149" s="38"/>
-      <c r="E149" s="39"/>
-      <c r="F149" s="37"/>
+      <c r="D149" s="32"/>
+      <c r="E149" s="33"/>
+      <c r="F149" s="36"/>
       <c r="G149" s="22" t="s">
         <v>341</v>
       </c>
@@ -7821,14 +7841,14 @@
     </row>
     <row r="150" spans="2:10" ht="49.95" customHeight="1">
       <c r="B150" s="22">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="C150" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D150" s="38"/>
-      <c r="E150" s="39"/>
-      <c r="F150" s="35" t="s">
+      <c r="D150" s="32"/>
+      <c r="E150" s="33"/>
+      <c r="F150" s="34" t="s">
         <v>129</v>
       </c>
       <c r="G150" s="22" t="s">
@@ -7844,14 +7864,14 @@
     </row>
     <row r="151" spans="2:10" ht="49.95" customHeight="1">
       <c r="B151" s="22">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C151" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D151" s="38"/>
-      <c r="E151" s="39"/>
-      <c r="F151" s="36"/>
+      <c r="D151" s="32"/>
+      <c r="E151" s="33"/>
+      <c r="F151" s="35"/>
       <c r="G151" s="22" t="s">
         <v>344</v>
       </c>
@@ -7865,14 +7885,14 @@
     </row>
     <row r="152" spans="2:10" ht="49.95" customHeight="1">
       <c r="B152" s="22">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C152" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D152" s="38"/>
-      <c r="E152" s="39"/>
-      <c r="F152" s="36"/>
+      <c r="D152" s="32"/>
+      <c r="E152" s="33"/>
+      <c r="F152" s="35"/>
       <c r="G152" s="22" t="s">
         <v>344</v>
       </c>
@@ -7886,14 +7906,14 @@
     </row>
     <row r="153" spans="2:10" ht="49.95" customHeight="1">
       <c r="B153" s="22">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C153" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D153" s="38"/>
-      <c r="E153" s="39"/>
-      <c r="F153" s="36"/>
+      <c r="D153" s="32"/>
+      <c r="E153" s="33"/>
+      <c r="F153" s="35"/>
       <c r="G153" s="22" t="s">
         <v>344</v>
       </c>
@@ -7907,14 +7927,14 @@
     </row>
     <row r="154" spans="2:10" ht="49.95" customHeight="1">
       <c r="B154" s="22">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C154" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D154" s="38"/>
-      <c r="E154" s="39"/>
-      <c r="F154" s="36"/>
+      <c r="D154" s="32"/>
+      <c r="E154" s="33"/>
+      <c r="F154" s="35"/>
       <c r="G154" s="22" t="s">
         <v>344</v>
       </c>
@@ -7928,14 +7948,14 @@
     </row>
     <row r="155" spans="2:10" ht="49.95" customHeight="1">
       <c r="B155" s="22">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C155" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D155" s="38"/>
-      <c r="E155" s="39"/>
-      <c r="F155" s="37"/>
+      <c r="D155" s="32"/>
+      <c r="E155" s="33"/>
+      <c r="F155" s="36"/>
       <c r="G155" s="22" t="s">
         <v>344</v>
       </c>
@@ -7949,14 +7969,14 @@
     </row>
     <row r="156" spans="2:10" ht="49.95" customHeight="1">
       <c r="B156" s="22">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C156" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D156" s="38"/>
-      <c r="E156" s="39"/>
-      <c r="F156" s="35" t="s">
+      <c r="D156" s="32"/>
+      <c r="E156" s="33"/>
+      <c r="F156" s="34" t="s">
         <v>122</v>
       </c>
       <c r="G156" s="22" t="s">
@@ -7972,14 +7992,14 @@
     </row>
     <row r="157" spans="2:10" ht="49.95" customHeight="1">
       <c r="B157" s="22">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="C157" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D157" s="38"/>
-      <c r="E157" s="39"/>
-      <c r="F157" s="36"/>
+      <c r="D157" s="32"/>
+      <c r="E157" s="33"/>
+      <c r="F157" s="35"/>
       <c r="G157" s="22" t="s">
         <v>360</v>
       </c>
@@ -7993,14 +8013,14 @@
     </row>
     <row r="158" spans="2:10" ht="49.95" customHeight="1">
       <c r="B158" s="22">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C158" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D158" s="38"/>
-      <c r="E158" s="39"/>
-      <c r="F158" s="36"/>
+      <c r="D158" s="32"/>
+      <c r="E158" s="33"/>
+      <c r="F158" s="35"/>
       <c r="G158" s="22" t="s">
         <v>363</v>
       </c>
@@ -8014,14 +8034,14 @@
     </row>
     <row r="159" spans="2:10" ht="49.95" customHeight="1">
       <c r="B159" s="22">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C159" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D159" s="38"/>
-      <c r="E159" s="39"/>
-      <c r="F159" s="36"/>
+      <c r="D159" s="32"/>
+      <c r="E159" s="33"/>
+      <c r="F159" s="35"/>
       <c r="G159" s="22" t="s">
         <v>366</v>
       </c>
@@ -8035,14 +8055,14 @@
     </row>
     <row r="160" spans="2:10" ht="49.95" customHeight="1">
       <c r="B160" s="22">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="C160" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D160" s="38"/>
-      <c r="E160" s="39"/>
-      <c r="F160" s="36"/>
+      <c r="D160" s="32"/>
+      <c r="E160" s="33"/>
+      <c r="F160" s="35"/>
       <c r="G160" s="22" t="s">
         <v>369</v>
       </c>
@@ -8056,14 +8076,14 @@
     </row>
     <row r="161" spans="2:10" ht="49.95" customHeight="1">
       <c r="B161" s="22">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C161" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D161" s="38"/>
-      <c r="E161" s="39"/>
-      <c r="F161" s="37"/>
+      <c r="D161" s="32"/>
+      <c r="E161" s="33"/>
+      <c r="F161" s="36"/>
       <c r="G161" s="22" t="s">
         <v>372</v>
       </c>
@@ -8077,14 +8097,14 @@
     </row>
     <row r="162" spans="2:10" ht="49.95" customHeight="1">
       <c r="B162" s="22">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C162" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D162" s="38"/>
-      <c r="E162" s="39"/>
-      <c r="F162" s="35" t="s">
+      <c r="D162" s="32"/>
+      <c r="E162" s="33"/>
+      <c r="F162" s="34" t="s">
         <v>129</v>
       </c>
       <c r="G162" s="22" t="s">
@@ -8100,14 +8120,14 @@
     </row>
     <row r="163" spans="2:10" ht="49.95" customHeight="1">
       <c r="B163" s="22">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C163" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D163" s="38"/>
-      <c r="E163" s="39"/>
-      <c r="F163" s="36"/>
+      <c r="D163" s="32"/>
+      <c r="E163" s="33"/>
+      <c r="F163" s="35"/>
       <c r="G163" s="22" t="s">
         <v>375</v>
       </c>
@@ -8121,14 +8141,14 @@
     </row>
     <row r="164" spans="2:10" ht="49.95" customHeight="1">
       <c r="B164" s="22">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="C164" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D164" s="38"/>
-      <c r="E164" s="39"/>
-      <c r="F164" s="36"/>
+      <c r="D164" s="32"/>
+      <c r="E164" s="33"/>
+      <c r="F164" s="35"/>
       <c r="G164" s="22" t="s">
         <v>375</v>
       </c>
@@ -8142,14 +8162,14 @@
     </row>
     <row r="165" spans="2:10" ht="49.95" customHeight="1">
       <c r="B165" s="22">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="C165" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D165" s="38"/>
-      <c r="E165" s="39"/>
-      <c r="F165" s="36"/>
+      <c r="D165" s="32"/>
+      <c r="E165" s="33"/>
+      <c r="F165" s="35"/>
       <c r="G165" s="22" t="s">
         <v>375</v>
       </c>
@@ -8163,14 +8183,14 @@
     </row>
     <row r="166" spans="2:10" ht="49.95" customHeight="1">
       <c r="B166" s="22">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="C166" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D166" s="38"/>
-      <c r="E166" s="39"/>
-      <c r="F166" s="36"/>
+      <c r="D166" s="32"/>
+      <c r="E166" s="33"/>
+      <c r="F166" s="35"/>
       <c r="G166" s="22" t="s">
         <v>375</v>
       </c>
@@ -8184,14 +8204,14 @@
     </row>
     <row r="167" spans="2:10" ht="49.95" customHeight="1">
       <c r="B167" s="22">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="C167" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D167" s="38"/>
-      <c r="E167" s="39"/>
-      <c r="F167" s="36"/>
+      <c r="D167" s="32"/>
+      <c r="E167" s="33"/>
+      <c r="F167" s="35"/>
       <c r="G167" s="22" t="s">
         <v>375</v>
       </c>
@@ -8205,14 +8225,14 @@
     </row>
     <row r="168" spans="2:10" ht="49.95" customHeight="1">
       <c r="B168" s="22">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="C168" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D168" s="38"/>
-      <c r="E168" s="39"/>
-      <c r="F168" s="36"/>
+      <c r="D168" s="32"/>
+      <c r="E168" s="33"/>
+      <c r="F168" s="35"/>
       <c r="G168" s="22" t="s">
         <v>375</v>
       </c>
@@ -8226,14 +8246,14 @@
     </row>
     <row r="169" spans="2:10" ht="49.95" customHeight="1">
       <c r="B169" s="22">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C169" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D169" s="38"/>
-      <c r="E169" s="39"/>
-      <c r="F169" s="36"/>
+      <c r="D169" s="32"/>
+      <c r="E169" s="33"/>
+      <c r="F169" s="35"/>
       <c r="G169" s="22" t="s">
         <v>375</v>
       </c>
@@ -8247,14 +8267,14 @@
     </row>
     <row r="170" spans="2:10" ht="49.95" customHeight="1">
       <c r="B170" s="22">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="C170" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D170" s="38"/>
-      <c r="E170" s="39"/>
-      <c r="F170" s="36"/>
+      <c r="D170" s="32"/>
+      <c r="E170" s="33"/>
+      <c r="F170" s="35"/>
       <c r="G170" s="22" t="s">
         <v>375</v>
       </c>
@@ -8268,14 +8288,14 @@
     </row>
     <row r="171" spans="2:10" ht="49.95" customHeight="1">
       <c r="B171" s="22">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="C171" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D171" s="38"/>
-      <c r="E171" s="39"/>
-      <c r="F171" s="37"/>
+      <c r="D171" s="32"/>
+      <c r="E171" s="33"/>
+      <c r="F171" s="36"/>
       <c r="G171" s="22" t="s">
         <v>375</v>
       </c>
@@ -8289,14 +8309,14 @@
     </row>
     <row r="172" spans="2:10" ht="49.95" customHeight="1">
       <c r="B172" s="22">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="C172" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D172" s="38"/>
-      <c r="E172" s="39"/>
-      <c r="F172" s="35" t="s">
+      <c r="D172" s="32"/>
+      <c r="E172" s="33"/>
+      <c r="F172" s="34" t="s">
         <v>122</v>
       </c>
       <c r="G172" s="22" t="s">
@@ -8312,14 +8332,14 @@
     </row>
     <row r="173" spans="2:10" ht="49.95" customHeight="1">
       <c r="B173" s="22">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C173" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D173" s="38"/>
-      <c r="E173" s="39"/>
-      <c r="F173" s="36"/>
+      <c r="D173" s="32"/>
+      <c r="E173" s="33"/>
+      <c r="F173" s="35"/>
       <c r="G173" s="22" t="s">
         <v>399</v>
       </c>
@@ -8333,14 +8353,14 @@
     </row>
     <row r="174" spans="2:10" ht="49.95" customHeight="1">
       <c r="B174" s="22">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C174" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D174" s="38"/>
-      <c r="E174" s="39"/>
-      <c r="F174" s="36"/>
+      <c r="D174" s="32"/>
+      <c r="E174" s="33"/>
+      <c r="F174" s="35"/>
       <c r="G174" s="22" t="s">
         <v>402</v>
       </c>
@@ -8354,14 +8374,14 @@
     </row>
     <row r="175" spans="2:10" ht="49.95" customHeight="1">
       <c r="B175" s="22">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C175" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D175" s="38"/>
-      <c r="E175" s="39"/>
-      <c r="F175" s="37"/>
+      <c r="D175" s="32"/>
+      <c r="E175" s="33"/>
+      <c r="F175" s="36"/>
       <c r="G175" s="22" t="s">
         <v>405</v>
       </c>
@@ -8374,15 +8394,15 @@
       <c r="J175" s="22"/>
     </row>
     <row r="176" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B176" s="23">
-        <v>161</v>
+      <c r="B176" s="22">
+        <v>171</v>
       </c>
       <c r="C176" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D176" s="38"/>
-      <c r="E176" s="39"/>
-      <c r="F176" s="32" t="s">
+      <c r="D176" s="32"/>
+      <c r="E176" s="33"/>
+      <c r="F176" s="37" t="s">
         <v>129</v>
       </c>
       <c r="G176" s="23" t="s">
@@ -8397,15 +8417,15 @@
       <c r="J176" s="23"/>
     </row>
     <row r="177" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B177" s="23">
-        <v>162</v>
+      <c r="B177" s="22">
+        <v>172</v>
       </c>
       <c r="C177" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D177" s="38"/>
-      <c r="E177" s="39"/>
-      <c r="F177" s="33"/>
+      <c r="D177" s="32"/>
+      <c r="E177" s="33"/>
+      <c r="F177" s="39"/>
       <c r="G177" s="23" t="s">
         <v>408</v>
       </c>
@@ -8418,15 +8438,15 @@
       <c r="J177" s="23"/>
     </row>
     <row r="178" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B178" s="23">
-        <v>163</v>
+      <c r="B178" s="22">
+        <v>173</v>
       </c>
       <c r="C178" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D178" s="38"/>
-      <c r="E178" s="39"/>
-      <c r="F178" s="33"/>
+      <c r="D178" s="32"/>
+      <c r="E178" s="33"/>
+      <c r="F178" s="39"/>
       <c r="G178" s="23" t="s">
         <v>408</v>
       </c>
@@ -8439,15 +8459,15 @@
       <c r="J178" s="23"/>
     </row>
     <row r="179" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B179" s="23">
-        <v>164</v>
+      <c r="B179" s="22">
+        <v>174</v>
       </c>
       <c r="C179" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D179" s="38"/>
-      <c r="E179" s="39"/>
-      <c r="F179" s="34"/>
+      <c r="D179" s="32"/>
+      <c r="E179" s="33"/>
+      <c r="F179" s="38"/>
       <c r="G179" s="23" t="s">
         <v>408</v>
       </c>
@@ -8460,15 +8480,15 @@
       <c r="J179" s="23"/>
     </row>
     <row r="180" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B180" s="23">
-        <v>165</v>
+      <c r="B180" s="22">
+        <v>175</v>
       </c>
       <c r="C180" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D180" s="38"/>
-      <c r="E180" s="39"/>
-      <c r="F180" s="32" t="s">
+      <c r="D180" s="32"/>
+      <c r="E180" s="33"/>
+      <c r="F180" s="37" t="s">
         <v>122</v>
       </c>
       <c r="G180" s="23" t="s">
@@ -8483,15 +8503,15 @@
       <c r="J180" s="23"/>
     </row>
     <row r="181" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B181" s="23">
-        <v>166</v>
+      <c r="B181" s="22">
+        <v>176</v>
       </c>
       <c r="C181" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D181" s="38"/>
-      <c r="E181" s="39"/>
-      <c r="F181" s="34"/>
+      <c r="D181" s="32"/>
+      <c r="E181" s="33"/>
+      <c r="F181" s="38"/>
       <c r="G181" s="23" t="s">
         <v>420</v>
       </c>
@@ -8504,15 +8524,15 @@
       <c r="J181" s="23"/>
     </row>
     <row r="182" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B182" s="23">
-        <v>167</v>
+      <c r="B182" s="22">
+        <v>177</v>
       </c>
       <c r="C182" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D182" s="38"/>
-      <c r="E182" s="39"/>
-      <c r="F182" s="32" t="s">
+      <c r="D182" s="32"/>
+      <c r="E182" s="33"/>
+      <c r="F182" s="37" t="s">
         <v>129</v>
       </c>
       <c r="G182" s="23" t="s">
@@ -8527,15 +8547,15 @@
       <c r="J182" s="23"/>
     </row>
     <row r="183" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B183" s="23">
-        <v>168</v>
+      <c r="B183" s="22">
+        <v>178</v>
       </c>
       <c r="C183" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D183" s="38"/>
-      <c r="E183" s="39"/>
-      <c r="F183" s="33"/>
+      <c r="D183" s="32"/>
+      <c r="E183" s="33"/>
+      <c r="F183" s="39"/>
       <c r="G183" s="23" t="s">
         <v>423</v>
       </c>
@@ -8548,15 +8568,15 @@
       <c r="J183" s="23"/>
     </row>
     <row r="184" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B184" s="23">
-        <v>169</v>
+      <c r="B184" s="22">
+        <v>179</v>
       </c>
       <c r="C184" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D184" s="38"/>
-      <c r="E184" s="39"/>
-      <c r="F184" s="33"/>
+      <c r="D184" s="32"/>
+      <c r="E184" s="33"/>
+      <c r="F184" s="39"/>
       <c r="G184" s="23" t="s">
         <v>423</v>
       </c>
@@ -8569,15 +8589,15 @@
       <c r="J184" s="23"/>
     </row>
     <row r="185" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B185" s="23">
-        <v>170</v>
+      <c r="B185" s="22">
+        <v>180</v>
       </c>
       <c r="C185" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D185" s="38"/>
-      <c r="E185" s="39"/>
-      <c r="F185" s="33"/>
+      <c r="D185" s="32"/>
+      <c r="E185" s="33"/>
+      <c r="F185" s="39"/>
       <c r="G185" s="23" t="s">
         <v>423</v>
       </c>
@@ -8590,15 +8610,15 @@
       <c r="J185" s="23"/>
     </row>
     <row r="186" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B186" s="23">
-        <v>171</v>
+      <c r="B186" s="22">
+        <v>181</v>
       </c>
       <c r="C186" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D186" s="38"/>
-      <c r="E186" s="39"/>
-      <c r="F186" s="33"/>
+      <c r="D186" s="32"/>
+      <c r="E186" s="33"/>
+      <c r="F186" s="39"/>
       <c r="G186" s="23" t="s">
         <v>423</v>
       </c>
@@ -8611,15 +8631,15 @@
       <c r="J186" s="23"/>
     </row>
     <row r="187" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B187" s="23">
-        <v>172</v>
+      <c r="B187" s="22">
+        <v>182</v>
       </c>
       <c r="C187" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D187" s="38"/>
-      <c r="E187" s="39"/>
-      <c r="F187" s="34"/>
+      <c r="D187" s="32"/>
+      <c r="E187" s="33"/>
+      <c r="F187" s="38"/>
       <c r="G187" s="23" t="s">
         <v>423</v>
       </c>
@@ -8632,15 +8652,15 @@
       <c r="J187" s="23"/>
     </row>
     <row r="188" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B188" s="23">
-        <v>173</v>
+      <c r="B188" s="22">
+        <v>183</v>
       </c>
       <c r="C188" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D188" s="38"/>
-      <c r="E188" s="39"/>
-      <c r="F188" s="32" t="s">
+      <c r="D188" s="32"/>
+      <c r="E188" s="33"/>
+      <c r="F188" s="37" t="s">
         <v>122</v>
       </c>
       <c r="G188" s="23" t="s">
@@ -8655,15 +8675,15 @@
       <c r="J188" s="23"/>
     </row>
     <row r="189" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B189" s="23">
-        <v>174</v>
+      <c r="B189" s="22">
+        <v>184</v>
       </c>
       <c r="C189" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D189" s="38"/>
-      <c r="E189" s="39"/>
-      <c r="F189" s="34"/>
+      <c r="D189" s="32"/>
+      <c r="E189" s="33"/>
+      <c r="F189" s="38"/>
       <c r="G189" s="23" t="s">
         <v>439</v>
       </c>
@@ -8676,15 +8696,15 @@
       <c r="J189" s="23"/>
     </row>
     <row r="190" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B190" s="23">
-        <v>175</v>
+      <c r="B190" s="22">
+        <v>185</v>
       </c>
       <c r="C190" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D190" s="38"/>
-      <c r="E190" s="39"/>
-      <c r="F190" s="32" t="s">
+      <c r="D190" s="32"/>
+      <c r="E190" s="33"/>
+      <c r="F190" s="37" t="s">
         <v>129</v>
       </c>
       <c r="G190" s="23" t="s">
@@ -8699,15 +8719,15 @@
       <c r="J190" s="23"/>
     </row>
     <row r="191" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B191" s="23">
-        <v>176</v>
+      <c r="B191" s="22">
+        <v>186</v>
       </c>
       <c r="C191" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D191" s="38"/>
-      <c r="E191" s="39"/>
-      <c r="F191" s="33"/>
+      <c r="D191" s="32"/>
+      <c r="E191" s="33"/>
+      <c r="F191" s="39"/>
       <c r="G191" s="23" t="s">
         <v>442</v>
       </c>
@@ -8720,15 +8740,15 @@
       <c r="J191" s="23"/>
     </row>
     <row r="192" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B192" s="23">
-        <v>177</v>
+      <c r="B192" s="22">
+        <v>187</v>
       </c>
       <c r="C192" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D192" s="38"/>
-      <c r="E192" s="39"/>
-      <c r="F192" s="33"/>
+      <c r="D192" s="32"/>
+      <c r="E192" s="33"/>
+      <c r="F192" s="39"/>
       <c r="G192" s="23" t="s">
         <v>442</v>
       </c>
@@ -8741,15 +8761,15 @@
       <c r="J192" s="23"/>
     </row>
     <row r="193" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B193" s="23">
-        <v>178</v>
+      <c r="B193" s="22">
+        <v>188</v>
       </c>
       <c r="C193" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D193" s="38"/>
-      <c r="E193" s="39"/>
-      <c r="F193" s="33"/>
+      <c r="D193" s="32"/>
+      <c r="E193" s="33"/>
+      <c r="F193" s="39"/>
       <c r="G193" s="23" t="s">
         <v>442</v>
       </c>
@@ -8762,15 +8782,15 @@
       <c r="J193" s="23"/>
     </row>
     <row r="194" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B194" s="23">
-        <v>179</v>
+      <c r="B194" s="22">
+        <v>189</v>
       </c>
       <c r="C194" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D194" s="38"/>
-      <c r="E194" s="39"/>
-      <c r="F194" s="33"/>
+      <c r="D194" s="32"/>
+      <c r="E194" s="33"/>
+      <c r="F194" s="39"/>
       <c r="G194" s="23" t="s">
         <v>442</v>
       </c>
@@ -8783,15 +8803,15 @@
       <c r="J194" s="23"/>
     </row>
     <row r="195" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B195" s="23">
-        <v>180</v>
+      <c r="B195" s="22">
+        <v>190</v>
       </c>
       <c r="C195" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D195" s="38"/>
-      <c r="E195" s="39"/>
-      <c r="F195" s="33"/>
+      <c r="D195" s="32"/>
+      <c r="E195" s="33"/>
+      <c r="F195" s="39"/>
       <c r="G195" s="23" t="s">
         <v>442</v>
       </c>
@@ -8804,15 +8824,15 @@
       <c r="J195" s="23"/>
     </row>
     <row r="196" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B196" s="23">
-        <v>181</v>
+      <c r="B196" s="22">
+        <v>191</v>
       </c>
       <c r="C196" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D196" s="38"/>
-      <c r="E196" s="39"/>
-      <c r="F196" s="33"/>
+      <c r="D196" s="32"/>
+      <c r="E196" s="33"/>
+      <c r="F196" s="39"/>
       <c r="G196" s="23" t="s">
         <v>442</v>
       </c>
@@ -8825,15 +8845,15 @@
       <c r="J196" s="23"/>
     </row>
     <row r="197" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B197" s="23">
-        <v>182</v>
+      <c r="B197" s="22">
+        <v>192</v>
       </c>
       <c r="C197" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D197" s="38"/>
-      <c r="E197" s="39"/>
-      <c r="F197" s="33"/>
+      <c r="D197" s="32"/>
+      <c r="E197" s="33"/>
+      <c r="F197" s="39"/>
       <c r="G197" s="23" t="s">
         <v>442</v>
       </c>
@@ -8846,15 +8866,15 @@
       <c r="J197" s="23"/>
     </row>
     <row r="198" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B198" s="23">
-        <v>183</v>
+      <c r="B198" s="22">
+        <v>193</v>
       </c>
       <c r="C198" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D198" s="38"/>
-      <c r="E198" s="39"/>
-      <c r="F198" s="33"/>
+      <c r="D198" s="32"/>
+      <c r="E198" s="33"/>
+      <c r="F198" s="39"/>
       <c r="G198" s="23" t="s">
         <v>442</v>
       </c>
@@ -8867,15 +8887,15 @@
       <c r="J198" s="23"/>
     </row>
     <row r="199" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B199" s="23">
-        <v>184</v>
+      <c r="B199" s="22">
+        <v>194</v>
       </c>
       <c r="C199" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D199" s="38"/>
-      <c r="E199" s="39"/>
-      <c r="F199" s="33"/>
+      <c r="D199" s="32"/>
+      <c r="E199" s="33"/>
+      <c r="F199" s="39"/>
       <c r="G199" s="23" t="s">
         <v>442</v>
       </c>
@@ -8888,15 +8908,15 @@
       <c r="J199" s="23"/>
     </row>
     <row r="200" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B200" s="23">
-        <v>185</v>
+      <c r="B200" s="22">
+        <v>195</v>
       </c>
       <c r="C200" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D200" s="38"/>
-      <c r="E200" s="39"/>
-      <c r="F200" s="33"/>
+      <c r="D200" s="32"/>
+      <c r="E200" s="33"/>
+      <c r="F200" s="39"/>
       <c r="G200" s="23" t="s">
         <v>442</v>
       </c>
@@ -8909,15 +8929,15 @@
       <c r="J200" s="23"/>
     </row>
     <row r="201" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B201" s="23">
-        <v>186</v>
+      <c r="B201" s="22">
+        <v>196</v>
       </c>
       <c r="C201" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D201" s="38"/>
-      <c r="E201" s="39"/>
-      <c r="F201" s="33"/>
+      <c r="D201" s="32"/>
+      <c r="E201" s="33"/>
+      <c r="F201" s="39"/>
       <c r="G201" s="23" t="s">
         <v>442</v>
       </c>
@@ -8930,15 +8950,15 @@
       <c r="J201" s="23"/>
     </row>
     <row r="202" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B202" s="23">
-        <v>187</v>
+      <c r="B202" s="22">
+        <v>197</v>
       </c>
       <c r="C202" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D202" s="38"/>
-      <c r="E202" s="39"/>
-      <c r="F202" s="33"/>
+      <c r="D202" s="32"/>
+      <c r="E202" s="33"/>
+      <c r="F202" s="39"/>
       <c r="G202" s="23" t="s">
         <v>442</v>
       </c>
@@ -8951,15 +8971,15 @@
       <c r="J202" s="23"/>
     </row>
     <row r="203" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B203" s="23">
-        <v>188</v>
+      <c r="B203" s="22">
+        <v>198</v>
       </c>
       <c r="C203" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D203" s="38"/>
-      <c r="E203" s="39"/>
-      <c r="F203" s="33"/>
+      <c r="D203" s="32"/>
+      <c r="E203" s="33"/>
+      <c r="F203" s="39"/>
       <c r="G203" s="23" t="s">
         <v>442</v>
       </c>
@@ -8972,15 +8992,15 @@
       <c r="J203" s="23"/>
     </row>
     <row r="204" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B204" s="23">
-        <v>189</v>
+      <c r="B204" s="22">
+        <v>199</v>
       </c>
       <c r="C204" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D204" s="38"/>
-      <c r="E204" s="39"/>
-      <c r="F204" s="33"/>
+      <c r="D204" s="32"/>
+      <c r="E204" s="33"/>
+      <c r="F204" s="39"/>
       <c r="G204" s="23" t="s">
         <v>442</v>
       </c>
@@ -8993,15 +9013,15 @@
       <c r="J204" s="23"/>
     </row>
     <row r="205" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B205" s="23">
-        <v>190</v>
+      <c r="B205" s="22">
+        <v>200</v>
       </c>
       <c r="C205" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D205" s="38"/>
-      <c r="E205" s="39"/>
-      <c r="F205" s="33"/>
+      <c r="D205" s="32"/>
+      <c r="E205" s="33"/>
+      <c r="F205" s="39"/>
       <c r="G205" s="23" t="s">
         <v>442</v>
       </c>
@@ -9014,15 +9034,15 @@
       <c r="J205" s="23"/>
     </row>
     <row r="206" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B206" s="23">
-        <v>191</v>
+      <c r="B206" s="22">
+        <v>201</v>
       </c>
       <c r="C206" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D206" s="38"/>
-      <c r="E206" s="39"/>
-      <c r="F206" s="33"/>
+      <c r="D206" s="32"/>
+      <c r="E206" s="33"/>
+      <c r="F206" s="39"/>
       <c r="G206" s="23" t="s">
         <v>442</v>
       </c>
@@ -9035,15 +9055,15 @@
       <c r="J206" s="23"/>
     </row>
     <row r="207" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B207" s="23">
-        <v>192</v>
+      <c r="B207" s="22">
+        <v>202</v>
       </c>
       <c r="C207" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D207" s="38"/>
-      <c r="E207" s="39"/>
-      <c r="F207" s="34"/>
+      <c r="D207" s="32"/>
+      <c r="E207" s="33"/>
+      <c r="F207" s="38"/>
       <c r="G207" s="23" t="s">
         <v>442</v>
       </c>
@@ -9056,15 +9076,15 @@
       <c r="J207" s="23"/>
     </row>
     <row r="208" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B208" s="23">
-        <v>193</v>
+      <c r="B208" s="22">
+        <v>203</v>
       </c>
       <c r="C208" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D208" s="38"/>
-      <c r="E208" s="39"/>
-      <c r="F208" s="32" t="s">
+      <c r="D208" s="32"/>
+      <c r="E208" s="33"/>
+      <c r="F208" s="37" t="s">
         <v>122</v>
       </c>
       <c r="G208" s="23" t="s">
@@ -9079,15 +9099,15 @@
       <c r="J208" s="23"/>
     </row>
     <row r="209" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B209" s="23">
-        <v>194</v>
+      <c r="B209" s="22">
+        <v>204</v>
       </c>
       <c r="C209" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D209" s="38"/>
-      <c r="E209" s="39"/>
-      <c r="F209" s="34"/>
+      <c r="D209" s="32"/>
+      <c r="E209" s="33"/>
+      <c r="F209" s="38"/>
       <c r="G209" s="23" t="s">
         <v>482</v>
       </c>
@@ -9100,15 +9120,15 @@
       <c r="J209" s="23"/>
     </row>
     <row r="210" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B210" s="23">
-        <v>195</v>
+      <c r="B210" s="22">
+        <v>205</v>
       </c>
       <c r="C210" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D210" s="38"/>
-      <c r="E210" s="39"/>
-      <c r="F210" s="32" t="s">
+      <c r="D210" s="32"/>
+      <c r="E210" s="33"/>
+      <c r="F210" s="37" t="s">
         <v>129</v>
       </c>
       <c r="G210" s="23" t="s">
@@ -9123,15 +9143,15 @@
       <c r="J210" s="23"/>
     </row>
     <row r="211" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B211" s="23">
-        <v>196</v>
+      <c r="B211" s="22">
+        <v>206</v>
       </c>
       <c r="C211" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D211" s="38"/>
-      <c r="E211" s="39"/>
-      <c r="F211" s="33"/>
+      <c r="D211" s="32"/>
+      <c r="E211" s="33"/>
+      <c r="F211" s="39"/>
       <c r="G211" s="23" t="s">
         <v>485</v>
       </c>
@@ -9144,15 +9164,15 @@
       <c r="J211" s="23"/>
     </row>
     <row r="212" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B212" s="23">
-        <v>197</v>
+      <c r="B212" s="22">
+        <v>207</v>
       </c>
       <c r="C212" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D212" s="38"/>
-      <c r="E212" s="39"/>
-      <c r="F212" s="33"/>
+      <c r="D212" s="32"/>
+      <c r="E212" s="33"/>
+      <c r="F212" s="39"/>
       <c r="G212" s="23" t="s">
         <v>485</v>
       </c>
@@ -9165,15 +9185,15 @@
       <c r="J212" s="23"/>
     </row>
     <row r="213" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B213" s="23">
-        <v>198</v>
+      <c r="B213" s="22">
+        <v>208</v>
       </c>
       <c r="C213" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D213" s="38"/>
-      <c r="E213" s="39"/>
-      <c r="F213" s="33"/>
+      <c r="D213" s="32"/>
+      <c r="E213" s="33"/>
+      <c r="F213" s="39"/>
       <c r="G213" s="23" t="s">
         <v>485</v>
       </c>
@@ -9186,15 +9206,15 @@
       <c r="J213" s="23"/>
     </row>
     <row r="214" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B214" s="23">
-        <v>199</v>
+      <c r="B214" s="22">
+        <v>209</v>
       </c>
       <c r="C214" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D214" s="38"/>
-      <c r="E214" s="39"/>
-      <c r="F214" s="33"/>
+      <c r="D214" s="32"/>
+      <c r="E214" s="33"/>
+      <c r="F214" s="39"/>
       <c r="G214" s="23" t="s">
         <v>485</v>
       </c>
@@ -9207,15 +9227,15 @@
       <c r="J214" s="23"/>
     </row>
     <row r="215" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B215" s="23">
-        <v>200</v>
+      <c r="B215" s="22">
+        <v>210</v>
       </c>
       <c r="C215" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D215" s="38"/>
-      <c r="E215" s="39"/>
-      <c r="F215" s="34"/>
+      <c r="D215" s="32"/>
+      <c r="E215" s="33"/>
+      <c r="F215" s="38"/>
       <c r="G215" s="23" t="s">
         <v>485</v>
       </c>
@@ -9228,15 +9248,15 @@
       <c r="J215" s="23"/>
     </row>
     <row r="216" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B216" s="23">
-        <v>201</v>
+      <c r="B216" s="22">
+        <v>211</v>
       </c>
       <c r="C216" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D216" s="38"/>
-      <c r="E216" s="39"/>
-      <c r="F216" s="32" t="s">
+      <c r="D216" s="32"/>
+      <c r="E216" s="33"/>
+      <c r="F216" s="37" t="s">
         <v>122</v>
       </c>
       <c r="G216" s="23" t="s">
@@ -9251,15 +9271,15 @@
       <c r="J216" s="23"/>
     </row>
     <row r="217" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B217" s="23">
-        <v>202</v>
+      <c r="B217" s="22">
+        <v>212</v>
       </c>
       <c r="C217" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D217" s="38"/>
-      <c r="E217" s="39"/>
-      <c r="F217" s="34"/>
+      <c r="D217" s="32"/>
+      <c r="E217" s="33"/>
+      <c r="F217" s="38"/>
       <c r="G217" s="23" t="s">
         <v>499</v>
       </c>
@@ -9272,15 +9292,15 @@
       <c r="J217" s="23"/>
     </row>
     <row r="218" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B218" s="23">
-        <v>203</v>
+      <c r="B218" s="22">
+        <v>213</v>
       </c>
       <c r="C218" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D218" s="38"/>
-      <c r="E218" s="39"/>
-      <c r="F218" s="32" t="s">
+      <c r="D218" s="32"/>
+      <c r="E218" s="33"/>
+      <c r="F218" s="37" t="s">
         <v>129</v>
       </c>
       <c r="G218" s="23" t="s">
@@ -9295,15 +9315,15 @@
       <c r="J218" s="23"/>
     </row>
     <row r="219" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B219" s="23">
-        <v>204</v>
+      <c r="B219" s="22">
+        <v>214</v>
       </c>
       <c r="C219" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D219" s="38"/>
-      <c r="E219" s="39"/>
-      <c r="F219" s="33"/>
+      <c r="D219" s="32"/>
+      <c r="E219" s="33"/>
+      <c r="F219" s="39"/>
       <c r="G219" s="23" t="s">
         <v>502</v>
       </c>
@@ -9316,15 +9336,15 @@
       <c r="J219" s="23"/>
     </row>
     <row r="220" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B220" s="23">
-        <v>205</v>
+      <c r="B220" s="22">
+        <v>215</v>
       </c>
       <c r="C220" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D220" s="38"/>
-      <c r="E220" s="39"/>
-      <c r="F220" s="33"/>
+      <c r="D220" s="32"/>
+      <c r="E220" s="33"/>
+      <c r="F220" s="39"/>
       <c r="G220" s="23" t="s">
         <v>502</v>
       </c>
@@ -9337,15 +9357,15 @@
       <c r="J220" s="23"/>
     </row>
     <row r="221" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B221" s="23">
-        <v>206</v>
+      <c r="B221" s="22">
+        <v>216</v>
       </c>
       <c r="C221" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D221" s="38"/>
-      <c r="E221" s="39"/>
-      <c r="F221" s="33"/>
+      <c r="D221" s="32"/>
+      <c r="E221" s="33"/>
+      <c r="F221" s="39"/>
       <c r="G221" s="23" t="s">
         <v>502</v>
       </c>
@@ -9358,15 +9378,15 @@
       <c r="J221" s="23"/>
     </row>
     <row r="222" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B222" s="23">
-        <v>207</v>
+      <c r="B222" s="22">
+        <v>217</v>
       </c>
       <c r="C222" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D222" s="38"/>
-      <c r="E222" s="39"/>
-      <c r="F222" s="33"/>
+      <c r="D222" s="32"/>
+      <c r="E222" s="33"/>
+      <c r="F222" s="39"/>
       <c r="G222" s="23" t="s">
         <v>502</v>
       </c>
@@ -9379,15 +9399,15 @@
       <c r="J222" s="23"/>
     </row>
     <row r="223" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B223" s="23">
-        <v>208</v>
+      <c r="B223" s="22">
+        <v>218</v>
       </c>
       <c r="C223" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D223" s="38"/>
-      <c r="E223" s="39"/>
-      <c r="F223" s="34"/>
+      <c r="D223" s="32"/>
+      <c r="E223" s="33"/>
+      <c r="F223" s="38"/>
       <c r="G223" s="23" t="s">
         <v>502</v>
       </c>
@@ -9400,15 +9420,15 @@
       <c r="J223" s="23"/>
     </row>
     <row r="224" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B224" s="23">
-        <v>209</v>
+      <c r="B224" s="22">
+        <v>219</v>
       </c>
       <c r="C224" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D224" s="38"/>
-      <c r="E224" s="39"/>
-      <c r="F224" s="32" t="s">
+      <c r="D224" s="32"/>
+      <c r="E224" s="33"/>
+      <c r="F224" s="37" t="s">
         <v>122</v>
       </c>
       <c r="G224" s="23" t="s">
@@ -9423,15 +9443,15 @@
       <c r="J224" s="23"/>
     </row>
     <row r="225" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B225" s="23">
-        <v>210</v>
+      <c r="B225" s="22">
+        <v>220</v>
       </c>
       <c r="C225" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D225" s="38"/>
-      <c r="E225" s="39"/>
-      <c r="F225" s="33"/>
+      <c r="D225" s="32"/>
+      <c r="E225" s="33"/>
+      <c r="F225" s="39"/>
       <c r="G225" s="23" t="s">
         <v>518</v>
       </c>
@@ -9444,15 +9464,15 @@
       <c r="J225" s="23"/>
     </row>
     <row r="226" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B226" s="23">
-        <v>211</v>
+      <c r="B226" s="22">
+        <v>221</v>
       </c>
       <c r="C226" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D226" s="38"/>
-      <c r="E226" s="39"/>
-      <c r="F226" s="33"/>
+      <c r="D226" s="32"/>
+      <c r="E226" s="33"/>
+      <c r="F226" s="39"/>
       <c r="G226" s="23" t="s">
         <v>521</v>
       </c>
@@ -9465,15 +9485,15 @@
       <c r="J226" s="23"/>
     </row>
     <row r="227" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B227" s="23">
-        <v>212</v>
+      <c r="B227" s="22">
+        <v>222</v>
       </c>
       <c r="C227" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D227" s="38"/>
-      <c r="E227" s="39"/>
-      <c r="F227" s="33"/>
+      <c r="D227" s="32"/>
+      <c r="E227" s="33"/>
+      <c r="F227" s="39"/>
       <c r="G227" s="23" t="s">
         <v>524</v>
       </c>
@@ -9486,15 +9506,15 @@
       <c r="J227" s="23"/>
     </row>
     <row r="228" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B228" s="23">
-        <v>213</v>
+      <c r="B228" s="22">
+        <v>223</v>
       </c>
       <c r="C228" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D228" s="38"/>
-      <c r="E228" s="39"/>
-      <c r="F228" s="33"/>
+      <c r="D228" s="32"/>
+      <c r="E228" s="33"/>
+      <c r="F228" s="39"/>
       <c r="G228" s="23" t="s">
         <v>527</v>
       </c>
@@ -9507,15 +9527,15 @@
       <c r="J228" s="23"/>
     </row>
     <row r="229" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B229" s="23">
-        <v>214</v>
+      <c r="B229" s="22">
+        <v>224</v>
       </c>
       <c r="C229" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D229" s="38"/>
-      <c r="E229" s="39"/>
-      <c r="F229" s="33"/>
+      <c r="D229" s="32"/>
+      <c r="E229" s="33"/>
+      <c r="F229" s="39"/>
       <c r="G229" s="23" t="s">
         <v>530</v>
       </c>
@@ -9528,15 +9548,15 @@
       <c r="J229" s="23"/>
     </row>
     <row r="230" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B230" s="23">
-        <v>215</v>
+      <c r="B230" s="22">
+        <v>225</v>
       </c>
       <c r="C230" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D230" s="38"/>
-      <c r="E230" s="39"/>
-      <c r="F230" s="33"/>
+      <c r="D230" s="32"/>
+      <c r="E230" s="33"/>
+      <c r="F230" s="39"/>
       <c r="G230" s="23" t="s">
         <v>533</v>
       </c>
@@ -9549,15 +9569,15 @@
       <c r="J230" s="23"/>
     </row>
     <row r="231" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B231" s="23">
-        <v>216</v>
+      <c r="B231" s="22">
+        <v>226</v>
       </c>
       <c r="C231" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D231" s="38"/>
-      <c r="E231" s="39"/>
-      <c r="F231" s="33"/>
+      <c r="D231" s="32"/>
+      <c r="E231" s="33"/>
+      <c r="F231" s="39"/>
       <c r="G231" s="23" t="s">
         <v>536</v>
       </c>
@@ -9570,15 +9590,15 @@
       <c r="J231" s="23"/>
     </row>
     <row r="232" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B232" s="23">
-        <v>217</v>
+      <c r="B232" s="22">
+        <v>227</v>
       </c>
       <c r="C232" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D232" s="38"/>
-      <c r="E232" s="39"/>
-      <c r="F232" s="33"/>
+      <c r="D232" s="32"/>
+      <c r="E232" s="33"/>
+      <c r="F232" s="39"/>
       <c r="G232" s="23" t="s">
         <v>539</v>
       </c>
@@ -9591,15 +9611,15 @@
       <c r="J232" s="23"/>
     </row>
     <row r="233" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B233" s="23">
-        <v>218</v>
+      <c r="B233" s="22">
+        <v>228</v>
       </c>
       <c r="C233" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D233" s="38"/>
-      <c r="E233" s="39"/>
-      <c r="F233" s="34"/>
+      <c r="D233" s="32"/>
+      <c r="E233" s="33"/>
+      <c r="F233" s="38"/>
       <c r="G233" s="23" t="s">
         <v>542</v>
       </c>
@@ -9612,15 +9632,15 @@
       <c r="J233" s="23"/>
     </row>
     <row r="234" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B234" s="23">
-        <v>219</v>
+      <c r="B234" s="22">
+        <v>229</v>
       </c>
       <c r="C234" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D234" s="38"/>
-      <c r="E234" s="39"/>
-      <c r="F234" s="32" t="s">
+      <c r="D234" s="32"/>
+      <c r="E234" s="33"/>
+      <c r="F234" s="37" t="s">
         <v>129</v>
       </c>
       <c r="G234" s="23" t="s">
@@ -9635,15 +9655,15 @@
       <c r="J234" s="23"/>
     </row>
     <row r="235" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B235" s="23">
-        <v>220</v>
+      <c r="B235" s="22">
+        <v>230</v>
       </c>
       <c r="C235" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D235" s="38"/>
-      <c r="E235" s="39"/>
-      <c r="F235" s="33"/>
+      <c r="D235" s="32"/>
+      <c r="E235" s="33"/>
+      <c r="F235" s="39"/>
       <c r="G235" s="23" t="s">
         <v>545</v>
       </c>
@@ -9656,15 +9676,15 @@
       <c r="J235" s="23"/>
     </row>
     <row r="236" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B236" s="23">
-        <v>221</v>
+      <c r="B236" s="22">
+        <v>231</v>
       </c>
       <c r="C236" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D236" s="38"/>
-      <c r="E236" s="39"/>
-      <c r="F236" s="33"/>
+      <c r="D236" s="32"/>
+      <c r="E236" s="33"/>
+      <c r="F236" s="39"/>
       <c r="G236" s="23" t="s">
         <v>545</v>
       </c>
@@ -9677,15 +9697,15 @@
       <c r="J236" s="23"/>
     </row>
     <row r="237" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B237" s="23">
-        <v>222</v>
+      <c r="B237" s="22">
+        <v>232</v>
       </c>
       <c r="C237" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D237" s="38"/>
-      <c r="E237" s="39"/>
-      <c r="F237" s="33"/>
+      <c r="D237" s="32"/>
+      <c r="E237" s="33"/>
+      <c r="F237" s="39"/>
       <c r="G237" s="23" t="s">
         <v>545</v>
       </c>
@@ -9698,15 +9718,15 @@
       <c r="J237" s="23"/>
     </row>
     <row r="238" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B238" s="23">
-        <v>223</v>
+      <c r="B238" s="22">
+        <v>233</v>
       </c>
       <c r="C238" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D238" s="38"/>
-      <c r="E238" s="39"/>
-      <c r="F238" s="33"/>
+      <c r="D238" s="32"/>
+      <c r="E238" s="33"/>
+      <c r="F238" s="39"/>
       <c r="G238" s="23" t="s">
         <v>545</v>
       </c>
@@ -9719,15 +9739,15 @@
       <c r="J238" s="23"/>
     </row>
     <row r="239" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B239" s="23">
-        <v>224</v>
+      <c r="B239" s="22">
+        <v>234</v>
       </c>
       <c r="C239" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D239" s="38"/>
-      <c r="E239" s="39"/>
-      <c r="F239" s="33"/>
+      <c r="D239" s="32"/>
+      <c r="E239" s="33"/>
+      <c r="F239" s="39"/>
       <c r="G239" s="23" t="s">
         <v>545</v>
       </c>
@@ -9740,15 +9760,15 @@
       <c r="J239" s="23"/>
     </row>
     <row r="240" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B240" s="23">
-        <v>225</v>
+      <c r="B240" s="22">
+        <v>235</v>
       </c>
       <c r="C240" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D240" s="38"/>
-      <c r="E240" s="39"/>
-      <c r="F240" s="33"/>
+      <c r="D240" s="32"/>
+      <c r="E240" s="33"/>
+      <c r="F240" s="39"/>
       <c r="G240" s="23" t="s">
         <v>545</v>
       </c>
@@ -9761,15 +9781,15 @@
       <c r="J240" s="23"/>
     </row>
     <row r="241" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B241" s="23">
-        <v>226</v>
+      <c r="B241" s="22">
+        <v>236</v>
       </c>
       <c r="C241" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D241" s="38"/>
-      <c r="E241" s="39"/>
-      <c r="F241" s="34"/>
+      <c r="D241" s="32"/>
+      <c r="E241" s="33"/>
+      <c r="F241" s="38"/>
       <c r="G241" s="23" t="s">
         <v>545</v>
       </c>
@@ -9782,15 +9802,15 @@
       <c r="J241" s="23"/>
     </row>
     <row r="242" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B242" s="23">
-        <v>227</v>
+      <c r="B242" s="22">
+        <v>237</v>
       </c>
       <c r="C242" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D242" s="38"/>
-      <c r="E242" s="39"/>
-      <c r="F242" s="32" t="s">
+      <c r="D242" s="32"/>
+      <c r="E242" s="33"/>
+      <c r="F242" s="37" t="s">
         <v>122</v>
       </c>
       <c r="G242" s="23" t="s">
@@ -9805,15 +9825,15 @@
       <c r="J242" s="23"/>
     </row>
     <row r="243" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B243" s="23">
-        <v>228</v>
+      <c r="B243" s="22">
+        <v>238</v>
       </c>
       <c r="C243" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D243" s="38"/>
-      <c r="E243" s="39"/>
-      <c r="F243" s="34"/>
+      <c r="D243" s="32"/>
+      <c r="E243" s="33"/>
+      <c r="F243" s="38"/>
       <c r="G243" s="23" t="s">
         <v>565</v>
       </c>
@@ -9826,15 +9846,15 @@
       <c r="J243" s="23"/>
     </row>
     <row r="244" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B244" s="23">
-        <v>229</v>
+      <c r="B244" s="22">
+        <v>239</v>
       </c>
       <c r="C244" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D244" s="38"/>
-      <c r="E244" s="39"/>
-      <c r="F244" s="32" t="s">
+      <c r="D244" s="32"/>
+      <c r="E244" s="33"/>
+      <c r="F244" s="37" t="s">
         <v>129</v>
       </c>
       <c r="G244" s="23" t="s">
@@ -9849,15 +9869,15 @@
       <c r="J244" s="23"/>
     </row>
     <row r="245" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B245" s="23">
-        <v>230</v>
+      <c r="B245" s="22">
+        <v>240</v>
       </c>
       <c r="C245" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D245" s="38"/>
-      <c r="E245" s="39"/>
-      <c r="F245" s="33"/>
+      <c r="D245" s="32"/>
+      <c r="E245" s="33"/>
+      <c r="F245" s="39"/>
       <c r="G245" s="23" t="s">
         <v>568</v>
       </c>
@@ -9870,15 +9890,15 @@
       <c r="J245" s="23"/>
     </row>
     <row r="246" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B246" s="23">
-        <v>231</v>
+      <c r="B246" s="22">
+        <v>241</v>
       </c>
       <c r="C246" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D246" s="38"/>
-      <c r="E246" s="39"/>
-      <c r="F246" s="33"/>
+      <c r="D246" s="32"/>
+      <c r="E246" s="33"/>
+      <c r="F246" s="39"/>
       <c r="G246" s="23" t="s">
         <v>568</v>
       </c>
@@ -9891,15 +9911,15 @@
       <c r="J246" s="23"/>
     </row>
     <row r="247" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B247" s="23">
-        <v>232</v>
+      <c r="B247" s="22">
+        <v>242</v>
       </c>
       <c r="C247" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D247" s="38"/>
-      <c r="E247" s="39"/>
-      <c r="F247" s="34"/>
+      <c r="D247" s="32"/>
+      <c r="E247" s="33"/>
+      <c r="F247" s="38"/>
       <c r="G247" s="23" t="s">
         <v>568</v>
       </c>
@@ -9912,15 +9932,15 @@
       <c r="J247" s="23"/>
     </row>
     <row r="248" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B248" s="23">
-        <v>233</v>
+      <c r="B248" s="22">
+        <v>243</v>
       </c>
       <c r="C248" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D248" s="38"/>
-      <c r="E248" s="39"/>
-      <c r="F248" s="32" t="s">
+      <c r="D248" s="32"/>
+      <c r="E248" s="33"/>
+      <c r="F248" s="37" t="s">
         <v>122</v>
       </c>
       <c r="G248" s="23" t="s">
@@ -9935,15 +9955,15 @@
       <c r="J248" s="23"/>
     </row>
     <row r="249" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B249" s="23">
-        <v>234</v>
+      <c r="B249" s="22">
+        <v>244</v>
       </c>
       <c r="C249" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D249" s="38"/>
-      <c r="E249" s="39"/>
-      <c r="F249" s="33"/>
+      <c r="D249" s="32"/>
+      <c r="E249" s="33"/>
+      <c r="F249" s="39"/>
       <c r="G249" s="23" t="s">
         <v>580</v>
       </c>
@@ -9956,15 +9976,15 @@
       <c r="J249" s="23"/>
     </row>
     <row r="250" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B250" s="23">
-        <v>235</v>
+      <c r="B250" s="22">
+        <v>245</v>
       </c>
       <c r="C250" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D250" s="38"/>
-      <c r="E250" s="39"/>
-      <c r="F250" s="33"/>
+      <c r="D250" s="32"/>
+      <c r="E250" s="33"/>
+      <c r="F250" s="39"/>
       <c r="G250" s="23" t="s">
         <v>583</v>
       </c>
@@ -9977,15 +9997,15 @@
       <c r="J250" s="23"/>
     </row>
     <row r="251" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B251" s="23">
-        <v>236</v>
+      <c r="B251" s="22">
+        <v>246</v>
       </c>
       <c r="C251" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D251" s="38"/>
-      <c r="E251" s="39"/>
-      <c r="F251" s="34"/>
+      <c r="D251" s="32"/>
+      <c r="E251" s="33"/>
+      <c r="F251" s="38"/>
       <c r="G251" s="23" t="s">
         <v>586</v>
       </c>
@@ -9998,15 +10018,15 @@
       <c r="J251" s="23"/>
     </row>
     <row r="252" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B252" s="23">
-        <v>237</v>
+      <c r="B252" s="22">
+        <v>247</v>
       </c>
       <c r="C252" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D252" s="38"/>
-      <c r="E252" s="39"/>
-      <c r="F252" s="32" t="s">
+      <c r="D252" s="32"/>
+      <c r="E252" s="33"/>
+      <c r="F252" s="37" t="s">
         <v>129</v>
       </c>
       <c r="G252" s="23" t="s">
@@ -10021,15 +10041,15 @@
       <c r="J252" s="23"/>
     </row>
     <row r="253" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B253" s="23">
-        <v>238</v>
+      <c r="B253" s="22">
+        <v>248</v>
       </c>
       <c r="C253" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D253" s="38"/>
-      <c r="E253" s="39"/>
-      <c r="F253" s="33"/>
+      <c r="D253" s="32"/>
+      <c r="E253" s="33"/>
+      <c r="F253" s="39"/>
       <c r="G253" s="23" t="s">
         <v>589</v>
       </c>
@@ -10042,15 +10062,15 @@
       <c r="J253" s="23"/>
     </row>
     <row r="254" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B254" s="23">
-        <v>239</v>
+      <c r="B254" s="22">
+        <v>249</v>
       </c>
       <c r="C254" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D254" s="38"/>
-      <c r="E254" s="39"/>
-      <c r="F254" s="33"/>
+      <c r="D254" s="32"/>
+      <c r="E254" s="33"/>
+      <c r="F254" s="39"/>
       <c r="G254" s="23" t="s">
         <v>589</v>
       </c>
@@ -10063,15 +10083,15 @@
       <c r="J254" s="23"/>
     </row>
     <row r="255" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B255" s="23">
-        <v>240</v>
+      <c r="B255" s="22">
+        <v>250</v>
       </c>
       <c r="C255" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D255" s="38"/>
-      <c r="E255" s="39"/>
-      <c r="F255" s="33"/>
+      <c r="D255" s="32"/>
+      <c r="E255" s="33"/>
+      <c r="F255" s="39"/>
       <c r="G255" s="23" t="s">
         <v>589</v>
       </c>
@@ -10084,15 +10104,15 @@
       <c r="J255" s="23"/>
     </row>
     <row r="256" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B256" s="23">
-        <v>241</v>
+      <c r="B256" s="22">
+        <v>251</v>
       </c>
       <c r="C256" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D256" s="38"/>
-      <c r="E256" s="39"/>
-      <c r="F256" s="33"/>
+      <c r="D256" s="32"/>
+      <c r="E256" s="33"/>
+      <c r="F256" s="39"/>
       <c r="G256" s="23" t="s">
         <v>589</v>
       </c>
@@ -10105,15 +10125,15 @@
       <c r="J256" s="23"/>
     </row>
     <row r="257" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B257" s="23">
-        <v>242</v>
+      <c r="B257" s="22">
+        <v>252</v>
       </c>
       <c r="C257" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D257" s="38"/>
-      <c r="E257" s="39"/>
-      <c r="F257" s="34"/>
+      <c r="D257" s="32"/>
+      <c r="E257" s="33"/>
+      <c r="F257" s="38"/>
       <c r="G257" s="23" t="s">
         <v>589</v>
       </c>
@@ -10126,15 +10146,15 @@
       <c r="J257" s="23"/>
     </row>
     <row r="258" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B258" s="23">
-        <v>243</v>
+      <c r="B258" s="22">
+        <v>253</v>
       </c>
       <c r="C258" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D258" s="38"/>
-      <c r="E258" s="39"/>
-      <c r="F258" s="32" t="s">
+      <c r="D258" s="32"/>
+      <c r="E258" s="33"/>
+      <c r="F258" s="37" t="s">
         <v>122</v>
       </c>
       <c r="G258" s="23" t="s">
@@ -10149,15 +10169,15 @@
       <c r="J258" s="23"/>
     </row>
     <row r="259" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B259" s="23">
-        <v>244</v>
+      <c r="B259" s="22">
+        <v>254</v>
       </c>
       <c r="C259" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D259" s="38"/>
-      <c r="E259" s="39"/>
-      <c r="F259" s="33"/>
+      <c r="D259" s="32"/>
+      <c r="E259" s="33"/>
+      <c r="F259" s="39"/>
       <c r="G259" s="23" t="s">
         <v>605</v>
       </c>
@@ -10170,15 +10190,15 @@
       <c r="J259" s="23"/>
     </row>
     <row r="260" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B260" s="23">
-        <v>245</v>
+      <c r="B260" s="22">
+        <v>255</v>
       </c>
       <c r="C260" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D260" s="38"/>
-      <c r="E260" s="39"/>
-      <c r="F260" s="33"/>
+      <c r="D260" s="32"/>
+      <c r="E260" s="33"/>
+      <c r="F260" s="39"/>
       <c r="G260" s="23" t="s">
         <v>608</v>
       </c>
@@ -10191,15 +10211,15 @@
       <c r="J260" s="23"/>
     </row>
     <row r="261" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B261" s="23">
-        <v>246</v>
+      <c r="B261" s="22">
+        <v>256</v>
       </c>
       <c r="C261" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D261" s="38"/>
-      <c r="E261" s="39"/>
-      <c r="F261" s="33"/>
+      <c r="D261" s="32"/>
+      <c r="E261" s="33"/>
+      <c r="F261" s="39"/>
       <c r="G261" s="23" t="s">
         <v>611</v>
       </c>
@@ -10212,15 +10232,15 @@
       <c r="J261" s="23"/>
     </row>
     <row r="262" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B262" s="23">
-        <v>247</v>
+      <c r="B262" s="22">
+        <v>257</v>
       </c>
       <c r="C262" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D262" s="38"/>
-      <c r="E262" s="39"/>
-      <c r="F262" s="34"/>
+      <c r="D262" s="32"/>
+      <c r="E262" s="33"/>
+      <c r="F262" s="38"/>
       <c r="G262" s="23" t="s">
         <v>28</v>
       </c>
@@ -10233,15 +10253,15 @@
       <c r="J262" s="23"/>
     </row>
     <row r="263" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B263" s="23">
-        <v>248</v>
+      <c r="B263" s="22">
+        <v>258</v>
       </c>
       <c r="C263" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D263" s="38"/>
-      <c r="E263" s="39"/>
-      <c r="F263" s="32" t="s">
+      <c r="D263" s="32"/>
+      <c r="E263" s="33"/>
+      <c r="F263" s="37" t="s">
         <v>616</v>
       </c>
       <c r="G263" s="23" t="s">
@@ -10256,15 +10276,15 @@
       <c r="J263" s="23"/>
     </row>
     <row r="264" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B264" s="23">
-        <v>249</v>
+      <c r="B264" s="22">
+        <v>259</v>
       </c>
       <c r="C264" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D264" s="38"/>
-      <c r="E264" s="39"/>
-      <c r="F264" s="33"/>
+      <c r="D264" s="32"/>
+      <c r="E264" s="33"/>
+      <c r="F264" s="39"/>
       <c r="G264" s="23" t="s">
         <v>617</v>
       </c>
@@ -10277,15 +10297,15 @@
       <c r="J264" s="23"/>
     </row>
     <row r="265" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B265" s="23">
-        <v>250</v>
+      <c r="B265" s="22">
+        <v>260</v>
       </c>
       <c r="C265" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D265" s="38"/>
-      <c r="E265" s="39"/>
-      <c r="F265" s="33"/>
+      <c r="D265" s="32"/>
+      <c r="E265" s="33"/>
+      <c r="F265" s="39"/>
       <c r="G265" s="23" t="s">
         <v>617</v>
       </c>
@@ -10298,15 +10318,15 @@
       <c r="J265" s="23"/>
     </row>
     <row r="266" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B266" s="23">
-        <v>251</v>
+      <c r="B266" s="22">
+        <v>261</v>
       </c>
       <c r="C266" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D266" s="38"/>
-      <c r="E266" s="39"/>
-      <c r="F266" s="33"/>
+      <c r="D266" s="32"/>
+      <c r="E266" s="33"/>
+      <c r="F266" s="39"/>
       <c r="G266" s="23" t="s">
         <v>617</v>
       </c>
@@ -10319,15 +10339,15 @@
       <c r="J266" s="23"/>
     </row>
     <row r="267" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B267" s="23">
-        <v>252</v>
+      <c r="B267" s="22">
+        <v>262</v>
       </c>
       <c r="C267" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D267" s="38"/>
-      <c r="E267" s="39"/>
-      <c r="F267" s="33"/>
+      <c r="D267" s="32"/>
+      <c r="E267" s="33"/>
+      <c r="F267" s="39"/>
       <c r="G267" s="23" t="s">
         <v>617</v>
       </c>
@@ -10340,15 +10360,15 @@
       <c r="J267" s="23"/>
     </row>
     <row r="268" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B268" s="23">
-        <v>253</v>
+      <c r="B268" s="22">
+        <v>263</v>
       </c>
       <c r="C268" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D268" s="38"/>
-      <c r="E268" s="39"/>
-      <c r="F268" s="33"/>
+      <c r="D268" s="32"/>
+      <c r="E268" s="33"/>
+      <c r="F268" s="39"/>
       <c r="G268" s="23" t="s">
         <v>617</v>
       </c>
@@ -10361,15 +10381,15 @@
       <c r="J268" s="23"/>
     </row>
     <row r="269" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B269" s="23">
-        <v>254</v>
+      <c r="B269" s="22">
+        <v>264</v>
       </c>
       <c r="C269" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D269" s="38"/>
-      <c r="E269" s="39"/>
-      <c r="F269" s="33"/>
+      <c r="D269" s="32"/>
+      <c r="E269" s="33"/>
+      <c r="F269" s="39"/>
       <c r="G269" s="23" t="s">
         <v>617</v>
       </c>
@@ -10382,15 +10402,15 @@
       <c r="J269" s="23"/>
     </row>
     <row r="270" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B270" s="23">
-        <v>255</v>
+      <c r="B270" s="22">
+        <v>265</v>
       </c>
       <c r="C270" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D270" s="38"/>
-      <c r="E270" s="39"/>
-      <c r="F270" s="33"/>
+      <c r="D270" s="32"/>
+      <c r="E270" s="33"/>
+      <c r="F270" s="39"/>
       <c r="G270" s="23" t="s">
         <v>617</v>
       </c>
@@ -10403,15 +10423,15 @@
       <c r="J270" s="23"/>
     </row>
     <row r="271" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B271" s="23">
-        <v>256</v>
+      <c r="B271" s="22">
+        <v>266</v>
       </c>
       <c r="C271" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D271" s="38"/>
-      <c r="E271" s="39"/>
-      <c r="F271" s="33"/>
+      <c r="D271" s="32"/>
+      <c r="E271" s="33"/>
+      <c r="F271" s="39"/>
       <c r="G271" s="23" t="s">
         <v>617</v>
       </c>
@@ -10424,15 +10444,15 @@
       <c r="J271" s="23"/>
     </row>
     <row r="272" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B272" s="23">
-        <v>257</v>
+      <c r="B272" s="22">
+        <v>267</v>
       </c>
       <c r="C272" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D272" s="38"/>
-      <c r="E272" s="39"/>
-      <c r="F272" s="33"/>
+      <c r="D272" s="32"/>
+      <c r="E272" s="33"/>
+      <c r="F272" s="39"/>
       <c r="G272" s="23" t="s">
         <v>617</v>
       </c>
@@ -10445,15 +10465,15 @@
       <c r="J272" s="23"/>
     </row>
     <row r="273" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B273" s="23">
-        <v>258</v>
+      <c r="B273" s="22">
+        <v>268</v>
       </c>
       <c r="C273" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D273" s="38"/>
-      <c r="E273" s="39"/>
-      <c r="F273" s="33"/>
+      <c r="D273" s="32"/>
+      <c r="E273" s="33"/>
+      <c r="F273" s="39"/>
       <c r="G273" s="23" t="s">
         <v>617</v>
       </c>
@@ -10466,15 +10486,15 @@
       <c r="J273" s="23"/>
     </row>
     <row r="274" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B274" s="23">
-        <v>259</v>
+      <c r="B274" s="22">
+        <v>269</v>
       </c>
       <c r="C274" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D274" s="38"/>
-      <c r="E274" s="39"/>
-      <c r="F274" s="33"/>
+      <c r="D274" s="32"/>
+      <c r="E274" s="33"/>
+      <c r="F274" s="39"/>
       <c r="G274" s="23" t="s">
         <v>617</v>
       </c>
@@ -10487,15 +10507,15 @@
       <c r="J274" s="23"/>
     </row>
     <row r="275" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B275" s="23">
-        <v>260</v>
+      <c r="B275" s="22">
+        <v>270</v>
       </c>
       <c r="C275" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D275" s="38"/>
-      <c r="E275" s="39"/>
-      <c r="F275" s="33"/>
+      <c r="D275" s="32"/>
+      <c r="E275" s="33"/>
+      <c r="F275" s="39"/>
       <c r="G275" s="23" t="s">
         <v>642</v>
       </c>
@@ -10508,15 +10528,15 @@
       <c r="J275" s="23"/>
     </row>
     <row r="276" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B276" s="23">
-        <v>261</v>
+      <c r="B276" s="22">
+        <v>271</v>
       </c>
       <c r="C276" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D276" s="38"/>
-      <c r="E276" s="39"/>
-      <c r="F276" s="33"/>
+      <c r="D276" s="32"/>
+      <c r="E276" s="33"/>
+      <c r="F276" s="39"/>
       <c r="G276" s="23" t="s">
         <v>642</v>
       </c>
@@ -10529,15 +10549,15 @@
       <c r="J276" s="23"/>
     </row>
     <row r="277" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B277" s="23">
-        <v>262</v>
+      <c r="B277" s="22">
+        <v>272</v>
       </c>
       <c r="C277" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D277" s="38"/>
-      <c r="E277" s="39"/>
-      <c r="F277" s="33"/>
+      <c r="D277" s="32"/>
+      <c r="E277" s="33"/>
+      <c r="F277" s="39"/>
       <c r="G277" s="23" t="s">
         <v>642</v>
       </c>
@@ -10550,15 +10570,15 @@
       <c r="J277" s="23"/>
     </row>
     <row r="278" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B278" s="23">
-        <v>263</v>
+      <c r="B278" s="22">
+        <v>273</v>
       </c>
       <c r="C278" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D278" s="38"/>
-      <c r="E278" s="39"/>
-      <c r="F278" s="33"/>
+      <c r="D278" s="32"/>
+      <c r="E278" s="33"/>
+      <c r="F278" s="39"/>
       <c r="G278" s="23" t="s">
         <v>642</v>
       </c>
@@ -10571,15 +10591,15 @@
       <c r="J278" s="23"/>
     </row>
     <row r="279" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B279" s="23">
-        <v>264</v>
+      <c r="B279" s="22">
+        <v>274</v>
       </c>
       <c r="C279" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D279" s="38"/>
-      <c r="E279" s="39"/>
-      <c r="F279" s="33"/>
+      <c r="D279" s="32"/>
+      <c r="E279" s="33"/>
+      <c r="F279" s="39"/>
       <c r="G279" s="23" t="s">
         <v>642</v>
       </c>
@@ -10592,15 +10612,15 @@
       <c r="J279" s="23"/>
     </row>
     <row r="280" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B280" s="23">
-        <v>265</v>
+      <c r="B280" s="22">
+        <v>275</v>
       </c>
       <c r="C280" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D280" s="38"/>
-      <c r="E280" s="39"/>
-      <c r="F280" s="33"/>
+      <c r="D280" s="32"/>
+      <c r="E280" s="33"/>
+      <c r="F280" s="39"/>
       <c r="G280" s="23" t="s">
         <v>642</v>
       </c>
@@ -10613,15 +10633,15 @@
       <c r="J280" s="23"/>
     </row>
     <row r="281" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B281" s="23">
-        <v>266</v>
+      <c r="B281" s="22">
+        <v>276</v>
       </c>
       <c r="C281" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D281" s="38"/>
-      <c r="E281" s="39"/>
-      <c r="F281" s="33"/>
+      <c r="D281" s="32"/>
+      <c r="E281" s="33"/>
+      <c r="F281" s="39"/>
       <c r="G281" s="23" t="s">
         <v>642</v>
       </c>
@@ -10634,15 +10654,15 @@
       <c r="J281" s="23"/>
     </row>
     <row r="282" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B282" s="23">
-        <v>267</v>
+      <c r="B282" s="22">
+        <v>277</v>
       </c>
       <c r="C282" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D282" s="38"/>
-      <c r="E282" s="39"/>
-      <c r="F282" s="33"/>
+      <c r="D282" s="32"/>
+      <c r="E282" s="33"/>
+      <c r="F282" s="39"/>
       <c r="G282" s="23" t="s">
         <v>642</v>
       </c>
@@ -10655,15 +10675,15 @@
       <c r="J282" s="23"/>
     </row>
     <row r="283" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B283" s="23">
-        <v>268</v>
+      <c r="B283" s="22">
+        <v>278</v>
       </c>
       <c r="C283" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D283" s="38"/>
-      <c r="E283" s="39"/>
-      <c r="F283" s="33"/>
+      <c r="D283" s="32"/>
+      <c r="E283" s="33"/>
+      <c r="F283" s="39"/>
       <c r="G283" s="23" t="s">
         <v>642</v>
       </c>
@@ -10676,15 +10696,15 @@
       <c r="J283" s="23"/>
     </row>
     <row r="284" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B284" s="23">
-        <v>269</v>
+      <c r="B284" s="22">
+        <v>279</v>
       </c>
       <c r="C284" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D284" s="38"/>
-      <c r="E284" s="39"/>
-      <c r="F284" s="33"/>
+      <c r="D284" s="32"/>
+      <c r="E284" s="33"/>
+      <c r="F284" s="39"/>
       <c r="G284" s="23" t="s">
         <v>642</v>
       </c>
@@ -10697,15 +10717,15 @@
       <c r="J284" s="23"/>
     </row>
     <row r="285" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B285" s="23">
-        <v>270</v>
+      <c r="B285" s="22">
+        <v>280</v>
       </c>
       <c r="C285" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D285" s="38"/>
-      <c r="E285" s="39"/>
-      <c r="F285" s="33"/>
+      <c r="D285" s="32"/>
+      <c r="E285" s="33"/>
+      <c r="F285" s="39"/>
       <c r="G285" s="23" t="s">
         <v>642</v>
       </c>
@@ -10718,15 +10738,15 @@
       <c r="J285" s="23"/>
     </row>
     <row r="286" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B286" s="23">
-        <v>271</v>
+      <c r="B286" s="22">
+        <v>281</v>
       </c>
       <c r="C286" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D286" s="38"/>
-      <c r="E286" s="39"/>
-      <c r="F286" s="33"/>
+      <c r="D286" s="32"/>
+      <c r="E286" s="33"/>
+      <c r="F286" s="39"/>
       <c r="G286" s="23" t="s">
         <v>642</v>
       </c>
@@ -10739,15 +10759,15 @@
       <c r="J286" s="23"/>
     </row>
     <row r="287" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B287" s="23">
-        <v>272</v>
+      <c r="B287" s="22">
+        <v>282</v>
       </c>
       <c r="C287" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D287" s="38"/>
-      <c r="E287" s="39"/>
-      <c r="F287" s="33"/>
+      <c r="D287" s="32"/>
+      <c r="E287" s="33"/>
+      <c r="F287" s="39"/>
       <c r="G287" s="23" t="s">
         <v>667</v>
       </c>
@@ -10760,15 +10780,15 @@
       <c r="J287" s="23"/>
     </row>
     <row r="288" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B288" s="23">
-        <v>273</v>
+      <c r="B288" s="22">
+        <v>283</v>
       </c>
       <c r="C288" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D288" s="38"/>
-      <c r="E288" s="39"/>
-      <c r="F288" s="33"/>
+      <c r="D288" s="32"/>
+      <c r="E288" s="33"/>
+      <c r="F288" s="39"/>
       <c r="G288" s="23" t="s">
         <v>667</v>
       </c>
@@ -10781,15 +10801,15 @@
       <c r="J288" s="23"/>
     </row>
     <row r="289" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B289" s="23">
-        <v>274</v>
+      <c r="B289" s="22">
+        <v>284</v>
       </c>
       <c r="C289" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D289" s="38"/>
-      <c r="E289" s="39"/>
-      <c r="F289" s="33"/>
+      <c r="D289" s="32"/>
+      <c r="E289" s="33"/>
+      <c r="F289" s="39"/>
       <c r="G289" s="23" t="s">
         <v>667</v>
       </c>
@@ -10802,15 +10822,15 @@
       <c r="J289" s="23"/>
     </row>
     <row r="290" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B290" s="23">
-        <v>275</v>
+      <c r="B290" s="22">
+        <v>285</v>
       </c>
       <c r="C290" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D290" s="38"/>
-      <c r="E290" s="39"/>
-      <c r="F290" s="33"/>
+      <c r="D290" s="32"/>
+      <c r="E290" s="33"/>
+      <c r="F290" s="39"/>
       <c r="G290" s="23" t="s">
         <v>667</v>
       </c>
@@ -10823,15 +10843,15 @@
       <c r="J290" s="23"/>
     </row>
     <row r="291" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B291" s="23">
-        <v>276</v>
+      <c r="B291" s="22">
+        <v>286</v>
       </c>
       <c r="C291" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D291" s="38"/>
-      <c r="E291" s="39"/>
-      <c r="F291" s="33"/>
+      <c r="D291" s="32"/>
+      <c r="E291" s="33"/>
+      <c r="F291" s="39"/>
       <c r="G291" s="23" t="s">
         <v>667</v>
       </c>
@@ -10844,15 +10864,15 @@
       <c r="J291" s="23"/>
     </row>
     <row r="292" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B292" s="23">
-        <v>277</v>
+      <c r="B292" s="22">
+        <v>287</v>
       </c>
       <c r="C292" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D292" s="38"/>
-      <c r="E292" s="39"/>
-      <c r="F292" s="33"/>
+      <c r="D292" s="32"/>
+      <c r="E292" s="33"/>
+      <c r="F292" s="39"/>
       <c r="G292" s="23" t="s">
         <v>667</v>
       </c>
@@ -10865,15 +10885,15 @@
       <c r="J292" s="23"/>
     </row>
     <row r="293" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B293" s="23">
-        <v>278</v>
+      <c r="B293" s="22">
+        <v>288</v>
       </c>
       <c r="C293" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D293" s="38"/>
-      <c r="E293" s="39"/>
-      <c r="F293" s="33"/>
+      <c r="D293" s="32"/>
+      <c r="E293" s="33"/>
+      <c r="F293" s="39"/>
       <c r="G293" s="23" t="s">
         <v>667</v>
       </c>
@@ -10886,15 +10906,15 @@
       <c r="J293" s="23"/>
     </row>
     <row r="294" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B294" s="23">
-        <v>279</v>
+      <c r="B294" s="22">
+        <v>289</v>
       </c>
       <c r="C294" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D294" s="38"/>
-      <c r="E294" s="39"/>
-      <c r="F294" s="33"/>
+      <c r="D294" s="32"/>
+      <c r="E294" s="33"/>
+      <c r="F294" s="39"/>
       <c r="G294" s="23" t="s">
         <v>667</v>
       </c>
@@ -10907,15 +10927,15 @@
       <c r="J294" s="23"/>
     </row>
     <row r="295" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B295" s="23">
-        <v>280</v>
+      <c r="B295" s="22">
+        <v>290</v>
       </c>
       <c r="C295" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D295" s="38"/>
-      <c r="E295" s="39"/>
-      <c r="F295" s="33"/>
+      <c r="D295" s="32"/>
+      <c r="E295" s="33"/>
+      <c r="F295" s="39"/>
       <c r="G295" s="23" t="s">
         <v>667</v>
       </c>
@@ -10928,15 +10948,15 @@
       <c r="J295" s="23"/>
     </row>
     <row r="296" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B296" s="23">
-        <v>281</v>
+      <c r="B296" s="22">
+        <v>291</v>
       </c>
       <c r="C296" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D296" s="38"/>
-      <c r="E296" s="39"/>
-      <c r="F296" s="33"/>
+      <c r="D296" s="32"/>
+      <c r="E296" s="33"/>
+      <c r="F296" s="39"/>
       <c r="G296" s="23" t="s">
         <v>667</v>
       </c>
@@ -10949,15 +10969,15 @@
       <c r="J296" s="23"/>
     </row>
     <row r="297" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B297" s="23">
-        <v>282</v>
+      <c r="B297" s="22">
+        <v>292</v>
       </c>
       <c r="C297" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D297" s="38"/>
-      <c r="E297" s="39"/>
-      <c r="F297" s="33"/>
+      <c r="D297" s="32"/>
+      <c r="E297" s="33"/>
+      <c r="F297" s="39"/>
       <c r="G297" s="23" t="s">
         <v>667</v>
       </c>
@@ -10970,15 +10990,15 @@
       <c r="J297" s="23"/>
     </row>
     <row r="298" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B298" s="23">
-        <v>283</v>
+      <c r="B298" s="22">
+        <v>293</v>
       </c>
       <c r="C298" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D298" s="38"/>
-      <c r="E298" s="39"/>
-      <c r="F298" s="33"/>
+      <c r="D298" s="32"/>
+      <c r="E298" s="33"/>
+      <c r="F298" s="39"/>
       <c r="G298" s="23" t="s">
         <v>667</v>
       </c>
@@ -10991,15 +11011,15 @@
       <c r="J298" s="23"/>
     </row>
     <row r="299" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B299" s="23">
-        <v>284</v>
+      <c r="B299" s="22">
+        <v>294</v>
       </c>
       <c r="C299" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D299" s="38"/>
-      <c r="E299" s="39"/>
-      <c r="F299" s="33"/>
+      <c r="D299" s="32"/>
+      <c r="E299" s="33"/>
+      <c r="F299" s="39"/>
       <c r="G299" s="23" t="s">
         <v>692</v>
       </c>
@@ -11012,15 +11032,15 @@
       <c r="J299" s="23"/>
     </row>
     <row r="300" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B300" s="23">
-        <v>285</v>
+      <c r="B300" s="22">
+        <v>295</v>
       </c>
       <c r="C300" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D300" s="38"/>
-      <c r="E300" s="39"/>
-      <c r="F300" s="33"/>
+      <c r="D300" s="32"/>
+      <c r="E300" s="33"/>
+      <c r="F300" s="39"/>
       <c r="G300" s="23" t="s">
         <v>692</v>
       </c>
@@ -11033,15 +11053,15 @@
       <c r="J300" s="23"/>
     </row>
     <row r="301" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B301" s="23">
-        <v>286</v>
+      <c r="B301" s="22">
+        <v>296</v>
       </c>
       <c r="C301" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D301" s="38"/>
-      <c r="E301" s="39"/>
-      <c r="F301" s="33"/>
+      <c r="D301" s="32"/>
+      <c r="E301" s="33"/>
+      <c r="F301" s="39"/>
       <c r="G301" s="23" t="s">
         <v>692</v>
       </c>
@@ -11054,15 +11074,15 @@
       <c r="J301" s="23"/>
     </row>
     <row r="302" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B302" s="23">
-        <v>287</v>
+      <c r="B302" s="22">
+        <v>297</v>
       </c>
       <c r="C302" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D302" s="38"/>
-      <c r="E302" s="39"/>
-      <c r="F302" s="33"/>
+      <c r="D302" s="32"/>
+      <c r="E302" s="33"/>
+      <c r="F302" s="39"/>
       <c r="G302" s="23" t="s">
         <v>692</v>
       </c>
@@ -11075,15 +11095,15 @@
       <c r="J302" s="23"/>
     </row>
     <row r="303" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B303" s="23">
-        <v>288</v>
+      <c r="B303" s="22">
+        <v>298</v>
       </c>
       <c r="C303" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D303" s="38"/>
-      <c r="E303" s="39"/>
-      <c r="F303" s="33"/>
+      <c r="D303" s="32"/>
+      <c r="E303" s="33"/>
+      <c r="F303" s="39"/>
       <c r="G303" s="23" t="s">
         <v>692</v>
       </c>
@@ -11096,15 +11116,15 @@
       <c r="J303" s="23"/>
     </row>
     <row r="304" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B304" s="23">
-        <v>289</v>
+      <c r="B304" s="22">
+        <v>299</v>
       </c>
       <c r="C304" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D304" s="38"/>
-      <c r="E304" s="39"/>
-      <c r="F304" s="33"/>
+      <c r="D304" s="32"/>
+      <c r="E304" s="33"/>
+      <c r="F304" s="39"/>
       <c r="G304" s="23" t="s">
         <v>692</v>
       </c>
@@ -11117,15 +11137,15 @@
       <c r="J304" s="23"/>
     </row>
     <row r="305" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B305" s="23">
-        <v>290</v>
+      <c r="B305" s="22">
+        <v>300</v>
       </c>
       <c r="C305" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D305" s="38"/>
-      <c r="E305" s="39"/>
-      <c r="F305" s="33"/>
+      <c r="D305" s="32"/>
+      <c r="E305" s="33"/>
+      <c r="F305" s="39"/>
       <c r="G305" s="23" t="s">
         <v>692</v>
       </c>
@@ -11138,15 +11158,15 @@
       <c r="J305" s="23"/>
     </row>
     <row r="306" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B306" s="23">
-        <v>291</v>
+      <c r="B306" s="22">
+        <v>301</v>
       </c>
       <c r="C306" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D306" s="38"/>
-      <c r="E306" s="39"/>
-      <c r="F306" s="33"/>
+      <c r="D306" s="32"/>
+      <c r="E306" s="33"/>
+      <c r="F306" s="39"/>
       <c r="G306" s="23" t="s">
         <v>692</v>
       </c>
@@ -11159,15 +11179,15 @@
       <c r="J306" s="23"/>
     </row>
     <row r="307" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B307" s="23">
-        <v>292</v>
+      <c r="B307" s="22">
+        <v>302</v>
       </c>
       <c r="C307" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D307" s="38"/>
-      <c r="E307" s="39"/>
-      <c r="F307" s="33"/>
+      <c r="D307" s="32"/>
+      <c r="E307" s="33"/>
+      <c r="F307" s="39"/>
       <c r="G307" s="23" t="s">
         <v>692</v>
       </c>
@@ -11180,15 +11200,15 @@
       <c r="J307" s="23"/>
     </row>
     <row r="308" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B308" s="23">
-        <v>293</v>
+      <c r="B308" s="22">
+        <v>303</v>
       </c>
       <c r="C308" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D308" s="38"/>
-      <c r="E308" s="39"/>
-      <c r="F308" s="33"/>
+      <c r="D308" s="32"/>
+      <c r="E308" s="33"/>
+      <c r="F308" s="39"/>
       <c r="G308" s="23" t="s">
         <v>692</v>
       </c>
@@ -11201,15 +11221,15 @@
       <c r="J308" s="23"/>
     </row>
     <row r="309" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B309" s="23">
-        <v>294</v>
+      <c r="B309" s="22">
+        <v>304</v>
       </c>
       <c r="C309" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D309" s="38"/>
-      <c r="E309" s="39"/>
-      <c r="F309" s="33"/>
+      <c r="D309" s="32"/>
+      <c r="E309" s="33"/>
+      <c r="F309" s="39"/>
       <c r="G309" s="23" t="s">
         <v>692</v>
       </c>
@@ -11222,15 +11242,15 @@
       <c r="J309" s="23"/>
     </row>
     <row r="310" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B310" s="23">
-        <v>295</v>
+      <c r="B310" s="22">
+        <v>305</v>
       </c>
       <c r="C310" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D310" s="38"/>
-      <c r="E310" s="39"/>
-      <c r="F310" s="33"/>
+      <c r="D310" s="32"/>
+      <c r="E310" s="33"/>
+      <c r="F310" s="39"/>
       <c r="G310" s="23" t="s">
         <v>692</v>
       </c>
@@ -11243,15 +11263,15 @@
       <c r="J310" s="23"/>
     </row>
     <row r="311" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B311" s="23">
-        <v>296</v>
+      <c r="B311" s="22">
+        <v>306</v>
       </c>
       <c r="C311" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D311" s="38"/>
-      <c r="E311" s="39"/>
-      <c r="F311" s="33"/>
+      <c r="D311" s="32"/>
+      <c r="E311" s="33"/>
+      <c r="F311" s="39"/>
       <c r="G311" s="23" t="s">
         <v>717</v>
       </c>
@@ -11264,15 +11284,15 @@
       <c r="J311" s="23"/>
     </row>
     <row r="312" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B312" s="23">
-        <v>297</v>
+      <c r="B312" s="22">
+        <v>307</v>
       </c>
       <c r="C312" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D312" s="38"/>
-      <c r="E312" s="39"/>
-      <c r="F312" s="33"/>
+      <c r="D312" s="32"/>
+      <c r="E312" s="33"/>
+      <c r="F312" s="39"/>
       <c r="G312" s="23" t="s">
         <v>717</v>
       </c>
@@ -11285,15 +11305,15 @@
       <c r="J312" s="23"/>
     </row>
     <row r="313" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B313" s="23">
-        <v>298</v>
+      <c r="B313" s="22">
+        <v>308</v>
       </c>
       <c r="C313" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D313" s="38"/>
-      <c r="E313" s="39"/>
-      <c r="F313" s="33"/>
+      <c r="D313" s="32"/>
+      <c r="E313" s="33"/>
+      <c r="F313" s="39"/>
       <c r="G313" s="23" t="s">
         <v>717</v>
       </c>
@@ -11306,15 +11326,15 @@
       <c r="J313" s="23"/>
     </row>
     <row r="314" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B314" s="23">
-        <v>299</v>
+      <c r="B314" s="22">
+        <v>309</v>
       </c>
       <c r="C314" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D314" s="38"/>
-      <c r="E314" s="39"/>
-      <c r="F314" s="33"/>
+      <c r="D314" s="32"/>
+      <c r="E314" s="33"/>
+      <c r="F314" s="39"/>
       <c r="G314" s="23" t="s">
         <v>717</v>
       </c>
@@ -11327,15 +11347,15 @@
       <c r="J314" s="23"/>
     </row>
     <row r="315" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B315" s="23">
-        <v>300</v>
+      <c r="B315" s="22">
+        <v>310</v>
       </c>
       <c r="C315" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D315" s="38"/>
-      <c r="E315" s="39"/>
-      <c r="F315" s="33"/>
+      <c r="D315" s="32"/>
+      <c r="E315" s="33"/>
+      <c r="F315" s="39"/>
       <c r="G315" s="23" t="s">
         <v>717</v>
       </c>
@@ -11348,15 +11368,15 @@
       <c r="J315" s="23"/>
     </row>
     <row r="316" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B316" s="23">
-        <v>301</v>
+      <c r="B316" s="22">
+        <v>311</v>
       </c>
       <c r="C316" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D316" s="38"/>
-      <c r="E316" s="39"/>
-      <c r="F316" s="33"/>
+      <c r="D316" s="32"/>
+      <c r="E316" s="33"/>
+      <c r="F316" s="39"/>
       <c r="G316" s="23" t="s">
         <v>717</v>
       </c>
@@ -11369,15 +11389,15 @@
       <c r="J316" s="23"/>
     </row>
     <row r="317" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B317" s="23">
-        <v>302</v>
+      <c r="B317" s="22">
+        <v>312</v>
       </c>
       <c r="C317" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D317" s="38"/>
-      <c r="E317" s="39"/>
-      <c r="F317" s="33"/>
+      <c r="D317" s="32"/>
+      <c r="E317" s="33"/>
+      <c r="F317" s="39"/>
       <c r="G317" s="23" t="s">
         <v>717</v>
       </c>
@@ -11390,15 +11410,15 @@
       <c r="J317" s="23"/>
     </row>
     <row r="318" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B318" s="23">
-        <v>303</v>
+      <c r="B318" s="22">
+        <v>313</v>
       </c>
       <c r="C318" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D318" s="38"/>
-      <c r="E318" s="39"/>
-      <c r="F318" s="33"/>
+      <c r="D318" s="32"/>
+      <c r="E318" s="33"/>
+      <c r="F318" s="39"/>
       <c r="G318" s="23" t="s">
         <v>717</v>
       </c>
@@ -11411,15 +11431,15 @@
       <c r="J318" s="23"/>
     </row>
     <row r="319" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B319" s="23">
-        <v>304</v>
+      <c r="B319" s="22">
+        <v>314</v>
       </c>
       <c r="C319" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D319" s="38"/>
-      <c r="E319" s="39"/>
-      <c r="F319" s="33"/>
+      <c r="D319" s="32"/>
+      <c r="E319" s="33"/>
+      <c r="F319" s="39"/>
       <c r="G319" s="23" t="s">
         <v>717</v>
       </c>
@@ -11432,15 +11452,15 @@
       <c r="J319" s="23"/>
     </row>
     <row r="320" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B320" s="23">
-        <v>305</v>
+      <c r="B320" s="22">
+        <v>315</v>
       </c>
       <c r="C320" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D320" s="38"/>
-      <c r="E320" s="39"/>
-      <c r="F320" s="33"/>
+      <c r="D320" s="32"/>
+      <c r="E320" s="33"/>
+      <c r="F320" s="39"/>
       <c r="G320" s="23" t="s">
         <v>717</v>
       </c>
@@ -11453,15 +11473,15 @@
       <c r="J320" s="23"/>
     </row>
     <row r="321" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B321" s="23">
-        <v>306</v>
+      <c r="B321" s="22">
+        <v>316</v>
       </c>
       <c r="C321" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D321" s="38"/>
-      <c r="E321" s="39"/>
-      <c r="F321" s="33"/>
+      <c r="D321" s="32"/>
+      <c r="E321" s="33"/>
+      <c r="F321" s="39"/>
       <c r="G321" s="23" t="s">
         <v>717</v>
       </c>
@@ -11474,15 +11494,15 @@
       <c r="J321" s="23"/>
     </row>
     <row r="322" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B322" s="23">
-        <v>307</v>
+      <c r="B322" s="22">
+        <v>317</v>
       </c>
       <c r="C322" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D322" s="38"/>
-      <c r="E322" s="39"/>
-      <c r="F322" s="33"/>
+      <c r="D322" s="32"/>
+      <c r="E322" s="33"/>
+      <c r="F322" s="39"/>
       <c r="G322" s="23" t="s">
         <v>717</v>
       </c>
@@ -11495,15 +11515,15 @@
       <c r="J322" s="23"/>
     </row>
     <row r="323" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B323" s="23">
-        <v>308</v>
+      <c r="B323" s="22">
+        <v>318</v>
       </c>
       <c r="C323" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D323" s="38"/>
-      <c r="E323" s="39"/>
-      <c r="F323" s="33"/>
+      <c r="D323" s="32"/>
+      <c r="E323" s="33"/>
+      <c r="F323" s="39"/>
       <c r="G323" s="23" t="s">
         <v>742</v>
       </c>
@@ -11516,15 +11536,15 @@
       <c r="J323" s="23"/>
     </row>
     <row r="324" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B324" s="23">
-        <v>309</v>
+      <c r="B324" s="22">
+        <v>319</v>
       </c>
       <c r="C324" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D324" s="38"/>
-      <c r="E324" s="39"/>
-      <c r="F324" s="33"/>
+      <c r="D324" s="32"/>
+      <c r="E324" s="33"/>
+      <c r="F324" s="39"/>
       <c r="G324" s="23" t="s">
         <v>742</v>
       </c>
@@ -11537,15 +11557,15 @@
       <c r="J324" s="23"/>
     </row>
     <row r="325" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B325" s="23">
-        <v>310</v>
+      <c r="B325" s="22">
+        <v>320</v>
       </c>
       <c r="C325" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D325" s="38"/>
-      <c r="E325" s="39"/>
-      <c r="F325" s="33"/>
+      <c r="D325" s="32"/>
+      <c r="E325" s="33"/>
+      <c r="F325" s="39"/>
       <c r="G325" s="23" t="s">
         <v>742</v>
       </c>
@@ -11558,15 +11578,15 @@
       <c r="J325" s="23"/>
     </row>
     <row r="326" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B326" s="23">
-        <v>311</v>
+      <c r="B326" s="22">
+        <v>321</v>
       </c>
       <c r="C326" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D326" s="38"/>
-      <c r="E326" s="39"/>
-      <c r="F326" s="33"/>
+      <c r="D326" s="32"/>
+      <c r="E326" s="33"/>
+      <c r="F326" s="39"/>
       <c r="G326" s="23" t="s">
         <v>742</v>
       </c>
@@ -11579,15 +11599,15 @@
       <c r="J326" s="23"/>
     </row>
     <row r="327" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B327" s="23">
-        <v>312</v>
+      <c r="B327" s="22">
+        <v>322</v>
       </c>
       <c r="C327" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D327" s="38"/>
-      <c r="E327" s="39"/>
-      <c r="F327" s="33"/>
+      <c r="D327" s="32"/>
+      <c r="E327" s="33"/>
+      <c r="F327" s="39"/>
       <c r="G327" s="23" t="s">
         <v>742</v>
       </c>
@@ -11600,15 +11620,15 @@
       <c r="J327" s="23"/>
     </row>
     <row r="328" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B328" s="23">
-        <v>313</v>
+      <c r="B328" s="22">
+        <v>323</v>
       </c>
       <c r="C328" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D328" s="38"/>
-      <c r="E328" s="39"/>
-      <c r="F328" s="33"/>
+      <c r="D328" s="32"/>
+      <c r="E328" s="33"/>
+      <c r="F328" s="39"/>
       <c r="G328" s="23" t="s">
         <v>742</v>
       </c>
@@ -11621,15 +11641,15 @@
       <c r="J328" s="23"/>
     </row>
     <row r="329" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B329" s="23">
-        <v>314</v>
+      <c r="B329" s="22">
+        <v>324</v>
       </c>
       <c r="C329" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D329" s="38"/>
-      <c r="E329" s="39"/>
-      <c r="F329" s="33"/>
+      <c r="D329" s="32"/>
+      <c r="E329" s="33"/>
+      <c r="F329" s="39"/>
       <c r="G329" s="23" t="s">
         <v>742</v>
       </c>
@@ -11642,15 +11662,15 @@
       <c r="J329" s="23"/>
     </row>
     <row r="330" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B330" s="23">
-        <v>315</v>
+      <c r="B330" s="22">
+        <v>325</v>
       </c>
       <c r="C330" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D330" s="38"/>
-      <c r="E330" s="39"/>
-      <c r="F330" s="33"/>
+      <c r="D330" s="32"/>
+      <c r="E330" s="33"/>
+      <c r="F330" s="39"/>
       <c r="G330" s="23" t="s">
         <v>742</v>
       </c>
@@ -11663,15 +11683,15 @@
       <c r="J330" s="23"/>
     </row>
     <row r="331" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B331" s="23">
-        <v>316</v>
+      <c r="B331" s="22">
+        <v>326</v>
       </c>
       <c r="C331" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D331" s="38"/>
-      <c r="E331" s="39"/>
-      <c r="F331" s="33"/>
+      <c r="D331" s="32"/>
+      <c r="E331" s="33"/>
+      <c r="F331" s="39"/>
       <c r="G331" s="23" t="s">
         <v>742</v>
       </c>
@@ -11684,15 +11704,15 @@
       <c r="J331" s="23"/>
     </row>
     <row r="332" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B332" s="23">
-        <v>317</v>
+      <c r="B332" s="22">
+        <v>327</v>
       </c>
       <c r="C332" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D332" s="38"/>
-      <c r="E332" s="39"/>
-      <c r="F332" s="33"/>
+      <c r="D332" s="32"/>
+      <c r="E332" s="33"/>
+      <c r="F332" s="39"/>
       <c r="G332" s="23" t="s">
         <v>742</v>
       </c>
@@ -11705,15 +11725,15 @@
       <c r="J332" s="23"/>
     </row>
     <row r="333" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B333" s="23">
-        <v>318</v>
+      <c r="B333" s="22">
+        <v>328</v>
       </c>
       <c r="C333" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D333" s="38"/>
-      <c r="E333" s="39"/>
-      <c r="F333" s="33"/>
+      <c r="D333" s="32"/>
+      <c r="E333" s="33"/>
+      <c r="F333" s="39"/>
       <c r="G333" s="23" t="s">
         <v>742</v>
       </c>
@@ -11726,15 +11746,15 @@
       <c r="J333" s="23"/>
     </row>
     <row r="334" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B334" s="23">
-        <v>319</v>
+      <c r="B334" s="22">
+        <v>329</v>
       </c>
       <c r="C334" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D334" s="38"/>
-      <c r="E334" s="39"/>
-      <c r="F334" s="33"/>
+      <c r="D334" s="32"/>
+      <c r="E334" s="33"/>
+      <c r="F334" s="39"/>
       <c r="G334" s="23" t="s">
         <v>742</v>
       </c>
@@ -11747,15 +11767,15 @@
       <c r="J334" s="23"/>
     </row>
     <row r="335" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B335" s="23">
-        <v>320</v>
+      <c r="B335" s="22">
+        <v>330</v>
       </c>
       <c r="C335" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D335" s="38"/>
-      <c r="E335" s="39"/>
-      <c r="F335" s="33"/>
+      <c r="D335" s="32"/>
+      <c r="E335" s="33"/>
+      <c r="F335" s="39"/>
       <c r="G335" s="23" t="s">
         <v>767</v>
       </c>
@@ -11768,15 +11788,15 @@
       <c r="J335" s="23"/>
     </row>
     <row r="336" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B336" s="23">
-        <v>321</v>
+      <c r="B336" s="22">
+        <v>331</v>
       </c>
       <c r="C336" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D336" s="38"/>
-      <c r="E336" s="39"/>
-      <c r="F336" s="33"/>
+      <c r="D336" s="32"/>
+      <c r="E336" s="33"/>
+      <c r="F336" s="39"/>
       <c r="G336" s="23" t="s">
         <v>767</v>
       </c>
@@ -11789,15 +11809,15 @@
       <c r="J336" s="23"/>
     </row>
     <row r="337" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B337" s="23">
-        <v>322</v>
+      <c r="B337" s="22">
+        <v>332</v>
       </c>
       <c r="C337" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D337" s="38"/>
-      <c r="E337" s="39"/>
-      <c r="F337" s="33"/>
+      <c r="D337" s="32"/>
+      <c r="E337" s="33"/>
+      <c r="F337" s="39"/>
       <c r="G337" s="23" t="s">
         <v>767</v>
       </c>
@@ -11810,15 +11830,15 @@
       <c r="J337" s="23"/>
     </row>
     <row r="338" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B338" s="23">
-        <v>323</v>
+      <c r="B338" s="22">
+        <v>333</v>
       </c>
       <c r="C338" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D338" s="38"/>
-      <c r="E338" s="39"/>
-      <c r="F338" s="33"/>
+      <c r="D338" s="32"/>
+      <c r="E338" s="33"/>
+      <c r="F338" s="39"/>
       <c r="G338" s="23" t="s">
         <v>767</v>
       </c>
@@ -11831,15 +11851,15 @@
       <c r="J338" s="23"/>
     </row>
     <row r="339" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B339" s="23">
-        <v>324</v>
+      <c r="B339" s="22">
+        <v>334</v>
       </c>
       <c r="C339" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D339" s="38"/>
-      <c r="E339" s="39"/>
-      <c r="F339" s="33"/>
+      <c r="D339" s="32"/>
+      <c r="E339" s="33"/>
+      <c r="F339" s="39"/>
       <c r="G339" s="23" t="s">
         <v>767</v>
       </c>
@@ -11852,15 +11872,15 @@
       <c r="J339" s="23"/>
     </row>
     <row r="340" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B340" s="23">
-        <v>325</v>
+      <c r="B340" s="22">
+        <v>335</v>
       </c>
       <c r="C340" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D340" s="38"/>
-      <c r="E340" s="39"/>
-      <c r="F340" s="33"/>
+      <c r="D340" s="32"/>
+      <c r="E340" s="33"/>
+      <c r="F340" s="39"/>
       <c r="G340" s="23" t="s">
         <v>767</v>
       </c>
@@ -11873,15 +11893,15 @@
       <c r="J340" s="23"/>
     </row>
     <row r="341" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B341" s="23">
-        <v>326</v>
+      <c r="B341" s="22">
+        <v>336</v>
       </c>
       <c r="C341" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D341" s="38"/>
-      <c r="E341" s="39"/>
-      <c r="F341" s="33"/>
+      <c r="D341" s="32"/>
+      <c r="E341" s="33"/>
+      <c r="F341" s="39"/>
       <c r="G341" s="23" t="s">
         <v>767</v>
       </c>
@@ -11894,15 +11914,15 @@
       <c r="J341" s="23"/>
     </row>
     <row r="342" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B342" s="23">
-        <v>327</v>
+      <c r="B342" s="22">
+        <v>337</v>
       </c>
       <c r="C342" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D342" s="38"/>
-      <c r="E342" s="39"/>
-      <c r="F342" s="33"/>
+      <c r="D342" s="32"/>
+      <c r="E342" s="33"/>
+      <c r="F342" s="39"/>
       <c r="G342" s="23" t="s">
         <v>767</v>
       </c>
@@ -11915,15 +11935,15 @@
       <c r="J342" s="23"/>
     </row>
     <row r="343" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B343" s="23">
-        <v>328</v>
+      <c r="B343" s="22">
+        <v>338</v>
       </c>
       <c r="C343" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D343" s="38"/>
-      <c r="E343" s="39"/>
-      <c r="F343" s="33"/>
+      <c r="D343" s="32"/>
+      <c r="E343" s="33"/>
+      <c r="F343" s="39"/>
       <c r="G343" s="23" t="s">
         <v>767</v>
       </c>
@@ -11936,15 +11956,15 @@
       <c r="J343" s="23"/>
     </row>
     <row r="344" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B344" s="23">
-        <v>329</v>
+      <c r="B344" s="22">
+        <v>339</v>
       </c>
       <c r="C344" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D344" s="38"/>
-      <c r="E344" s="39"/>
-      <c r="F344" s="33"/>
+      <c r="D344" s="32"/>
+      <c r="E344" s="33"/>
+      <c r="F344" s="39"/>
       <c r="G344" s="23" t="s">
         <v>767</v>
       </c>
@@ -11957,15 +11977,15 @@
       <c r="J344" s="23"/>
     </row>
     <row r="345" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B345" s="23">
-        <v>330</v>
+      <c r="B345" s="22">
+        <v>340</v>
       </c>
       <c r="C345" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D345" s="38"/>
-      <c r="E345" s="39"/>
-      <c r="F345" s="33"/>
+      <c r="D345" s="32"/>
+      <c r="E345" s="33"/>
+      <c r="F345" s="39"/>
       <c r="G345" s="23" t="s">
         <v>767</v>
       </c>
@@ -11978,15 +11998,15 @@
       <c r="J345" s="23"/>
     </row>
     <row r="346" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B346" s="23">
-        <v>331</v>
+      <c r="B346" s="22">
+        <v>341</v>
       </c>
       <c r="C346" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D346" s="38"/>
-      <c r="E346" s="39"/>
-      <c r="F346" s="33"/>
+      <c r="D346" s="32"/>
+      <c r="E346" s="33"/>
+      <c r="F346" s="39"/>
       <c r="G346" s="23" t="s">
         <v>767</v>
       </c>
@@ -11999,15 +12019,15 @@
       <c r="J346" s="23"/>
     </row>
     <row r="347" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B347" s="23">
-        <v>332</v>
+      <c r="B347" s="22">
+        <v>342</v>
       </c>
       <c r="C347" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D347" s="38"/>
-      <c r="E347" s="39"/>
-      <c r="F347" s="33"/>
+      <c r="D347" s="32"/>
+      <c r="E347" s="33"/>
+      <c r="F347" s="39"/>
       <c r="G347" s="23" t="s">
         <v>792</v>
       </c>
@@ -12020,15 +12040,15 @@
       <c r="J347" s="23"/>
     </row>
     <row r="348" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B348" s="23">
-        <v>333</v>
+      <c r="B348" s="22">
+        <v>343</v>
       </c>
       <c r="C348" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D348" s="38"/>
-      <c r="E348" s="39"/>
-      <c r="F348" s="33"/>
+      <c r="D348" s="32"/>
+      <c r="E348" s="33"/>
+      <c r="F348" s="39"/>
       <c r="G348" s="23" t="s">
         <v>792</v>
       </c>
@@ -12041,15 +12061,15 @@
       <c r="J348" s="23"/>
     </row>
     <row r="349" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B349" s="23">
-        <v>334</v>
+      <c r="B349" s="22">
+        <v>344</v>
       </c>
       <c r="C349" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D349" s="38"/>
-      <c r="E349" s="39"/>
-      <c r="F349" s="33"/>
+      <c r="D349" s="32"/>
+      <c r="E349" s="33"/>
+      <c r="F349" s="39"/>
       <c r="G349" s="23" t="s">
         <v>792</v>
       </c>
@@ -12062,15 +12082,15 @@
       <c r="J349" s="23"/>
     </row>
     <row r="350" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B350" s="23">
-        <v>335</v>
+      <c r="B350" s="22">
+        <v>345</v>
       </c>
       <c r="C350" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D350" s="38"/>
-      <c r="E350" s="39"/>
-      <c r="F350" s="33"/>
+      <c r="D350" s="32"/>
+      <c r="E350" s="33"/>
+      <c r="F350" s="39"/>
       <c r="G350" s="23" t="s">
         <v>792</v>
       </c>
@@ -12083,15 +12103,15 @@
       <c r="J350" s="23"/>
     </row>
     <row r="351" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B351" s="23">
-        <v>336</v>
+      <c r="B351" s="22">
+        <v>346</v>
       </c>
       <c r="C351" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D351" s="38"/>
-      <c r="E351" s="39"/>
-      <c r="F351" s="33"/>
+      <c r="D351" s="32"/>
+      <c r="E351" s="33"/>
+      <c r="F351" s="39"/>
       <c r="G351" s="23" t="s">
         <v>792</v>
       </c>
@@ -12104,15 +12124,15 @@
       <c r="J351" s="23"/>
     </row>
     <row r="352" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B352" s="23">
-        <v>337</v>
+      <c r="B352" s="22">
+        <v>347</v>
       </c>
       <c r="C352" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D352" s="38"/>
-      <c r="E352" s="39"/>
-      <c r="F352" s="33"/>
+      <c r="D352" s="32"/>
+      <c r="E352" s="33"/>
+      <c r="F352" s="39"/>
       <c r="G352" s="23" t="s">
         <v>792</v>
       </c>
@@ -12125,15 +12145,15 @@
       <c r="J352" s="23"/>
     </row>
     <row r="353" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B353" s="23">
-        <v>338</v>
+      <c r="B353" s="22">
+        <v>348</v>
       </c>
       <c r="C353" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D353" s="38"/>
-      <c r="E353" s="39"/>
-      <c r="F353" s="33"/>
+      <c r="D353" s="32"/>
+      <c r="E353" s="33"/>
+      <c r="F353" s="39"/>
       <c r="G353" s="23" t="s">
         <v>792</v>
       </c>
@@ -12146,15 +12166,15 @@
       <c r="J353" s="23"/>
     </row>
     <row r="354" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B354" s="23">
-        <v>339</v>
+      <c r="B354" s="22">
+        <v>349</v>
       </c>
       <c r="C354" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D354" s="38"/>
-      <c r="E354" s="39"/>
-      <c r="F354" s="33"/>
+      <c r="D354" s="32"/>
+      <c r="E354" s="33"/>
+      <c r="F354" s="39"/>
       <c r="G354" s="23" t="s">
         <v>792</v>
       </c>
@@ -12167,15 +12187,15 @@
       <c r="J354" s="23"/>
     </row>
     <row r="355" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B355" s="23">
-        <v>340</v>
+      <c r="B355" s="22">
+        <v>350</v>
       </c>
       <c r="C355" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D355" s="38"/>
-      <c r="E355" s="39"/>
-      <c r="F355" s="33"/>
+      <c r="D355" s="32"/>
+      <c r="E355" s="33"/>
+      <c r="F355" s="39"/>
       <c r="G355" s="23" t="s">
         <v>792</v>
       </c>
@@ -12188,15 +12208,15 @@
       <c r="J355" s="23"/>
     </row>
     <row r="356" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B356" s="23">
-        <v>341</v>
+      <c r="B356" s="22">
+        <v>351</v>
       </c>
       <c r="C356" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D356" s="38"/>
-      <c r="E356" s="39"/>
-      <c r="F356" s="33"/>
+      <c r="D356" s="32"/>
+      <c r="E356" s="33"/>
+      <c r="F356" s="39"/>
       <c r="G356" s="23" t="s">
         <v>792</v>
       </c>
@@ -12209,15 +12229,15 @@
       <c r="J356" s="23"/>
     </row>
     <row r="357" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B357" s="23">
-        <v>342</v>
+      <c r="B357" s="22">
+        <v>352</v>
       </c>
       <c r="C357" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D357" s="38"/>
-      <c r="E357" s="39"/>
-      <c r="F357" s="33"/>
+      <c r="D357" s="32"/>
+      <c r="E357" s="33"/>
+      <c r="F357" s="39"/>
       <c r="G357" s="23" t="s">
         <v>792</v>
       </c>
@@ -12230,15 +12250,15 @@
       <c r="J357" s="23"/>
     </row>
     <row r="358" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B358" s="23">
-        <v>343</v>
+      <c r="B358" s="22">
+        <v>353</v>
       </c>
       <c r="C358" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D358" s="38"/>
-      <c r="E358" s="39"/>
-      <c r="F358" s="33"/>
+      <c r="D358" s="32"/>
+      <c r="E358" s="33"/>
+      <c r="F358" s="39"/>
       <c r="G358" s="23" t="s">
         <v>792</v>
       </c>
@@ -12251,15 +12271,15 @@
       <c r="J358" s="23"/>
     </row>
     <row r="359" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B359" s="23">
-        <v>344</v>
+      <c r="B359" s="22">
+        <v>354</v>
       </c>
       <c r="C359" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D359" s="38"/>
-      <c r="E359" s="39"/>
-      <c r="F359" s="33"/>
+      <c r="D359" s="32"/>
+      <c r="E359" s="33"/>
+      <c r="F359" s="39"/>
       <c r="G359" s="23" t="s">
         <v>817</v>
       </c>
@@ -12272,15 +12292,15 @@
       <c r="J359" s="23"/>
     </row>
     <row r="360" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B360" s="23">
-        <v>345</v>
+      <c r="B360" s="22">
+        <v>355</v>
       </c>
       <c r="C360" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D360" s="38"/>
-      <c r="E360" s="39"/>
-      <c r="F360" s="33"/>
+      <c r="D360" s="32"/>
+      <c r="E360" s="33"/>
+      <c r="F360" s="39"/>
       <c r="G360" s="23" t="s">
         <v>817</v>
       </c>
@@ -12293,15 +12313,15 @@
       <c r="J360" s="23"/>
     </row>
     <row r="361" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B361" s="23">
-        <v>346</v>
+      <c r="B361" s="22">
+        <v>356</v>
       </c>
       <c r="C361" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D361" s="38"/>
-      <c r="E361" s="39"/>
-      <c r="F361" s="33"/>
+      <c r="D361" s="32"/>
+      <c r="E361" s="33"/>
+      <c r="F361" s="39"/>
       <c r="G361" s="23" t="s">
         <v>817</v>
       </c>
@@ -12314,15 +12334,15 @@
       <c r="J361" s="23"/>
     </row>
     <row r="362" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B362" s="23">
-        <v>347</v>
+      <c r="B362" s="22">
+        <v>357</v>
       </c>
       <c r="C362" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D362" s="38"/>
-      <c r="E362" s="39"/>
-      <c r="F362" s="33"/>
+      <c r="D362" s="32"/>
+      <c r="E362" s="33"/>
+      <c r="F362" s="39"/>
       <c r="G362" s="23" t="s">
         <v>817</v>
       </c>
@@ -12335,15 +12355,15 @@
       <c r="J362" s="23"/>
     </row>
     <row r="363" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B363" s="23">
-        <v>348</v>
+      <c r="B363" s="22">
+        <v>358</v>
       </c>
       <c r="C363" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D363" s="38"/>
-      <c r="E363" s="39"/>
-      <c r="F363" s="33"/>
+      <c r="D363" s="32"/>
+      <c r="E363" s="33"/>
+      <c r="F363" s="39"/>
       <c r="G363" s="23" t="s">
         <v>817</v>
       </c>
@@ -12356,15 +12376,15 @@
       <c r="J363" s="23"/>
     </row>
     <row r="364" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B364" s="23">
-        <v>349</v>
+      <c r="B364" s="22">
+        <v>359</v>
       </c>
       <c r="C364" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D364" s="38"/>
-      <c r="E364" s="39"/>
-      <c r="F364" s="33"/>
+      <c r="D364" s="32"/>
+      <c r="E364" s="33"/>
+      <c r="F364" s="39"/>
       <c r="G364" s="23" t="s">
         <v>817</v>
       </c>
@@ -12377,15 +12397,15 @@
       <c r="J364" s="23"/>
     </row>
     <row r="365" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B365" s="23">
-        <v>350</v>
+      <c r="B365" s="22">
+        <v>360</v>
       </c>
       <c r="C365" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D365" s="38"/>
-      <c r="E365" s="39"/>
-      <c r="F365" s="33"/>
+      <c r="D365" s="32"/>
+      <c r="E365" s="33"/>
+      <c r="F365" s="39"/>
       <c r="G365" s="23" t="s">
         <v>817</v>
       </c>
@@ -12398,15 +12418,15 @@
       <c r="J365" s="23"/>
     </row>
     <row r="366" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B366" s="23">
-        <v>351</v>
+      <c r="B366" s="22">
+        <v>361</v>
       </c>
       <c r="C366" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D366" s="38"/>
-      <c r="E366" s="39"/>
-      <c r="F366" s="33"/>
+      <c r="D366" s="32"/>
+      <c r="E366" s="33"/>
+      <c r="F366" s="39"/>
       <c r="G366" s="23" t="s">
         <v>817</v>
       </c>
@@ -12419,15 +12439,15 @@
       <c r="J366" s="23"/>
     </row>
     <row r="367" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B367" s="23">
-        <v>352</v>
+      <c r="B367" s="22">
+        <v>362</v>
       </c>
       <c r="C367" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D367" s="38"/>
-      <c r="E367" s="39"/>
-      <c r="F367" s="33"/>
+      <c r="D367" s="32"/>
+      <c r="E367" s="33"/>
+      <c r="F367" s="39"/>
       <c r="G367" s="23" t="s">
         <v>817</v>
       </c>
@@ -12440,15 +12460,15 @@
       <c r="J367" s="23"/>
     </row>
     <row r="368" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B368" s="23">
-        <v>353</v>
+      <c r="B368" s="22">
+        <v>363</v>
       </c>
       <c r="C368" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D368" s="38"/>
-      <c r="E368" s="39"/>
-      <c r="F368" s="33"/>
+      <c r="D368" s="32"/>
+      <c r="E368" s="33"/>
+      <c r="F368" s="39"/>
       <c r="G368" s="23" t="s">
         <v>817</v>
       </c>
@@ -12461,15 +12481,15 @@
       <c r="J368" s="23"/>
     </row>
     <row r="369" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B369" s="23">
-        <v>354</v>
+      <c r="B369" s="22">
+        <v>364</v>
       </c>
       <c r="C369" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D369" s="38"/>
-      <c r="E369" s="39"/>
-      <c r="F369" s="33"/>
+      <c r="D369" s="32"/>
+      <c r="E369" s="33"/>
+      <c r="F369" s="39"/>
       <c r="G369" s="23" t="s">
         <v>817</v>
       </c>
@@ -12482,15 +12502,15 @@
       <c r="J369" s="23"/>
     </row>
     <row r="370" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B370" s="23">
-        <v>355</v>
+      <c r="B370" s="22">
+        <v>365</v>
       </c>
       <c r="C370" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D370" s="38"/>
-      <c r="E370" s="39"/>
-      <c r="F370" s="33"/>
+      <c r="D370" s="32"/>
+      <c r="E370" s="33"/>
+      <c r="F370" s="39"/>
       <c r="G370" s="23" t="s">
         <v>817</v>
       </c>
@@ -12503,15 +12523,15 @@
       <c r="J370" s="23"/>
     </row>
     <row r="371" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B371" s="23">
-        <v>356</v>
+      <c r="B371" s="22">
+        <v>366</v>
       </c>
       <c r="C371" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D371" s="38"/>
-      <c r="E371" s="39"/>
-      <c r="F371" s="33"/>
+      <c r="D371" s="32"/>
+      <c r="E371" s="33"/>
+      <c r="F371" s="39"/>
       <c r="G371" s="23" t="s">
         <v>842</v>
       </c>
@@ -12524,15 +12544,15 @@
       <c r="J371" s="23"/>
     </row>
     <row r="372" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B372" s="23">
-        <v>357</v>
+      <c r="B372" s="22">
+        <v>367</v>
       </c>
       <c r="C372" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D372" s="38"/>
-      <c r="E372" s="39"/>
-      <c r="F372" s="33"/>
+      <c r="D372" s="32"/>
+      <c r="E372" s="33"/>
+      <c r="F372" s="39"/>
       <c r="G372" s="23" t="s">
         <v>842</v>
       </c>
@@ -12545,15 +12565,15 @@
       <c r="J372" s="23"/>
     </row>
     <row r="373" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B373" s="23">
-        <v>358</v>
+      <c r="B373" s="22">
+        <v>368</v>
       </c>
       <c r="C373" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D373" s="38"/>
-      <c r="E373" s="39"/>
-      <c r="F373" s="33"/>
+      <c r="D373" s="32"/>
+      <c r="E373" s="33"/>
+      <c r="F373" s="39"/>
       <c r="G373" s="23" t="s">
         <v>842</v>
       </c>
@@ -12566,15 +12586,15 @@
       <c r="J373" s="23"/>
     </row>
     <row r="374" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B374" s="23">
-        <v>359</v>
+      <c r="B374" s="22">
+        <v>369</v>
       </c>
       <c r="C374" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D374" s="38"/>
-      <c r="E374" s="39"/>
-      <c r="F374" s="33"/>
+      <c r="D374" s="32"/>
+      <c r="E374" s="33"/>
+      <c r="F374" s="39"/>
       <c r="G374" s="23" t="s">
         <v>842</v>
       </c>
@@ -12587,15 +12607,15 @@
       <c r="J374" s="23"/>
     </row>
     <row r="375" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B375" s="23">
-        <v>360</v>
+      <c r="B375" s="22">
+        <v>370</v>
       </c>
       <c r="C375" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D375" s="38"/>
-      <c r="E375" s="39"/>
-      <c r="F375" s="33"/>
+      <c r="D375" s="32"/>
+      <c r="E375" s="33"/>
+      <c r="F375" s="39"/>
       <c r="G375" s="23" t="s">
         <v>842</v>
       </c>
@@ -12608,15 +12628,15 @@
       <c r="J375" s="23"/>
     </row>
     <row r="376" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B376" s="23">
-        <v>361</v>
+      <c r="B376" s="22">
+        <v>371</v>
       </c>
       <c r="C376" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D376" s="38"/>
-      <c r="E376" s="39"/>
-      <c r="F376" s="33"/>
+      <c r="D376" s="32"/>
+      <c r="E376" s="33"/>
+      <c r="F376" s="39"/>
       <c r="G376" s="23" t="s">
         <v>842</v>
       </c>
@@ -12629,15 +12649,15 @@
       <c r="J376" s="23"/>
     </row>
     <row r="377" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B377" s="23">
-        <v>362</v>
+      <c r="B377" s="22">
+        <v>372</v>
       </c>
       <c r="C377" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D377" s="38"/>
-      <c r="E377" s="39"/>
-      <c r="F377" s="33"/>
+      <c r="D377" s="32"/>
+      <c r="E377" s="33"/>
+      <c r="F377" s="39"/>
       <c r="G377" s="23" t="s">
         <v>842</v>
       </c>
@@ -12650,15 +12670,15 @@
       <c r="J377" s="23"/>
     </row>
     <row r="378" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B378" s="23">
-        <v>363</v>
+      <c r="B378" s="22">
+        <v>373</v>
       </c>
       <c r="C378" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D378" s="38"/>
-      <c r="E378" s="39"/>
-      <c r="F378" s="33"/>
+      <c r="D378" s="32"/>
+      <c r="E378" s="33"/>
+      <c r="F378" s="39"/>
       <c r="G378" s="23" t="s">
         <v>842</v>
       </c>
@@ -12671,15 +12691,15 @@
       <c r="J378" s="23"/>
     </row>
     <row r="379" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B379" s="23">
-        <v>364</v>
+      <c r="B379" s="22">
+        <v>374</v>
       </c>
       <c r="C379" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D379" s="38"/>
-      <c r="E379" s="39"/>
-      <c r="F379" s="33"/>
+      <c r="D379" s="32"/>
+      <c r="E379" s="33"/>
+      <c r="F379" s="39"/>
       <c r="G379" s="23" t="s">
         <v>842</v>
       </c>
@@ -12692,15 +12712,15 @@
       <c r="J379" s="23"/>
     </row>
     <row r="380" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B380" s="23">
-        <v>365</v>
+      <c r="B380" s="22">
+        <v>375</v>
       </c>
       <c r="C380" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D380" s="38"/>
-      <c r="E380" s="39"/>
-      <c r="F380" s="33"/>
+      <c r="D380" s="32"/>
+      <c r="E380" s="33"/>
+      <c r="F380" s="39"/>
       <c r="G380" s="23" t="s">
         <v>842</v>
       </c>
@@ -12713,15 +12733,15 @@
       <c r="J380" s="23"/>
     </row>
     <row r="381" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B381" s="23">
-        <v>366</v>
+      <c r="B381" s="22">
+        <v>376</v>
       </c>
       <c r="C381" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D381" s="38"/>
-      <c r="E381" s="39"/>
-      <c r="F381" s="33"/>
+      <c r="D381" s="32"/>
+      <c r="E381" s="33"/>
+      <c r="F381" s="39"/>
       <c r="G381" s="23" t="s">
         <v>842</v>
       </c>
@@ -12734,15 +12754,15 @@
       <c r="J381" s="23"/>
     </row>
     <row r="382" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B382" s="23">
-        <v>367</v>
+      <c r="B382" s="22">
+        <v>377</v>
       </c>
       <c r="C382" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D382" s="38"/>
-      <c r="E382" s="39"/>
-      <c r="F382" s="33"/>
+      <c r="D382" s="32"/>
+      <c r="E382" s="33"/>
+      <c r="F382" s="39"/>
       <c r="G382" s="23" t="s">
         <v>842</v>
       </c>
@@ -12755,15 +12775,15 @@
       <c r="J382" s="23"/>
     </row>
     <row r="383" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B383" s="23">
-        <v>368</v>
+      <c r="B383" s="22">
+        <v>378</v>
       </c>
       <c r="C383" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D383" s="38"/>
-      <c r="E383" s="39"/>
-      <c r="F383" s="33"/>
+      <c r="D383" s="32"/>
+      <c r="E383" s="33"/>
+      <c r="F383" s="39"/>
       <c r="G383" s="23" t="s">
         <v>867</v>
       </c>
@@ -12776,15 +12796,15 @@
       <c r="J383" s="23"/>
     </row>
     <row r="384" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B384" s="23">
-        <v>369</v>
+      <c r="B384" s="22">
+        <v>379</v>
       </c>
       <c r="C384" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D384" s="38"/>
-      <c r="E384" s="39"/>
-      <c r="F384" s="33"/>
+      <c r="D384" s="32"/>
+      <c r="E384" s="33"/>
+      <c r="F384" s="39"/>
       <c r="G384" s="23" t="s">
         <v>867</v>
       </c>
@@ -12797,15 +12817,15 @@
       <c r="J384" s="23"/>
     </row>
     <row r="385" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B385" s="23">
-        <v>370</v>
+      <c r="B385" s="22">
+        <v>380</v>
       </c>
       <c r="C385" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D385" s="38"/>
-      <c r="E385" s="39"/>
-      <c r="F385" s="33"/>
+      <c r="D385" s="32"/>
+      <c r="E385" s="33"/>
+      <c r="F385" s="39"/>
       <c r="G385" s="23" t="s">
         <v>867</v>
       </c>
@@ -12818,15 +12838,15 @@
       <c r="J385" s="23"/>
     </row>
     <row r="386" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B386" s="23">
-        <v>371</v>
+      <c r="B386" s="22">
+        <v>381</v>
       </c>
       <c r="C386" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D386" s="38"/>
-      <c r="E386" s="39"/>
-      <c r="F386" s="33"/>
+      <c r="D386" s="32"/>
+      <c r="E386" s="33"/>
+      <c r="F386" s="39"/>
       <c r="G386" s="23" t="s">
         <v>867</v>
       </c>
@@ -12839,15 +12859,15 @@
       <c r="J386" s="23"/>
     </row>
     <row r="387" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B387" s="23">
-        <v>372</v>
+      <c r="B387" s="22">
+        <v>382</v>
       </c>
       <c r="C387" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D387" s="38"/>
-      <c r="E387" s="39"/>
-      <c r="F387" s="33"/>
+      <c r="D387" s="32"/>
+      <c r="E387" s="33"/>
+      <c r="F387" s="39"/>
       <c r="G387" s="23" t="s">
         <v>867</v>
       </c>
@@ -12860,15 +12880,15 @@
       <c r="J387" s="23"/>
     </row>
     <row r="388" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B388" s="23">
-        <v>373</v>
+      <c r="B388" s="22">
+        <v>383</v>
       </c>
       <c r="C388" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D388" s="38"/>
-      <c r="E388" s="39"/>
-      <c r="F388" s="33"/>
+      <c r="D388" s="32"/>
+      <c r="E388" s="33"/>
+      <c r="F388" s="39"/>
       <c r="G388" s="23" t="s">
         <v>867</v>
       </c>
@@ -12881,15 +12901,15 @@
       <c r="J388" s="23"/>
     </row>
     <row r="389" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B389" s="23">
-        <v>374</v>
+      <c r="B389" s="22">
+        <v>384</v>
       </c>
       <c r="C389" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D389" s="38"/>
-      <c r="E389" s="39"/>
-      <c r="F389" s="33"/>
+      <c r="D389" s="32"/>
+      <c r="E389" s="33"/>
+      <c r="F389" s="39"/>
       <c r="G389" s="23" t="s">
         <v>867</v>
       </c>
@@ -12902,15 +12922,15 @@
       <c r="J389" s="23"/>
     </row>
     <row r="390" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B390" s="23">
-        <v>375</v>
+      <c r="B390" s="22">
+        <v>385</v>
       </c>
       <c r="C390" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D390" s="38"/>
-      <c r="E390" s="39"/>
-      <c r="F390" s="33"/>
+      <c r="D390" s="32"/>
+      <c r="E390" s="33"/>
+      <c r="F390" s="39"/>
       <c r="G390" s="23" t="s">
         <v>867</v>
       </c>
@@ -12923,15 +12943,15 @@
       <c r="J390" s="23"/>
     </row>
     <row r="391" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B391" s="23">
-        <v>376</v>
+      <c r="B391" s="22">
+        <v>386</v>
       </c>
       <c r="C391" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D391" s="38"/>
-      <c r="E391" s="39"/>
-      <c r="F391" s="33"/>
+      <c r="D391" s="32"/>
+      <c r="E391" s="33"/>
+      <c r="F391" s="39"/>
       <c r="G391" s="23" t="s">
         <v>867</v>
       </c>
@@ -12944,15 +12964,15 @@
       <c r="J391" s="23"/>
     </row>
     <row r="392" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B392" s="23">
-        <v>377</v>
+      <c r="B392" s="22">
+        <v>387</v>
       </c>
       <c r="C392" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D392" s="38"/>
-      <c r="E392" s="39"/>
-      <c r="F392" s="33"/>
+      <c r="D392" s="32"/>
+      <c r="E392" s="33"/>
+      <c r="F392" s="39"/>
       <c r="G392" s="23" t="s">
         <v>867</v>
       </c>
@@ -12965,15 +12985,15 @@
       <c r="J392" s="23"/>
     </row>
     <row r="393" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B393" s="23">
-        <v>378</v>
+      <c r="B393" s="22">
+        <v>388</v>
       </c>
       <c r="C393" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D393" s="38"/>
-      <c r="E393" s="39"/>
-      <c r="F393" s="33"/>
+      <c r="D393" s="32"/>
+      <c r="E393" s="33"/>
+      <c r="F393" s="39"/>
       <c r="G393" s="23" t="s">
         <v>867</v>
       </c>
@@ -12986,15 +13006,15 @@
       <c r="J393" s="23"/>
     </row>
     <row r="394" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B394" s="23">
-        <v>379</v>
+      <c r="B394" s="22">
+        <v>389</v>
       </c>
       <c r="C394" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D394" s="38"/>
-      <c r="E394" s="39"/>
-      <c r="F394" s="33"/>
+      <c r="D394" s="32"/>
+      <c r="E394" s="33"/>
+      <c r="F394" s="39"/>
       <c r="G394" s="23" t="s">
         <v>867</v>
       </c>
@@ -13007,15 +13027,15 @@
       <c r="J394" s="23"/>
     </row>
     <row r="395" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B395" s="23">
-        <v>380</v>
+      <c r="B395" s="22">
+        <v>390</v>
       </c>
       <c r="C395" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D395" s="38"/>
-      <c r="E395" s="39"/>
-      <c r="F395" s="33"/>
+      <c r="D395" s="32"/>
+      <c r="E395" s="33"/>
+      <c r="F395" s="39"/>
       <c r="G395" s="23" t="s">
         <v>892</v>
       </c>
@@ -13028,15 +13048,15 @@
       <c r="J395" s="23"/>
     </row>
     <row r="396" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B396" s="23">
-        <v>381</v>
+      <c r="B396" s="22">
+        <v>391</v>
       </c>
       <c r="C396" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D396" s="38"/>
-      <c r="E396" s="39"/>
-      <c r="F396" s="33"/>
+      <c r="D396" s="32"/>
+      <c r="E396" s="33"/>
+      <c r="F396" s="39"/>
       <c r="G396" s="23" t="s">
         <v>892</v>
       </c>
@@ -13049,15 +13069,15 @@
       <c r="J396" s="23"/>
     </row>
     <row r="397" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B397" s="23">
-        <v>382</v>
+      <c r="B397" s="22">
+        <v>392</v>
       </c>
       <c r="C397" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D397" s="38"/>
-      <c r="E397" s="39"/>
-      <c r="F397" s="33"/>
+      <c r="D397" s="32"/>
+      <c r="E397" s="33"/>
+      <c r="F397" s="39"/>
       <c r="G397" s="23" t="s">
         <v>892</v>
       </c>
@@ -13070,15 +13090,15 @@
       <c r="J397" s="23"/>
     </row>
     <row r="398" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B398" s="23">
-        <v>383</v>
+      <c r="B398" s="22">
+        <v>393</v>
       </c>
       <c r="C398" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D398" s="38"/>
-      <c r="E398" s="39"/>
-      <c r="F398" s="33"/>
+      <c r="D398" s="32"/>
+      <c r="E398" s="33"/>
+      <c r="F398" s="39"/>
       <c r="G398" s="23" t="s">
         <v>892</v>
       </c>
@@ -13091,15 +13111,15 @@
       <c r="J398" s="23"/>
     </row>
     <row r="399" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B399" s="23">
-        <v>384</v>
+      <c r="B399" s="22">
+        <v>394</v>
       </c>
       <c r="C399" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D399" s="38"/>
-      <c r="E399" s="39"/>
-      <c r="F399" s="33"/>
+      <c r="D399" s="32"/>
+      <c r="E399" s="33"/>
+      <c r="F399" s="39"/>
       <c r="G399" s="23" t="s">
         <v>892</v>
       </c>
@@ -13112,15 +13132,15 @@
       <c r="J399" s="23"/>
     </row>
     <row r="400" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B400" s="23">
-        <v>385</v>
+      <c r="B400" s="22">
+        <v>395</v>
       </c>
       <c r="C400" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D400" s="38"/>
-      <c r="E400" s="39"/>
-      <c r="F400" s="33"/>
+      <c r="D400" s="32"/>
+      <c r="E400" s="33"/>
+      <c r="F400" s="39"/>
       <c r="G400" s="23" t="s">
         <v>892</v>
       </c>
@@ -13133,15 +13153,15 @@
       <c r="J400" s="23"/>
     </row>
     <row r="401" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B401" s="23">
-        <v>386</v>
+      <c r="B401" s="22">
+        <v>396</v>
       </c>
       <c r="C401" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D401" s="38"/>
-      <c r="E401" s="39"/>
-      <c r="F401" s="33"/>
+      <c r="D401" s="32"/>
+      <c r="E401" s="33"/>
+      <c r="F401" s="39"/>
       <c r="G401" s="23" t="s">
         <v>892</v>
       </c>
@@ -13154,15 +13174,15 @@
       <c r="J401" s="23"/>
     </row>
     <row r="402" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B402" s="23">
-        <v>387</v>
+      <c r="B402" s="22">
+        <v>397</v>
       </c>
       <c r="C402" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D402" s="38"/>
-      <c r="E402" s="39"/>
-      <c r="F402" s="33"/>
+      <c r="D402" s="32"/>
+      <c r="E402" s="33"/>
+      <c r="F402" s="39"/>
       <c r="G402" s="23" t="s">
         <v>892</v>
       </c>
@@ -13175,15 +13195,15 @@
       <c r="J402" s="23"/>
     </row>
     <row r="403" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B403" s="23">
-        <v>388</v>
+      <c r="B403" s="22">
+        <v>398</v>
       </c>
       <c r="C403" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D403" s="38"/>
-      <c r="E403" s="39"/>
-      <c r="F403" s="33"/>
+      <c r="D403" s="32"/>
+      <c r="E403" s="33"/>
+      <c r="F403" s="39"/>
       <c r="G403" s="23" t="s">
         <v>892</v>
       </c>
@@ -13196,15 +13216,15 @@
       <c r="J403" s="23"/>
     </row>
     <row r="404" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B404" s="23">
-        <v>389</v>
+      <c r="B404" s="22">
+        <v>399</v>
       </c>
       <c r="C404" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D404" s="38"/>
-      <c r="E404" s="39"/>
-      <c r="F404" s="33"/>
+      <c r="D404" s="32"/>
+      <c r="E404" s="33"/>
+      <c r="F404" s="39"/>
       <c r="G404" s="23" t="s">
         <v>892</v>
       </c>
@@ -13217,15 +13237,15 @@
       <c r="J404" s="23"/>
     </row>
     <row r="405" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B405" s="23">
-        <v>390</v>
+      <c r="B405" s="22">
+        <v>400</v>
       </c>
       <c r="C405" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D405" s="38"/>
-      <c r="E405" s="39"/>
-      <c r="F405" s="33"/>
+      <c r="D405" s="32"/>
+      <c r="E405" s="33"/>
+      <c r="F405" s="39"/>
       <c r="G405" s="23" t="s">
         <v>892</v>
       </c>
@@ -13238,15 +13258,15 @@
       <c r="J405" s="23"/>
     </row>
     <row r="406" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B406" s="23">
-        <v>391</v>
+      <c r="B406" s="22">
+        <v>401</v>
       </c>
       <c r="C406" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D406" s="38"/>
-      <c r="E406" s="39"/>
-      <c r="F406" s="34"/>
+      <c r="D406" s="32"/>
+      <c r="E406" s="33"/>
+      <c r="F406" s="38"/>
       <c r="G406" s="23" t="s">
         <v>892</v>
       </c>
@@ -13259,15 +13279,15 @@
       <c r="J406" s="23"/>
     </row>
     <row r="407" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B407" s="23">
-        <v>392</v>
+      <c r="B407" s="22">
+        <v>402</v>
       </c>
       <c r="C407" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D407" s="38"/>
-      <c r="E407" s="39"/>
-      <c r="F407" s="32" t="s">
+      <c r="D407" s="32"/>
+      <c r="E407" s="33"/>
+      <c r="F407" s="37" t="s">
         <v>917</v>
       </c>
       <c r="G407" s="23" t="s">
@@ -13282,15 +13302,15 @@
       <c r="J407" s="23"/>
     </row>
     <row r="408" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B408" s="23">
-        <v>393</v>
+      <c r="B408" s="22">
+        <v>403</v>
       </c>
       <c r="C408" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D408" s="38"/>
-      <c r="E408" s="39"/>
-      <c r="F408" s="33"/>
+      <c r="D408" s="32"/>
+      <c r="E408" s="33"/>
+      <c r="F408" s="39"/>
       <c r="G408" s="23" t="s">
         <v>921</v>
       </c>
@@ -13305,15 +13325,15 @@
       </c>
     </row>
     <row r="409" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B409" s="23">
-        <v>394</v>
+      <c r="B409" s="22">
+        <v>404</v>
       </c>
       <c r="C409" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D409" s="38"/>
-      <c r="E409" s="39"/>
-      <c r="F409" s="33"/>
+      <c r="D409" s="32"/>
+      <c r="E409" s="33"/>
+      <c r="F409" s="39"/>
       <c r="G409" s="23" t="s">
         <v>925</v>
       </c>
@@ -13328,15 +13348,15 @@
       </c>
     </row>
     <row r="410" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B410" s="23">
-        <v>395</v>
+      <c r="B410" s="22">
+        <v>405</v>
       </c>
       <c r="C410" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D410" s="38"/>
-      <c r="E410" s="39"/>
-      <c r="F410" s="33"/>
+      <c r="D410" s="32"/>
+      <c r="E410" s="33"/>
+      <c r="F410" s="39"/>
       <c r="G410" s="23" t="s">
         <v>929</v>
       </c>
@@ -13351,15 +13371,15 @@
       </c>
     </row>
     <row r="411" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B411" s="23">
-        <v>396</v>
+      <c r="B411" s="22">
+        <v>406</v>
       </c>
       <c r="C411" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D411" s="38"/>
-      <c r="E411" s="39"/>
-      <c r="F411" s="33"/>
+      <c r="D411" s="32"/>
+      <c r="E411" s="33"/>
+      <c r="F411" s="39"/>
       <c r="G411" s="23" t="s">
         <v>933</v>
       </c>
@@ -13374,15 +13394,15 @@
       </c>
     </row>
     <row r="412" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B412" s="23">
-        <v>397</v>
+      <c r="B412" s="22">
+        <v>407</v>
       </c>
       <c r="C412" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D412" s="38"/>
-      <c r="E412" s="39"/>
-      <c r="F412" s="33"/>
+      <c r="D412" s="32"/>
+      <c r="E412" s="33"/>
+      <c r="F412" s="39"/>
       <c r="G412" s="23" t="s">
         <v>937</v>
       </c>
@@ -13397,15 +13417,15 @@
       </c>
     </row>
     <row r="413" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B413" s="23">
-        <v>398</v>
+      <c r="B413" s="22">
+        <v>408</v>
       </c>
       <c r="C413" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D413" s="38"/>
-      <c r="E413" s="39"/>
-      <c r="F413" s="33"/>
+      <c r="D413" s="32"/>
+      <c r="E413" s="33"/>
+      <c r="F413" s="39"/>
       <c r="G413" s="23" t="s">
         <v>941</v>
       </c>
@@ -13418,15 +13438,15 @@
       <c r="J413" s="23"/>
     </row>
     <row r="414" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B414" s="23">
-        <v>399</v>
+      <c r="B414" s="22">
+        <v>409</v>
       </c>
       <c r="C414" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D414" s="38"/>
-      <c r="E414" s="39"/>
-      <c r="F414" s="33"/>
+      <c r="D414" s="32"/>
+      <c r="E414" s="33"/>
+      <c r="F414" s="39"/>
       <c r="G414" s="23" t="s">
         <v>944</v>
       </c>
@@ -13439,15 +13459,15 @@
       <c r="J414" s="23"/>
     </row>
     <row r="415" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B415" s="23">
-        <v>400</v>
+      <c r="B415" s="22">
+        <v>410</v>
       </c>
       <c r="C415" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D415" s="38"/>
-      <c r="E415" s="39"/>
-      <c r="F415" s="33"/>
+      <c r="D415" s="32"/>
+      <c r="E415" s="33"/>
+      <c r="F415" s="39"/>
       <c r="G415" s="23" t="s">
         <v>947</v>
       </c>
@@ -13460,15 +13480,15 @@
       <c r="J415" s="23"/>
     </row>
     <row r="416" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B416" s="23">
-        <v>401</v>
+      <c r="B416" s="22">
+        <v>411</v>
       </c>
       <c r="C416" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D416" s="38"/>
-      <c r="E416" s="39"/>
-      <c r="F416" s="33"/>
+      <c r="D416" s="32"/>
+      <c r="E416" s="33"/>
+      <c r="F416" s="39"/>
       <c r="G416" s="23" t="s">
         <v>947</v>
       </c>
@@ -13481,15 +13501,15 @@
       <c r="J416" s="23"/>
     </row>
     <row r="417" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B417" s="23">
-        <v>402</v>
+      <c r="B417" s="22">
+        <v>412</v>
       </c>
       <c r="C417" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D417" s="38"/>
-      <c r="E417" s="39"/>
-      <c r="F417" s="33"/>
+      <c r="D417" s="32"/>
+      <c r="E417" s="33"/>
+      <c r="F417" s="39"/>
       <c r="G417" s="23" t="s">
         <v>952</v>
       </c>
@@ -13502,15 +13522,15 @@
       <c r="J417" s="23"/>
     </row>
     <row r="418" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B418" s="23">
-        <v>403</v>
+      <c r="B418" s="22">
+        <v>413</v>
       </c>
       <c r="C418" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D418" s="38"/>
-      <c r="E418" s="39"/>
-      <c r="F418" s="34"/>
+      <c r="D418" s="32"/>
+      <c r="E418" s="33"/>
+      <c r="F418" s="38"/>
       <c r="G418" s="23" t="s">
         <v>955</v>
       </c>
@@ -13523,15 +13543,15 @@
       <c r="J418" s="23"/>
     </row>
     <row r="419" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B419" s="23">
-        <v>404</v>
+      <c r="B419" s="22">
+        <v>414</v>
       </c>
       <c r="C419" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D419" s="38"/>
-      <c r="E419" s="39"/>
-      <c r="F419" s="32" t="s">
+      <c r="D419" s="32"/>
+      <c r="E419" s="33"/>
+      <c r="F419" s="37" t="s">
         <v>958</v>
       </c>
       <c r="G419" s="23" t="s">
@@ -13546,15 +13566,15 @@
       <c r="J419" s="23"/>
     </row>
     <row r="420" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B420" s="23">
-        <v>405</v>
+      <c r="B420" s="22">
+        <v>415</v>
       </c>
       <c r="C420" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D420" s="38"/>
-      <c r="E420" s="39"/>
-      <c r="F420" s="33"/>
+      <c r="D420" s="32"/>
+      <c r="E420" s="33"/>
+      <c r="F420" s="39"/>
       <c r="G420" s="23" t="s">
         <v>959</v>
       </c>
@@ -13567,15 +13587,15 @@
       <c r="J420" s="23"/>
     </row>
     <row r="421" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B421" s="23">
-        <v>406</v>
+      <c r="B421" s="22">
+        <v>416</v>
       </c>
       <c r="C421" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D421" s="38"/>
-      <c r="E421" s="39"/>
-      <c r="F421" s="33"/>
+      <c r="D421" s="32"/>
+      <c r="E421" s="33"/>
+      <c r="F421" s="39"/>
       <c r="G421" s="23" t="s">
         <v>964</v>
       </c>
@@ -13588,15 +13608,15 @@
       <c r="J421" s="23"/>
     </row>
     <row r="422" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B422" s="23">
-        <v>407</v>
+      <c r="B422" s="22">
+        <v>417</v>
       </c>
       <c r="C422" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D422" s="38"/>
-      <c r="E422" s="39"/>
-      <c r="F422" s="33"/>
+      <c r="D422" s="32"/>
+      <c r="E422" s="33"/>
+      <c r="F422" s="39"/>
       <c r="G422" s="23" t="s">
         <v>959</v>
       </c>
@@ -13609,15 +13629,15 @@
       <c r="J422" s="23"/>
     </row>
     <row r="423" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B423" s="23">
-        <v>408</v>
+      <c r="B423" s="22">
+        <v>418</v>
       </c>
       <c r="C423" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D423" s="38"/>
-      <c r="E423" s="39"/>
-      <c r="F423" s="33"/>
+      <c r="D423" s="32"/>
+      <c r="E423" s="33"/>
+      <c r="F423" s="39"/>
       <c r="G423" s="23" t="s">
         <v>959</v>
       </c>
@@ -13630,15 +13650,15 @@
       <c r="J423" s="23"/>
     </row>
     <row r="424" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B424" s="23">
-        <v>409</v>
+      <c r="B424" s="22">
+        <v>419</v>
       </c>
       <c r="C424" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D424" s="38"/>
-      <c r="E424" s="39"/>
-      <c r="F424" s="33"/>
+      <c r="D424" s="32"/>
+      <c r="E424" s="33"/>
+      <c r="F424" s="39"/>
       <c r="G424" s="23" t="s">
         <v>971</v>
       </c>
@@ -13651,15 +13671,15 @@
       <c r="J424" s="23"/>
     </row>
     <row r="425" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B425" s="23">
-        <v>410</v>
+      <c r="B425" s="22">
+        <v>420</v>
       </c>
       <c r="C425" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D425" s="38"/>
-      <c r="E425" s="39"/>
-      <c r="F425" s="33"/>
+      <c r="D425" s="32"/>
+      <c r="E425" s="33"/>
+      <c r="F425" s="39"/>
       <c r="G425" s="23" t="s">
         <v>974</v>
       </c>
@@ -13672,15 +13692,15 @@
       <c r="J425" s="23"/>
     </row>
     <row r="426" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B426" s="23">
-        <v>411</v>
+      <c r="B426" s="22">
+        <v>421</v>
       </c>
       <c r="C426" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D426" s="38"/>
-      <c r="E426" s="39"/>
-      <c r="F426" s="33"/>
+      <c r="D426" s="32"/>
+      <c r="E426" s="33"/>
+      <c r="F426" s="39"/>
       <c r="G426" s="23" t="s">
         <v>977</v>
       </c>
@@ -13693,15 +13713,15 @@
       <c r="J426" s="23"/>
     </row>
     <row r="427" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B427" s="23">
-        <v>412</v>
+      <c r="B427" s="22">
+        <v>422</v>
       </c>
       <c r="C427" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D427" s="38"/>
-      <c r="E427" s="39"/>
-      <c r="F427" s="33"/>
+      <c r="D427" s="32"/>
+      <c r="E427" s="33"/>
+      <c r="F427" s="39"/>
       <c r="G427" s="23" t="s">
         <v>980</v>
       </c>
@@ -13714,15 +13734,15 @@
       <c r="J427" s="23"/>
     </row>
     <row r="428" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B428" s="23">
-        <v>413</v>
+      <c r="B428" s="22">
+        <v>423</v>
       </c>
       <c r="C428" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D428" s="38"/>
-      <c r="E428" s="39"/>
-      <c r="F428" s="33"/>
+      <c r="D428" s="32"/>
+      <c r="E428" s="33"/>
+      <c r="F428" s="39"/>
       <c r="G428" s="23" t="s">
         <v>983</v>
       </c>
@@ -13735,15 +13755,15 @@
       <c r="J428" s="23"/>
     </row>
     <row r="429" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B429" s="23">
-        <v>414</v>
+      <c r="B429" s="22">
+        <v>424</v>
       </c>
       <c r="C429" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D429" s="38"/>
-      <c r="E429" s="39"/>
-      <c r="F429" s="33"/>
+      <c r="D429" s="32"/>
+      <c r="E429" s="33"/>
+      <c r="F429" s="39"/>
       <c r="G429" s="23" t="s">
         <v>986</v>
       </c>
@@ -13756,15 +13776,15 @@
       <c r="J429" s="23"/>
     </row>
     <row r="430" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B430" s="23">
-        <v>415</v>
+      <c r="B430" s="22">
+        <v>425</v>
       </c>
       <c r="C430" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D430" s="38"/>
-      <c r="E430" s="39"/>
-      <c r="F430" s="33"/>
+      <c r="D430" s="32"/>
+      <c r="E430" s="33"/>
+      <c r="F430" s="39"/>
       <c r="G430" s="23" t="s">
         <v>989</v>
       </c>
@@ -13777,15 +13797,15 @@
       <c r="J430" s="23"/>
     </row>
     <row r="431" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B431" s="23">
-        <v>416</v>
+      <c r="B431" s="22">
+        <v>426</v>
       </c>
       <c r="C431" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D431" s="38"/>
-      <c r="E431" s="39"/>
-      <c r="F431" s="34"/>
+      <c r="D431" s="32"/>
+      <c r="E431" s="33"/>
+      <c r="F431" s="38"/>
       <c r="G431" s="23" t="s">
         <v>992</v>
       </c>
@@ -13798,15 +13818,15 @@
       <c r="J431" s="23"/>
     </row>
     <row r="432" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B432" s="23">
-        <v>417</v>
+      <c r="B432" s="22">
+        <v>427</v>
       </c>
       <c r="C432" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D432" s="38"/>
-      <c r="E432" s="39"/>
-      <c r="F432" s="32" t="s">
+      <c r="D432" s="32"/>
+      <c r="E432" s="33"/>
+      <c r="F432" s="37" t="s">
         <v>995</v>
       </c>
       <c r="G432" s="23" t="s">
@@ -13821,15 +13841,15 @@
       <c r="J432" s="23"/>
     </row>
     <row r="433" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B433" s="23">
-        <v>418</v>
+      <c r="B433" s="22">
+        <v>428</v>
       </c>
       <c r="C433" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D433" s="38"/>
-      <c r="E433" s="39"/>
-      <c r="F433" s="33"/>
+      <c r="D433" s="32"/>
+      <c r="E433" s="33"/>
+      <c r="F433" s="39"/>
       <c r="G433" s="23" t="s">
         <v>996</v>
       </c>
@@ -13842,15 +13862,15 @@
       <c r="J433" s="23"/>
     </row>
     <row r="434" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B434" s="23">
-        <v>419</v>
+      <c r="B434" s="22">
+        <v>429</v>
       </c>
       <c r="C434" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D434" s="38"/>
-      <c r="E434" s="39"/>
-      <c r="F434" s="33"/>
+      <c r="D434" s="32"/>
+      <c r="E434" s="33"/>
+      <c r="F434" s="39"/>
       <c r="G434" s="23" t="s">
         <v>1001</v>
       </c>
@@ -13863,15 +13883,15 @@
       <c r="J434" s="23"/>
     </row>
     <row r="435" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B435" s="23">
-        <v>420</v>
+      <c r="B435" s="22">
+        <v>430</v>
       </c>
       <c r="C435" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D435" s="38"/>
-      <c r="E435" s="39"/>
-      <c r="F435" s="33"/>
+      <c r="D435" s="32"/>
+      <c r="E435" s="33"/>
+      <c r="F435" s="39"/>
       <c r="G435" s="23" t="s">
         <v>947</v>
       </c>
@@ -13884,15 +13904,15 @@
       <c r="J435" s="23"/>
     </row>
     <row r="436" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B436" s="23">
-        <v>421</v>
+      <c r="B436" s="22">
+        <v>431</v>
       </c>
       <c r="C436" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D436" s="38"/>
-      <c r="E436" s="39"/>
-      <c r="F436" s="33"/>
+      <c r="D436" s="32"/>
+      <c r="E436" s="33"/>
+      <c r="F436" s="39"/>
       <c r="G436" s="23" t="s">
         <v>947</v>
       </c>
@@ -13905,15 +13925,15 @@
       <c r="J436" s="23"/>
     </row>
     <row r="437" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B437" s="23">
-        <v>422</v>
+      <c r="B437" s="22">
+        <v>432</v>
       </c>
       <c r="C437" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D437" s="38"/>
-      <c r="E437" s="39"/>
-      <c r="F437" s="33"/>
+      <c r="D437" s="32"/>
+      <c r="E437" s="33"/>
+      <c r="F437" s="39"/>
       <c r="G437" s="23" t="s">
         <v>947</v>
       </c>
@@ -13926,15 +13946,15 @@
       <c r="J437" s="23"/>
     </row>
     <row r="438" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B438" s="23">
-        <v>423</v>
+      <c r="B438" s="22">
+        <v>433</v>
       </c>
       <c r="C438" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D438" s="38"/>
-      <c r="E438" s="39"/>
-      <c r="F438" s="34"/>
+      <c r="D438" s="32"/>
+      <c r="E438" s="33"/>
+      <c r="F438" s="38"/>
       <c r="G438" s="23" t="s">
         <v>1010</v>
       </c>
@@ -13947,15 +13967,15 @@
       <c r="J438" s="23"/>
     </row>
     <row r="439" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B439" s="23">
-        <v>424</v>
+      <c r="B439" s="22">
+        <v>434</v>
       </c>
       <c r="C439" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D439" s="38"/>
-      <c r="E439" s="39"/>
-      <c r="F439" s="32" t="s">
+      <c r="D439" s="32"/>
+      <c r="E439" s="33"/>
+      <c r="F439" s="37" t="s">
         <v>1013</v>
       </c>
       <c r="G439" s="23" t="s">
@@ -13970,15 +13990,15 @@
       <c r="J439" s="23"/>
     </row>
     <row r="440" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B440" s="23">
-        <v>425</v>
+      <c r="B440" s="22">
+        <v>435</v>
       </c>
       <c r="C440" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D440" s="38"/>
-      <c r="E440" s="39"/>
-      <c r="F440" s="33"/>
+      <c r="D440" s="32"/>
+      <c r="E440" s="33"/>
+      <c r="F440" s="39"/>
       <c r="G440" s="23" t="s">
         <v>1017</v>
       </c>
@@ -13991,15 +14011,15 @@
       <c r="J440" s="23"/>
     </row>
     <row r="441" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B441" s="23">
-        <v>426</v>
+      <c r="B441" s="22">
+        <v>436</v>
       </c>
       <c r="C441" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D441" s="38"/>
-      <c r="E441" s="39"/>
-      <c r="F441" s="33"/>
+      <c r="D441" s="32"/>
+      <c r="E441" s="33"/>
+      <c r="F441" s="39"/>
       <c r="G441" s="23" t="s">
         <v>1020</v>
       </c>
@@ -14012,15 +14032,15 @@
       <c r="J441" s="23"/>
     </row>
     <row r="442" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B442" s="23">
-        <v>427</v>
+      <c r="B442" s="22">
+        <v>437</v>
       </c>
       <c r="C442" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D442" s="38"/>
-      <c r="E442" s="39"/>
-      <c r="F442" s="33"/>
+      <c r="D442" s="32"/>
+      <c r="E442" s="33"/>
+      <c r="F442" s="39"/>
       <c r="G442" s="23" t="s">
         <v>1023</v>
       </c>
@@ -14033,15 +14053,15 @@
       <c r="J442" s="23"/>
     </row>
     <row r="443" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B443" s="23">
-        <v>428</v>
+      <c r="B443" s="22">
+        <v>438</v>
       </c>
       <c r="C443" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D443" s="38"/>
-      <c r="E443" s="39"/>
-      <c r="F443" s="33"/>
+      <c r="D443" s="32"/>
+      <c r="E443" s="33"/>
+      <c r="F443" s="39"/>
       <c r="G443" s="23" t="s">
         <v>1026</v>
       </c>
@@ -14054,15 +14074,15 @@
       <c r="J443" s="23"/>
     </row>
     <row r="444" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B444" s="23">
-        <v>429</v>
+      <c r="B444" s="22">
+        <v>439</v>
       </c>
       <c r="C444" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D444" s="38"/>
-      <c r="E444" s="39"/>
-      <c r="F444" s="33"/>
+      <c r="D444" s="32"/>
+      <c r="E444" s="33"/>
+      <c r="F444" s="39"/>
       <c r="G444" s="23" t="s">
         <v>1029</v>
       </c>
@@ -14075,15 +14095,15 @@
       <c r="J444" s="23"/>
     </row>
     <row r="445" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B445" s="23">
-        <v>430</v>
+      <c r="B445" s="22">
+        <v>440</v>
       </c>
       <c r="C445" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D445" s="38"/>
-      <c r="E445" s="39"/>
-      <c r="F445" s="33"/>
+      <c r="D445" s="32"/>
+      <c r="E445" s="33"/>
+      <c r="F445" s="39"/>
       <c r="G445" s="23" t="s">
         <v>1032</v>
       </c>
@@ -14096,15 +14116,15 @@
       <c r="J445" s="23"/>
     </row>
     <row r="446" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B446" s="23">
-        <v>431</v>
+      <c r="B446" s="22">
+        <v>441</v>
       </c>
       <c r="C446" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D446" s="38"/>
-      <c r="E446" s="39"/>
-      <c r="F446" s="34"/>
+      <c r="D446" s="32"/>
+      <c r="E446" s="33"/>
+      <c r="F446" s="38"/>
       <c r="G446" s="23" t="s">
         <v>1035</v>
       </c>
@@ -14117,15 +14137,15 @@
       <c r="J446" s="23"/>
     </row>
     <row r="447" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B447" s="23">
-        <v>432</v>
+      <c r="B447" s="22">
+        <v>442</v>
       </c>
       <c r="C447" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D447" s="38"/>
-      <c r="E447" s="39"/>
-      <c r="F447" s="32" t="s">
+      <c r="D447" s="32"/>
+      <c r="E447" s="33"/>
+      <c r="F447" s="37" t="s">
         <v>1038</v>
       </c>
       <c r="G447" s="23" t="s">
@@ -14140,15 +14160,15 @@
       <c r="J447" s="23"/>
     </row>
     <row r="448" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B448" s="23">
-        <v>433</v>
+      <c r="B448" s="22">
+        <v>443</v>
       </c>
       <c r="C448" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D448" s="38"/>
-      <c r="E448" s="39"/>
-      <c r="F448" s="33"/>
+      <c r="D448" s="32"/>
+      <c r="E448" s="33"/>
+      <c r="F448" s="39"/>
       <c r="G448" s="23" t="s">
         <v>1042</v>
       </c>
@@ -14161,15 +14181,15 @@
       <c r="J448" s="23"/>
     </row>
     <row r="449" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B449" s="23">
-        <v>434</v>
+      <c r="B449" s="22">
+        <v>444</v>
       </c>
       <c r="C449" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D449" s="38"/>
-      <c r="E449" s="39"/>
-      <c r="F449" s="34"/>
+      <c r="D449" s="32"/>
+      <c r="E449" s="33"/>
+      <c r="F449" s="38"/>
       <c r="G449" s="23" t="s">
         <v>1045</v>
       </c>
@@ -14182,15 +14202,15 @@
       <c r="J449" s="23"/>
     </row>
     <row r="450" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B450" s="23">
-        <v>435</v>
+      <c r="B450" s="22">
+        <v>445</v>
       </c>
       <c r="C450" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D450" s="38"/>
-      <c r="E450" s="39"/>
-      <c r="F450" s="32" t="s">
+      <c r="D450" s="32"/>
+      <c r="E450" s="33"/>
+      <c r="F450" s="37" t="s">
         <v>1048</v>
       </c>
       <c r="G450" s="23" t="s">
@@ -14205,15 +14225,15 @@
       <c r="J450" s="23"/>
     </row>
     <row r="451" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B451" s="23">
-        <v>436</v>
+      <c r="B451" s="22">
+        <v>446</v>
       </c>
       <c r="C451" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D451" s="38"/>
-      <c r="E451" s="39"/>
-      <c r="F451" s="33"/>
+      <c r="D451" s="32"/>
+      <c r="E451" s="33"/>
+      <c r="F451" s="39"/>
       <c r="G451" s="23" t="s">
         <v>1052</v>
       </c>
@@ -14226,15 +14246,15 @@
       <c r="J451" s="23"/>
     </row>
     <row r="452" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B452" s="23">
-        <v>437</v>
+      <c r="B452" s="22">
+        <v>447</v>
       </c>
       <c r="C452" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D452" s="38"/>
-      <c r="E452" s="39"/>
-      <c r="F452" s="33"/>
+      <c r="D452" s="32"/>
+      <c r="E452" s="33"/>
+      <c r="F452" s="39"/>
       <c r="G452" s="23" t="s">
         <v>1055</v>
       </c>
@@ -14247,15 +14267,15 @@
       <c r="J452" s="23"/>
     </row>
     <row r="453" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B453" s="23">
-        <v>438</v>
+      <c r="B453" s="22">
+        <v>448</v>
       </c>
       <c r="C453" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D453" s="38"/>
-      <c r="E453" s="39"/>
-      <c r="F453" s="33"/>
+      <c r="D453" s="32"/>
+      <c r="E453" s="33"/>
+      <c r="F453" s="39"/>
       <c r="G453" s="23" t="s">
         <v>1058</v>
       </c>
@@ -14268,15 +14288,15 @@
       <c r="J453" s="23"/>
     </row>
     <row r="454" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B454" s="23">
-        <v>439</v>
+      <c r="B454" s="22">
+        <v>449</v>
       </c>
       <c r="C454" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D454" s="38"/>
-      <c r="E454" s="39"/>
-      <c r="F454" s="33"/>
+      <c r="D454" s="32"/>
+      <c r="E454" s="33"/>
+      <c r="F454" s="39"/>
       <c r="G454" s="23" t="s">
         <v>1058</v>
       </c>
@@ -14289,15 +14309,15 @@
       <c r="J454" s="23"/>
     </row>
     <row r="455" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B455" s="23">
-        <v>440</v>
+      <c r="B455" s="22">
+        <v>450</v>
       </c>
       <c r="C455" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D455" s="38"/>
-      <c r="E455" s="39"/>
-      <c r="F455" s="33"/>
+      <c r="D455" s="32"/>
+      <c r="E455" s="33"/>
+      <c r="F455" s="39"/>
       <c r="G455" s="23" t="s">
         <v>1058</v>
       </c>
@@ -14310,15 +14330,15 @@
       <c r="J455" s="23"/>
     </row>
     <row r="456" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B456" s="23">
-        <v>441</v>
+      <c r="B456" s="22">
+        <v>451</v>
       </c>
       <c r="C456" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D456" s="38"/>
-      <c r="E456" s="39"/>
-      <c r="F456" s="33"/>
+      <c r="D456" s="32"/>
+      <c r="E456" s="33"/>
+      <c r="F456" s="39"/>
       <c r="G456" s="23" t="s">
         <v>1065</v>
       </c>
@@ -14331,15 +14351,15 @@
       <c r="J456" s="23"/>
     </row>
     <row r="457" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B457" s="23">
-        <v>442</v>
+      <c r="B457" s="22">
+        <v>452</v>
       </c>
       <c r="C457" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D457" s="38"/>
-      <c r="E457" s="39"/>
-      <c r="F457" s="33"/>
+      <c r="D457" s="32"/>
+      <c r="E457" s="33"/>
+      <c r="F457" s="39"/>
       <c r="G457" s="23" t="s">
         <v>1065</v>
       </c>
@@ -14352,15 +14372,15 @@
       <c r="J457" s="23"/>
     </row>
     <row r="458" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B458" s="23">
-        <v>443</v>
+      <c r="B458" s="22">
+        <v>453</v>
       </c>
       <c r="C458" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D458" s="38"/>
-      <c r="E458" s="39"/>
-      <c r="F458" s="33"/>
+      <c r="D458" s="32"/>
+      <c r="E458" s="33"/>
+      <c r="F458" s="39"/>
       <c r="G458" s="23" t="s">
         <v>1065</v>
       </c>
@@ -14373,15 +14393,15 @@
       <c r="J458" s="23"/>
     </row>
     <row r="459" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B459" s="23">
-        <v>444</v>
+      <c r="B459" s="22">
+        <v>454</v>
       </c>
       <c r="C459" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D459" s="38"/>
-      <c r="E459" s="39"/>
-      <c r="F459" s="33"/>
+      <c r="D459" s="32"/>
+      <c r="E459" s="33"/>
+      <c r="F459" s="39"/>
       <c r="G459" s="23" t="s">
         <v>1065</v>
       </c>
@@ -14394,15 +14414,15 @@
       <c r="J459" s="23"/>
     </row>
     <row r="460" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B460" s="23">
-        <v>445</v>
+      <c r="B460" s="22">
+        <v>455</v>
       </c>
       <c r="C460" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D460" s="38"/>
-      <c r="E460" s="39"/>
-      <c r="F460" s="33"/>
+      <c r="D460" s="32"/>
+      <c r="E460" s="33"/>
+      <c r="F460" s="39"/>
       <c r="G460" s="23" t="s">
         <v>1074</v>
       </c>
@@ -14415,15 +14435,15 @@
       <c r="J460" s="23"/>
     </row>
     <row r="461" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B461" s="23">
-        <v>446</v>
+      <c r="B461" s="22">
+        <v>456</v>
       </c>
       <c r="C461" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D461" s="38"/>
-      <c r="E461" s="39"/>
-      <c r="F461" s="33"/>
+      <c r="D461" s="32"/>
+      <c r="E461" s="33"/>
+      <c r="F461" s="39"/>
       <c r="G461" s="23" t="s">
         <v>1077</v>
       </c>
@@ -14436,15 +14456,15 @@
       <c r="J461" s="23"/>
     </row>
     <row r="462" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B462" s="23">
-        <v>447</v>
+      <c r="B462" s="22">
+        <v>457</v>
       </c>
       <c r="C462" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D462" s="38"/>
-      <c r="E462" s="39"/>
-      <c r="F462" s="34"/>
+      <c r="D462" s="32"/>
+      <c r="E462" s="33"/>
+      <c r="F462" s="38"/>
       <c r="G462" s="23" t="s">
         <v>1080</v>
       </c>
@@ -14457,15 +14477,15 @@
       <c r="J462" s="23"/>
     </row>
     <row r="463" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B463" s="23">
-        <v>448</v>
+      <c r="B463" s="22">
+        <v>458</v>
       </c>
       <c r="C463" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D463" s="38"/>
-      <c r="E463" s="39"/>
-      <c r="F463" s="32" t="s">
+      <c r="D463" s="32"/>
+      <c r="E463" s="33"/>
+      <c r="F463" s="37" t="s">
         <v>1083</v>
       </c>
       <c r="G463" s="23" t="s">
@@ -14480,15 +14500,15 @@
       <c r="J463" s="23"/>
     </row>
     <row r="464" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B464" s="23">
-        <v>449</v>
+      <c r="B464" s="22">
+        <v>459</v>
       </c>
       <c r="C464" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D464" s="38"/>
-      <c r="E464" s="39"/>
-      <c r="F464" s="33"/>
+      <c r="D464" s="32"/>
+      <c r="E464" s="33"/>
+      <c r="F464" s="39"/>
       <c r="G464" s="23" t="s">
         <v>1087</v>
       </c>
@@ -14501,15 +14521,15 @@
       <c r="J464" s="23"/>
     </row>
     <row r="465" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B465" s="23">
-        <v>450</v>
+      <c r="B465" s="22">
+        <v>460</v>
       </c>
       <c r="C465" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D465" s="38"/>
-      <c r="E465" s="39"/>
-      <c r="F465" s="33"/>
+      <c r="D465" s="32"/>
+      <c r="E465" s="33"/>
+      <c r="F465" s="39"/>
       <c r="G465" s="23" t="s">
         <v>1090</v>
       </c>
@@ -14522,15 +14542,15 @@
       <c r="J465" s="23"/>
     </row>
     <row r="466" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B466" s="23">
-        <v>451</v>
+      <c r="B466" s="22">
+        <v>461</v>
       </c>
       <c r="C466" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D466" s="38"/>
-      <c r="E466" s="39"/>
-      <c r="F466" s="33"/>
+      <c r="D466" s="32"/>
+      <c r="E466" s="33"/>
+      <c r="F466" s="39"/>
       <c r="G466" s="23" t="s">
         <v>1093</v>
       </c>
@@ -14543,15 +14563,15 @@
       <c r="J466" s="23"/>
     </row>
     <row r="467" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B467" s="23">
-        <v>452</v>
+      <c r="B467" s="22">
+        <v>462</v>
       </c>
       <c r="C467" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D467" s="38"/>
-      <c r="E467" s="39"/>
-      <c r="F467" s="33"/>
+      <c r="D467" s="32"/>
+      <c r="E467" s="33"/>
+      <c r="F467" s="39"/>
       <c r="G467" s="23" t="s">
         <v>1096</v>
       </c>
@@ -14564,15 +14584,15 @@
       <c r="J467" s="23"/>
     </row>
     <row r="468" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B468" s="23">
-        <v>453</v>
+      <c r="B468" s="22">
+        <v>463</v>
       </c>
       <c r="C468" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D468" s="38"/>
-      <c r="E468" s="39"/>
-      <c r="F468" s="33"/>
+      <c r="D468" s="32"/>
+      <c r="E468" s="33"/>
+      <c r="F468" s="39"/>
       <c r="G468" s="23" t="s">
         <v>1099</v>
       </c>
@@ -14585,15 +14605,15 @@
       <c r="J468" s="23"/>
     </row>
     <row r="469" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B469" s="23">
-        <v>454</v>
+      <c r="B469" s="22">
+        <v>464</v>
       </c>
       <c r="C469" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D469" s="38"/>
-      <c r="E469" s="39"/>
-      <c r="F469" s="33"/>
+      <c r="D469" s="32"/>
+      <c r="E469" s="33"/>
+      <c r="F469" s="39"/>
       <c r="G469" s="23" t="s">
         <v>1102</v>
       </c>
@@ -14606,15 +14626,15 @@
       <c r="J469" s="23"/>
     </row>
     <row r="470" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B470" s="23">
-        <v>455</v>
+      <c r="B470" s="22">
+        <v>465</v>
       </c>
       <c r="C470" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D470" s="38"/>
-      <c r="E470" s="39"/>
-      <c r="F470" s="33"/>
+      <c r="D470" s="32"/>
+      <c r="E470" s="33"/>
+      <c r="F470" s="39"/>
       <c r="G470" s="23" t="s">
         <v>1105</v>
       </c>
@@ -14627,15 +14647,15 @@
       <c r="J470" s="23"/>
     </row>
     <row r="471" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B471" s="23">
-        <v>456</v>
+      <c r="B471" s="22">
+        <v>466</v>
       </c>
       <c r="C471" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D471" s="38"/>
-      <c r="E471" s="39"/>
-      <c r="F471" s="33"/>
+      <c r="D471" s="32"/>
+      <c r="E471" s="33"/>
+      <c r="F471" s="39"/>
       <c r="G471" s="23" t="s">
         <v>1108</v>
       </c>
@@ -14648,15 +14668,15 @@
       <c r="J471" s="23"/>
     </row>
     <row r="472" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B472" s="23">
-        <v>457</v>
+      <c r="B472" s="22">
+        <v>467</v>
       </c>
       <c r="C472" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D472" s="38"/>
-      <c r="E472" s="39"/>
-      <c r="F472" s="34"/>
+      <c r="D472" s="32"/>
+      <c r="E472" s="33"/>
+      <c r="F472" s="38"/>
       <c r="G472" s="23" t="s">
         <v>1093</v>
       </c>
@@ -14669,15 +14689,15 @@
       <c r="J472" s="23"/>
     </row>
     <row r="473" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B473" s="23">
-        <v>458</v>
+      <c r="B473" s="22">
+        <v>468</v>
       </c>
       <c r="C473" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D473" s="38"/>
-      <c r="E473" s="39"/>
-      <c r="F473" s="32" t="s">
+      <c r="D473" s="32"/>
+      <c r="E473" s="33"/>
+      <c r="F473" s="37" t="s">
         <v>1113</v>
       </c>
       <c r="G473" s="23" t="s">
@@ -14692,15 +14712,15 @@
       <c r="J473" s="23"/>
     </row>
     <row r="474" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B474" s="23">
-        <v>459</v>
+      <c r="B474" s="22">
+        <v>469</v>
       </c>
       <c r="C474" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D474" s="38"/>
-      <c r="E474" s="39"/>
-      <c r="F474" s="33"/>
+      <c r="D474" s="32"/>
+      <c r="E474" s="33"/>
+      <c r="F474" s="39"/>
       <c r="G474" s="23" t="s">
         <v>1117</v>
       </c>
@@ -14713,15 +14733,15 @@
       <c r="J474" s="23"/>
     </row>
     <row r="475" spans="2:10" ht="49.95" customHeight="1">
-      <c r="B475" s="23">
-        <v>460</v>
+      <c r="B475" s="22">
+        <v>470</v>
       </c>
       <c r="C475" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D475" s="38"/>
-      <c r="E475" s="39"/>
-      <c r="F475" s="34"/>
+      <c r="D475" s="32"/>
+      <c r="E475" s="33"/>
+      <c r="F475" s="38"/>
       <c r="G475" s="23" t="s">
         <v>1120</v>
       </c>
@@ -14735,6 +14755,43 @@
     </row>
   </sheetData>
   <mergeCells count="53">
+    <mergeCell ref="F473:F475"/>
+    <mergeCell ref="F419:F431"/>
+    <mergeCell ref="F432:F438"/>
+    <mergeCell ref="F439:F446"/>
+    <mergeCell ref="F447:F449"/>
+    <mergeCell ref="F450:F462"/>
+    <mergeCell ref="F463:F472"/>
+    <mergeCell ref="F407:F418"/>
+    <mergeCell ref="F210:F215"/>
+    <mergeCell ref="F216:F217"/>
+    <mergeCell ref="F218:F223"/>
+    <mergeCell ref="F224:F233"/>
+    <mergeCell ref="F234:F241"/>
+    <mergeCell ref="F242:F243"/>
+    <mergeCell ref="F244:F247"/>
+    <mergeCell ref="F248:F251"/>
+    <mergeCell ref="F252:F257"/>
+    <mergeCell ref="F258:F262"/>
+    <mergeCell ref="F263:F406"/>
+    <mergeCell ref="F132:F141"/>
+    <mergeCell ref="F208:F209"/>
+    <mergeCell ref="F144:F147"/>
+    <mergeCell ref="F148:F149"/>
+    <mergeCell ref="F150:F155"/>
+    <mergeCell ref="F156:F161"/>
+    <mergeCell ref="F162:F171"/>
+    <mergeCell ref="F172:F175"/>
+    <mergeCell ref="F176:F179"/>
+    <mergeCell ref="F180:F181"/>
+    <mergeCell ref="F182:F187"/>
+    <mergeCell ref="F188:F189"/>
+    <mergeCell ref="F190:F207"/>
+    <mergeCell ref="F98:F99"/>
+    <mergeCell ref="F100:F115"/>
+    <mergeCell ref="F116:F117"/>
+    <mergeCell ref="F118:F129"/>
+    <mergeCell ref="F130:F131"/>
     <mergeCell ref="D6:D475"/>
     <mergeCell ref="E6:E33"/>
     <mergeCell ref="E34:E475"/>
@@ -14751,43 +14808,6 @@
     <mergeCell ref="F52:F75"/>
     <mergeCell ref="F76:F77"/>
     <mergeCell ref="F78:F97"/>
-    <mergeCell ref="F98:F99"/>
-    <mergeCell ref="F100:F115"/>
-    <mergeCell ref="F116:F117"/>
-    <mergeCell ref="F118:F129"/>
-    <mergeCell ref="F130:F131"/>
-    <mergeCell ref="F132:F141"/>
-    <mergeCell ref="F208:F209"/>
-    <mergeCell ref="F144:F147"/>
-    <mergeCell ref="F148:F149"/>
-    <mergeCell ref="F150:F155"/>
-    <mergeCell ref="F156:F161"/>
-    <mergeCell ref="F162:F171"/>
-    <mergeCell ref="F172:F175"/>
-    <mergeCell ref="F176:F179"/>
-    <mergeCell ref="F180:F181"/>
-    <mergeCell ref="F182:F187"/>
-    <mergeCell ref="F188:F189"/>
-    <mergeCell ref="F190:F207"/>
-    <mergeCell ref="F407:F418"/>
-    <mergeCell ref="F210:F215"/>
-    <mergeCell ref="F216:F217"/>
-    <mergeCell ref="F218:F223"/>
-    <mergeCell ref="F224:F233"/>
-    <mergeCell ref="F234:F241"/>
-    <mergeCell ref="F242:F243"/>
-    <mergeCell ref="F244:F247"/>
-    <mergeCell ref="F248:F251"/>
-    <mergeCell ref="F252:F257"/>
-    <mergeCell ref="F258:F262"/>
-    <mergeCell ref="F263:F406"/>
-    <mergeCell ref="F473:F475"/>
-    <mergeCell ref="F419:F431"/>
-    <mergeCell ref="F432:F438"/>
-    <mergeCell ref="F439:F446"/>
-    <mergeCell ref="F447:F449"/>
-    <mergeCell ref="F450:F462"/>
-    <mergeCell ref="F463:F472"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">

--- a/TC/나이트크로우_일반제작_TC.xlsx
+++ b/TC/나이트크로우_일반제작_TC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\leegm0430\01_포토폴리오\TC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263C915A-8427-4302-A492-9E2D3C2D2A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E3504C-B6B0-4C09-8F92-FBD9B0E9A8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3406,9 +3406,6 @@
     <t>제작 요청이 중복 처리되지 않고 재료가 의도치 않게 이중 차감되지 않음</t>
   </si>
   <si>
-    <t>데이터 정확성 검증</t>
-  </si>
-  <si>
     <t>일반 제작 전체 아이템 목록 및 기획 레시피 데이터 테이블 확보</t>
   </si>
   <si>
@@ -3458,6 +3455,10 @@
   </si>
   <si>
     <t>버전 1.30.6</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터 검증</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -3840,10 +3841,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3855,13 +3859,10 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4718,7 +4719,7 @@
         <v>2</v>
       </c>
       <c r="J3" s="27" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="4" spans="2:10">
@@ -4733,7 +4734,7 @@
         <v>3</v>
       </c>
       <c r="J4" s="27" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="31.2" customHeight="1">
@@ -4772,13 +4773,13 @@
       <c r="C6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="F6" s="38" t="s">
         <v>16</v>
       </c>
       <c r="G6" s="23" t="s">
@@ -4799,9 +4800,9 @@
       <c r="C7" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
       <c r="G7" s="23" t="s">
         <v>20</v>
       </c>
@@ -4820,9 +4821,9 @@
       <c r="C8" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
       <c r="G8" s="22" t="s">
         <v>22</v>
       </c>
@@ -4841,9 +4842,9 @@
       <c r="C9" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
       <c r="G9" s="22" t="s">
         <v>25</v>
       </c>
@@ -4862,9 +4863,9 @@
       <c r="C10" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="33" t="s">
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="39" t="s">
         <v>27</v>
       </c>
       <c r="G10" s="22" t="s">
@@ -4885,9 +4886,9 @@
       <c r="C11" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="33"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="39"/>
       <c r="G11" s="22" t="s">
         <v>28</v>
       </c>
@@ -4906,9 +4907,9 @@
       <c r="C12" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="33"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="39"/>
       <c r="G12" s="22" t="s">
         <v>28</v>
       </c>
@@ -4927,9 +4928,9 @@
       <c r="C13" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="33"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="39"/>
       <c r="G13" s="22" t="s">
         <v>28</v>
       </c>
@@ -4948,9 +4949,9 @@
       <c r="C14" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="33"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="39"/>
       <c r="G14" s="22" t="s">
         <v>28</v>
       </c>
@@ -4969,9 +4970,9 @@
       <c r="C15" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="33" t="s">
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="39" t="s">
         <v>40</v>
       </c>
       <c r="G15" s="22" t="s">
@@ -4992,9 +4993,9 @@
       <c r="C16" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="33"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="39"/>
       <c r="G16" s="22" t="s">
         <v>44</v>
       </c>
@@ -5013,9 +5014,9 @@
       <c r="C17" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="33"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="39"/>
       <c r="G17" s="22" t="s">
         <v>47</v>
       </c>
@@ -5034,9 +5035,9 @@
       <c r="C18" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="33"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="39"/>
       <c r="G18" s="22" t="s">
         <v>44</v>
       </c>
@@ -5055,9 +5056,9 @@
       <c r="C19" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="33" t="s">
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="39" t="s">
         <v>27</v>
       </c>
       <c r="G19" s="22" t="s">
@@ -5078,9 +5079,9 @@
       <c r="C20" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="33"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="39"/>
       <c r="G20" s="22" t="s">
         <v>28</v>
       </c>
@@ -5099,9 +5100,9 @@
       <c r="C21" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="33"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="39"/>
       <c r="G21" s="22" t="s">
         <v>28</v>
       </c>
@@ -5120,9 +5121,9 @@
       <c r="C22" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="33"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="39"/>
       <c r="G22" s="22" t="s">
         <v>28</v>
       </c>
@@ -5141,9 +5142,9 @@
       <c r="C23" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="33"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="39"/>
       <c r="G23" s="22" t="s">
         <v>60</v>
       </c>
@@ -5162,9 +5163,9 @@
       <c r="C24" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="33"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="39"/>
       <c r="G24" s="22" t="s">
         <v>28</v>
       </c>
@@ -5183,9 +5184,9 @@
       <c r="C25" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="33"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="39"/>
       <c r="G25" s="22" t="s">
         <v>28</v>
       </c>
@@ -5204,9 +5205,9 @@
       <c r="C26" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="33"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="39"/>
       <c r="G26" s="22" t="s">
         <v>28</v>
       </c>
@@ -5225,9 +5226,9 @@
       <c r="C27" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="33"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="39"/>
       <c r="G27" s="22" t="s">
         <v>28</v>
       </c>
@@ -5246,9 +5247,9 @@
       <c r="C28" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="33"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="39"/>
       <c r="G28" s="22" t="s">
         <v>28</v>
       </c>
@@ -5267,9 +5268,9 @@
       <c r="C29" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="34" t="s">
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="35" t="s">
         <v>74</v>
       </c>
       <c r="G29" s="22" t="s">
@@ -5290,9 +5291,9 @@
       <c r="C30" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="35"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="36"/>
       <c r="G30" s="22" t="s">
         <v>28</v>
       </c>
@@ -5311,9 +5312,9 @@
       <c r="C31" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="35"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="36"/>
       <c r="G31" s="22" t="s">
         <v>79</v>
       </c>
@@ -5332,9 +5333,9 @@
       <c r="C32" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="35"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="36"/>
       <c r="G32" s="22" t="s">
         <v>82</v>
       </c>
@@ -5353,9 +5354,9 @@
       <c r="C33" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="36"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="37"/>
       <c r="G33" s="22" t="s">
         <v>84</v>
       </c>
@@ -5374,11 +5375,11 @@
       <c r="C34" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="32"/>
-      <c r="E34" s="33" t="s">
+      <c r="D34" s="38"/>
+      <c r="E34" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="F34" s="34" t="s">
+      <c r="F34" s="35" t="s">
         <v>86</v>
       </c>
       <c r="G34" s="22" t="s">
@@ -5399,9 +5400,9 @@
       <c r="C35" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D35" s="32"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="35"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="36"/>
       <c r="G35" s="22" t="s">
         <v>87</v>
       </c>
@@ -5420,9 +5421,9 @@
       <c r="C36" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="32"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="35"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="36"/>
       <c r="G36" s="22" t="s">
         <v>87</v>
       </c>
@@ -5441,9 +5442,9 @@
       <c r="C37" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D37" s="32"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="36"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="37"/>
       <c r="G37" s="22" t="s">
         <v>87</v>
       </c>
@@ -5462,9 +5463,9 @@
       <c r="C38" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D38" s="32"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="34" t="s">
+      <c r="D38" s="38"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="35" t="s">
         <v>27</v>
       </c>
       <c r="G38" s="22" t="s">
@@ -5485,9 +5486,9 @@
       <c r="C39" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="32"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="35"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="36"/>
       <c r="G39" s="22" t="s">
         <v>28</v>
       </c>
@@ -5506,9 +5507,9 @@
       <c r="C40" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D40" s="32"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="36"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="37"/>
       <c r="G40" s="22" t="s">
         <v>100</v>
       </c>
@@ -5529,9 +5530,9 @@
       <c r="C41" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D41" s="32"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="34" t="s">
+      <c r="D41" s="38"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="35" t="s">
         <v>104</v>
       </c>
       <c r="G41" s="22" t="s">
@@ -5552,9 +5553,9 @@
       <c r="C42" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D42" s="32"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="35"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="36"/>
       <c r="G42" s="22" t="s">
         <v>28</v>
       </c>
@@ -5573,9 +5574,9 @@
       <c r="C43" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D43" s="32"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="35"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="39"/>
+      <c r="F43" s="36"/>
       <c r="G43" s="22" t="s">
         <v>28</v>
       </c>
@@ -5594,9 +5595,9 @@
       <c r="C44" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D44" s="32"/>
-      <c r="E44" s="33"/>
-      <c r="F44" s="35"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="36"/>
       <c r="G44" s="22" t="s">
         <v>28</v>
       </c>
@@ -5604,7 +5605,7 @@
         <v>111</v>
       </c>
       <c r="I44" s="22" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="J44" s="22"/>
     </row>
@@ -5615,9 +5616,9 @@
       <c r="C45" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D45" s="32"/>
-      <c r="E45" s="33"/>
-      <c r="F45" s="35"/>
+      <c r="D45" s="38"/>
+      <c r="E45" s="39"/>
+      <c r="F45" s="36"/>
       <c r="G45" s="22" t="s">
         <v>28</v>
       </c>
@@ -5625,7 +5626,7 @@
         <v>112</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="J45" s="22"/>
     </row>
@@ -5636,9 +5637,9 @@
       <c r="C46" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D46" s="32"/>
-      <c r="E46" s="33"/>
-      <c r="F46" s="35"/>
+      <c r="D46" s="38"/>
+      <c r="E46" s="39"/>
+      <c r="F46" s="36"/>
       <c r="G46" s="22" t="s">
         <v>28</v>
       </c>
@@ -5646,7 +5647,7 @@
         <v>113</v>
       </c>
       <c r="I46" s="22" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="J46" s="22"/>
     </row>
@@ -5657,14 +5658,14 @@
       <c r="C47" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D47" s="32"/>
-      <c r="E47" s="33"/>
-      <c r="F47" s="35"/>
+      <c r="D47" s="38"/>
+      <c r="E47" s="39"/>
+      <c r="F47" s="36"/>
       <c r="G47" s="22" t="s">
         <v>114</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="I47" s="22" t="s">
         <v>115</v>
@@ -5678,9 +5679,9 @@
       <c r="C48" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D48" s="32"/>
-      <c r="E48" s="33"/>
-      <c r="F48" s="35"/>
+      <c r="D48" s="38"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="36"/>
       <c r="G48" s="22" t="s">
         <v>116</v>
       </c>
@@ -5699,9 +5700,9 @@
       <c r="C49" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D49" s="32"/>
-      <c r="E49" s="33"/>
-      <c r="F49" s="36"/>
+      <c r="D49" s="38"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="37"/>
       <c r="G49" s="22" t="s">
         <v>119</v>
       </c>
@@ -5720,9 +5721,9 @@
       <c r="C50" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D50" s="32"/>
-      <c r="E50" s="33"/>
-      <c r="F50" s="34" t="s">
+      <c r="D50" s="38"/>
+      <c r="E50" s="39"/>
+      <c r="F50" s="35" t="s">
         <v>122</v>
       </c>
       <c r="G50" s="22" t="s">
@@ -5743,9 +5744,9 @@
       <c r="C51" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D51" s="32"/>
-      <c r="E51" s="33"/>
-      <c r="F51" s="36"/>
+      <c r="D51" s="38"/>
+      <c r="E51" s="39"/>
+      <c r="F51" s="37"/>
       <c r="G51" s="22" t="s">
         <v>126</v>
       </c>
@@ -5764,9 +5765,9 @@
       <c r="C52" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D52" s="32"/>
-      <c r="E52" s="33"/>
-      <c r="F52" s="34" t="s">
+      <c r="D52" s="38"/>
+      <c r="E52" s="39"/>
+      <c r="F52" s="35" t="s">
         <v>129</v>
       </c>
       <c r="G52" s="22" t="s">
@@ -5787,9 +5788,9 @@
       <c r="C53" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D53" s="32"/>
-      <c r="E53" s="33"/>
-      <c r="F53" s="35"/>
+      <c r="D53" s="38"/>
+      <c r="E53" s="39"/>
+      <c r="F53" s="36"/>
       <c r="G53" s="22" t="s">
         <v>130</v>
       </c>
@@ -5808,9 +5809,9 @@
       <c r="C54" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D54" s="32"/>
-      <c r="E54" s="33"/>
-      <c r="F54" s="35"/>
+      <c r="D54" s="38"/>
+      <c r="E54" s="39"/>
+      <c r="F54" s="36"/>
       <c r="G54" s="22" t="s">
         <v>130</v>
       </c>
@@ -5829,9 +5830,9 @@
       <c r="C55" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D55" s="32"/>
-      <c r="E55" s="33"/>
-      <c r="F55" s="35"/>
+      <c r="D55" s="38"/>
+      <c r="E55" s="39"/>
+      <c r="F55" s="36"/>
       <c r="G55" s="22" t="s">
         <v>130</v>
       </c>
@@ -5850,9 +5851,9 @@
       <c r="C56" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D56" s="32"/>
-      <c r="E56" s="33"/>
-      <c r="F56" s="35"/>
+      <c r="D56" s="38"/>
+      <c r="E56" s="39"/>
+      <c r="F56" s="36"/>
       <c r="G56" s="22" t="s">
         <v>130</v>
       </c>
@@ -5871,9 +5872,9 @@
       <c r="C57" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D57" s="32"/>
-      <c r="E57" s="33"/>
-      <c r="F57" s="35"/>
+      <c r="D57" s="38"/>
+      <c r="E57" s="39"/>
+      <c r="F57" s="36"/>
       <c r="G57" s="22" t="s">
         <v>130</v>
       </c>
@@ -5892,9 +5893,9 @@
       <c r="C58" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D58" s="32"/>
-      <c r="E58" s="33"/>
-      <c r="F58" s="35"/>
+      <c r="D58" s="38"/>
+      <c r="E58" s="39"/>
+      <c r="F58" s="36"/>
       <c r="G58" s="22" t="s">
         <v>130</v>
       </c>
@@ -5913,9 +5914,9 @@
       <c r="C59" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D59" s="32"/>
-      <c r="E59" s="33"/>
-      <c r="F59" s="35"/>
+      <c r="D59" s="38"/>
+      <c r="E59" s="39"/>
+      <c r="F59" s="36"/>
       <c r="G59" s="22" t="s">
         <v>130</v>
       </c>
@@ -5934,9 +5935,9 @@
       <c r="C60" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D60" s="32"/>
-      <c r="E60" s="33"/>
-      <c r="F60" s="35"/>
+      <c r="D60" s="38"/>
+      <c r="E60" s="39"/>
+      <c r="F60" s="36"/>
       <c r="G60" s="22" t="s">
         <v>130</v>
       </c>
@@ -5955,9 +5956,9 @@
       <c r="C61" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D61" s="32"/>
-      <c r="E61" s="33"/>
-      <c r="F61" s="35"/>
+      <c r="D61" s="38"/>
+      <c r="E61" s="39"/>
+      <c r="F61" s="36"/>
       <c r="G61" s="22" t="s">
         <v>130</v>
       </c>
@@ -5976,9 +5977,9 @@
       <c r="C62" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D62" s="32"/>
-      <c r="E62" s="33"/>
-      <c r="F62" s="35"/>
+      <c r="D62" s="38"/>
+      <c r="E62" s="39"/>
+      <c r="F62" s="36"/>
       <c r="G62" s="22" t="s">
         <v>130</v>
       </c>
@@ -5997,9 +5998,9 @@
       <c r="C63" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D63" s="32"/>
-      <c r="E63" s="33"/>
-      <c r="F63" s="35"/>
+      <c r="D63" s="38"/>
+      <c r="E63" s="39"/>
+      <c r="F63" s="36"/>
       <c r="G63" s="22" t="s">
         <v>130</v>
       </c>
@@ -6018,9 +6019,9 @@
       <c r="C64" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D64" s="32"/>
-      <c r="E64" s="33"/>
-      <c r="F64" s="35"/>
+      <c r="D64" s="38"/>
+      <c r="E64" s="39"/>
+      <c r="F64" s="36"/>
       <c r="G64" s="22" t="s">
         <v>130</v>
       </c>
@@ -6039,9 +6040,9 @@
       <c r="C65" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D65" s="32"/>
-      <c r="E65" s="33"/>
-      <c r="F65" s="35"/>
+      <c r="D65" s="38"/>
+      <c r="E65" s="39"/>
+      <c r="F65" s="36"/>
       <c r="G65" s="22" t="s">
         <v>130</v>
       </c>
@@ -6060,9 +6061,9 @@
       <c r="C66" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D66" s="32"/>
-      <c r="E66" s="33"/>
-      <c r="F66" s="35"/>
+      <c r="D66" s="38"/>
+      <c r="E66" s="39"/>
+      <c r="F66" s="36"/>
       <c r="G66" s="22" t="s">
         <v>130</v>
       </c>
@@ -6081,9 +6082,9 @@
       <c r="C67" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D67" s="32"/>
-      <c r="E67" s="33"/>
-      <c r="F67" s="35"/>
+      <c r="D67" s="38"/>
+      <c r="E67" s="39"/>
+      <c r="F67" s="36"/>
       <c r="G67" s="22" t="s">
         <v>130</v>
       </c>
@@ -6102,9 +6103,9 @@
       <c r="C68" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D68" s="32"/>
-      <c r="E68" s="33"/>
-      <c r="F68" s="35"/>
+      <c r="D68" s="38"/>
+      <c r="E68" s="39"/>
+      <c r="F68" s="36"/>
       <c r="G68" s="22" t="s">
         <v>130</v>
       </c>
@@ -6123,9 +6124,9 @@
       <c r="C69" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D69" s="32"/>
-      <c r="E69" s="33"/>
-      <c r="F69" s="35"/>
+      <c r="D69" s="38"/>
+      <c r="E69" s="39"/>
+      <c r="F69" s="36"/>
       <c r="G69" s="22" t="s">
         <v>130</v>
       </c>
@@ -6144,9 +6145,9 @@
       <c r="C70" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D70" s="32"/>
-      <c r="E70" s="33"/>
-      <c r="F70" s="35"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="36"/>
       <c r="G70" s="22" t="s">
         <v>130</v>
       </c>
@@ -6165,9 +6166,9 @@
       <c r="C71" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D71" s="32"/>
-      <c r="E71" s="33"/>
-      <c r="F71" s="35"/>
+      <c r="D71" s="38"/>
+      <c r="E71" s="39"/>
+      <c r="F71" s="36"/>
       <c r="G71" s="22" t="s">
         <v>130</v>
       </c>
@@ -6186,9 +6187,9 @@
       <c r="C72" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D72" s="32"/>
-      <c r="E72" s="33"/>
-      <c r="F72" s="35"/>
+      <c r="D72" s="38"/>
+      <c r="E72" s="39"/>
+      <c r="F72" s="36"/>
       <c r="G72" s="22" t="s">
         <v>130</v>
       </c>
@@ -6207,9 +6208,9 @@
       <c r="C73" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D73" s="32"/>
-      <c r="E73" s="33"/>
-      <c r="F73" s="35"/>
+      <c r="D73" s="38"/>
+      <c r="E73" s="39"/>
+      <c r="F73" s="36"/>
       <c r="G73" s="22" t="s">
         <v>130</v>
       </c>
@@ -6228,9 +6229,9 @@
       <c r="C74" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D74" s="32"/>
-      <c r="E74" s="33"/>
-      <c r="F74" s="35"/>
+      <c r="D74" s="38"/>
+      <c r="E74" s="39"/>
+      <c r="F74" s="36"/>
       <c r="G74" s="22" t="s">
         <v>130</v>
       </c>
@@ -6249,9 +6250,9 @@
       <c r="C75" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D75" s="32"/>
-      <c r="E75" s="33"/>
-      <c r="F75" s="36"/>
+      <c r="D75" s="38"/>
+      <c r="E75" s="39"/>
+      <c r="F75" s="37"/>
       <c r="G75" s="22" t="s">
         <v>130</v>
       </c>
@@ -6270,9 +6271,9 @@
       <c r="C76" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D76" s="32"/>
-      <c r="E76" s="33"/>
-      <c r="F76" s="34" t="s">
+      <c r="D76" s="38"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="35" t="s">
         <v>122</v>
       </c>
       <c r="G76" s="22" t="s">
@@ -6293,9 +6294,9 @@
       <c r="C77" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D77" s="32"/>
-      <c r="E77" s="33"/>
-      <c r="F77" s="36"/>
+      <c r="D77" s="38"/>
+      <c r="E77" s="39"/>
+      <c r="F77" s="37"/>
       <c r="G77" s="22" t="s">
         <v>182</v>
       </c>
@@ -6314,9 +6315,9 @@
       <c r="C78" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D78" s="32"/>
-      <c r="E78" s="33"/>
-      <c r="F78" s="34" t="s">
+      <c r="D78" s="38"/>
+      <c r="E78" s="39"/>
+      <c r="F78" s="35" t="s">
         <v>129</v>
       </c>
       <c r="G78" s="22" t="s">
@@ -6337,9 +6338,9 @@
       <c r="C79" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D79" s="32"/>
-      <c r="E79" s="33"/>
-      <c r="F79" s="35"/>
+      <c r="D79" s="38"/>
+      <c r="E79" s="39"/>
+      <c r="F79" s="36"/>
       <c r="G79" s="22" t="s">
         <v>185</v>
       </c>
@@ -6358,9 +6359,9 @@
       <c r="C80" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D80" s="32"/>
-      <c r="E80" s="33"/>
-      <c r="F80" s="35"/>
+      <c r="D80" s="38"/>
+      <c r="E80" s="39"/>
+      <c r="F80" s="36"/>
       <c r="G80" s="22" t="s">
         <v>185</v>
       </c>
@@ -6379,9 +6380,9 @@
       <c r="C81" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D81" s="32"/>
-      <c r="E81" s="33"/>
-      <c r="F81" s="35"/>
+      <c r="D81" s="38"/>
+      <c r="E81" s="39"/>
+      <c r="F81" s="36"/>
       <c r="G81" s="22" t="s">
         <v>185</v>
       </c>
@@ -6400,9 +6401,9 @@
       <c r="C82" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D82" s="32"/>
-      <c r="E82" s="33"/>
-      <c r="F82" s="35"/>
+      <c r="D82" s="38"/>
+      <c r="E82" s="39"/>
+      <c r="F82" s="36"/>
       <c r="G82" s="22" t="s">
         <v>185</v>
       </c>
@@ -6421,9 +6422,9 @@
       <c r="C83" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D83" s="32"/>
-      <c r="E83" s="33"/>
-      <c r="F83" s="35"/>
+      <c r="D83" s="38"/>
+      <c r="E83" s="39"/>
+      <c r="F83" s="36"/>
       <c r="G83" s="22" t="s">
         <v>185</v>
       </c>
@@ -6442,9 +6443,9 @@
       <c r="C84" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D84" s="32"/>
-      <c r="E84" s="33"/>
-      <c r="F84" s="35"/>
+      <c r="D84" s="38"/>
+      <c r="E84" s="39"/>
+      <c r="F84" s="36"/>
       <c r="G84" s="22" t="s">
         <v>185</v>
       </c>
@@ -6463,9 +6464,9 @@
       <c r="C85" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D85" s="32"/>
-      <c r="E85" s="33"/>
-      <c r="F85" s="35"/>
+      <c r="D85" s="38"/>
+      <c r="E85" s="39"/>
+      <c r="F85" s="36"/>
       <c r="G85" s="22" t="s">
         <v>185</v>
       </c>
@@ -6484,9 +6485,9 @@
       <c r="C86" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D86" s="32"/>
-      <c r="E86" s="33"/>
-      <c r="F86" s="35"/>
+      <c r="D86" s="38"/>
+      <c r="E86" s="39"/>
+      <c r="F86" s="36"/>
       <c r="G86" s="22" t="s">
         <v>185</v>
       </c>
@@ -6505,9 +6506,9 @@
       <c r="C87" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D87" s="32"/>
-      <c r="E87" s="33"/>
-      <c r="F87" s="35"/>
+      <c r="D87" s="38"/>
+      <c r="E87" s="39"/>
+      <c r="F87" s="36"/>
       <c r="G87" s="22" t="s">
         <v>185</v>
       </c>
@@ -6526,9 +6527,9 @@
       <c r="C88" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D88" s="32"/>
-      <c r="E88" s="33"/>
-      <c r="F88" s="35"/>
+      <c r="D88" s="38"/>
+      <c r="E88" s="39"/>
+      <c r="F88" s="36"/>
       <c r="G88" s="22" t="s">
         <v>185</v>
       </c>
@@ -6547,9 +6548,9 @@
       <c r="C89" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D89" s="32"/>
-      <c r="E89" s="33"/>
-      <c r="F89" s="35"/>
+      <c r="D89" s="38"/>
+      <c r="E89" s="39"/>
+      <c r="F89" s="36"/>
       <c r="G89" s="22" t="s">
         <v>185</v>
       </c>
@@ -6568,9 +6569,9 @@
       <c r="C90" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D90" s="32"/>
-      <c r="E90" s="33"/>
-      <c r="F90" s="35"/>
+      <c r="D90" s="38"/>
+      <c r="E90" s="39"/>
+      <c r="F90" s="36"/>
       <c r="G90" s="22" t="s">
         <v>185</v>
       </c>
@@ -6589,9 +6590,9 @@
       <c r="C91" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D91" s="32"/>
-      <c r="E91" s="33"/>
-      <c r="F91" s="35"/>
+      <c r="D91" s="38"/>
+      <c r="E91" s="39"/>
+      <c r="F91" s="36"/>
       <c r="G91" s="22" t="s">
         <v>185</v>
       </c>
@@ -6610,9 +6611,9 @@
       <c r="C92" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D92" s="32"/>
-      <c r="E92" s="33"/>
-      <c r="F92" s="35"/>
+      <c r="D92" s="38"/>
+      <c r="E92" s="39"/>
+      <c r="F92" s="36"/>
       <c r="G92" s="22" t="s">
         <v>185</v>
       </c>
@@ -6631,9 +6632,9 @@
       <c r="C93" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D93" s="32"/>
-      <c r="E93" s="33"/>
-      <c r="F93" s="35"/>
+      <c r="D93" s="38"/>
+      <c r="E93" s="39"/>
+      <c r="F93" s="36"/>
       <c r="G93" s="22" t="s">
         <v>185</v>
       </c>
@@ -6652,9 +6653,9 @@
       <c r="C94" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D94" s="32"/>
-      <c r="E94" s="33"/>
-      <c r="F94" s="35"/>
+      <c r="D94" s="38"/>
+      <c r="E94" s="39"/>
+      <c r="F94" s="36"/>
       <c r="G94" s="22" t="s">
         <v>185</v>
       </c>
@@ -6673,9 +6674,9 @@
       <c r="C95" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D95" s="32"/>
-      <c r="E95" s="33"/>
-      <c r="F95" s="35"/>
+      <c r="D95" s="38"/>
+      <c r="E95" s="39"/>
+      <c r="F95" s="36"/>
       <c r="G95" s="22" t="s">
         <v>185</v>
       </c>
@@ -6694,9 +6695,9 @@
       <c r="C96" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D96" s="32"/>
-      <c r="E96" s="33"/>
-      <c r="F96" s="35"/>
+      <c r="D96" s="38"/>
+      <c r="E96" s="39"/>
+      <c r="F96" s="36"/>
       <c r="G96" s="22" t="s">
         <v>185</v>
       </c>
@@ -6715,9 +6716,9 @@
       <c r="C97" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D97" s="32"/>
-      <c r="E97" s="33"/>
-      <c r="F97" s="36"/>
+      <c r="D97" s="38"/>
+      <c r="E97" s="39"/>
+      <c r="F97" s="37"/>
       <c r="G97" s="22" t="s">
         <v>185</v>
       </c>
@@ -6736,9 +6737,9 @@
       <c r="C98" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D98" s="32"/>
-      <c r="E98" s="33"/>
-      <c r="F98" s="34" t="s">
+      <c r="D98" s="38"/>
+      <c r="E98" s="39"/>
+      <c r="F98" s="35" t="s">
         <v>122</v>
       </c>
       <c r="G98" s="22" t="s">
@@ -6759,9 +6760,9 @@
       <c r="C99" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D99" s="32"/>
-      <c r="E99" s="33"/>
-      <c r="F99" s="36"/>
+      <c r="D99" s="38"/>
+      <c r="E99" s="39"/>
+      <c r="F99" s="37"/>
       <c r="G99" s="22" t="s">
         <v>229</v>
       </c>
@@ -6780,9 +6781,9 @@
       <c r="C100" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D100" s="32"/>
-      <c r="E100" s="33"/>
-      <c r="F100" s="34" t="s">
+      <c r="D100" s="38"/>
+      <c r="E100" s="39"/>
+      <c r="F100" s="35" t="s">
         <v>129</v>
       </c>
       <c r="G100" s="22" t="s">
@@ -6803,9 +6804,9 @@
       <c r="C101" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D101" s="32"/>
-      <c r="E101" s="33"/>
-      <c r="F101" s="35"/>
+      <c r="D101" s="38"/>
+      <c r="E101" s="39"/>
+      <c r="F101" s="36"/>
       <c r="G101" s="22" t="s">
         <v>232</v>
       </c>
@@ -6824,9 +6825,9 @@
       <c r="C102" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D102" s="32"/>
-      <c r="E102" s="33"/>
-      <c r="F102" s="35"/>
+      <c r="D102" s="38"/>
+      <c r="E102" s="39"/>
+      <c r="F102" s="36"/>
       <c r="G102" s="22" t="s">
         <v>232</v>
       </c>
@@ -6845,9 +6846,9 @@
       <c r="C103" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D103" s="32"/>
-      <c r="E103" s="33"/>
-      <c r="F103" s="35"/>
+      <c r="D103" s="38"/>
+      <c r="E103" s="39"/>
+      <c r="F103" s="36"/>
       <c r="G103" s="22" t="s">
         <v>232</v>
       </c>
@@ -6866,9 +6867,9 @@
       <c r="C104" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D104" s="32"/>
-      <c r="E104" s="33"/>
-      <c r="F104" s="35"/>
+      <c r="D104" s="38"/>
+      <c r="E104" s="39"/>
+      <c r="F104" s="36"/>
       <c r="G104" s="22" t="s">
         <v>232</v>
       </c>
@@ -6887,9 +6888,9 @@
       <c r="C105" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D105" s="32"/>
-      <c r="E105" s="33"/>
-      <c r="F105" s="35"/>
+      <c r="D105" s="38"/>
+      <c r="E105" s="39"/>
+      <c r="F105" s="36"/>
       <c r="G105" s="22" t="s">
         <v>232</v>
       </c>
@@ -6908,9 +6909,9 @@
       <c r="C106" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D106" s="32"/>
-      <c r="E106" s="33"/>
-      <c r="F106" s="35"/>
+      <c r="D106" s="38"/>
+      <c r="E106" s="39"/>
+      <c r="F106" s="36"/>
       <c r="G106" s="22" t="s">
         <v>232</v>
       </c>
@@ -6929,9 +6930,9 @@
       <c r="C107" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D107" s="32"/>
-      <c r="E107" s="33"/>
-      <c r="F107" s="35"/>
+      <c r="D107" s="38"/>
+      <c r="E107" s="39"/>
+      <c r="F107" s="36"/>
       <c r="G107" s="22" t="s">
         <v>232</v>
       </c>
@@ -6950,9 +6951,9 @@
       <c r="C108" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D108" s="32"/>
-      <c r="E108" s="33"/>
-      <c r="F108" s="35"/>
+      <c r="D108" s="38"/>
+      <c r="E108" s="39"/>
+      <c r="F108" s="36"/>
       <c r="G108" s="22" t="s">
         <v>232</v>
       </c>
@@ -6971,9 +6972,9 @@
       <c r="C109" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D109" s="32"/>
-      <c r="E109" s="33"/>
-      <c r="F109" s="35"/>
+      <c r="D109" s="38"/>
+      <c r="E109" s="39"/>
+      <c r="F109" s="36"/>
       <c r="G109" s="22" t="s">
         <v>232</v>
       </c>
@@ -6992,9 +6993,9 @@
       <c r="C110" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D110" s="32"/>
-      <c r="E110" s="33"/>
-      <c r="F110" s="35"/>
+      <c r="D110" s="38"/>
+      <c r="E110" s="39"/>
+      <c r="F110" s="36"/>
       <c r="G110" s="22" t="s">
         <v>232</v>
       </c>
@@ -7013,9 +7014,9 @@
       <c r="C111" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D111" s="32"/>
-      <c r="E111" s="33"/>
-      <c r="F111" s="35"/>
+      <c r="D111" s="38"/>
+      <c r="E111" s="39"/>
+      <c r="F111" s="36"/>
       <c r="G111" s="22" t="s">
         <v>232</v>
       </c>
@@ -7034,9 +7035,9 @@
       <c r="C112" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D112" s="32"/>
-      <c r="E112" s="33"/>
-      <c r="F112" s="35"/>
+      <c r="D112" s="38"/>
+      <c r="E112" s="39"/>
+      <c r="F112" s="36"/>
       <c r="G112" s="22" t="s">
         <v>232</v>
       </c>
@@ -7055,9 +7056,9 @@
       <c r="C113" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D113" s="32"/>
-      <c r="E113" s="33"/>
-      <c r="F113" s="35"/>
+      <c r="D113" s="38"/>
+      <c r="E113" s="39"/>
+      <c r="F113" s="36"/>
       <c r="G113" s="22" t="s">
         <v>232</v>
       </c>
@@ -7076,9 +7077,9 @@
       <c r="C114" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D114" s="32"/>
-      <c r="E114" s="33"/>
-      <c r="F114" s="35"/>
+      <c r="D114" s="38"/>
+      <c r="E114" s="39"/>
+      <c r="F114" s="36"/>
       <c r="G114" s="22" t="s">
         <v>232</v>
       </c>
@@ -7097,9 +7098,9 @@
       <c r="C115" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D115" s="32"/>
-      <c r="E115" s="33"/>
-      <c r="F115" s="36"/>
+      <c r="D115" s="38"/>
+      <c r="E115" s="39"/>
+      <c r="F115" s="37"/>
       <c r="G115" s="22" t="s">
         <v>232</v>
       </c>
@@ -7118,9 +7119,9 @@
       <c r="C116" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D116" s="32"/>
-      <c r="E116" s="33"/>
-      <c r="F116" s="34" t="s">
+      <c r="D116" s="38"/>
+      <c r="E116" s="39"/>
+      <c r="F116" s="35" t="s">
         <v>122</v>
       </c>
       <c r="G116" s="22" t="s">
@@ -7141,9 +7142,9 @@
       <c r="C117" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D117" s="32"/>
-      <c r="E117" s="33"/>
-      <c r="F117" s="36"/>
+      <c r="D117" s="38"/>
+      <c r="E117" s="39"/>
+      <c r="F117" s="37"/>
       <c r="G117" s="22" t="s">
         <v>268</v>
       </c>
@@ -7162,9 +7163,9 @@
       <c r="C118" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D118" s="32"/>
-      <c r="E118" s="33"/>
-      <c r="F118" s="34" t="s">
+      <c r="D118" s="38"/>
+      <c r="E118" s="39"/>
+      <c r="F118" s="35" t="s">
         <v>129</v>
       </c>
       <c r="G118" s="22" t="s">
@@ -7185,9 +7186,9 @@
       <c r="C119" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D119" s="32"/>
-      <c r="E119" s="33"/>
-      <c r="F119" s="35"/>
+      <c r="D119" s="38"/>
+      <c r="E119" s="39"/>
+      <c r="F119" s="36"/>
       <c r="G119" s="22" t="s">
         <v>271</v>
       </c>
@@ -7206,9 +7207,9 @@
       <c r="C120" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D120" s="32"/>
-      <c r="E120" s="33"/>
-      <c r="F120" s="35"/>
+      <c r="D120" s="38"/>
+      <c r="E120" s="39"/>
+      <c r="F120" s="36"/>
       <c r="G120" s="22" t="s">
         <v>271</v>
       </c>
@@ -7227,9 +7228,9 @@
       <c r="C121" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D121" s="32"/>
-      <c r="E121" s="33"/>
-      <c r="F121" s="35"/>
+      <c r="D121" s="38"/>
+      <c r="E121" s="39"/>
+      <c r="F121" s="36"/>
       <c r="G121" s="22" t="s">
         <v>271</v>
       </c>
@@ -7248,9 +7249,9 @@
       <c r="C122" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D122" s="32"/>
-      <c r="E122" s="33"/>
-      <c r="F122" s="35"/>
+      <c r="D122" s="38"/>
+      <c r="E122" s="39"/>
+      <c r="F122" s="36"/>
       <c r="G122" s="22" t="s">
         <v>271</v>
       </c>
@@ -7269,9 +7270,9 @@
       <c r="C123" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D123" s="32"/>
-      <c r="E123" s="33"/>
-      <c r="F123" s="35"/>
+      <c r="D123" s="38"/>
+      <c r="E123" s="39"/>
+      <c r="F123" s="36"/>
       <c r="G123" s="22" t="s">
         <v>271</v>
       </c>
@@ -7290,9 +7291,9 @@
       <c r="C124" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D124" s="32"/>
-      <c r="E124" s="33"/>
-      <c r="F124" s="35"/>
+      <c r="D124" s="38"/>
+      <c r="E124" s="39"/>
+      <c r="F124" s="36"/>
       <c r="G124" s="22" t="s">
         <v>271</v>
       </c>
@@ -7311,9 +7312,9 @@
       <c r="C125" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D125" s="32"/>
-      <c r="E125" s="33"/>
-      <c r="F125" s="35"/>
+      <c r="D125" s="38"/>
+      <c r="E125" s="39"/>
+      <c r="F125" s="36"/>
       <c r="G125" s="22" t="s">
         <v>271</v>
       </c>
@@ -7332,9 +7333,9 @@
       <c r="C126" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D126" s="32"/>
-      <c r="E126" s="33"/>
-      <c r="F126" s="35"/>
+      <c r="D126" s="38"/>
+      <c r="E126" s="39"/>
+      <c r="F126" s="36"/>
       <c r="G126" s="22" t="s">
         <v>271</v>
       </c>
@@ -7353,9 +7354,9 @@
       <c r="C127" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D127" s="32"/>
-      <c r="E127" s="33"/>
-      <c r="F127" s="35"/>
+      <c r="D127" s="38"/>
+      <c r="E127" s="39"/>
+      <c r="F127" s="36"/>
       <c r="G127" s="22" t="s">
         <v>271</v>
       </c>
@@ -7374,9 +7375,9 @@
       <c r="C128" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D128" s="32"/>
-      <c r="E128" s="33"/>
-      <c r="F128" s="35"/>
+      <c r="D128" s="38"/>
+      <c r="E128" s="39"/>
+      <c r="F128" s="36"/>
       <c r="G128" s="22" t="s">
         <v>271</v>
       </c>
@@ -7395,9 +7396,9 @@
       <c r="C129" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D129" s="32"/>
-      <c r="E129" s="33"/>
-      <c r="F129" s="36"/>
+      <c r="D129" s="38"/>
+      <c r="E129" s="39"/>
+      <c r="F129" s="37"/>
       <c r="G129" s="22" t="s">
         <v>271</v>
       </c>
@@ -7416,9 +7417,9 @@
       <c r="C130" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D130" s="32"/>
-      <c r="E130" s="33"/>
-      <c r="F130" s="34" t="s">
+      <c r="D130" s="38"/>
+      <c r="E130" s="39"/>
+      <c r="F130" s="35" t="s">
         <v>122</v>
       </c>
       <c r="G130" s="22" t="s">
@@ -7439,9 +7440,9 @@
       <c r="C131" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D131" s="32"/>
-      <c r="E131" s="33"/>
-      <c r="F131" s="36"/>
+      <c r="D131" s="38"/>
+      <c r="E131" s="39"/>
+      <c r="F131" s="37"/>
       <c r="G131" s="22" t="s">
         <v>299</v>
       </c>
@@ -7460,9 +7461,9 @@
       <c r="C132" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D132" s="32"/>
-      <c r="E132" s="33"/>
-      <c r="F132" s="34" t="s">
+      <c r="D132" s="38"/>
+      <c r="E132" s="39"/>
+      <c r="F132" s="35" t="s">
         <v>129</v>
       </c>
       <c r="G132" s="22" t="s">
@@ -7483,9 +7484,9 @@
       <c r="C133" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D133" s="32"/>
-      <c r="E133" s="33"/>
-      <c r="F133" s="35"/>
+      <c r="D133" s="38"/>
+      <c r="E133" s="39"/>
+      <c r="F133" s="36"/>
       <c r="G133" s="22" t="s">
         <v>302</v>
       </c>
@@ -7504,9 +7505,9 @@
       <c r="C134" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D134" s="32"/>
-      <c r="E134" s="33"/>
-      <c r="F134" s="35"/>
+      <c r="D134" s="38"/>
+      <c r="E134" s="39"/>
+      <c r="F134" s="36"/>
       <c r="G134" s="22" t="s">
         <v>302</v>
       </c>
@@ -7525,9 +7526,9 @@
       <c r="C135" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D135" s="32"/>
-      <c r="E135" s="33"/>
-      <c r="F135" s="35"/>
+      <c r="D135" s="38"/>
+      <c r="E135" s="39"/>
+      <c r="F135" s="36"/>
       <c r="G135" s="22" t="s">
         <v>302</v>
       </c>
@@ -7546,9 +7547,9 @@
       <c r="C136" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D136" s="32"/>
-      <c r="E136" s="33"/>
-      <c r="F136" s="35"/>
+      <c r="D136" s="38"/>
+      <c r="E136" s="39"/>
+      <c r="F136" s="36"/>
       <c r="G136" s="22" t="s">
         <v>302</v>
       </c>
@@ -7567,9 +7568,9 @@
       <c r="C137" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D137" s="32"/>
-      <c r="E137" s="33"/>
-      <c r="F137" s="35"/>
+      <c r="D137" s="38"/>
+      <c r="E137" s="39"/>
+      <c r="F137" s="36"/>
       <c r="G137" s="22" t="s">
         <v>302</v>
       </c>
@@ -7588,9 +7589,9 @@
       <c r="C138" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D138" s="32"/>
-      <c r="E138" s="33"/>
-      <c r="F138" s="35"/>
+      <c r="D138" s="38"/>
+      <c r="E138" s="39"/>
+      <c r="F138" s="36"/>
       <c r="G138" s="22" t="s">
         <v>302</v>
       </c>
@@ -7609,9 +7610,9 @@
       <c r="C139" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D139" s="32"/>
-      <c r="E139" s="33"/>
-      <c r="F139" s="35"/>
+      <c r="D139" s="38"/>
+      <c r="E139" s="39"/>
+      <c r="F139" s="36"/>
       <c r="G139" s="22" t="s">
         <v>302</v>
       </c>
@@ -7630,9 +7631,9 @@
       <c r="C140" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D140" s="32"/>
-      <c r="E140" s="33"/>
-      <c r="F140" s="35"/>
+      <c r="D140" s="38"/>
+      <c r="E140" s="39"/>
+      <c r="F140" s="36"/>
       <c r="G140" s="22" t="s">
         <v>302</v>
       </c>
@@ -7651,9 +7652,9 @@
       <c r="C141" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D141" s="32"/>
-      <c r="E141" s="33"/>
-      <c r="F141" s="36"/>
+      <c r="D141" s="38"/>
+      <c r="E141" s="39"/>
+      <c r="F141" s="37"/>
       <c r="G141" s="22" t="s">
         <v>302</v>
       </c>
@@ -7672,9 +7673,9 @@
       <c r="C142" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D142" s="32"/>
-      <c r="E142" s="33"/>
-      <c r="F142" s="34" t="s">
+      <c r="D142" s="38"/>
+      <c r="E142" s="39"/>
+      <c r="F142" s="35" t="s">
         <v>122</v>
       </c>
       <c r="G142" s="22" t="s">
@@ -7695,9 +7696,9 @@
       <c r="C143" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D143" s="32"/>
-      <c r="E143" s="33"/>
-      <c r="F143" s="36"/>
+      <c r="D143" s="38"/>
+      <c r="E143" s="39"/>
+      <c r="F143" s="37"/>
       <c r="G143" s="22" t="s">
         <v>326</v>
       </c>
@@ -7716,9 +7717,9 @@
       <c r="C144" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D144" s="32"/>
-      <c r="E144" s="33"/>
-      <c r="F144" s="34" t="s">
+      <c r="D144" s="38"/>
+      <c r="E144" s="39"/>
+      <c r="F144" s="35" t="s">
         <v>129</v>
       </c>
       <c r="G144" s="22" t="s">
@@ -7739,9 +7740,9 @@
       <c r="C145" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D145" s="32"/>
-      <c r="E145" s="33"/>
-      <c r="F145" s="35"/>
+      <c r="D145" s="38"/>
+      <c r="E145" s="39"/>
+      <c r="F145" s="36"/>
       <c r="G145" s="22" t="s">
         <v>329</v>
       </c>
@@ -7760,9 +7761,9 @@
       <c r="C146" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D146" s="32"/>
-      <c r="E146" s="33"/>
-      <c r="F146" s="35"/>
+      <c r="D146" s="38"/>
+      <c r="E146" s="39"/>
+      <c r="F146" s="36"/>
       <c r="G146" s="22" t="s">
         <v>329</v>
       </c>
@@ -7781,9 +7782,9 @@
       <c r="C147" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D147" s="32"/>
-      <c r="E147" s="33"/>
-      <c r="F147" s="36"/>
+      <c r="D147" s="38"/>
+      <c r="E147" s="39"/>
+      <c r="F147" s="37"/>
       <c r="G147" s="22" t="s">
         <v>329</v>
       </c>
@@ -7802,9 +7803,9 @@
       <c r="C148" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D148" s="32"/>
-      <c r="E148" s="33"/>
-      <c r="F148" s="34" t="s">
+      <c r="D148" s="38"/>
+      <c r="E148" s="39"/>
+      <c r="F148" s="35" t="s">
         <v>122</v>
       </c>
       <c r="G148" s="22" t="s">
@@ -7825,9 +7826,9 @@
       <c r="C149" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D149" s="32"/>
-      <c r="E149" s="33"/>
-      <c r="F149" s="36"/>
+      <c r="D149" s="38"/>
+      <c r="E149" s="39"/>
+      <c r="F149" s="37"/>
       <c r="G149" s="22" t="s">
         <v>341</v>
       </c>
@@ -7846,9 +7847,9 @@
       <c r="C150" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D150" s="32"/>
-      <c r="E150" s="33"/>
-      <c r="F150" s="34" t="s">
+      <c r="D150" s="38"/>
+      <c r="E150" s="39"/>
+      <c r="F150" s="35" t="s">
         <v>129</v>
       </c>
       <c r="G150" s="22" t="s">
@@ -7869,9 +7870,9 @@
       <c r="C151" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D151" s="32"/>
-      <c r="E151" s="33"/>
-      <c r="F151" s="35"/>
+      <c r="D151" s="38"/>
+      <c r="E151" s="39"/>
+      <c r="F151" s="36"/>
       <c r="G151" s="22" t="s">
         <v>344</v>
       </c>
@@ -7890,9 +7891,9 @@
       <c r="C152" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D152" s="32"/>
-      <c r="E152" s="33"/>
-      <c r="F152" s="35"/>
+      <c r="D152" s="38"/>
+      <c r="E152" s="39"/>
+      <c r="F152" s="36"/>
       <c r="G152" s="22" t="s">
         <v>344</v>
       </c>
@@ -7911,9 +7912,9 @@
       <c r="C153" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D153" s="32"/>
-      <c r="E153" s="33"/>
-      <c r="F153" s="35"/>
+      <c r="D153" s="38"/>
+      <c r="E153" s="39"/>
+      <c r="F153" s="36"/>
       <c r="G153" s="22" t="s">
         <v>344</v>
       </c>
@@ -7932,9 +7933,9 @@
       <c r="C154" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D154" s="32"/>
-      <c r="E154" s="33"/>
-      <c r="F154" s="35"/>
+      <c r="D154" s="38"/>
+      <c r="E154" s="39"/>
+      <c r="F154" s="36"/>
       <c r="G154" s="22" t="s">
         <v>344</v>
       </c>
@@ -7953,9 +7954,9 @@
       <c r="C155" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D155" s="32"/>
-      <c r="E155" s="33"/>
-      <c r="F155" s="36"/>
+      <c r="D155" s="38"/>
+      <c r="E155" s="39"/>
+      <c r="F155" s="37"/>
       <c r="G155" s="22" t="s">
         <v>344</v>
       </c>
@@ -7974,9 +7975,9 @@
       <c r="C156" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D156" s="32"/>
-      <c r="E156" s="33"/>
-      <c r="F156" s="34" t="s">
+      <c r="D156" s="38"/>
+      <c r="E156" s="39"/>
+      <c r="F156" s="35" t="s">
         <v>122</v>
       </c>
       <c r="G156" s="22" t="s">
@@ -7997,9 +7998,9 @@
       <c r="C157" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D157" s="32"/>
-      <c r="E157" s="33"/>
-      <c r="F157" s="35"/>
+      <c r="D157" s="38"/>
+      <c r="E157" s="39"/>
+      <c r="F157" s="36"/>
       <c r="G157" s="22" t="s">
         <v>360</v>
       </c>
@@ -8018,9 +8019,9 @@
       <c r="C158" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D158" s="32"/>
-      <c r="E158" s="33"/>
-      <c r="F158" s="35"/>
+      <c r="D158" s="38"/>
+      <c r="E158" s="39"/>
+      <c r="F158" s="36"/>
       <c r="G158" s="22" t="s">
         <v>363</v>
       </c>
@@ -8039,9 +8040,9 @@
       <c r="C159" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D159" s="32"/>
-      <c r="E159" s="33"/>
-      <c r="F159" s="35"/>
+      <c r="D159" s="38"/>
+      <c r="E159" s="39"/>
+      <c r="F159" s="36"/>
       <c r="G159" s="22" t="s">
         <v>366</v>
       </c>
@@ -8060,9 +8061,9 @@
       <c r="C160" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D160" s="32"/>
-      <c r="E160" s="33"/>
-      <c r="F160" s="35"/>
+      <c r="D160" s="38"/>
+      <c r="E160" s="39"/>
+      <c r="F160" s="36"/>
       <c r="G160" s="22" t="s">
         <v>369</v>
       </c>
@@ -8081,9 +8082,9 @@
       <c r="C161" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D161" s="32"/>
-      <c r="E161" s="33"/>
-      <c r="F161" s="36"/>
+      <c r="D161" s="38"/>
+      <c r="E161" s="39"/>
+      <c r="F161" s="37"/>
       <c r="G161" s="22" t="s">
         <v>372</v>
       </c>
@@ -8102,9 +8103,9 @@
       <c r="C162" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D162" s="32"/>
-      <c r="E162" s="33"/>
-      <c r="F162" s="34" t="s">
+      <c r="D162" s="38"/>
+      <c r="E162" s="39"/>
+      <c r="F162" s="35" t="s">
         <v>129</v>
       </c>
       <c r="G162" s="22" t="s">
@@ -8125,9 +8126,9 @@
       <c r="C163" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D163" s="32"/>
-      <c r="E163" s="33"/>
-      <c r="F163" s="35"/>
+      <c r="D163" s="38"/>
+      <c r="E163" s="39"/>
+      <c r="F163" s="36"/>
       <c r="G163" s="22" t="s">
         <v>375</v>
       </c>
@@ -8146,9 +8147,9 @@
       <c r="C164" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D164" s="32"/>
-      <c r="E164" s="33"/>
-      <c r="F164" s="35"/>
+      <c r="D164" s="38"/>
+      <c r="E164" s="39"/>
+      <c r="F164" s="36"/>
       <c r="G164" s="22" t="s">
         <v>375</v>
       </c>
@@ -8167,9 +8168,9 @@
       <c r="C165" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D165" s="32"/>
-      <c r="E165" s="33"/>
-      <c r="F165" s="35"/>
+      <c r="D165" s="38"/>
+      <c r="E165" s="39"/>
+      <c r="F165" s="36"/>
       <c r="G165" s="22" t="s">
         <v>375</v>
       </c>
@@ -8188,9 +8189,9 @@
       <c r="C166" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D166" s="32"/>
-      <c r="E166" s="33"/>
-      <c r="F166" s="35"/>
+      <c r="D166" s="38"/>
+      <c r="E166" s="39"/>
+      <c r="F166" s="36"/>
       <c r="G166" s="22" t="s">
         <v>375</v>
       </c>
@@ -8209,9 +8210,9 @@
       <c r="C167" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D167" s="32"/>
-      <c r="E167" s="33"/>
-      <c r="F167" s="35"/>
+      <c r="D167" s="38"/>
+      <c r="E167" s="39"/>
+      <c r="F167" s="36"/>
       <c r="G167" s="22" t="s">
         <v>375</v>
       </c>
@@ -8230,9 +8231,9 @@
       <c r="C168" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D168" s="32"/>
-      <c r="E168" s="33"/>
-      <c r="F168" s="35"/>
+      <c r="D168" s="38"/>
+      <c r="E168" s="39"/>
+      <c r="F168" s="36"/>
       <c r="G168" s="22" t="s">
         <v>375</v>
       </c>
@@ -8251,9 +8252,9 @@
       <c r="C169" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D169" s="32"/>
-      <c r="E169" s="33"/>
-      <c r="F169" s="35"/>
+      <c r="D169" s="38"/>
+      <c r="E169" s="39"/>
+      <c r="F169" s="36"/>
       <c r="G169" s="22" t="s">
         <v>375</v>
       </c>
@@ -8272,9 +8273,9 @@
       <c r="C170" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D170" s="32"/>
-      <c r="E170" s="33"/>
-      <c r="F170" s="35"/>
+      <c r="D170" s="38"/>
+      <c r="E170" s="39"/>
+      <c r="F170" s="36"/>
       <c r="G170" s="22" t="s">
         <v>375</v>
       </c>
@@ -8293,9 +8294,9 @@
       <c r="C171" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D171" s="32"/>
-      <c r="E171" s="33"/>
-      <c r="F171" s="36"/>
+      <c r="D171" s="38"/>
+      <c r="E171" s="39"/>
+      <c r="F171" s="37"/>
       <c r="G171" s="22" t="s">
         <v>375</v>
       </c>
@@ -8314,9 +8315,9 @@
       <c r="C172" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D172" s="32"/>
-      <c r="E172" s="33"/>
-      <c r="F172" s="34" t="s">
+      <c r="D172" s="38"/>
+      <c r="E172" s="39"/>
+      <c r="F172" s="35" t="s">
         <v>122</v>
       </c>
       <c r="G172" s="22" t="s">
@@ -8337,9 +8338,9 @@
       <c r="C173" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D173" s="32"/>
-      <c r="E173" s="33"/>
-      <c r="F173" s="35"/>
+      <c r="D173" s="38"/>
+      <c r="E173" s="39"/>
+      <c r="F173" s="36"/>
       <c r="G173" s="22" t="s">
         <v>399</v>
       </c>
@@ -8358,9 +8359,9 @@
       <c r="C174" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D174" s="32"/>
-      <c r="E174" s="33"/>
-      <c r="F174" s="35"/>
+      <c r="D174" s="38"/>
+      <c r="E174" s="39"/>
+      <c r="F174" s="36"/>
       <c r="G174" s="22" t="s">
         <v>402</v>
       </c>
@@ -8379,9 +8380,9 @@
       <c r="C175" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D175" s="32"/>
-      <c r="E175" s="33"/>
-      <c r="F175" s="36"/>
+      <c r="D175" s="38"/>
+      <c r="E175" s="39"/>
+      <c r="F175" s="37"/>
       <c r="G175" s="22" t="s">
         <v>405</v>
       </c>
@@ -8400,9 +8401,9 @@
       <c r="C176" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D176" s="32"/>
-      <c r="E176" s="33"/>
-      <c r="F176" s="37" t="s">
+      <c r="D176" s="38"/>
+      <c r="E176" s="39"/>
+      <c r="F176" s="32" t="s">
         <v>129</v>
       </c>
       <c r="G176" s="23" t="s">
@@ -8423,9 +8424,9 @@
       <c r="C177" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D177" s="32"/>
-      <c r="E177" s="33"/>
-      <c r="F177" s="39"/>
+      <c r="D177" s="38"/>
+      <c r="E177" s="39"/>
+      <c r="F177" s="33"/>
       <c r="G177" s="23" t="s">
         <v>408</v>
       </c>
@@ -8444,9 +8445,9 @@
       <c r="C178" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D178" s="32"/>
-      <c r="E178" s="33"/>
-      <c r="F178" s="39"/>
+      <c r="D178" s="38"/>
+      <c r="E178" s="39"/>
+      <c r="F178" s="33"/>
       <c r="G178" s="23" t="s">
         <v>408</v>
       </c>
@@ -8465,9 +8466,9 @@
       <c r="C179" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D179" s="32"/>
-      <c r="E179" s="33"/>
-      <c r="F179" s="38"/>
+      <c r="D179" s="38"/>
+      <c r="E179" s="39"/>
+      <c r="F179" s="34"/>
       <c r="G179" s="23" t="s">
         <v>408</v>
       </c>
@@ -8486,9 +8487,9 @@
       <c r="C180" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D180" s="32"/>
-      <c r="E180" s="33"/>
-      <c r="F180" s="37" t="s">
+      <c r="D180" s="38"/>
+      <c r="E180" s="39"/>
+      <c r="F180" s="32" t="s">
         <v>122</v>
       </c>
       <c r="G180" s="23" t="s">
@@ -8509,9 +8510,9 @@
       <c r="C181" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D181" s="32"/>
-      <c r="E181" s="33"/>
-      <c r="F181" s="38"/>
+      <c r="D181" s="38"/>
+      <c r="E181" s="39"/>
+      <c r="F181" s="34"/>
       <c r="G181" s="23" t="s">
         <v>420</v>
       </c>
@@ -8530,9 +8531,9 @@
       <c r="C182" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D182" s="32"/>
-      <c r="E182" s="33"/>
-      <c r="F182" s="37" t="s">
+      <c r="D182" s="38"/>
+      <c r="E182" s="39"/>
+      <c r="F182" s="32" t="s">
         <v>129</v>
       </c>
       <c r="G182" s="23" t="s">
@@ -8553,9 +8554,9 @@
       <c r="C183" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D183" s="32"/>
-      <c r="E183" s="33"/>
-      <c r="F183" s="39"/>
+      <c r="D183" s="38"/>
+      <c r="E183" s="39"/>
+      <c r="F183" s="33"/>
       <c r="G183" s="23" t="s">
         <v>423</v>
       </c>
@@ -8574,9 +8575,9 @@
       <c r="C184" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D184" s="32"/>
-      <c r="E184" s="33"/>
-      <c r="F184" s="39"/>
+      <c r="D184" s="38"/>
+      <c r="E184" s="39"/>
+      <c r="F184" s="33"/>
       <c r="G184" s="23" t="s">
         <v>423</v>
       </c>
@@ -8595,9 +8596,9 @@
       <c r="C185" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D185" s="32"/>
-      <c r="E185" s="33"/>
-      <c r="F185" s="39"/>
+      <c r="D185" s="38"/>
+      <c r="E185" s="39"/>
+      <c r="F185" s="33"/>
       <c r="G185" s="23" t="s">
         <v>423</v>
       </c>
@@ -8616,9 +8617,9 @@
       <c r="C186" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D186" s="32"/>
-      <c r="E186" s="33"/>
-      <c r="F186" s="39"/>
+      <c r="D186" s="38"/>
+      <c r="E186" s="39"/>
+      <c r="F186" s="33"/>
       <c r="G186" s="23" t="s">
         <v>423</v>
       </c>
@@ -8637,9 +8638,9 @@
       <c r="C187" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D187" s="32"/>
-      <c r="E187" s="33"/>
-      <c r="F187" s="38"/>
+      <c r="D187" s="38"/>
+      <c r="E187" s="39"/>
+      <c r="F187" s="34"/>
       <c r="G187" s="23" t="s">
         <v>423</v>
       </c>
@@ -8658,9 +8659,9 @@
       <c r="C188" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D188" s="32"/>
-      <c r="E188" s="33"/>
-      <c r="F188" s="37" t="s">
+      <c r="D188" s="38"/>
+      <c r="E188" s="39"/>
+      <c r="F188" s="32" t="s">
         <v>122</v>
       </c>
       <c r="G188" s="23" t="s">
@@ -8681,9 +8682,9 @@
       <c r="C189" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D189" s="32"/>
-      <c r="E189" s="33"/>
-      <c r="F189" s="38"/>
+      <c r="D189" s="38"/>
+      <c r="E189" s="39"/>
+      <c r="F189" s="34"/>
       <c r="G189" s="23" t="s">
         <v>439</v>
       </c>
@@ -8702,9 +8703,9 @@
       <c r="C190" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D190" s="32"/>
-      <c r="E190" s="33"/>
-      <c r="F190" s="37" t="s">
+      <c r="D190" s="38"/>
+      <c r="E190" s="39"/>
+      <c r="F190" s="32" t="s">
         <v>129</v>
       </c>
       <c r="G190" s="23" t="s">
@@ -8725,9 +8726,9 @@
       <c r="C191" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D191" s="32"/>
-      <c r="E191" s="33"/>
-      <c r="F191" s="39"/>
+      <c r="D191" s="38"/>
+      <c r="E191" s="39"/>
+      <c r="F191" s="33"/>
       <c r="G191" s="23" t="s">
         <v>442</v>
       </c>
@@ -8746,9 +8747,9 @@
       <c r="C192" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D192" s="32"/>
-      <c r="E192" s="33"/>
-      <c r="F192" s="39"/>
+      <c r="D192" s="38"/>
+      <c r="E192" s="39"/>
+      <c r="F192" s="33"/>
       <c r="G192" s="23" t="s">
         <v>442</v>
       </c>
@@ -8767,9 +8768,9 @@
       <c r="C193" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D193" s="32"/>
-      <c r="E193" s="33"/>
-      <c r="F193" s="39"/>
+      <c r="D193" s="38"/>
+      <c r="E193" s="39"/>
+      <c r="F193" s="33"/>
       <c r="G193" s="23" t="s">
         <v>442</v>
       </c>
@@ -8788,9 +8789,9 @@
       <c r="C194" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D194" s="32"/>
-      <c r="E194" s="33"/>
-      <c r="F194" s="39"/>
+      <c r="D194" s="38"/>
+      <c r="E194" s="39"/>
+      <c r="F194" s="33"/>
       <c r="G194" s="23" t="s">
         <v>442</v>
       </c>
@@ -8809,9 +8810,9 @@
       <c r="C195" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D195" s="32"/>
-      <c r="E195" s="33"/>
-      <c r="F195" s="39"/>
+      <c r="D195" s="38"/>
+      <c r="E195" s="39"/>
+      <c r="F195" s="33"/>
       <c r="G195" s="23" t="s">
         <v>442</v>
       </c>
@@ -8830,9 +8831,9 @@
       <c r="C196" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D196" s="32"/>
-      <c r="E196" s="33"/>
-      <c r="F196" s="39"/>
+      <c r="D196" s="38"/>
+      <c r="E196" s="39"/>
+      <c r="F196" s="33"/>
       <c r="G196" s="23" t="s">
         <v>442</v>
       </c>
@@ -8851,9 +8852,9 @@
       <c r="C197" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D197" s="32"/>
-      <c r="E197" s="33"/>
-      <c r="F197" s="39"/>
+      <c r="D197" s="38"/>
+      <c r="E197" s="39"/>
+      <c r="F197" s="33"/>
       <c r="G197" s="23" t="s">
         <v>442</v>
       </c>
@@ -8872,9 +8873,9 @@
       <c r="C198" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D198" s="32"/>
-      <c r="E198" s="33"/>
-      <c r="F198" s="39"/>
+      <c r="D198" s="38"/>
+      <c r="E198" s="39"/>
+      <c r="F198" s="33"/>
       <c r="G198" s="23" t="s">
         <v>442</v>
       </c>
@@ -8893,9 +8894,9 @@
       <c r="C199" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D199" s="32"/>
-      <c r="E199" s="33"/>
-      <c r="F199" s="39"/>
+      <c r="D199" s="38"/>
+      <c r="E199" s="39"/>
+      <c r="F199" s="33"/>
       <c r="G199" s="23" t="s">
         <v>442</v>
       </c>
@@ -8914,9 +8915,9 @@
       <c r="C200" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D200" s="32"/>
-      <c r="E200" s="33"/>
-      <c r="F200" s="39"/>
+      <c r="D200" s="38"/>
+      <c r="E200" s="39"/>
+      <c r="F200" s="33"/>
       <c r="G200" s="23" t="s">
         <v>442</v>
       </c>
@@ -8935,9 +8936,9 @@
       <c r="C201" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D201" s="32"/>
-      <c r="E201" s="33"/>
-      <c r="F201" s="39"/>
+      <c r="D201" s="38"/>
+      <c r="E201" s="39"/>
+      <c r="F201" s="33"/>
       <c r="G201" s="23" t="s">
         <v>442</v>
       </c>
@@ -8956,9 +8957,9 @@
       <c r="C202" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D202" s="32"/>
-      <c r="E202" s="33"/>
-      <c r="F202" s="39"/>
+      <c r="D202" s="38"/>
+      <c r="E202" s="39"/>
+      <c r="F202" s="33"/>
       <c r="G202" s="23" t="s">
         <v>442</v>
       </c>
@@ -8977,9 +8978,9 @@
       <c r="C203" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D203" s="32"/>
-      <c r="E203" s="33"/>
-      <c r="F203" s="39"/>
+      <c r="D203" s="38"/>
+      <c r="E203" s="39"/>
+      <c r="F203" s="33"/>
       <c r="G203" s="23" t="s">
         <v>442</v>
       </c>
@@ -8998,9 +8999,9 @@
       <c r="C204" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D204" s="32"/>
-      <c r="E204" s="33"/>
-      <c r="F204" s="39"/>
+      <c r="D204" s="38"/>
+      <c r="E204" s="39"/>
+      <c r="F204" s="33"/>
       <c r="G204" s="23" t="s">
         <v>442</v>
       </c>
@@ -9019,9 +9020,9 @@
       <c r="C205" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D205" s="32"/>
-      <c r="E205" s="33"/>
-      <c r="F205" s="39"/>
+      <c r="D205" s="38"/>
+      <c r="E205" s="39"/>
+      <c r="F205" s="33"/>
       <c r="G205" s="23" t="s">
         <v>442</v>
       </c>
@@ -9040,9 +9041,9 @@
       <c r="C206" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D206" s="32"/>
-      <c r="E206" s="33"/>
-      <c r="F206" s="39"/>
+      <c r="D206" s="38"/>
+      <c r="E206" s="39"/>
+      <c r="F206" s="33"/>
       <c r="G206" s="23" t="s">
         <v>442</v>
       </c>
@@ -9061,9 +9062,9 @@
       <c r="C207" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D207" s="32"/>
-      <c r="E207" s="33"/>
-      <c r="F207" s="38"/>
+      <c r="D207" s="38"/>
+      <c r="E207" s="39"/>
+      <c r="F207" s="34"/>
       <c r="G207" s="23" t="s">
         <v>442</v>
       </c>
@@ -9082,9 +9083,9 @@
       <c r="C208" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D208" s="32"/>
-      <c r="E208" s="33"/>
-      <c r="F208" s="37" t="s">
+      <c r="D208" s="38"/>
+      <c r="E208" s="39"/>
+      <c r="F208" s="32" t="s">
         <v>122</v>
       </c>
       <c r="G208" s="23" t="s">
@@ -9105,9 +9106,9 @@
       <c r="C209" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D209" s="32"/>
-      <c r="E209" s="33"/>
-      <c r="F209" s="38"/>
+      <c r="D209" s="38"/>
+      <c r="E209" s="39"/>
+      <c r="F209" s="34"/>
       <c r="G209" s="23" t="s">
         <v>482</v>
       </c>
@@ -9126,9 +9127,9 @@
       <c r="C210" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D210" s="32"/>
-      <c r="E210" s="33"/>
-      <c r="F210" s="37" t="s">
+      <c r="D210" s="38"/>
+      <c r="E210" s="39"/>
+      <c r="F210" s="32" t="s">
         <v>129</v>
       </c>
       <c r="G210" s="23" t="s">
@@ -9149,9 +9150,9 @@
       <c r="C211" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D211" s="32"/>
-      <c r="E211" s="33"/>
-      <c r="F211" s="39"/>
+      <c r="D211" s="38"/>
+      <c r="E211" s="39"/>
+      <c r="F211" s="33"/>
       <c r="G211" s="23" t="s">
         <v>485</v>
       </c>
@@ -9170,9 +9171,9 @@
       <c r="C212" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D212" s="32"/>
-      <c r="E212" s="33"/>
-      <c r="F212" s="39"/>
+      <c r="D212" s="38"/>
+      <c r="E212" s="39"/>
+      <c r="F212" s="33"/>
       <c r="G212" s="23" t="s">
         <v>485</v>
       </c>
@@ -9191,9 +9192,9 @@
       <c r="C213" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D213" s="32"/>
-      <c r="E213" s="33"/>
-      <c r="F213" s="39"/>
+      <c r="D213" s="38"/>
+      <c r="E213" s="39"/>
+      <c r="F213" s="33"/>
       <c r="G213" s="23" t="s">
         <v>485</v>
       </c>
@@ -9212,9 +9213,9 @@
       <c r="C214" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D214" s="32"/>
-      <c r="E214" s="33"/>
-      <c r="F214" s="39"/>
+      <c r="D214" s="38"/>
+      <c r="E214" s="39"/>
+      <c r="F214" s="33"/>
       <c r="G214" s="23" t="s">
         <v>485</v>
       </c>
@@ -9233,9 +9234,9 @@
       <c r="C215" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D215" s="32"/>
-      <c r="E215" s="33"/>
-      <c r="F215" s="38"/>
+      <c r="D215" s="38"/>
+      <c r="E215" s="39"/>
+      <c r="F215" s="34"/>
       <c r="G215" s="23" t="s">
         <v>485</v>
       </c>
@@ -9254,9 +9255,9 @@
       <c r="C216" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D216" s="32"/>
-      <c r="E216" s="33"/>
-      <c r="F216" s="37" t="s">
+      <c r="D216" s="38"/>
+      <c r="E216" s="39"/>
+      <c r="F216" s="32" t="s">
         <v>122</v>
       </c>
       <c r="G216" s="23" t="s">
@@ -9277,9 +9278,9 @@
       <c r="C217" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D217" s="32"/>
-      <c r="E217" s="33"/>
-      <c r="F217" s="38"/>
+      <c r="D217" s="38"/>
+      <c r="E217" s="39"/>
+      <c r="F217" s="34"/>
       <c r="G217" s="23" t="s">
         <v>499</v>
       </c>
@@ -9298,9 +9299,9 @@
       <c r="C218" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D218" s="32"/>
-      <c r="E218" s="33"/>
-      <c r="F218" s="37" t="s">
+      <c r="D218" s="38"/>
+      <c r="E218" s="39"/>
+      <c r="F218" s="32" t="s">
         <v>129</v>
       </c>
       <c r="G218" s="23" t="s">
@@ -9321,9 +9322,9 @@
       <c r="C219" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D219" s="32"/>
-      <c r="E219" s="33"/>
-      <c r="F219" s="39"/>
+      <c r="D219" s="38"/>
+      <c r="E219" s="39"/>
+      <c r="F219" s="33"/>
       <c r="G219" s="23" t="s">
         <v>502</v>
       </c>
@@ -9342,9 +9343,9 @@
       <c r="C220" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D220" s="32"/>
-      <c r="E220" s="33"/>
-      <c r="F220" s="39"/>
+      <c r="D220" s="38"/>
+      <c r="E220" s="39"/>
+      <c r="F220" s="33"/>
       <c r="G220" s="23" t="s">
         <v>502</v>
       </c>
@@ -9363,9 +9364,9 @@
       <c r="C221" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D221" s="32"/>
-      <c r="E221" s="33"/>
-      <c r="F221" s="39"/>
+      <c r="D221" s="38"/>
+      <c r="E221" s="39"/>
+      <c r="F221" s="33"/>
       <c r="G221" s="23" t="s">
         <v>502</v>
       </c>
@@ -9384,9 +9385,9 @@
       <c r="C222" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D222" s="32"/>
-      <c r="E222" s="33"/>
-      <c r="F222" s="39"/>
+      <c r="D222" s="38"/>
+      <c r="E222" s="39"/>
+      <c r="F222" s="33"/>
       <c r="G222" s="23" t="s">
         <v>502</v>
       </c>
@@ -9405,9 +9406,9 @@
       <c r="C223" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D223" s="32"/>
-      <c r="E223" s="33"/>
-      <c r="F223" s="38"/>
+      <c r="D223" s="38"/>
+      <c r="E223" s="39"/>
+      <c r="F223" s="34"/>
       <c r="G223" s="23" t="s">
         <v>502</v>
       </c>
@@ -9426,9 +9427,9 @@
       <c r="C224" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D224" s="32"/>
-      <c r="E224" s="33"/>
-      <c r="F224" s="37" t="s">
+      <c r="D224" s="38"/>
+      <c r="E224" s="39"/>
+      <c r="F224" s="32" t="s">
         <v>122</v>
       </c>
       <c r="G224" s="23" t="s">
@@ -9449,9 +9450,9 @@
       <c r="C225" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D225" s="32"/>
-      <c r="E225" s="33"/>
-      <c r="F225" s="39"/>
+      <c r="D225" s="38"/>
+      <c r="E225" s="39"/>
+      <c r="F225" s="33"/>
       <c r="G225" s="23" t="s">
         <v>518</v>
       </c>
@@ -9470,9 +9471,9 @@
       <c r="C226" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D226" s="32"/>
-      <c r="E226" s="33"/>
-      <c r="F226" s="39"/>
+      <c r="D226" s="38"/>
+      <c r="E226" s="39"/>
+      <c r="F226" s="33"/>
       <c r="G226" s="23" t="s">
         <v>521</v>
       </c>
@@ -9491,9 +9492,9 @@
       <c r="C227" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D227" s="32"/>
-      <c r="E227" s="33"/>
-      <c r="F227" s="39"/>
+      <c r="D227" s="38"/>
+      <c r="E227" s="39"/>
+      <c r="F227" s="33"/>
       <c r="G227" s="23" t="s">
         <v>524</v>
       </c>
@@ -9512,9 +9513,9 @@
       <c r="C228" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D228" s="32"/>
-      <c r="E228" s="33"/>
-      <c r="F228" s="39"/>
+      <c r="D228" s="38"/>
+      <c r="E228" s="39"/>
+      <c r="F228" s="33"/>
       <c r="G228" s="23" t="s">
         <v>527</v>
       </c>
@@ -9533,9 +9534,9 @@
       <c r="C229" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D229" s="32"/>
-      <c r="E229" s="33"/>
-      <c r="F229" s="39"/>
+      <c r="D229" s="38"/>
+      <c r="E229" s="39"/>
+      <c r="F229" s="33"/>
       <c r="G229" s="23" t="s">
         <v>530</v>
       </c>
@@ -9554,9 +9555,9 @@
       <c r="C230" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D230" s="32"/>
-      <c r="E230" s="33"/>
-      <c r="F230" s="39"/>
+      <c r="D230" s="38"/>
+      <c r="E230" s="39"/>
+      <c r="F230" s="33"/>
       <c r="G230" s="23" t="s">
         <v>533</v>
       </c>
@@ -9575,9 +9576,9 @@
       <c r="C231" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D231" s="32"/>
-      <c r="E231" s="33"/>
-      <c r="F231" s="39"/>
+      <c r="D231" s="38"/>
+      <c r="E231" s="39"/>
+      <c r="F231" s="33"/>
       <c r="G231" s="23" t="s">
         <v>536</v>
       </c>
@@ -9596,9 +9597,9 @@
       <c r="C232" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D232" s="32"/>
-      <c r="E232" s="33"/>
-      <c r="F232" s="39"/>
+      <c r="D232" s="38"/>
+      <c r="E232" s="39"/>
+      <c r="F232" s="33"/>
       <c r="G232" s="23" t="s">
         <v>539</v>
       </c>
@@ -9617,9 +9618,9 @@
       <c r="C233" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D233" s="32"/>
-      <c r="E233" s="33"/>
-      <c r="F233" s="38"/>
+      <c r="D233" s="38"/>
+      <c r="E233" s="39"/>
+      <c r="F233" s="34"/>
       <c r="G233" s="23" t="s">
         <v>542</v>
       </c>
@@ -9638,9 +9639,9 @@
       <c r="C234" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D234" s="32"/>
-      <c r="E234" s="33"/>
-      <c r="F234" s="37" t="s">
+      <c r="D234" s="38"/>
+      <c r="E234" s="39"/>
+      <c r="F234" s="32" t="s">
         <v>129</v>
       </c>
       <c r="G234" s="23" t="s">
@@ -9661,9 +9662,9 @@
       <c r="C235" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D235" s="32"/>
-      <c r="E235" s="33"/>
-      <c r="F235" s="39"/>
+      <c r="D235" s="38"/>
+      <c r="E235" s="39"/>
+      <c r="F235" s="33"/>
       <c r="G235" s="23" t="s">
         <v>545</v>
       </c>
@@ -9682,9 +9683,9 @@
       <c r="C236" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D236" s="32"/>
-      <c r="E236" s="33"/>
-      <c r="F236" s="39"/>
+      <c r="D236" s="38"/>
+      <c r="E236" s="39"/>
+      <c r="F236" s="33"/>
       <c r="G236" s="23" t="s">
         <v>545</v>
       </c>
@@ -9703,9 +9704,9 @@
       <c r="C237" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D237" s="32"/>
-      <c r="E237" s="33"/>
-      <c r="F237" s="39"/>
+      <c r="D237" s="38"/>
+      <c r="E237" s="39"/>
+      <c r="F237" s="33"/>
       <c r="G237" s="23" t="s">
         <v>545</v>
       </c>
@@ -9724,9 +9725,9 @@
       <c r="C238" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D238" s="32"/>
-      <c r="E238" s="33"/>
-      <c r="F238" s="39"/>
+      <c r="D238" s="38"/>
+      <c r="E238" s="39"/>
+      <c r="F238" s="33"/>
       <c r="G238" s="23" t="s">
         <v>545</v>
       </c>
@@ -9745,9 +9746,9 @@
       <c r="C239" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D239" s="32"/>
-      <c r="E239" s="33"/>
-      <c r="F239" s="39"/>
+      <c r="D239" s="38"/>
+      <c r="E239" s="39"/>
+      <c r="F239" s="33"/>
       <c r="G239" s="23" t="s">
         <v>545</v>
       </c>
@@ -9766,9 +9767,9 @@
       <c r="C240" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D240" s="32"/>
-      <c r="E240" s="33"/>
-      <c r="F240" s="39"/>
+      <c r="D240" s="38"/>
+      <c r="E240" s="39"/>
+      <c r="F240" s="33"/>
       <c r="G240" s="23" t="s">
         <v>545</v>
       </c>
@@ -9787,9 +9788,9 @@
       <c r="C241" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D241" s="32"/>
-      <c r="E241" s="33"/>
-      <c r="F241" s="38"/>
+      <c r="D241" s="38"/>
+      <c r="E241" s="39"/>
+      <c r="F241" s="34"/>
       <c r="G241" s="23" t="s">
         <v>545</v>
       </c>
@@ -9808,9 +9809,9 @@
       <c r="C242" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D242" s="32"/>
-      <c r="E242" s="33"/>
-      <c r="F242" s="37" t="s">
+      <c r="D242" s="38"/>
+      <c r="E242" s="39"/>
+      <c r="F242" s="32" t="s">
         <v>122</v>
       </c>
       <c r="G242" s="23" t="s">
@@ -9831,9 +9832,9 @@
       <c r="C243" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D243" s="32"/>
-      <c r="E243" s="33"/>
-      <c r="F243" s="38"/>
+      <c r="D243" s="38"/>
+      <c r="E243" s="39"/>
+      <c r="F243" s="34"/>
       <c r="G243" s="23" t="s">
         <v>565</v>
       </c>
@@ -9852,9 +9853,9 @@
       <c r="C244" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D244" s="32"/>
-      <c r="E244" s="33"/>
-      <c r="F244" s="37" t="s">
+      <c r="D244" s="38"/>
+      <c r="E244" s="39"/>
+      <c r="F244" s="32" t="s">
         <v>129</v>
       </c>
       <c r="G244" s="23" t="s">
@@ -9875,9 +9876,9 @@
       <c r="C245" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D245" s="32"/>
-      <c r="E245" s="33"/>
-      <c r="F245" s="39"/>
+      <c r="D245" s="38"/>
+      <c r="E245" s="39"/>
+      <c r="F245" s="33"/>
       <c r="G245" s="23" t="s">
         <v>568</v>
       </c>
@@ -9896,9 +9897,9 @@
       <c r="C246" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D246" s="32"/>
-      <c r="E246" s="33"/>
-      <c r="F246" s="39"/>
+      <c r="D246" s="38"/>
+      <c r="E246" s="39"/>
+      <c r="F246" s="33"/>
       <c r="G246" s="23" t="s">
         <v>568</v>
       </c>
@@ -9917,9 +9918,9 @@
       <c r="C247" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D247" s="32"/>
-      <c r="E247" s="33"/>
-      <c r="F247" s="38"/>
+      <c r="D247" s="38"/>
+      <c r="E247" s="39"/>
+      <c r="F247" s="34"/>
       <c r="G247" s="23" t="s">
         <v>568</v>
       </c>
@@ -9938,9 +9939,9 @@
       <c r="C248" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D248" s="32"/>
-      <c r="E248" s="33"/>
-      <c r="F248" s="37" t="s">
+      <c r="D248" s="38"/>
+      <c r="E248" s="39"/>
+      <c r="F248" s="32" t="s">
         <v>122</v>
       </c>
       <c r="G248" s="23" t="s">
@@ -9961,9 +9962,9 @@
       <c r="C249" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D249" s="32"/>
-      <c r="E249" s="33"/>
-      <c r="F249" s="39"/>
+      <c r="D249" s="38"/>
+      <c r="E249" s="39"/>
+      <c r="F249" s="33"/>
       <c r="G249" s="23" t="s">
         <v>580</v>
       </c>
@@ -9982,9 +9983,9 @@
       <c r="C250" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D250" s="32"/>
-      <c r="E250" s="33"/>
-      <c r="F250" s="39"/>
+      <c r="D250" s="38"/>
+      <c r="E250" s="39"/>
+      <c r="F250" s="33"/>
       <c r="G250" s="23" t="s">
         <v>583</v>
       </c>
@@ -10003,9 +10004,9 @@
       <c r="C251" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D251" s="32"/>
-      <c r="E251" s="33"/>
-      <c r="F251" s="38"/>
+      <c r="D251" s="38"/>
+      <c r="E251" s="39"/>
+      <c r="F251" s="34"/>
       <c r="G251" s="23" t="s">
         <v>586</v>
       </c>
@@ -10024,9 +10025,9 @@
       <c r="C252" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D252" s="32"/>
-      <c r="E252" s="33"/>
-      <c r="F252" s="37" t="s">
+      <c r="D252" s="38"/>
+      <c r="E252" s="39"/>
+      <c r="F252" s="32" t="s">
         <v>129</v>
       </c>
       <c r="G252" s="23" t="s">
@@ -10047,9 +10048,9 @@
       <c r="C253" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D253" s="32"/>
-      <c r="E253" s="33"/>
-      <c r="F253" s="39"/>
+      <c r="D253" s="38"/>
+      <c r="E253" s="39"/>
+      <c r="F253" s="33"/>
       <c r="G253" s="23" t="s">
         <v>589</v>
       </c>
@@ -10068,9 +10069,9 @@
       <c r="C254" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D254" s="32"/>
-      <c r="E254" s="33"/>
-      <c r="F254" s="39"/>
+      <c r="D254" s="38"/>
+      <c r="E254" s="39"/>
+      <c r="F254" s="33"/>
       <c r="G254" s="23" t="s">
         <v>589</v>
       </c>
@@ -10089,9 +10090,9 @@
       <c r="C255" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D255" s="32"/>
-      <c r="E255" s="33"/>
-      <c r="F255" s="39"/>
+      <c r="D255" s="38"/>
+      <c r="E255" s="39"/>
+      <c r="F255" s="33"/>
       <c r="G255" s="23" t="s">
         <v>589</v>
       </c>
@@ -10110,9 +10111,9 @@
       <c r="C256" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D256" s="32"/>
-      <c r="E256" s="33"/>
-      <c r="F256" s="39"/>
+      <c r="D256" s="38"/>
+      <c r="E256" s="39"/>
+      <c r="F256" s="33"/>
       <c r="G256" s="23" t="s">
         <v>589</v>
       </c>
@@ -10131,9 +10132,9 @@
       <c r="C257" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D257" s="32"/>
-      <c r="E257" s="33"/>
-      <c r="F257" s="38"/>
+      <c r="D257" s="38"/>
+      <c r="E257" s="39"/>
+      <c r="F257" s="34"/>
       <c r="G257" s="23" t="s">
         <v>589</v>
       </c>
@@ -10152,9 +10153,9 @@
       <c r="C258" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D258" s="32"/>
-      <c r="E258" s="33"/>
-      <c r="F258" s="37" t="s">
+      <c r="D258" s="38"/>
+      <c r="E258" s="39"/>
+      <c r="F258" s="32" t="s">
         <v>122</v>
       </c>
       <c r="G258" s="23" t="s">
@@ -10175,9 +10176,9 @@
       <c r="C259" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D259" s="32"/>
-      <c r="E259" s="33"/>
-      <c r="F259" s="39"/>
+      <c r="D259" s="38"/>
+      <c r="E259" s="39"/>
+      <c r="F259" s="33"/>
       <c r="G259" s="23" t="s">
         <v>605</v>
       </c>
@@ -10196,9 +10197,9 @@
       <c r="C260" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D260" s="32"/>
-      <c r="E260" s="33"/>
-      <c r="F260" s="39"/>
+      <c r="D260" s="38"/>
+      <c r="E260" s="39"/>
+      <c r="F260" s="33"/>
       <c r="G260" s="23" t="s">
         <v>608</v>
       </c>
@@ -10217,9 +10218,9 @@
       <c r="C261" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D261" s="32"/>
-      <c r="E261" s="33"/>
-      <c r="F261" s="39"/>
+      <c r="D261" s="38"/>
+      <c r="E261" s="39"/>
+      <c r="F261" s="33"/>
       <c r="G261" s="23" t="s">
         <v>611</v>
       </c>
@@ -10238,9 +10239,9 @@
       <c r="C262" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D262" s="32"/>
-      <c r="E262" s="33"/>
-      <c r="F262" s="38"/>
+      <c r="D262" s="38"/>
+      <c r="E262" s="39"/>
+      <c r="F262" s="34"/>
       <c r="G262" s="23" t="s">
         <v>28</v>
       </c>
@@ -10259,9 +10260,9 @@
       <c r="C263" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D263" s="32"/>
-      <c r="E263" s="33"/>
-      <c r="F263" s="37" t="s">
+      <c r="D263" s="38"/>
+      <c r="E263" s="39"/>
+      <c r="F263" s="32" t="s">
         <v>616</v>
       </c>
       <c r="G263" s="23" t="s">
@@ -10282,9 +10283,9 @@
       <c r="C264" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D264" s="32"/>
-      <c r="E264" s="33"/>
-      <c r="F264" s="39"/>
+      <c r="D264" s="38"/>
+      <c r="E264" s="39"/>
+      <c r="F264" s="33"/>
       <c r="G264" s="23" t="s">
         <v>617</v>
       </c>
@@ -10303,9 +10304,9 @@
       <c r="C265" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D265" s="32"/>
-      <c r="E265" s="33"/>
-      <c r="F265" s="39"/>
+      <c r="D265" s="38"/>
+      <c r="E265" s="39"/>
+      <c r="F265" s="33"/>
       <c r="G265" s="23" t="s">
         <v>617</v>
       </c>
@@ -10324,9 +10325,9 @@
       <c r="C266" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D266" s="32"/>
-      <c r="E266" s="33"/>
-      <c r="F266" s="39"/>
+      <c r="D266" s="38"/>
+      <c r="E266" s="39"/>
+      <c r="F266" s="33"/>
       <c r="G266" s="23" t="s">
         <v>617</v>
       </c>
@@ -10345,9 +10346,9 @@
       <c r="C267" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D267" s="32"/>
-      <c r="E267" s="33"/>
-      <c r="F267" s="39"/>
+      <c r="D267" s="38"/>
+      <c r="E267" s="39"/>
+      <c r="F267" s="33"/>
       <c r="G267" s="23" t="s">
         <v>617</v>
       </c>
@@ -10366,9 +10367,9 @@
       <c r="C268" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D268" s="32"/>
-      <c r="E268" s="33"/>
-      <c r="F268" s="39"/>
+      <c r="D268" s="38"/>
+      <c r="E268" s="39"/>
+      <c r="F268" s="33"/>
       <c r="G268" s="23" t="s">
         <v>617</v>
       </c>
@@ -10387,9 +10388,9 @@
       <c r="C269" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D269" s="32"/>
-      <c r="E269" s="33"/>
-      <c r="F269" s="39"/>
+      <c r="D269" s="38"/>
+      <c r="E269" s="39"/>
+      <c r="F269" s="33"/>
       <c r="G269" s="23" t="s">
         <v>617</v>
       </c>
@@ -10408,9 +10409,9 @@
       <c r="C270" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D270" s="32"/>
-      <c r="E270" s="33"/>
-      <c r="F270" s="39"/>
+      <c r="D270" s="38"/>
+      <c r="E270" s="39"/>
+      <c r="F270" s="33"/>
       <c r="G270" s="23" t="s">
         <v>617</v>
       </c>
@@ -10429,9 +10430,9 @@
       <c r="C271" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D271" s="32"/>
-      <c r="E271" s="33"/>
-      <c r="F271" s="39"/>
+      <c r="D271" s="38"/>
+      <c r="E271" s="39"/>
+      <c r="F271" s="33"/>
       <c r="G271" s="23" t="s">
         <v>617</v>
       </c>
@@ -10450,9 +10451,9 @@
       <c r="C272" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D272" s="32"/>
-      <c r="E272" s="33"/>
-      <c r="F272" s="39"/>
+      <c r="D272" s="38"/>
+      <c r="E272" s="39"/>
+      <c r="F272" s="33"/>
       <c r="G272" s="23" t="s">
         <v>617</v>
       </c>
@@ -10471,9 +10472,9 @@
       <c r="C273" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D273" s="32"/>
-      <c r="E273" s="33"/>
-      <c r="F273" s="39"/>
+      <c r="D273" s="38"/>
+      <c r="E273" s="39"/>
+      <c r="F273" s="33"/>
       <c r="G273" s="23" t="s">
         <v>617</v>
       </c>
@@ -10492,9 +10493,9 @@
       <c r="C274" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D274" s="32"/>
-      <c r="E274" s="33"/>
-      <c r="F274" s="39"/>
+      <c r="D274" s="38"/>
+      <c r="E274" s="39"/>
+      <c r="F274" s="33"/>
       <c r="G274" s="23" t="s">
         <v>617</v>
       </c>
@@ -10513,9 +10514,9 @@
       <c r="C275" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D275" s="32"/>
-      <c r="E275" s="33"/>
-      <c r="F275" s="39"/>
+      <c r="D275" s="38"/>
+      <c r="E275" s="39"/>
+      <c r="F275" s="33"/>
       <c r="G275" s="23" t="s">
         <v>642</v>
       </c>
@@ -10534,9 +10535,9 @@
       <c r="C276" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D276" s="32"/>
-      <c r="E276" s="33"/>
-      <c r="F276" s="39"/>
+      <c r="D276" s="38"/>
+      <c r="E276" s="39"/>
+      <c r="F276" s="33"/>
       <c r="G276" s="23" t="s">
         <v>642</v>
       </c>
@@ -10555,9 +10556,9 @@
       <c r="C277" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D277" s="32"/>
-      <c r="E277" s="33"/>
-      <c r="F277" s="39"/>
+      <c r="D277" s="38"/>
+      <c r="E277" s="39"/>
+      <c r="F277" s="33"/>
       <c r="G277" s="23" t="s">
         <v>642</v>
       </c>
@@ -10576,9 +10577,9 @@
       <c r="C278" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D278" s="32"/>
-      <c r="E278" s="33"/>
-      <c r="F278" s="39"/>
+      <c r="D278" s="38"/>
+      <c r="E278" s="39"/>
+      <c r="F278" s="33"/>
       <c r="G278" s="23" t="s">
         <v>642</v>
       </c>
@@ -10597,9 +10598,9 @@
       <c r="C279" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D279" s="32"/>
-      <c r="E279" s="33"/>
-      <c r="F279" s="39"/>
+      <c r="D279" s="38"/>
+      <c r="E279" s="39"/>
+      <c r="F279" s="33"/>
       <c r="G279" s="23" t="s">
         <v>642</v>
       </c>
@@ -10618,9 +10619,9 @@
       <c r="C280" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D280" s="32"/>
-      <c r="E280" s="33"/>
-      <c r="F280" s="39"/>
+      <c r="D280" s="38"/>
+      <c r="E280" s="39"/>
+      <c r="F280" s="33"/>
       <c r="G280" s="23" t="s">
         <v>642</v>
       </c>
@@ -10639,9 +10640,9 @@
       <c r="C281" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D281" s="32"/>
-      <c r="E281" s="33"/>
-      <c r="F281" s="39"/>
+      <c r="D281" s="38"/>
+      <c r="E281" s="39"/>
+      <c r="F281" s="33"/>
       <c r="G281" s="23" t="s">
         <v>642</v>
       </c>
@@ -10660,9 +10661,9 @@
       <c r="C282" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D282" s="32"/>
-      <c r="E282" s="33"/>
-      <c r="F282" s="39"/>
+      <c r="D282" s="38"/>
+      <c r="E282" s="39"/>
+      <c r="F282" s="33"/>
       <c r="G282" s="23" t="s">
         <v>642</v>
       </c>
@@ -10681,9 +10682,9 @@
       <c r="C283" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D283" s="32"/>
-      <c r="E283" s="33"/>
-      <c r="F283" s="39"/>
+      <c r="D283" s="38"/>
+      <c r="E283" s="39"/>
+      <c r="F283" s="33"/>
       <c r="G283" s="23" t="s">
         <v>642</v>
       </c>
@@ -10702,9 +10703,9 @@
       <c r="C284" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D284" s="32"/>
-      <c r="E284" s="33"/>
-      <c r="F284" s="39"/>
+      <c r="D284" s="38"/>
+      <c r="E284" s="39"/>
+      <c r="F284" s="33"/>
       <c r="G284" s="23" t="s">
         <v>642</v>
       </c>
@@ -10723,9 +10724,9 @@
       <c r="C285" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D285" s="32"/>
-      <c r="E285" s="33"/>
-      <c r="F285" s="39"/>
+      <c r="D285" s="38"/>
+      <c r="E285" s="39"/>
+      <c r="F285" s="33"/>
       <c r="G285" s="23" t="s">
         <v>642</v>
       </c>
@@ -10744,9 +10745,9 @@
       <c r="C286" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D286" s="32"/>
-      <c r="E286" s="33"/>
-      <c r="F286" s="39"/>
+      <c r="D286" s="38"/>
+      <c r="E286" s="39"/>
+      <c r="F286" s="33"/>
       <c r="G286" s="23" t="s">
         <v>642</v>
       </c>
@@ -10765,9 +10766,9 @@
       <c r="C287" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D287" s="32"/>
-      <c r="E287" s="33"/>
-      <c r="F287" s="39"/>
+      <c r="D287" s="38"/>
+      <c r="E287" s="39"/>
+      <c r="F287" s="33"/>
       <c r="G287" s="23" t="s">
         <v>667</v>
       </c>
@@ -10786,9 +10787,9 @@
       <c r="C288" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D288" s="32"/>
-      <c r="E288" s="33"/>
-      <c r="F288" s="39"/>
+      <c r="D288" s="38"/>
+      <c r="E288" s="39"/>
+      <c r="F288" s="33"/>
       <c r="G288" s="23" t="s">
         <v>667</v>
       </c>
@@ -10807,9 +10808,9 @@
       <c r="C289" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D289" s="32"/>
-      <c r="E289" s="33"/>
-      <c r="F289" s="39"/>
+      <c r="D289" s="38"/>
+      <c r="E289" s="39"/>
+      <c r="F289" s="33"/>
       <c r="G289" s="23" t="s">
         <v>667</v>
       </c>
@@ -10828,9 +10829,9 @@
       <c r="C290" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D290" s="32"/>
-      <c r="E290" s="33"/>
-      <c r="F290" s="39"/>
+      <c r="D290" s="38"/>
+      <c r="E290" s="39"/>
+      <c r="F290" s="33"/>
       <c r="G290" s="23" t="s">
         <v>667</v>
       </c>
@@ -10849,9 +10850,9 @@
       <c r="C291" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D291" s="32"/>
-      <c r="E291" s="33"/>
-      <c r="F291" s="39"/>
+      <c r="D291" s="38"/>
+      <c r="E291" s="39"/>
+      <c r="F291" s="33"/>
       <c r="G291" s="23" t="s">
         <v>667</v>
       </c>
@@ -10870,9 +10871,9 @@
       <c r="C292" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D292" s="32"/>
-      <c r="E292" s="33"/>
-      <c r="F292" s="39"/>
+      <c r="D292" s="38"/>
+      <c r="E292" s="39"/>
+      <c r="F292" s="33"/>
       <c r="G292" s="23" t="s">
         <v>667</v>
       </c>
@@ -10891,9 +10892,9 @@
       <c r="C293" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D293" s="32"/>
-      <c r="E293" s="33"/>
-      <c r="F293" s="39"/>
+      <c r="D293" s="38"/>
+      <c r="E293" s="39"/>
+      <c r="F293" s="33"/>
       <c r="G293" s="23" t="s">
         <v>667</v>
       </c>
@@ -10912,9 +10913,9 @@
       <c r="C294" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D294" s="32"/>
-      <c r="E294" s="33"/>
-      <c r="F294" s="39"/>
+      <c r="D294" s="38"/>
+      <c r="E294" s="39"/>
+      <c r="F294" s="33"/>
       <c r="G294" s="23" t="s">
         <v>667</v>
       </c>
@@ -10933,9 +10934,9 @@
       <c r="C295" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D295" s="32"/>
-      <c r="E295" s="33"/>
-      <c r="F295" s="39"/>
+      <c r="D295" s="38"/>
+      <c r="E295" s="39"/>
+      <c r="F295" s="33"/>
       <c r="G295" s="23" t="s">
         <v>667</v>
       </c>
@@ -10954,9 +10955,9 @@
       <c r="C296" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D296" s="32"/>
-      <c r="E296" s="33"/>
-      <c r="F296" s="39"/>
+      <c r="D296" s="38"/>
+      <c r="E296" s="39"/>
+      <c r="F296" s="33"/>
       <c r="G296" s="23" t="s">
         <v>667</v>
       </c>
@@ -10975,9 +10976,9 @@
       <c r="C297" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D297" s="32"/>
-      <c r="E297" s="33"/>
-      <c r="F297" s="39"/>
+      <c r="D297" s="38"/>
+      <c r="E297" s="39"/>
+      <c r="F297" s="33"/>
       <c r="G297" s="23" t="s">
         <v>667</v>
       </c>
@@ -10996,9 +10997,9 @@
       <c r="C298" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D298" s="32"/>
-      <c r="E298" s="33"/>
-      <c r="F298" s="39"/>
+      <c r="D298" s="38"/>
+      <c r="E298" s="39"/>
+      <c r="F298" s="33"/>
       <c r="G298" s="23" t="s">
         <v>667</v>
       </c>
@@ -11017,9 +11018,9 @@
       <c r="C299" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D299" s="32"/>
-      <c r="E299" s="33"/>
-      <c r="F299" s="39"/>
+      <c r="D299" s="38"/>
+      <c r="E299" s="39"/>
+      <c r="F299" s="33"/>
       <c r="G299" s="23" t="s">
         <v>692</v>
       </c>
@@ -11038,9 +11039,9 @@
       <c r="C300" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D300" s="32"/>
-      <c r="E300" s="33"/>
-      <c r="F300" s="39"/>
+      <c r="D300" s="38"/>
+      <c r="E300" s="39"/>
+      <c r="F300" s="33"/>
       <c r="G300" s="23" t="s">
         <v>692</v>
       </c>
@@ -11059,9 +11060,9 @@
       <c r="C301" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D301" s="32"/>
-      <c r="E301" s="33"/>
-      <c r="F301" s="39"/>
+      <c r="D301" s="38"/>
+      <c r="E301" s="39"/>
+      <c r="F301" s="33"/>
       <c r="G301" s="23" t="s">
         <v>692</v>
       </c>
@@ -11080,9 +11081,9 @@
       <c r="C302" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D302" s="32"/>
-      <c r="E302" s="33"/>
-      <c r="F302" s="39"/>
+      <c r="D302" s="38"/>
+      <c r="E302" s="39"/>
+      <c r="F302" s="33"/>
       <c r="G302" s="23" t="s">
         <v>692</v>
       </c>
@@ -11101,9 +11102,9 @@
       <c r="C303" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D303" s="32"/>
-      <c r="E303" s="33"/>
-      <c r="F303" s="39"/>
+      <c r="D303" s="38"/>
+      <c r="E303" s="39"/>
+      <c r="F303" s="33"/>
       <c r="G303" s="23" t="s">
         <v>692</v>
       </c>
@@ -11122,9 +11123,9 @@
       <c r="C304" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D304" s="32"/>
-      <c r="E304" s="33"/>
-      <c r="F304" s="39"/>
+      <c r="D304" s="38"/>
+      <c r="E304" s="39"/>
+      <c r="F304" s="33"/>
       <c r="G304" s="23" t="s">
         <v>692</v>
       </c>
@@ -11143,9 +11144,9 @@
       <c r="C305" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D305" s="32"/>
-      <c r="E305" s="33"/>
-      <c r="F305" s="39"/>
+      <c r="D305" s="38"/>
+      <c r="E305" s="39"/>
+      <c r="F305" s="33"/>
       <c r="G305" s="23" t="s">
         <v>692</v>
       </c>
@@ -11164,9 +11165,9 @@
       <c r="C306" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D306" s="32"/>
-      <c r="E306" s="33"/>
-      <c r="F306" s="39"/>
+      <c r="D306" s="38"/>
+      <c r="E306" s="39"/>
+      <c r="F306" s="33"/>
       <c r="G306" s="23" t="s">
         <v>692</v>
       </c>
@@ -11185,9 +11186,9 @@
       <c r="C307" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D307" s="32"/>
-      <c r="E307" s="33"/>
-      <c r="F307" s="39"/>
+      <c r="D307" s="38"/>
+      <c r="E307" s="39"/>
+      <c r="F307" s="33"/>
       <c r="G307" s="23" t="s">
         <v>692</v>
       </c>
@@ -11206,9 +11207,9 @@
       <c r="C308" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D308" s="32"/>
-      <c r="E308" s="33"/>
-      <c r="F308" s="39"/>
+      <c r="D308" s="38"/>
+      <c r="E308" s="39"/>
+      <c r="F308" s="33"/>
       <c r="G308" s="23" t="s">
         <v>692</v>
       </c>
@@ -11227,9 +11228,9 @@
       <c r="C309" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D309" s="32"/>
-      <c r="E309" s="33"/>
-      <c r="F309" s="39"/>
+      <c r="D309" s="38"/>
+      <c r="E309" s="39"/>
+      <c r="F309" s="33"/>
       <c r="G309" s="23" t="s">
         <v>692</v>
       </c>
@@ -11248,9 +11249,9 @@
       <c r="C310" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D310" s="32"/>
-      <c r="E310" s="33"/>
-      <c r="F310" s="39"/>
+      <c r="D310" s="38"/>
+      <c r="E310" s="39"/>
+      <c r="F310" s="33"/>
       <c r="G310" s="23" t="s">
         <v>692</v>
       </c>
@@ -11269,9 +11270,9 @@
       <c r="C311" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D311" s="32"/>
-      <c r="E311" s="33"/>
-      <c r="F311" s="39"/>
+      <c r="D311" s="38"/>
+      <c r="E311" s="39"/>
+      <c r="F311" s="33"/>
       <c r="G311" s="23" t="s">
         <v>717</v>
       </c>
@@ -11290,9 +11291,9 @@
       <c r="C312" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D312" s="32"/>
-      <c r="E312" s="33"/>
-      <c r="F312" s="39"/>
+      <c r="D312" s="38"/>
+      <c r="E312" s="39"/>
+      <c r="F312" s="33"/>
       <c r="G312" s="23" t="s">
         <v>717</v>
       </c>
@@ -11311,9 +11312,9 @@
       <c r="C313" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D313" s="32"/>
-      <c r="E313" s="33"/>
-      <c r="F313" s="39"/>
+      <c r="D313" s="38"/>
+      <c r="E313" s="39"/>
+      <c r="F313" s="33"/>
       <c r="G313" s="23" t="s">
         <v>717</v>
       </c>
@@ -11332,9 +11333,9 @@
       <c r="C314" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D314" s="32"/>
-      <c r="E314" s="33"/>
-      <c r="F314" s="39"/>
+      <c r="D314" s="38"/>
+      <c r="E314" s="39"/>
+      <c r="F314" s="33"/>
       <c r="G314" s="23" t="s">
         <v>717</v>
       </c>
@@ -11353,9 +11354,9 @@
       <c r="C315" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D315" s="32"/>
-      <c r="E315" s="33"/>
-      <c r="F315" s="39"/>
+      <c r="D315" s="38"/>
+      <c r="E315" s="39"/>
+      <c r="F315" s="33"/>
       <c r="G315" s="23" t="s">
         <v>717</v>
       </c>
@@ -11374,9 +11375,9 @@
       <c r="C316" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D316" s="32"/>
-      <c r="E316" s="33"/>
-      <c r="F316" s="39"/>
+      <c r="D316" s="38"/>
+      <c r="E316" s="39"/>
+      <c r="F316" s="33"/>
       <c r="G316" s="23" t="s">
         <v>717</v>
       </c>
@@ -11395,9 +11396,9 @@
       <c r="C317" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D317" s="32"/>
-      <c r="E317" s="33"/>
-      <c r="F317" s="39"/>
+      <c r="D317" s="38"/>
+      <c r="E317" s="39"/>
+      <c r="F317" s="33"/>
       <c r="G317" s="23" t="s">
         <v>717</v>
       </c>
@@ -11416,9 +11417,9 @@
       <c r="C318" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D318" s="32"/>
-      <c r="E318" s="33"/>
-      <c r="F318" s="39"/>
+      <c r="D318" s="38"/>
+      <c r="E318" s="39"/>
+      <c r="F318" s="33"/>
       <c r="G318" s="23" t="s">
         <v>717</v>
       </c>
@@ -11437,9 +11438,9 @@
       <c r="C319" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D319" s="32"/>
-      <c r="E319" s="33"/>
-      <c r="F319" s="39"/>
+      <c r="D319" s="38"/>
+      <c r="E319" s="39"/>
+      <c r="F319" s="33"/>
       <c r="G319" s="23" t="s">
         <v>717</v>
       </c>
@@ -11458,9 +11459,9 @@
       <c r="C320" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D320" s="32"/>
-      <c r="E320" s="33"/>
-      <c r="F320" s="39"/>
+      <c r="D320" s="38"/>
+      <c r="E320" s="39"/>
+      <c r="F320" s="33"/>
       <c r="G320" s="23" t="s">
         <v>717</v>
       </c>
@@ -11479,9 +11480,9 @@
       <c r="C321" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D321" s="32"/>
-      <c r="E321" s="33"/>
-      <c r="F321" s="39"/>
+      <c r="D321" s="38"/>
+      <c r="E321" s="39"/>
+      <c r="F321" s="33"/>
       <c r="G321" s="23" t="s">
         <v>717</v>
       </c>
@@ -11500,9 +11501,9 @@
       <c r="C322" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D322" s="32"/>
-      <c r="E322" s="33"/>
-      <c r="F322" s="39"/>
+      <c r="D322" s="38"/>
+      <c r="E322" s="39"/>
+      <c r="F322" s="33"/>
       <c r="G322" s="23" t="s">
         <v>717</v>
       </c>
@@ -11521,9 +11522,9 @@
       <c r="C323" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D323" s="32"/>
-      <c r="E323" s="33"/>
-      <c r="F323" s="39"/>
+      <c r="D323" s="38"/>
+      <c r="E323" s="39"/>
+      <c r="F323" s="33"/>
       <c r="G323" s="23" t="s">
         <v>742</v>
       </c>
@@ -11542,9 +11543,9 @@
       <c r="C324" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D324" s="32"/>
-      <c r="E324" s="33"/>
-      <c r="F324" s="39"/>
+      <c r="D324" s="38"/>
+      <c r="E324" s="39"/>
+      <c r="F324" s="33"/>
       <c r="G324" s="23" t="s">
         <v>742</v>
       </c>
@@ -11563,9 +11564,9 @@
       <c r="C325" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D325" s="32"/>
-      <c r="E325" s="33"/>
-      <c r="F325" s="39"/>
+      <c r="D325" s="38"/>
+      <c r="E325" s="39"/>
+      <c r="F325" s="33"/>
       <c r="G325" s="23" t="s">
         <v>742</v>
       </c>
@@ -11584,9 +11585,9 @@
       <c r="C326" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D326" s="32"/>
-      <c r="E326" s="33"/>
-      <c r="F326" s="39"/>
+      <c r="D326" s="38"/>
+      <c r="E326" s="39"/>
+      <c r="F326" s="33"/>
       <c r="G326" s="23" t="s">
         <v>742</v>
       </c>
@@ -11605,9 +11606,9 @@
       <c r="C327" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D327" s="32"/>
-      <c r="E327" s="33"/>
-      <c r="F327" s="39"/>
+      <c r="D327" s="38"/>
+      <c r="E327" s="39"/>
+      <c r="F327" s="33"/>
       <c r="G327" s="23" t="s">
         <v>742</v>
       </c>
@@ -11626,9 +11627,9 @@
       <c r="C328" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D328" s="32"/>
-      <c r="E328" s="33"/>
-      <c r="F328" s="39"/>
+      <c r="D328" s="38"/>
+      <c r="E328" s="39"/>
+      <c r="F328" s="33"/>
       <c r="G328" s="23" t="s">
         <v>742</v>
       </c>
@@ -11647,9 +11648,9 @@
       <c r="C329" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D329" s="32"/>
-      <c r="E329" s="33"/>
-      <c r="F329" s="39"/>
+      <c r="D329" s="38"/>
+      <c r="E329" s="39"/>
+      <c r="F329" s="33"/>
       <c r="G329" s="23" t="s">
         <v>742</v>
       </c>
@@ -11668,9 +11669,9 @@
       <c r="C330" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D330" s="32"/>
-      <c r="E330" s="33"/>
-      <c r="F330" s="39"/>
+      <c r="D330" s="38"/>
+      <c r="E330" s="39"/>
+      <c r="F330" s="33"/>
       <c r="G330" s="23" t="s">
         <v>742</v>
       </c>
@@ -11689,9 +11690,9 @@
       <c r="C331" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D331" s="32"/>
-      <c r="E331" s="33"/>
-      <c r="F331" s="39"/>
+      <c r="D331" s="38"/>
+      <c r="E331" s="39"/>
+      <c r="F331" s="33"/>
       <c r="G331" s="23" t="s">
         <v>742</v>
       </c>
@@ -11710,9 +11711,9 @@
       <c r="C332" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D332" s="32"/>
-      <c r="E332" s="33"/>
-      <c r="F332" s="39"/>
+      <c r="D332" s="38"/>
+      <c r="E332" s="39"/>
+      <c r="F332" s="33"/>
       <c r="G332" s="23" t="s">
         <v>742</v>
       </c>
@@ -11731,9 +11732,9 @@
       <c r="C333" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D333" s="32"/>
-      <c r="E333" s="33"/>
-      <c r="F333" s="39"/>
+      <c r="D333" s="38"/>
+      <c r="E333" s="39"/>
+      <c r="F333" s="33"/>
       <c r="G333" s="23" t="s">
         <v>742</v>
       </c>
@@ -11752,9 +11753,9 @@
       <c r="C334" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D334" s="32"/>
-      <c r="E334" s="33"/>
-      <c r="F334" s="39"/>
+      <c r="D334" s="38"/>
+      <c r="E334" s="39"/>
+      <c r="F334" s="33"/>
       <c r="G334" s="23" t="s">
         <v>742</v>
       </c>
@@ -11773,9 +11774,9 @@
       <c r="C335" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D335" s="32"/>
-      <c r="E335" s="33"/>
-      <c r="F335" s="39"/>
+      <c r="D335" s="38"/>
+      <c r="E335" s="39"/>
+      <c r="F335" s="33"/>
       <c r="G335" s="23" t="s">
         <v>767</v>
       </c>
@@ -11794,9 +11795,9 @@
       <c r="C336" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D336" s="32"/>
-      <c r="E336" s="33"/>
-      <c r="F336" s="39"/>
+      <c r="D336" s="38"/>
+      <c r="E336" s="39"/>
+      <c r="F336" s="33"/>
       <c r="G336" s="23" t="s">
         <v>767</v>
       </c>
@@ -11815,9 +11816,9 @@
       <c r="C337" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D337" s="32"/>
-      <c r="E337" s="33"/>
-      <c r="F337" s="39"/>
+      <c r="D337" s="38"/>
+      <c r="E337" s="39"/>
+      <c r="F337" s="33"/>
       <c r="G337" s="23" t="s">
         <v>767</v>
       </c>
@@ -11836,9 +11837,9 @@
       <c r="C338" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D338" s="32"/>
-      <c r="E338" s="33"/>
-      <c r="F338" s="39"/>
+      <c r="D338" s="38"/>
+      <c r="E338" s="39"/>
+      <c r="F338" s="33"/>
       <c r="G338" s="23" t="s">
         <v>767</v>
       </c>
@@ -11857,9 +11858,9 @@
       <c r="C339" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D339" s="32"/>
-      <c r="E339" s="33"/>
-      <c r="F339" s="39"/>
+      <c r="D339" s="38"/>
+      <c r="E339" s="39"/>
+      <c r="F339" s="33"/>
       <c r="G339" s="23" t="s">
         <v>767</v>
       </c>
@@ -11878,9 +11879,9 @@
       <c r="C340" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D340" s="32"/>
-      <c r="E340" s="33"/>
-      <c r="F340" s="39"/>
+      <c r="D340" s="38"/>
+      <c r="E340" s="39"/>
+      <c r="F340" s="33"/>
       <c r="G340" s="23" t="s">
         <v>767</v>
       </c>
@@ -11899,9 +11900,9 @@
       <c r="C341" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D341" s="32"/>
-      <c r="E341" s="33"/>
-      <c r="F341" s="39"/>
+      <c r="D341" s="38"/>
+      <c r="E341" s="39"/>
+      <c r="F341" s="33"/>
       <c r="G341" s="23" t="s">
         <v>767</v>
       </c>
@@ -11920,9 +11921,9 @@
       <c r="C342" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D342" s="32"/>
-      <c r="E342" s="33"/>
-      <c r="F342" s="39"/>
+      <c r="D342" s="38"/>
+      <c r="E342" s="39"/>
+      <c r="F342" s="33"/>
       <c r="G342" s="23" t="s">
         <v>767</v>
       </c>
@@ -11941,9 +11942,9 @@
       <c r="C343" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D343" s="32"/>
-      <c r="E343" s="33"/>
-      <c r="F343" s="39"/>
+      <c r="D343" s="38"/>
+      <c r="E343" s="39"/>
+      <c r="F343" s="33"/>
       <c r="G343" s="23" t="s">
         <v>767</v>
       </c>
@@ -11962,9 +11963,9 @@
       <c r="C344" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D344" s="32"/>
-      <c r="E344" s="33"/>
-      <c r="F344" s="39"/>
+      <c r="D344" s="38"/>
+      <c r="E344" s="39"/>
+      <c r="F344" s="33"/>
       <c r="G344" s="23" t="s">
         <v>767</v>
       </c>
@@ -11983,9 +11984,9 @@
       <c r="C345" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D345" s="32"/>
-      <c r="E345" s="33"/>
-      <c r="F345" s="39"/>
+      <c r="D345" s="38"/>
+      <c r="E345" s="39"/>
+      <c r="F345" s="33"/>
       <c r="G345" s="23" t="s">
         <v>767</v>
       </c>
@@ -12004,9 +12005,9 @@
       <c r="C346" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D346" s="32"/>
-      <c r="E346" s="33"/>
-      <c r="F346" s="39"/>
+      <c r="D346" s="38"/>
+      <c r="E346" s="39"/>
+      <c r="F346" s="33"/>
       <c r="G346" s="23" t="s">
         <v>767</v>
       </c>
@@ -12025,9 +12026,9 @@
       <c r="C347" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D347" s="32"/>
-      <c r="E347" s="33"/>
-      <c r="F347" s="39"/>
+      <c r="D347" s="38"/>
+      <c r="E347" s="39"/>
+      <c r="F347" s="33"/>
       <c r="G347" s="23" t="s">
         <v>792</v>
       </c>
@@ -12046,9 +12047,9 @@
       <c r="C348" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D348" s="32"/>
-      <c r="E348" s="33"/>
-      <c r="F348" s="39"/>
+      <c r="D348" s="38"/>
+      <c r="E348" s="39"/>
+      <c r="F348" s="33"/>
       <c r="G348" s="23" t="s">
         <v>792</v>
       </c>
@@ -12067,9 +12068,9 @@
       <c r="C349" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D349" s="32"/>
-      <c r="E349" s="33"/>
-      <c r="F349" s="39"/>
+      <c r="D349" s="38"/>
+      <c r="E349" s="39"/>
+      <c r="F349" s="33"/>
       <c r="G349" s="23" t="s">
         <v>792</v>
       </c>
@@ -12088,9 +12089,9 @@
       <c r="C350" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D350" s="32"/>
-      <c r="E350" s="33"/>
-      <c r="F350" s="39"/>
+      <c r="D350" s="38"/>
+      <c r="E350" s="39"/>
+      <c r="F350" s="33"/>
       <c r="G350" s="23" t="s">
         <v>792</v>
       </c>
@@ -12109,9 +12110,9 @@
       <c r="C351" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D351" s="32"/>
-      <c r="E351" s="33"/>
-      <c r="F351" s="39"/>
+      <c r="D351" s="38"/>
+      <c r="E351" s="39"/>
+      <c r="F351" s="33"/>
       <c r="G351" s="23" t="s">
         <v>792</v>
       </c>
@@ -12130,9 +12131,9 @@
       <c r="C352" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D352" s="32"/>
-      <c r="E352" s="33"/>
-      <c r="F352" s="39"/>
+      <c r="D352" s="38"/>
+      <c r="E352" s="39"/>
+      <c r="F352" s="33"/>
       <c r="G352" s="23" t="s">
         <v>792</v>
       </c>
@@ -12151,9 +12152,9 @@
       <c r="C353" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D353" s="32"/>
-      <c r="E353" s="33"/>
-      <c r="F353" s="39"/>
+      <c r="D353" s="38"/>
+      <c r="E353" s="39"/>
+      <c r="F353" s="33"/>
       <c r="G353" s="23" t="s">
         <v>792</v>
       </c>
@@ -12172,9 +12173,9 @@
       <c r="C354" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D354" s="32"/>
-      <c r="E354" s="33"/>
-      <c r="F354" s="39"/>
+      <c r="D354" s="38"/>
+      <c r="E354" s="39"/>
+      <c r="F354" s="33"/>
       <c r="G354" s="23" t="s">
         <v>792</v>
       </c>
@@ -12193,9 +12194,9 @@
       <c r="C355" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D355" s="32"/>
-      <c r="E355" s="33"/>
-      <c r="F355" s="39"/>
+      <c r="D355" s="38"/>
+      <c r="E355" s="39"/>
+      <c r="F355" s="33"/>
       <c r="G355" s="23" t="s">
         <v>792</v>
       </c>
@@ -12214,9 +12215,9 @@
       <c r="C356" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D356" s="32"/>
-      <c r="E356" s="33"/>
-      <c r="F356" s="39"/>
+      <c r="D356" s="38"/>
+      <c r="E356" s="39"/>
+      <c r="F356" s="33"/>
       <c r="G356" s="23" t="s">
         <v>792</v>
       </c>
@@ -12235,9 +12236,9 @@
       <c r="C357" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D357" s="32"/>
-      <c r="E357" s="33"/>
-      <c r="F357" s="39"/>
+      <c r="D357" s="38"/>
+      <c r="E357" s="39"/>
+      <c r="F357" s="33"/>
       <c r="G357" s="23" t="s">
         <v>792</v>
       </c>
@@ -12256,9 +12257,9 @@
       <c r="C358" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D358" s="32"/>
-      <c r="E358" s="33"/>
-      <c r="F358" s="39"/>
+      <c r="D358" s="38"/>
+      <c r="E358" s="39"/>
+      <c r="F358" s="33"/>
       <c r="G358" s="23" t="s">
         <v>792</v>
       </c>
@@ -12277,9 +12278,9 @@
       <c r="C359" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D359" s="32"/>
-      <c r="E359" s="33"/>
-      <c r="F359" s="39"/>
+      <c r="D359" s="38"/>
+      <c r="E359" s="39"/>
+      <c r="F359" s="33"/>
       <c r="G359" s="23" t="s">
         <v>817</v>
       </c>
@@ -12298,9 +12299,9 @@
       <c r="C360" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D360" s="32"/>
-      <c r="E360" s="33"/>
-      <c r="F360" s="39"/>
+      <c r="D360" s="38"/>
+      <c r="E360" s="39"/>
+      <c r="F360" s="33"/>
       <c r="G360" s="23" t="s">
         <v>817</v>
       </c>
@@ -12319,9 +12320,9 @@
       <c r="C361" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D361" s="32"/>
-      <c r="E361" s="33"/>
-      <c r="F361" s="39"/>
+      <c r="D361" s="38"/>
+      <c r="E361" s="39"/>
+      <c r="F361" s="33"/>
       <c r="G361" s="23" t="s">
         <v>817</v>
       </c>
@@ -12340,9 +12341,9 @@
       <c r="C362" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D362" s="32"/>
-      <c r="E362" s="33"/>
-      <c r="F362" s="39"/>
+      <c r="D362" s="38"/>
+      <c r="E362" s="39"/>
+      <c r="F362" s="33"/>
       <c r="G362" s="23" t="s">
         <v>817</v>
       </c>
@@ -12361,9 +12362,9 @@
       <c r="C363" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D363" s="32"/>
-      <c r="E363" s="33"/>
-      <c r="F363" s="39"/>
+      <c r="D363" s="38"/>
+      <c r="E363" s="39"/>
+      <c r="F363" s="33"/>
       <c r="G363" s="23" t="s">
         <v>817</v>
       </c>
@@ -12382,9 +12383,9 @@
       <c r="C364" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D364" s="32"/>
-      <c r="E364" s="33"/>
-      <c r="F364" s="39"/>
+      <c r="D364" s="38"/>
+      <c r="E364" s="39"/>
+      <c r="F364" s="33"/>
       <c r="G364" s="23" t="s">
         <v>817</v>
       </c>
@@ -12403,9 +12404,9 @@
       <c r="C365" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D365" s="32"/>
-      <c r="E365" s="33"/>
-      <c r="F365" s="39"/>
+      <c r="D365" s="38"/>
+      <c r="E365" s="39"/>
+      <c r="F365" s="33"/>
       <c r="G365" s="23" t="s">
         <v>817</v>
       </c>
@@ -12424,9 +12425,9 @@
       <c r="C366" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D366" s="32"/>
-      <c r="E366" s="33"/>
-      <c r="F366" s="39"/>
+      <c r="D366" s="38"/>
+      <c r="E366" s="39"/>
+      <c r="F366" s="33"/>
       <c r="G366" s="23" t="s">
         <v>817</v>
       </c>
@@ -12445,9 +12446,9 @@
       <c r="C367" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D367" s="32"/>
-      <c r="E367" s="33"/>
-      <c r="F367" s="39"/>
+      <c r="D367" s="38"/>
+      <c r="E367" s="39"/>
+      <c r="F367" s="33"/>
       <c r="G367" s="23" t="s">
         <v>817</v>
       </c>
@@ -12466,9 +12467,9 @@
       <c r="C368" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D368" s="32"/>
-      <c r="E368" s="33"/>
-      <c r="F368" s="39"/>
+      <c r="D368" s="38"/>
+      <c r="E368" s="39"/>
+      <c r="F368" s="33"/>
       <c r="G368" s="23" t="s">
         <v>817</v>
       </c>
@@ -12487,9 +12488,9 @@
       <c r="C369" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D369" s="32"/>
-      <c r="E369" s="33"/>
-      <c r="F369" s="39"/>
+      <c r="D369" s="38"/>
+      <c r="E369" s="39"/>
+      <c r="F369" s="33"/>
       <c r="G369" s="23" t="s">
         <v>817</v>
       </c>
@@ -12508,9 +12509,9 @@
       <c r="C370" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D370" s="32"/>
-      <c r="E370" s="33"/>
-      <c r="F370" s="39"/>
+      <c r="D370" s="38"/>
+      <c r="E370" s="39"/>
+      <c r="F370" s="33"/>
       <c r="G370" s="23" t="s">
         <v>817</v>
       </c>
@@ -12529,9 +12530,9 @@
       <c r="C371" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D371" s="32"/>
-      <c r="E371" s="33"/>
-      <c r="F371" s="39"/>
+      <c r="D371" s="38"/>
+      <c r="E371" s="39"/>
+      <c r="F371" s="33"/>
       <c r="G371" s="23" t="s">
         <v>842</v>
       </c>
@@ -12550,9 +12551,9 @@
       <c r="C372" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D372" s="32"/>
-      <c r="E372" s="33"/>
-      <c r="F372" s="39"/>
+      <c r="D372" s="38"/>
+      <c r="E372" s="39"/>
+      <c r="F372" s="33"/>
       <c r="G372" s="23" t="s">
         <v>842</v>
       </c>
@@ -12571,9 +12572,9 @@
       <c r="C373" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D373" s="32"/>
-      <c r="E373" s="33"/>
-      <c r="F373" s="39"/>
+      <c r="D373" s="38"/>
+      <c r="E373" s="39"/>
+      <c r="F373" s="33"/>
       <c r="G373" s="23" t="s">
         <v>842</v>
       </c>
@@ -12592,9 +12593,9 @@
       <c r="C374" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D374" s="32"/>
-      <c r="E374" s="33"/>
-      <c r="F374" s="39"/>
+      <c r="D374" s="38"/>
+      <c r="E374" s="39"/>
+      <c r="F374" s="33"/>
       <c r="G374" s="23" t="s">
         <v>842</v>
       </c>
@@ -12613,9 +12614,9 @@
       <c r="C375" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D375" s="32"/>
-      <c r="E375" s="33"/>
-      <c r="F375" s="39"/>
+      <c r="D375" s="38"/>
+      <c r="E375" s="39"/>
+      <c r="F375" s="33"/>
       <c r="G375" s="23" t="s">
         <v>842</v>
       </c>
@@ -12634,9 +12635,9 @@
       <c r="C376" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D376" s="32"/>
-      <c r="E376" s="33"/>
-      <c r="F376" s="39"/>
+      <c r="D376" s="38"/>
+      <c r="E376" s="39"/>
+      <c r="F376" s="33"/>
       <c r="G376" s="23" t="s">
         <v>842</v>
       </c>
@@ -12655,9 +12656,9 @@
       <c r="C377" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D377" s="32"/>
-      <c r="E377" s="33"/>
-      <c r="F377" s="39"/>
+      <c r="D377" s="38"/>
+      <c r="E377" s="39"/>
+      <c r="F377" s="33"/>
       <c r="G377" s="23" t="s">
         <v>842</v>
       </c>
@@ -12676,9 +12677,9 @@
       <c r="C378" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D378" s="32"/>
-      <c r="E378" s="33"/>
-      <c r="F378" s="39"/>
+      <c r="D378" s="38"/>
+      <c r="E378" s="39"/>
+      <c r="F378" s="33"/>
       <c r="G378" s="23" t="s">
         <v>842</v>
       </c>
@@ -12697,9 +12698,9 @@
       <c r="C379" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D379" s="32"/>
-      <c r="E379" s="33"/>
-      <c r="F379" s="39"/>
+      <c r="D379" s="38"/>
+      <c r="E379" s="39"/>
+      <c r="F379" s="33"/>
       <c r="G379" s="23" t="s">
         <v>842</v>
       </c>
@@ -12718,9 +12719,9 @@
       <c r="C380" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D380" s="32"/>
-      <c r="E380" s="33"/>
-      <c r="F380" s="39"/>
+      <c r="D380" s="38"/>
+      <c r="E380" s="39"/>
+      <c r="F380" s="33"/>
       <c r="G380" s="23" t="s">
         <v>842</v>
       </c>
@@ -12739,9 +12740,9 @@
       <c r="C381" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D381" s="32"/>
-      <c r="E381" s="33"/>
-      <c r="F381" s="39"/>
+      <c r="D381" s="38"/>
+      <c r="E381" s="39"/>
+      <c r="F381" s="33"/>
       <c r="G381" s="23" t="s">
         <v>842</v>
       </c>
@@ -12760,9 +12761,9 @@
       <c r="C382" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D382" s="32"/>
-      <c r="E382" s="33"/>
-      <c r="F382" s="39"/>
+      <c r="D382" s="38"/>
+      <c r="E382" s="39"/>
+      <c r="F382" s="33"/>
       <c r="G382" s="23" t="s">
         <v>842</v>
       </c>
@@ -12781,9 +12782,9 @@
       <c r="C383" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D383" s="32"/>
-      <c r="E383" s="33"/>
-      <c r="F383" s="39"/>
+      <c r="D383" s="38"/>
+      <c r="E383" s="39"/>
+      <c r="F383" s="33"/>
       <c r="G383" s="23" t="s">
         <v>867</v>
       </c>
@@ -12802,9 +12803,9 @@
       <c r="C384" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D384" s="32"/>
-      <c r="E384" s="33"/>
-      <c r="F384" s="39"/>
+      <c r="D384" s="38"/>
+      <c r="E384" s="39"/>
+      <c r="F384" s="33"/>
       <c r="G384" s="23" t="s">
         <v>867</v>
       </c>
@@ -12823,9 +12824,9 @@
       <c r="C385" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D385" s="32"/>
-      <c r="E385" s="33"/>
-      <c r="F385" s="39"/>
+      <c r="D385" s="38"/>
+      <c r="E385" s="39"/>
+      <c r="F385" s="33"/>
       <c r="G385" s="23" t="s">
         <v>867</v>
       </c>
@@ -12844,9 +12845,9 @@
       <c r="C386" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D386" s="32"/>
-      <c r="E386" s="33"/>
-      <c r="F386" s="39"/>
+      <c r="D386" s="38"/>
+      <c r="E386" s="39"/>
+      <c r="F386" s="33"/>
       <c r="G386" s="23" t="s">
         <v>867</v>
       </c>
@@ -12865,9 +12866,9 @@
       <c r="C387" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D387" s="32"/>
-      <c r="E387" s="33"/>
-      <c r="F387" s="39"/>
+      <c r="D387" s="38"/>
+      <c r="E387" s="39"/>
+      <c r="F387" s="33"/>
       <c r="G387" s="23" t="s">
         <v>867</v>
       </c>
@@ -12886,9 +12887,9 @@
       <c r="C388" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D388" s="32"/>
-      <c r="E388" s="33"/>
-      <c r="F388" s="39"/>
+      <c r="D388" s="38"/>
+      <c r="E388" s="39"/>
+      <c r="F388" s="33"/>
       <c r="G388" s="23" t="s">
         <v>867</v>
       </c>
@@ -12907,9 +12908,9 @@
       <c r="C389" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D389" s="32"/>
-      <c r="E389" s="33"/>
-      <c r="F389" s="39"/>
+      <c r="D389" s="38"/>
+      <c r="E389" s="39"/>
+      <c r="F389" s="33"/>
       <c r="G389" s="23" t="s">
         <v>867</v>
       </c>
@@ -12928,9 +12929,9 @@
       <c r="C390" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D390" s="32"/>
-      <c r="E390" s="33"/>
-      <c r="F390" s="39"/>
+      <c r="D390" s="38"/>
+      <c r="E390" s="39"/>
+      <c r="F390" s="33"/>
       <c r="G390" s="23" t="s">
         <v>867</v>
       </c>
@@ -12949,9 +12950,9 @@
       <c r="C391" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D391" s="32"/>
-      <c r="E391" s="33"/>
-      <c r="F391" s="39"/>
+      <c r="D391" s="38"/>
+      <c r="E391" s="39"/>
+      <c r="F391" s="33"/>
       <c r="G391" s="23" t="s">
         <v>867</v>
       </c>
@@ -12970,9 +12971,9 @@
       <c r="C392" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D392" s="32"/>
-      <c r="E392" s="33"/>
-      <c r="F392" s="39"/>
+      <c r="D392" s="38"/>
+      <c r="E392" s="39"/>
+      <c r="F392" s="33"/>
       <c r="G392" s="23" t="s">
         <v>867</v>
       </c>
@@ -12991,9 +12992,9 @@
       <c r="C393" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D393" s="32"/>
-      <c r="E393" s="33"/>
-      <c r="F393" s="39"/>
+      <c r="D393" s="38"/>
+      <c r="E393" s="39"/>
+      <c r="F393" s="33"/>
       <c r="G393" s="23" t="s">
         <v>867</v>
       </c>
@@ -13012,9 +13013,9 @@
       <c r="C394" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D394" s="32"/>
-      <c r="E394" s="33"/>
-      <c r="F394" s="39"/>
+      <c r="D394" s="38"/>
+      <c r="E394" s="39"/>
+      <c r="F394" s="33"/>
       <c r="G394" s="23" t="s">
         <v>867</v>
       </c>
@@ -13033,9 +13034,9 @@
       <c r="C395" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D395" s="32"/>
-      <c r="E395" s="33"/>
-      <c r="F395" s="39"/>
+      <c r="D395" s="38"/>
+      <c r="E395" s="39"/>
+      <c r="F395" s="33"/>
       <c r="G395" s="23" t="s">
         <v>892</v>
       </c>
@@ -13054,9 +13055,9 @@
       <c r="C396" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D396" s="32"/>
-      <c r="E396" s="33"/>
-      <c r="F396" s="39"/>
+      <c r="D396" s="38"/>
+      <c r="E396" s="39"/>
+      <c r="F396" s="33"/>
       <c r="G396" s="23" t="s">
         <v>892</v>
       </c>
@@ -13075,9 +13076,9 @@
       <c r="C397" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D397" s="32"/>
-      <c r="E397" s="33"/>
-      <c r="F397" s="39"/>
+      <c r="D397" s="38"/>
+      <c r="E397" s="39"/>
+      <c r="F397" s="33"/>
       <c r="G397" s="23" t="s">
         <v>892</v>
       </c>
@@ -13096,9 +13097,9 @@
       <c r="C398" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D398" s="32"/>
-      <c r="E398" s="33"/>
-      <c r="F398" s="39"/>
+      <c r="D398" s="38"/>
+      <c r="E398" s="39"/>
+      <c r="F398" s="33"/>
       <c r="G398" s="23" t="s">
         <v>892</v>
       </c>
@@ -13117,9 +13118,9 @@
       <c r="C399" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D399" s="32"/>
-      <c r="E399" s="33"/>
-      <c r="F399" s="39"/>
+      <c r="D399" s="38"/>
+      <c r="E399" s="39"/>
+      <c r="F399" s="33"/>
       <c r="G399" s="23" t="s">
         <v>892</v>
       </c>
@@ -13138,9 +13139,9 @@
       <c r="C400" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D400" s="32"/>
-      <c r="E400" s="33"/>
-      <c r="F400" s="39"/>
+      <c r="D400" s="38"/>
+      <c r="E400" s="39"/>
+      <c r="F400" s="33"/>
       <c r="G400" s="23" t="s">
         <v>892</v>
       </c>
@@ -13159,9 +13160,9 @@
       <c r="C401" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D401" s="32"/>
-      <c r="E401" s="33"/>
-      <c r="F401" s="39"/>
+      <c r="D401" s="38"/>
+      <c r="E401" s="39"/>
+      <c r="F401" s="33"/>
       <c r="G401" s="23" t="s">
         <v>892</v>
       </c>
@@ -13180,9 +13181,9 @@
       <c r="C402" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D402" s="32"/>
-      <c r="E402" s="33"/>
-      <c r="F402" s="39"/>
+      <c r="D402" s="38"/>
+      <c r="E402" s="39"/>
+      <c r="F402" s="33"/>
       <c r="G402" s="23" t="s">
         <v>892</v>
       </c>
@@ -13201,9 +13202,9 @@
       <c r="C403" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D403" s="32"/>
-      <c r="E403" s="33"/>
-      <c r="F403" s="39"/>
+      <c r="D403" s="38"/>
+      <c r="E403" s="39"/>
+      <c r="F403" s="33"/>
       <c r="G403" s="23" t="s">
         <v>892</v>
       </c>
@@ -13222,9 +13223,9 @@
       <c r="C404" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D404" s="32"/>
-      <c r="E404" s="33"/>
-      <c r="F404" s="39"/>
+      <c r="D404" s="38"/>
+      <c r="E404" s="39"/>
+      <c r="F404" s="33"/>
       <c r="G404" s="23" t="s">
         <v>892</v>
       </c>
@@ -13243,9 +13244,9 @@
       <c r="C405" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D405" s="32"/>
-      <c r="E405" s="33"/>
-      <c r="F405" s="39"/>
+      <c r="D405" s="38"/>
+      <c r="E405" s="39"/>
+      <c r="F405" s="33"/>
       <c r="G405" s="23" t="s">
         <v>892</v>
       </c>
@@ -13264,9 +13265,9 @@
       <c r="C406" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D406" s="32"/>
-      <c r="E406" s="33"/>
-      <c r="F406" s="38"/>
+      <c r="D406" s="38"/>
+      <c r="E406" s="39"/>
+      <c r="F406" s="34"/>
       <c r="G406" s="23" t="s">
         <v>892</v>
       </c>
@@ -13285,9 +13286,9 @@
       <c r="C407" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D407" s="32"/>
-      <c r="E407" s="33"/>
-      <c r="F407" s="37" t="s">
+      <c r="D407" s="38"/>
+      <c r="E407" s="39"/>
+      <c r="F407" s="32" t="s">
         <v>917</v>
       </c>
       <c r="G407" s="23" t="s">
@@ -13308,9 +13309,9 @@
       <c r="C408" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D408" s="32"/>
-      <c r="E408" s="33"/>
-      <c r="F408" s="39"/>
+      <c r="D408" s="38"/>
+      <c r="E408" s="39"/>
+      <c r="F408" s="33"/>
       <c r="G408" s="23" t="s">
         <v>921</v>
       </c>
@@ -13331,9 +13332,9 @@
       <c r="C409" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D409" s="32"/>
-      <c r="E409" s="33"/>
-      <c r="F409" s="39"/>
+      <c r="D409" s="38"/>
+      <c r="E409" s="39"/>
+      <c r="F409" s="33"/>
       <c r="G409" s="23" t="s">
         <v>925</v>
       </c>
@@ -13354,9 +13355,9 @@
       <c r="C410" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D410" s="32"/>
-      <c r="E410" s="33"/>
-      <c r="F410" s="39"/>
+      <c r="D410" s="38"/>
+      <c r="E410" s="39"/>
+      <c r="F410" s="33"/>
       <c r="G410" s="23" t="s">
         <v>929</v>
       </c>
@@ -13377,9 +13378,9 @@
       <c r="C411" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D411" s="32"/>
-      <c r="E411" s="33"/>
-      <c r="F411" s="39"/>
+      <c r="D411" s="38"/>
+      <c r="E411" s="39"/>
+      <c r="F411" s="33"/>
       <c r="G411" s="23" t="s">
         <v>933</v>
       </c>
@@ -13400,9 +13401,9 @@
       <c r="C412" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D412" s="32"/>
-      <c r="E412" s="33"/>
-      <c r="F412" s="39"/>
+      <c r="D412" s="38"/>
+      <c r="E412" s="39"/>
+      <c r="F412" s="33"/>
       <c r="G412" s="23" t="s">
         <v>937</v>
       </c>
@@ -13423,9 +13424,9 @@
       <c r="C413" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D413" s="32"/>
-      <c r="E413" s="33"/>
-      <c r="F413" s="39"/>
+      <c r="D413" s="38"/>
+      <c r="E413" s="39"/>
+      <c r="F413" s="33"/>
       <c r="G413" s="23" t="s">
         <v>941</v>
       </c>
@@ -13444,9 +13445,9 @@
       <c r="C414" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D414" s="32"/>
-      <c r="E414" s="33"/>
-      <c r="F414" s="39"/>
+      <c r="D414" s="38"/>
+      <c r="E414" s="39"/>
+      <c r="F414" s="33"/>
       <c r="G414" s="23" t="s">
         <v>944</v>
       </c>
@@ -13465,9 +13466,9 @@
       <c r="C415" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D415" s="32"/>
-      <c r="E415" s="33"/>
-      <c r="F415" s="39"/>
+      <c r="D415" s="38"/>
+      <c r="E415" s="39"/>
+      <c r="F415" s="33"/>
       <c r="G415" s="23" t="s">
         <v>947</v>
       </c>
@@ -13486,9 +13487,9 @@
       <c r="C416" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D416" s="32"/>
-      <c r="E416" s="33"/>
-      <c r="F416" s="39"/>
+      <c r="D416" s="38"/>
+      <c r="E416" s="39"/>
+      <c r="F416" s="33"/>
       <c r="G416" s="23" t="s">
         <v>947</v>
       </c>
@@ -13507,9 +13508,9 @@
       <c r="C417" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D417" s="32"/>
-      <c r="E417" s="33"/>
-      <c r="F417" s="39"/>
+      <c r="D417" s="38"/>
+      <c r="E417" s="39"/>
+      <c r="F417" s="33"/>
       <c r="G417" s="23" t="s">
         <v>952</v>
       </c>
@@ -13528,9 +13529,9 @@
       <c r="C418" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D418" s="32"/>
-      <c r="E418" s="33"/>
-      <c r="F418" s="38"/>
+      <c r="D418" s="38"/>
+      <c r="E418" s="39"/>
+      <c r="F418" s="34"/>
       <c r="G418" s="23" t="s">
         <v>955</v>
       </c>
@@ -13549,9 +13550,9 @@
       <c r="C419" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D419" s="32"/>
-      <c r="E419" s="33"/>
-      <c r="F419" s="37" t="s">
+      <c r="D419" s="38"/>
+      <c r="E419" s="39"/>
+      <c r="F419" s="32" t="s">
         <v>958</v>
       </c>
       <c r="G419" s="23" t="s">
@@ -13572,9 +13573,9 @@
       <c r="C420" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D420" s="32"/>
-      <c r="E420" s="33"/>
-      <c r="F420" s="39"/>
+      <c r="D420" s="38"/>
+      <c r="E420" s="39"/>
+      <c r="F420" s="33"/>
       <c r="G420" s="23" t="s">
         <v>959</v>
       </c>
@@ -13593,9 +13594,9 @@
       <c r="C421" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D421" s="32"/>
-      <c r="E421" s="33"/>
-      <c r="F421" s="39"/>
+      <c r="D421" s="38"/>
+      <c r="E421" s="39"/>
+      <c r="F421" s="33"/>
       <c r="G421" s="23" t="s">
         <v>964</v>
       </c>
@@ -13614,9 +13615,9 @@
       <c r="C422" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D422" s="32"/>
-      <c r="E422" s="33"/>
-      <c r="F422" s="39"/>
+      <c r="D422" s="38"/>
+      <c r="E422" s="39"/>
+      <c r="F422" s="33"/>
       <c r="G422" s="23" t="s">
         <v>959</v>
       </c>
@@ -13635,9 +13636,9 @@
       <c r="C423" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D423" s="32"/>
-      <c r="E423" s="33"/>
-      <c r="F423" s="39"/>
+      <c r="D423" s="38"/>
+      <c r="E423" s="39"/>
+      <c r="F423" s="33"/>
       <c r="G423" s="23" t="s">
         <v>959</v>
       </c>
@@ -13656,9 +13657,9 @@
       <c r="C424" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D424" s="32"/>
-      <c r="E424" s="33"/>
-      <c r="F424" s="39"/>
+      <c r="D424" s="38"/>
+      <c r="E424" s="39"/>
+      <c r="F424" s="33"/>
       <c r="G424" s="23" t="s">
         <v>971</v>
       </c>
@@ -13677,9 +13678,9 @@
       <c r="C425" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D425" s="32"/>
-      <c r="E425" s="33"/>
-      <c r="F425" s="39"/>
+      <c r="D425" s="38"/>
+      <c r="E425" s="39"/>
+      <c r="F425" s="33"/>
       <c r="G425" s="23" t="s">
         <v>974</v>
       </c>
@@ -13698,9 +13699,9 @@
       <c r="C426" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D426" s="32"/>
-      <c r="E426" s="33"/>
-      <c r="F426" s="39"/>
+      <c r="D426" s="38"/>
+      <c r="E426" s="39"/>
+      <c r="F426" s="33"/>
       <c r="G426" s="23" t="s">
         <v>977</v>
       </c>
@@ -13719,9 +13720,9 @@
       <c r="C427" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D427" s="32"/>
-      <c r="E427" s="33"/>
-      <c r="F427" s="39"/>
+      <c r="D427" s="38"/>
+      <c r="E427" s="39"/>
+      <c r="F427" s="33"/>
       <c r="G427" s="23" t="s">
         <v>980</v>
       </c>
@@ -13740,9 +13741,9 @@
       <c r="C428" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D428" s="32"/>
-      <c r="E428" s="33"/>
-      <c r="F428" s="39"/>
+      <c r="D428" s="38"/>
+      <c r="E428" s="39"/>
+      <c r="F428" s="33"/>
       <c r="G428" s="23" t="s">
         <v>983</v>
       </c>
@@ -13761,9 +13762,9 @@
       <c r="C429" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D429" s="32"/>
-      <c r="E429" s="33"/>
-      <c r="F429" s="39"/>
+      <c r="D429" s="38"/>
+      <c r="E429" s="39"/>
+      <c r="F429" s="33"/>
       <c r="G429" s="23" t="s">
         <v>986</v>
       </c>
@@ -13782,9 +13783,9 @@
       <c r="C430" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D430" s="32"/>
-      <c r="E430" s="33"/>
-      <c r="F430" s="39"/>
+      <c r="D430" s="38"/>
+      <c r="E430" s="39"/>
+      <c r="F430" s="33"/>
       <c r="G430" s="23" t="s">
         <v>989</v>
       </c>
@@ -13803,9 +13804,9 @@
       <c r="C431" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D431" s="32"/>
-      <c r="E431" s="33"/>
-      <c r="F431" s="38"/>
+      <c r="D431" s="38"/>
+      <c r="E431" s="39"/>
+      <c r="F431" s="34"/>
       <c r="G431" s="23" t="s">
         <v>992</v>
       </c>
@@ -13824,9 +13825,9 @@
       <c r="C432" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D432" s="32"/>
-      <c r="E432" s="33"/>
-      <c r="F432" s="37" t="s">
+      <c r="D432" s="38"/>
+      <c r="E432" s="39"/>
+      <c r="F432" s="32" t="s">
         <v>995</v>
       </c>
       <c r="G432" s="23" t="s">
@@ -13847,9 +13848,9 @@
       <c r="C433" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D433" s="32"/>
-      <c r="E433" s="33"/>
-      <c r="F433" s="39"/>
+      <c r="D433" s="38"/>
+      <c r="E433" s="39"/>
+      <c r="F433" s="33"/>
       <c r="G433" s="23" t="s">
         <v>996</v>
       </c>
@@ -13868,9 +13869,9 @@
       <c r="C434" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D434" s="32"/>
-      <c r="E434" s="33"/>
-      <c r="F434" s="39"/>
+      <c r="D434" s="38"/>
+      <c r="E434" s="39"/>
+      <c r="F434" s="33"/>
       <c r="G434" s="23" t="s">
         <v>1001</v>
       </c>
@@ -13889,9 +13890,9 @@
       <c r="C435" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D435" s="32"/>
-      <c r="E435" s="33"/>
-      <c r="F435" s="39"/>
+      <c r="D435" s="38"/>
+      <c r="E435" s="39"/>
+      <c r="F435" s="33"/>
       <c r="G435" s="23" t="s">
         <v>947</v>
       </c>
@@ -13910,9 +13911,9 @@
       <c r="C436" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D436" s="32"/>
-      <c r="E436" s="33"/>
-      <c r="F436" s="39"/>
+      <c r="D436" s="38"/>
+      <c r="E436" s="39"/>
+      <c r="F436" s="33"/>
       <c r="G436" s="23" t="s">
         <v>947</v>
       </c>
@@ -13931,9 +13932,9 @@
       <c r="C437" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D437" s="32"/>
-      <c r="E437" s="33"/>
-      <c r="F437" s="39"/>
+      <c r="D437" s="38"/>
+      <c r="E437" s="39"/>
+      <c r="F437" s="33"/>
       <c r="G437" s="23" t="s">
         <v>947</v>
       </c>
@@ -13952,9 +13953,9 @@
       <c r="C438" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D438" s="32"/>
-      <c r="E438" s="33"/>
-      <c r="F438" s="38"/>
+      <c r="D438" s="38"/>
+      <c r="E438" s="39"/>
+      <c r="F438" s="34"/>
       <c r="G438" s="23" t="s">
         <v>1010</v>
       </c>
@@ -13973,9 +13974,9 @@
       <c r="C439" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D439" s="32"/>
-      <c r="E439" s="33"/>
-      <c r="F439" s="37" t="s">
+      <c r="D439" s="38"/>
+      <c r="E439" s="39"/>
+      <c r="F439" s="32" t="s">
         <v>1013</v>
       </c>
       <c r="G439" s="23" t="s">
@@ -13996,9 +13997,9 @@
       <c r="C440" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D440" s="32"/>
-      <c r="E440" s="33"/>
-      <c r="F440" s="39"/>
+      <c r="D440" s="38"/>
+      <c r="E440" s="39"/>
+      <c r="F440" s="33"/>
       <c r="G440" s="23" t="s">
         <v>1017</v>
       </c>
@@ -14017,9 +14018,9 @@
       <c r="C441" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D441" s="32"/>
-      <c r="E441" s="33"/>
-      <c r="F441" s="39"/>
+      <c r="D441" s="38"/>
+      <c r="E441" s="39"/>
+      <c r="F441" s="33"/>
       <c r="G441" s="23" t="s">
         <v>1020</v>
       </c>
@@ -14038,9 +14039,9 @@
       <c r="C442" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D442" s="32"/>
-      <c r="E442" s="33"/>
-      <c r="F442" s="39"/>
+      <c r="D442" s="38"/>
+      <c r="E442" s="39"/>
+      <c r="F442" s="33"/>
       <c r="G442" s="23" t="s">
         <v>1023</v>
       </c>
@@ -14059,9 +14060,9 @@
       <c r="C443" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D443" s="32"/>
-      <c r="E443" s="33"/>
-      <c r="F443" s="39"/>
+      <c r="D443" s="38"/>
+      <c r="E443" s="39"/>
+      <c r="F443" s="33"/>
       <c r="G443" s="23" t="s">
         <v>1026</v>
       </c>
@@ -14080,9 +14081,9 @@
       <c r="C444" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D444" s="32"/>
-      <c r="E444" s="33"/>
-      <c r="F444" s="39"/>
+      <c r="D444" s="38"/>
+      <c r="E444" s="39"/>
+      <c r="F444" s="33"/>
       <c r="G444" s="23" t="s">
         <v>1029</v>
       </c>
@@ -14101,9 +14102,9 @@
       <c r="C445" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D445" s="32"/>
-      <c r="E445" s="33"/>
-      <c r="F445" s="39"/>
+      <c r="D445" s="38"/>
+      <c r="E445" s="39"/>
+      <c r="F445" s="33"/>
       <c r="G445" s="23" t="s">
         <v>1032</v>
       </c>
@@ -14122,9 +14123,9 @@
       <c r="C446" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D446" s="32"/>
-      <c r="E446" s="33"/>
-      <c r="F446" s="38"/>
+      <c r="D446" s="38"/>
+      <c r="E446" s="39"/>
+      <c r="F446" s="34"/>
       <c r="G446" s="23" t="s">
         <v>1035</v>
       </c>
@@ -14143,9 +14144,9 @@
       <c r="C447" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D447" s="32"/>
-      <c r="E447" s="33"/>
-      <c r="F447" s="37" t="s">
+      <c r="D447" s="38"/>
+      <c r="E447" s="39"/>
+      <c r="F447" s="32" t="s">
         <v>1038</v>
       </c>
       <c r="G447" s="23" t="s">
@@ -14166,9 +14167,9 @@
       <c r="C448" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D448" s="32"/>
-      <c r="E448" s="33"/>
-      <c r="F448" s="39"/>
+      <c r="D448" s="38"/>
+      <c r="E448" s="39"/>
+      <c r="F448" s="33"/>
       <c r="G448" s="23" t="s">
         <v>1042</v>
       </c>
@@ -14187,9 +14188,9 @@
       <c r="C449" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D449" s="32"/>
-      <c r="E449" s="33"/>
-      <c r="F449" s="38"/>
+      <c r="D449" s="38"/>
+      <c r="E449" s="39"/>
+      <c r="F449" s="34"/>
       <c r="G449" s="23" t="s">
         <v>1045</v>
       </c>
@@ -14208,9 +14209,9 @@
       <c r="C450" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D450" s="32"/>
-      <c r="E450" s="33"/>
-      <c r="F450" s="37" t="s">
+      <c r="D450" s="38"/>
+      <c r="E450" s="39"/>
+      <c r="F450" s="32" t="s">
         <v>1048</v>
       </c>
       <c r="G450" s="23" t="s">
@@ -14231,9 +14232,9 @@
       <c r="C451" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D451" s="32"/>
-      <c r="E451" s="33"/>
-      <c r="F451" s="39"/>
+      <c r="D451" s="38"/>
+      <c r="E451" s="39"/>
+      <c r="F451" s="33"/>
       <c r="G451" s="23" t="s">
         <v>1052</v>
       </c>
@@ -14252,9 +14253,9 @@
       <c r="C452" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D452" s="32"/>
-      <c r="E452" s="33"/>
-      <c r="F452" s="39"/>
+      <c r="D452" s="38"/>
+      <c r="E452" s="39"/>
+      <c r="F452" s="33"/>
       <c r="G452" s="23" t="s">
         <v>1055</v>
       </c>
@@ -14273,9 +14274,9 @@
       <c r="C453" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D453" s="32"/>
-      <c r="E453" s="33"/>
-      <c r="F453" s="39"/>
+      <c r="D453" s="38"/>
+      <c r="E453" s="39"/>
+      <c r="F453" s="33"/>
       <c r="G453" s="23" t="s">
         <v>1058</v>
       </c>
@@ -14294,9 +14295,9 @@
       <c r="C454" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D454" s="32"/>
-      <c r="E454" s="33"/>
-      <c r="F454" s="39"/>
+      <c r="D454" s="38"/>
+      <c r="E454" s="39"/>
+      <c r="F454" s="33"/>
       <c r="G454" s="23" t="s">
         <v>1058</v>
       </c>
@@ -14315,9 +14316,9 @@
       <c r="C455" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D455" s="32"/>
-      <c r="E455" s="33"/>
-      <c r="F455" s="39"/>
+      <c r="D455" s="38"/>
+      <c r="E455" s="39"/>
+      <c r="F455" s="33"/>
       <c r="G455" s="23" t="s">
         <v>1058</v>
       </c>
@@ -14336,9 +14337,9 @@
       <c r="C456" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D456" s="32"/>
-      <c r="E456" s="33"/>
-      <c r="F456" s="39"/>
+      <c r="D456" s="38"/>
+      <c r="E456" s="39"/>
+      <c r="F456" s="33"/>
       <c r="G456" s="23" t="s">
         <v>1065</v>
       </c>
@@ -14357,9 +14358,9 @@
       <c r="C457" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D457" s="32"/>
-      <c r="E457" s="33"/>
-      <c r="F457" s="39"/>
+      <c r="D457" s="38"/>
+      <c r="E457" s="39"/>
+      <c r="F457" s="33"/>
       <c r="G457" s="23" t="s">
         <v>1065</v>
       </c>
@@ -14378,9 +14379,9 @@
       <c r="C458" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D458" s="32"/>
-      <c r="E458" s="33"/>
-      <c r="F458" s="39"/>
+      <c r="D458" s="38"/>
+      <c r="E458" s="39"/>
+      <c r="F458" s="33"/>
       <c r="G458" s="23" t="s">
         <v>1065</v>
       </c>
@@ -14399,9 +14400,9 @@
       <c r="C459" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D459" s="32"/>
-      <c r="E459" s="33"/>
-      <c r="F459" s="39"/>
+      <c r="D459" s="38"/>
+      <c r="E459" s="39"/>
+      <c r="F459" s="33"/>
       <c r="G459" s="23" t="s">
         <v>1065</v>
       </c>
@@ -14420,9 +14421,9 @@
       <c r="C460" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D460" s="32"/>
-      <c r="E460" s="33"/>
-      <c r="F460" s="39"/>
+      <c r="D460" s="38"/>
+      <c r="E460" s="39"/>
+      <c r="F460" s="33"/>
       <c r="G460" s="23" t="s">
         <v>1074</v>
       </c>
@@ -14441,9 +14442,9 @@
       <c r="C461" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D461" s="32"/>
-      <c r="E461" s="33"/>
-      <c r="F461" s="39"/>
+      <c r="D461" s="38"/>
+      <c r="E461" s="39"/>
+      <c r="F461" s="33"/>
       <c r="G461" s="23" t="s">
         <v>1077</v>
       </c>
@@ -14462,9 +14463,9 @@
       <c r="C462" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D462" s="32"/>
-      <c r="E462" s="33"/>
-      <c r="F462" s="38"/>
+      <c r="D462" s="38"/>
+      <c r="E462" s="39"/>
+      <c r="F462" s="34"/>
       <c r="G462" s="23" t="s">
         <v>1080</v>
       </c>
@@ -14483,9 +14484,9 @@
       <c r="C463" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D463" s="32"/>
-      <c r="E463" s="33"/>
-      <c r="F463" s="37" t="s">
+      <c r="D463" s="38"/>
+      <c r="E463" s="39"/>
+      <c r="F463" s="32" t="s">
         <v>1083</v>
       </c>
       <c r="G463" s="23" t="s">
@@ -14506,9 +14507,9 @@
       <c r="C464" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D464" s="32"/>
-      <c r="E464" s="33"/>
-      <c r="F464" s="39"/>
+      <c r="D464" s="38"/>
+      <c r="E464" s="39"/>
+      <c r="F464" s="33"/>
       <c r="G464" s="23" t="s">
         <v>1087</v>
       </c>
@@ -14527,9 +14528,9 @@
       <c r="C465" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D465" s="32"/>
-      <c r="E465" s="33"/>
-      <c r="F465" s="39"/>
+      <c r="D465" s="38"/>
+      <c r="E465" s="39"/>
+      <c r="F465" s="33"/>
       <c r="G465" s="23" t="s">
         <v>1090</v>
       </c>
@@ -14548,9 +14549,9 @@
       <c r="C466" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D466" s="32"/>
-      <c r="E466" s="33"/>
-      <c r="F466" s="39"/>
+      <c r="D466" s="38"/>
+      <c r="E466" s="39"/>
+      <c r="F466" s="33"/>
       <c r="G466" s="23" t="s">
         <v>1093</v>
       </c>
@@ -14569,9 +14570,9 @@
       <c r="C467" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D467" s="32"/>
-      <c r="E467" s="33"/>
-      <c r="F467" s="39"/>
+      <c r="D467" s="38"/>
+      <c r="E467" s="39"/>
+      <c r="F467" s="33"/>
       <c r="G467" s="23" t="s">
         <v>1096</v>
       </c>
@@ -14590,9 +14591,9 @@
       <c r="C468" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D468" s="32"/>
-      <c r="E468" s="33"/>
-      <c r="F468" s="39"/>
+      <c r="D468" s="38"/>
+      <c r="E468" s="39"/>
+      <c r="F468" s="33"/>
       <c r="G468" s="23" t="s">
         <v>1099</v>
       </c>
@@ -14611,9 +14612,9 @@
       <c r="C469" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D469" s="32"/>
-      <c r="E469" s="33"/>
-      <c r="F469" s="39"/>
+      <c r="D469" s="38"/>
+      <c r="E469" s="39"/>
+      <c r="F469" s="33"/>
       <c r="G469" s="23" t="s">
         <v>1102</v>
       </c>
@@ -14632,9 +14633,9 @@
       <c r="C470" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D470" s="32"/>
-      <c r="E470" s="33"/>
-      <c r="F470" s="39"/>
+      <c r="D470" s="38"/>
+      <c r="E470" s="39"/>
+      <c r="F470" s="33"/>
       <c r="G470" s="23" t="s">
         <v>1105</v>
       </c>
@@ -14653,9 +14654,9 @@
       <c r="C471" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D471" s="32"/>
-      <c r="E471" s="33"/>
-      <c r="F471" s="39"/>
+      <c r="D471" s="38"/>
+      <c r="E471" s="39"/>
+      <c r="F471" s="33"/>
       <c r="G471" s="23" t="s">
         <v>1108</v>
       </c>
@@ -14674,9 +14675,9 @@
       <c r="C472" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D472" s="32"/>
-      <c r="E472" s="33"/>
-      <c r="F472" s="38"/>
+      <c r="D472" s="38"/>
+      <c r="E472" s="39"/>
+      <c r="F472" s="34"/>
       <c r="G472" s="23" t="s">
         <v>1093</v>
       </c>
@@ -14695,19 +14696,19 @@
       <c r="C473" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D473" s="32"/>
-      <c r="E473" s="33"/>
-      <c r="F473" s="37" t="s">
+      <c r="D473" s="38"/>
+      <c r="E473" s="39"/>
+      <c r="F473" s="32" t="s">
+        <v>1128</v>
+      </c>
+      <c r="G473" s="23" t="s">
         <v>1113</v>
       </c>
-      <c r="G473" s="23" t="s">
+      <c r="H473" s="23" t="s">
         <v>1114</v>
       </c>
-      <c r="H473" s="23" t="s">
+      <c r="I473" s="23" t="s">
         <v>1115</v>
-      </c>
-      <c r="I473" s="23" t="s">
-        <v>1116</v>
       </c>
       <c r="J473" s="23"/>
     </row>
@@ -14718,17 +14719,17 @@
       <c r="C474" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D474" s="32"/>
-      <c r="E474" s="33"/>
-      <c r="F474" s="39"/>
+      <c r="D474" s="38"/>
+      <c r="E474" s="39"/>
+      <c r="F474" s="33"/>
       <c r="G474" s="23" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H474" s="23" t="s">
         <v>1117</v>
       </c>
-      <c r="H474" s="23" t="s">
+      <c r="I474" s="23" t="s">
         <v>1118</v>
-      </c>
-      <c r="I474" s="23" t="s">
-        <v>1119</v>
       </c>
       <c r="J474" s="23"/>
     </row>
@@ -14739,59 +14740,22 @@
       <c r="C475" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D475" s="32"/>
-      <c r="E475" s="33"/>
-      <c r="F475" s="38"/>
+      <c r="D475" s="38"/>
+      <c r="E475" s="39"/>
+      <c r="F475" s="34"/>
       <c r="G475" s="23" t="s">
+        <v>1119</v>
+      </c>
+      <c r="H475" s="23" t="s">
+        <v>1125</v>
+      </c>
+      <c r="I475" s="23" t="s">
         <v>1120</v>
-      </c>
-      <c r="H475" s="23" t="s">
-        <v>1126</v>
-      </c>
-      <c r="I475" s="23" t="s">
-        <v>1121</v>
       </c>
       <c r="J475" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="F473:F475"/>
-    <mergeCell ref="F419:F431"/>
-    <mergeCell ref="F432:F438"/>
-    <mergeCell ref="F439:F446"/>
-    <mergeCell ref="F447:F449"/>
-    <mergeCell ref="F450:F462"/>
-    <mergeCell ref="F463:F472"/>
-    <mergeCell ref="F407:F418"/>
-    <mergeCell ref="F210:F215"/>
-    <mergeCell ref="F216:F217"/>
-    <mergeCell ref="F218:F223"/>
-    <mergeCell ref="F224:F233"/>
-    <mergeCell ref="F234:F241"/>
-    <mergeCell ref="F242:F243"/>
-    <mergeCell ref="F244:F247"/>
-    <mergeCell ref="F248:F251"/>
-    <mergeCell ref="F252:F257"/>
-    <mergeCell ref="F258:F262"/>
-    <mergeCell ref="F263:F406"/>
-    <mergeCell ref="F132:F141"/>
-    <mergeCell ref="F208:F209"/>
-    <mergeCell ref="F144:F147"/>
-    <mergeCell ref="F148:F149"/>
-    <mergeCell ref="F150:F155"/>
-    <mergeCell ref="F156:F161"/>
-    <mergeCell ref="F162:F171"/>
-    <mergeCell ref="F172:F175"/>
-    <mergeCell ref="F176:F179"/>
-    <mergeCell ref="F180:F181"/>
-    <mergeCell ref="F182:F187"/>
-    <mergeCell ref="F188:F189"/>
-    <mergeCell ref="F190:F207"/>
-    <mergeCell ref="F98:F99"/>
-    <mergeCell ref="F100:F115"/>
-    <mergeCell ref="F116:F117"/>
-    <mergeCell ref="F118:F129"/>
-    <mergeCell ref="F130:F131"/>
     <mergeCell ref="D6:D475"/>
     <mergeCell ref="E6:E33"/>
     <mergeCell ref="E34:E475"/>
@@ -14808,6 +14772,43 @@
     <mergeCell ref="F52:F75"/>
     <mergeCell ref="F76:F77"/>
     <mergeCell ref="F78:F97"/>
+    <mergeCell ref="F98:F99"/>
+    <mergeCell ref="F100:F115"/>
+    <mergeCell ref="F116:F117"/>
+    <mergeCell ref="F118:F129"/>
+    <mergeCell ref="F130:F131"/>
+    <mergeCell ref="F132:F141"/>
+    <mergeCell ref="F208:F209"/>
+    <mergeCell ref="F144:F147"/>
+    <mergeCell ref="F148:F149"/>
+    <mergeCell ref="F150:F155"/>
+    <mergeCell ref="F156:F161"/>
+    <mergeCell ref="F162:F171"/>
+    <mergeCell ref="F172:F175"/>
+    <mergeCell ref="F176:F179"/>
+    <mergeCell ref="F180:F181"/>
+    <mergeCell ref="F182:F187"/>
+    <mergeCell ref="F188:F189"/>
+    <mergeCell ref="F190:F207"/>
+    <mergeCell ref="F407:F418"/>
+    <mergeCell ref="F210:F215"/>
+    <mergeCell ref="F216:F217"/>
+    <mergeCell ref="F218:F223"/>
+    <mergeCell ref="F224:F233"/>
+    <mergeCell ref="F234:F241"/>
+    <mergeCell ref="F242:F243"/>
+    <mergeCell ref="F244:F247"/>
+    <mergeCell ref="F248:F251"/>
+    <mergeCell ref="F252:F257"/>
+    <mergeCell ref="F258:F262"/>
+    <mergeCell ref="F263:F406"/>
+    <mergeCell ref="F473:F475"/>
+    <mergeCell ref="F419:F431"/>
+    <mergeCell ref="F432:F438"/>
+    <mergeCell ref="F439:F446"/>
+    <mergeCell ref="F447:F449"/>
+    <mergeCell ref="F450:F462"/>
+    <mergeCell ref="F463:F472"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
